--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -961,7 +961,7 @@
     <t>2021-08-30</t>
   </si>
   <si>
-    <t>2021-09-02</t>
+    <t>2021-09-03</t>
   </si>
   <si>
     <t>2016-07-29</t>
@@ -39088,7 +39088,7 @@
         <v>315</v>
       </c>
       <c r="E751">
-        <v>4.351677828379405</v>
+        <v>4.041243466552189</v>
       </c>
       <c r="F751">
         <v>-1</v>
@@ -39097,10 +39097,10 @@
         <v>0.05048816422186525</v>
       </c>
       <c r="H751">
-        <v>0.0507883221716206</v>
+        <v>0.05157875653344781</v>
       </c>
       <c r="I751">
-        <v>0.1001579497553458</v>
+        <v>0.4105923115825618</v>
       </c>
       <c r="J751">
         <v>1.00078974877675</v>
@@ -39112,10 +39112,10 @@
         <v>27.47</v>
       </c>
       <c r="M751">
-        <v>23.2</v>
+        <v>23.75</v>
       </c>
       <c r="N751">
-        <v>27.57</v>
+        <v>27.81</v>
       </c>
       <c r="O751">
         <v>1</v>
@@ -39138,7 +39138,7 @@
         <v>315</v>
       </c>
       <c r="E752">
-        <v>4.198168673390335</v>
+        <v>3.884095085906051</v>
       </c>
       <c r="F752">
         <v>-1</v>
@@ -39147,10 +39147,10 @@
         <v>0.05064035002206992</v>
       </c>
       <c r="H752">
-        <v>0.05094183132660967</v>
+        <v>0.05173590491409395</v>
       </c>
       <c r="I752">
-        <v>0.1014813045397354</v>
+        <v>0.4155548920240193</v>
       </c>
       <c r="J752">
         <v>1.007406522698693</v>
@@ -39162,10 +39162,10 @@
         <v>27.47</v>
       </c>
       <c r="M752">
-        <v>23.2</v>
+        <v>23.75</v>
       </c>
       <c r="N752">
-        <v>27.57</v>
+        <v>27.81</v>
       </c>
       <c r="O752">
         <v>1</v>
@@ -39188,7 +39188,7 @@
         <v>315</v>
       </c>
       <c r="E753">
-        <v>4.028214960679673</v>
+        <v>3.710112298109578</v>
       </c>
       <c r="F753">
         <v>-1</v>
@@ -39197,10 +39197,10 @@
         <v>0.05080883861656757</v>
       </c>
       <c r="H753">
-        <v>0.05111178503932032</v>
+        <v>0.05190988770189042</v>
       </c>
       <c r="I753">
-        <v>0.1029464227527583</v>
+        <v>0.4210490853228528</v>
       </c>
       <c r="J753">
         <v>1.014732113763807</v>
@@ -39212,10 +39212,10 @@
         <v>27.47</v>
       </c>
       <c r="M753">
-        <v>23.2</v>
+        <v>23.75</v>
       </c>
       <c r="N753">
-        <v>27.57</v>
+        <v>27.81</v>
       </c>
       <c r="O753">
         <v>1</v>
@@ -39238,7 +39238,7 @@
         <v>315</v>
       </c>
       <c r="E754">
-        <v>3.889036959018526</v>
+        <v>3.567634817960773</v>
       </c>
       <c r="F754">
         <v>-1</v>
@@ -39247,10 +39247,10 @@
         <v>0.05094681680786957</v>
       </c>
       <c r="H754">
-        <v>0.05125096304098148</v>
+        <v>0.05205236518203923</v>
       </c>
       <c r="I754">
-        <v>0.1041462331119085</v>
+        <v>0.4255483741696615</v>
       </c>
       <c r="J754">
         <v>1.020731165559546</v>
@@ -39262,10 +39262,10 @@
         <v>27.47</v>
       </c>
       <c r="M754">
-        <v>23.2</v>
+        <v>23.75</v>
       </c>
       <c r="N754">
-        <v>27.57</v>
+        <v>27.81</v>
       </c>
       <c r="O754">
         <v>1</v>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="404">
   <si>
     <t>trade_time</t>
   </si>
@@ -574,15 +574,15 @@
     <t>2021-08-26</t>
   </si>
   <si>
+    <t>2021-08-31</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-08-31</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
     <t>2016-09-12</t>
   </si>
   <si>
@@ -970,7 +970,7 @@
     <t>2021-09-03</t>
   </si>
   <si>
-    <t>2021-09-07</t>
+    <t>2021-09-08</t>
   </si>
   <si>
     <t>2016-07-29</t>
@@ -1223,6 +1223,9 @@
   </si>
   <si>
     <t>2021-08-27</t>
+  </si>
+  <si>
+    <t>2021-09-02</t>
   </si>
 </sst>
 </file>
@@ -1580,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P759"/>
+  <dimension ref="A1:P760"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -39082,40 +39085,40 @@
     </row>
     <row r="751" spans="1:16">
       <c r="A751" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B751" t="s">
         <v>186</v>
       </c>
       <c r="C751">
-        <v>4.941864750446115</v>
+        <v>4.382704501789181</v>
       </c>
       <c r="D751" t="s">
         <v>317</v>
       </c>
       <c r="E751">
-        <v>4.547251644482401</v>
+        <v>4.041243466552189</v>
       </c>
       <c r="F751">
         <v>-1</v>
       </c>
       <c r="G751">
-        <v>0.04999813524955388</v>
+        <v>0.04821729549821082</v>
       </c>
       <c r="H751">
-        <v>0.0510727483555176</v>
+        <v>0.05157875653344781</v>
       </c>
       <c r="I751">
-        <v>0.3946131059637139</v>
+        <v>0.3414610352369927</v>
       </c>
       <c r="J751">
-        <v>0.9794841412849514</v>
+        <v>1.00078974877675</v>
       </c>
       <c r="K751">
-        <v>23</v>
+        <v>21.9</v>
       </c>
       <c r="L751">
-        <v>27.47</v>
+        <v>26.3</v>
       </c>
       <c r="M751">
         <v>23.75</v>
@@ -39127,51 +39130,51 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>401</v>
+        <v>185</v>
       </c>
     </row>
     <row r="752" spans="1:16">
       <c r="A752" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B752" t="s">
         <v>187</v>
       </c>
       <c r="C752">
-        <v>4.382704501789181</v>
+        <v>3.920611667530789</v>
       </c>
       <c r="D752" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E752">
-        <v>4.041243466552189</v>
+        <v>4.341203979113352</v>
       </c>
       <c r="F752">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G752">
-        <v>0.04821729549821082</v>
+        <v>0.05305938833246921</v>
       </c>
       <c r="H752">
-        <v>0.05157875653344781</v>
+        <v>0.05197879602088665</v>
       </c>
       <c r="I752">
-        <v>0.3414610352369927</v>
+        <v>0.4205923115825634</v>
       </c>
       <c r="J752">
         <v>1.00078974877675</v>
       </c>
       <c r="K752">
-        <v>21.9</v>
+        <v>24.55</v>
       </c>
       <c r="L752">
-        <v>26.3</v>
+        <v>28.49</v>
       </c>
       <c r="M752">
-        <v>23.75</v>
+        <v>23.8</v>
       </c>
       <c r="N752">
-        <v>27.81</v>
+        <v>28.16</v>
       </c>
       <c r="O752">
         <v>1</v>
@@ -39185,10 +39188,10 @@
         <v>0</v>
       </c>
       <c r="B753" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C753">
-        <v>4.237797152898636</v>
+        <v>4.29964997793007</v>
       </c>
       <c r="D753" t="s">
         <v>317</v>
@@ -39200,22 +39203,22 @@
         <v>-1</v>
       </c>
       <c r="G753">
-        <v>0.04836220284710137</v>
+        <v>0.05064035002206992</v>
       </c>
       <c r="H753">
         <v>0.05173590491409395</v>
       </c>
       <c r="I753">
-        <v>0.3537020669925859</v>
+        <v>0.4155548920240193</v>
       </c>
       <c r="J753">
         <v>1.007406522698693</v>
       </c>
       <c r="K753">
-        <v>21.9</v>
+        <v>23</v>
       </c>
       <c r="L753">
-        <v>26.3</v>
+        <v>27.47</v>
       </c>
       <c r="M753">
         <v>23.75</v>
@@ -39235,7 +39238,7 @@
         <v>1</v>
       </c>
       <c r="B754" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C754">
         <v>3.758169867747096</v>
@@ -39244,7 +39247,7 @@
         <v>318</v>
       </c>
       <c r="E754">
-        <v>3.818910520016967</v>
+        <v>4.183724759771117</v>
       </c>
       <c r="F754">
         <v>1</v>
@@ -39253,10 +39256,10 @@
         <v>0.05322183013225291</v>
       </c>
       <c r="H754">
-        <v>0.05308108947998304</v>
+        <v>0.05213627524022888</v>
       </c>
       <c r="I754">
-        <v>0.06074065226987102</v>
+        <v>0.4255548920240209</v>
       </c>
       <c r="J754">
         <v>1.007406522698693</v>
@@ -39268,10 +39271,10 @@
         <v>28.49</v>
       </c>
       <c r="M754">
-        <v>24.45</v>
+        <v>23.8</v>
       </c>
       <c r="N754">
-        <v>28.45</v>
+        <v>28.16</v>
       </c>
       <c r="O754">
         <v>1</v>
@@ -39285,7 +39288,7 @@
         <v>0</v>
       </c>
       <c r="B755" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C755">
         <v>4.131161383432431</v>
@@ -39335,7 +39338,7 @@
         <v>1</v>
       </c>
       <c r="B756" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C756">
         <v>3.578326607098528</v>
@@ -39344,7 +39347,7 @@
         <v>318</v>
       </c>
       <c r="E756">
-        <v>3.639799818474913</v>
+        <v>4.009375692421386</v>
       </c>
       <c r="F756">
         <v>1</v>
@@ -39353,10 +39356,10 @@
         <v>0.05340167339290147</v>
       </c>
       <c r="H756">
-        <v>0.05326020018152509</v>
+        <v>0.05231062430757862</v>
       </c>
       <c r="I756">
-        <v>0.06147321137638428</v>
+        <v>0.4310490853228579</v>
       </c>
       <c r="J756">
         <v>1.014732113763807</v>
@@ -39368,10 +39371,10 @@
         <v>28.49</v>
       </c>
       <c r="M756">
-        <v>24.45</v>
+        <v>23.8</v>
       </c>
       <c r="N756">
-        <v>28.45</v>
+        <v>28.16</v>
       </c>
       <c r="O756">
         <v>1</v>
@@ -39385,7 +39388,7 @@
         <v>0</v>
       </c>
       <c r="B757" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C757">
         <v>3.993183192130434</v>
@@ -39427,7 +39430,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39435,7 +39438,7 @@
         <v>1</v>
       </c>
       <c r="B758" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C758">
         <v>3.431049885513136</v>
@@ -39444,7 +39447,7 @@
         <v>318</v>
       </c>
       <c r="E758">
-        <v>3.49312300206909</v>
+        <v>3.866598259682796</v>
       </c>
       <c r="F758">
         <v>1</v>
@@ -39453,10 +39456,10 @@
         <v>0.05354895011448686</v>
       </c>
       <c r="H758">
-        <v>0.05340687699793091</v>
+        <v>0.05245340174031721</v>
       </c>
       <c r="I758">
-        <v>0.06207311655595404</v>
+        <v>0.4355483741696595</v>
       </c>
       <c r="J758">
         <v>1.020731165559546</v>
@@ -39468,16 +39471,16 @@
         <v>28.49</v>
       </c>
       <c r="M758">
-        <v>24.45</v>
+        <v>23.8</v>
       </c>
       <c r="N758">
-        <v>28.45</v>
+        <v>28.16</v>
       </c>
       <c r="O758">
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39485,7 +39488,7 @@
         <v>0</v>
       </c>
       <c r="B759" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C759">
         <v>3.249078590284071</v>
@@ -39494,7 +39497,7 @@
         <v>318</v>
       </c>
       <c r="E759">
-        <v>3.311892934111839</v>
+        <v>3.690186168992298</v>
       </c>
       <c r="F759">
         <v>1</v>
@@ -39503,10 +39506,10 @@
         <v>0.05373092140971593</v>
       </c>
       <c r="H759">
-        <v>0.05358810706588816</v>
+        <v>0.0526298138310077</v>
       </c>
       <c r="I759">
-        <v>0.06281434382776752</v>
+        <v>0.4411075787082268</v>
       </c>
       <c r="J759">
         <v>1.028143438277634</v>
@@ -39518,16 +39521,66 @@
         <v>28.49</v>
       </c>
       <c r="M759">
-        <v>24.45</v>
+        <v>23.8</v>
       </c>
       <c r="N759">
-        <v>28.45</v>
+        <v>28.16</v>
       </c>
       <c r="O759">
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>186</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="760" spans="1:16">
+      <c r="A760" s="1">
+        <v>0</v>
+      </c>
+      <c r="B760" t="s">
+        <v>187</v>
+      </c>
+      <c r="C760">
+        <v>3.14672422434397</v>
+      </c>
+      <c r="D760" t="s">
+        <v>318</v>
+      </c>
+      <c r="E760">
+        <v>3.590958718508617</v>
+      </c>
+      <c r="F760">
+        <v>1</v>
+      </c>
+      <c r="G760">
+        <v>0.05383327577565603</v>
+      </c>
+      <c r="H760">
+        <v>0.05272904128149138</v>
+      </c>
+      <c r="I760">
+        <v>0.4442344941646468</v>
+      </c>
+      <c r="J760">
+        <v>1.032312658886193</v>
+      </c>
+      <c r="K760">
+        <v>24.55</v>
+      </c>
+      <c r="L760">
+        <v>28.49</v>
+      </c>
+      <c r="M760">
+        <v>23.8</v>
+      </c>
+      <c r="N760">
+        <v>28.16</v>
+      </c>
+      <c r="O760">
+        <v>1</v>
+      </c>
+      <c r="P760" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2298" uniqueCount="404">
   <si>
     <t>trade_time</t>
   </si>
@@ -574,12 +574,12 @@
     <t>2021-08-26</t>
   </si>
   <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
     <t>2021-08-31</t>
   </si>
   <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
     <t>2021-09-01</t>
   </si>
   <si>
@@ -967,10 +967,10 @@
     <t>2021-08-30</t>
   </si>
   <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
     <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
   </si>
   <si>
     <t>2016-07-29</t>
@@ -1583,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P760"/>
+  <dimension ref="A1:P762"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -39085,96 +39085,96 @@
     </row>
     <row r="751" spans="1:16">
       <c r="A751" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B751" t="s">
         <v>186</v>
       </c>
       <c r="C751">
-        <v>4.382704501789181</v>
+        <v>4.443664331454439</v>
       </c>
       <c r="D751" t="s">
         <v>317</v>
       </c>
       <c r="E751">
-        <v>4.041243466552189</v>
+        <v>4.848277437418155</v>
       </c>
       <c r="F751">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G751">
-        <v>0.04821729549821082</v>
+        <v>0.05253633566854556</v>
       </c>
       <c r="H751">
-        <v>0.05157875653344781</v>
+        <v>0.05147172256258185</v>
       </c>
       <c r="I751">
-        <v>0.3414610352369927</v>
+        <v>0.4046131059637155</v>
       </c>
       <c r="J751">
-        <v>1.00078974877675</v>
+        <v>0.9794841412849514</v>
       </c>
       <c r="K751">
-        <v>21.9</v>
+        <v>24.55</v>
       </c>
       <c r="L751">
-        <v>26.3</v>
+        <v>28.49</v>
       </c>
       <c r="M751">
-        <v>23.75</v>
+        <v>23.8</v>
       </c>
       <c r="N751">
-        <v>27.81</v>
+        <v>28.16</v>
       </c>
       <c r="O751">
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>185</v>
+        <v>401</v>
       </c>
     </row>
     <row r="752" spans="1:16">
       <c r="A752" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B752" t="s">
         <v>187</v>
       </c>
       <c r="C752">
-        <v>3.920611667530789</v>
+        <v>4.382704501789181</v>
       </c>
       <c r="D752" t="s">
         <v>318</v>
       </c>
       <c r="E752">
-        <v>4.341203979113352</v>
+        <v>4.041243466552189</v>
       </c>
       <c r="F752">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G752">
-        <v>0.05305938833246921</v>
+        <v>0.04821729549821082</v>
       </c>
       <c r="H752">
-        <v>0.05197879602088665</v>
+        <v>0.05157875653344781</v>
       </c>
       <c r="I752">
-        <v>0.4205923115825634</v>
+        <v>0.3414610352369927</v>
       </c>
       <c r="J752">
         <v>1.00078974877675</v>
       </c>
       <c r="K752">
-        <v>24.55</v>
+        <v>21.9</v>
       </c>
       <c r="L752">
-        <v>28.49</v>
+        <v>26.3</v>
       </c>
       <c r="M752">
-        <v>23.8</v>
+        <v>23.75</v>
       </c>
       <c r="N752">
-        <v>28.16</v>
+        <v>27.81</v>
       </c>
       <c r="O752">
         <v>1</v>
@@ -39185,96 +39185,96 @@
     </row>
     <row r="753" spans="1:16">
       <c r="A753" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B753" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C753">
-        <v>4.29964997793007</v>
+        <v>3.920611667530789</v>
       </c>
       <c r="D753" t="s">
         <v>317</v>
       </c>
       <c r="E753">
-        <v>3.884095085906051</v>
+        <v>4.341203979113352</v>
       </c>
       <c r="F753">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G753">
-        <v>0.05064035002206992</v>
+        <v>0.05305938833246921</v>
       </c>
       <c r="H753">
-        <v>0.05173590491409395</v>
+        <v>0.05197879602088665</v>
       </c>
       <c r="I753">
-        <v>0.4155548920240193</v>
+        <v>0.4205923115825634</v>
       </c>
       <c r="J753">
-        <v>1.007406522698693</v>
+        <v>1.00078974877675</v>
       </c>
       <c r="K753">
-        <v>23</v>
+        <v>24.55</v>
       </c>
       <c r="L753">
-        <v>27.47</v>
+        <v>28.49</v>
       </c>
       <c r="M753">
-        <v>23.75</v>
+        <v>23.8</v>
       </c>
       <c r="N753">
-        <v>27.81</v>
+        <v>28.16</v>
       </c>
       <c r="O753">
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>402</v>
+        <v>185</v>
       </c>
     </row>
     <row r="754" spans="1:16">
       <c r="A754" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B754" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C754">
-        <v>3.758169867747096</v>
+        <v>4.29964997793007</v>
       </c>
       <c r="D754" t="s">
         <v>318</v>
       </c>
       <c r="E754">
-        <v>4.183724759771117</v>
+        <v>3.884095085906051</v>
       </c>
       <c r="F754">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G754">
-        <v>0.05322183013225291</v>
+        <v>0.05064035002206992</v>
       </c>
       <c r="H754">
-        <v>0.05213627524022888</v>
+        <v>0.05173590491409395</v>
       </c>
       <c r="I754">
-        <v>0.4255548920240209</v>
+        <v>0.4155548920240193</v>
       </c>
       <c r="J754">
         <v>1.007406522698693</v>
       </c>
       <c r="K754">
-        <v>24.55</v>
+        <v>23</v>
       </c>
       <c r="L754">
-        <v>28.49</v>
+        <v>27.47</v>
       </c>
       <c r="M754">
-        <v>23.8</v>
+        <v>23.75</v>
       </c>
       <c r="N754">
-        <v>28.16</v>
+        <v>27.81</v>
       </c>
       <c r="O754">
         <v>1</v>
@@ -39285,96 +39285,96 @@
     </row>
     <row r="755" spans="1:16">
       <c r="A755" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B755" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C755">
-        <v>4.131161383432431</v>
+        <v>3.758169867747096</v>
       </c>
       <c r="D755" t="s">
         <v>317</v>
       </c>
       <c r="E755">
-        <v>3.710112298109578</v>
+        <v>4.183724759771117</v>
       </c>
       <c r="F755">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G755">
-        <v>0.05080883861656757</v>
+        <v>0.05322183013225291</v>
       </c>
       <c r="H755">
-        <v>0.05190988770189042</v>
+        <v>0.05213627524022888</v>
       </c>
       <c r="I755">
-        <v>0.4210490853228528</v>
+        <v>0.4255548920240209</v>
       </c>
       <c r="J755">
-        <v>1.014732113763807</v>
+        <v>1.007406522698693</v>
       </c>
       <c r="K755">
-        <v>23</v>
+        <v>24.55</v>
       </c>
       <c r="L755">
-        <v>27.47</v>
+        <v>28.49</v>
       </c>
       <c r="M755">
-        <v>23.75</v>
+        <v>23.8</v>
       </c>
       <c r="N755">
-        <v>27.81</v>
+        <v>28.16</v>
       </c>
       <c r="O755">
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>316</v>
+        <v>402</v>
       </c>
     </row>
     <row r="756" spans="1:16">
       <c r="A756" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B756" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C756">
-        <v>3.578326607098528</v>
+        <v>4.131161383432431</v>
       </c>
       <c r="D756" t="s">
         <v>318</v>
       </c>
       <c r="E756">
-        <v>4.009375692421386</v>
+        <v>3.710112298109578</v>
       </c>
       <c r="F756">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G756">
-        <v>0.05340167339290147</v>
+        <v>0.05080883861656757</v>
       </c>
       <c r="H756">
-        <v>0.05231062430757862</v>
+        <v>0.05190988770189042</v>
       </c>
       <c r="I756">
-        <v>0.4310490853228579</v>
+        <v>0.4210490853228528</v>
       </c>
       <c r="J756">
         <v>1.014732113763807</v>
       </c>
       <c r="K756">
-        <v>24.55</v>
+        <v>23</v>
       </c>
       <c r="L756">
-        <v>28.49</v>
+        <v>27.47</v>
       </c>
       <c r="M756">
-        <v>23.8</v>
+        <v>23.75</v>
       </c>
       <c r="N756">
-        <v>28.16</v>
+        <v>27.81</v>
       </c>
       <c r="O756">
         <v>1</v>
@@ -39385,134 +39385,134 @@
     </row>
     <row r="757" spans="1:16">
       <c r="A757" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B757" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C757">
-        <v>3.993183192130434</v>
+        <v>3.578326607098528</v>
       </c>
       <c r="D757" t="s">
         <v>317</v>
       </c>
       <c r="E757">
-        <v>3.567634817960773</v>
+        <v>4.009375692421386</v>
       </c>
       <c r="F757">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G757">
-        <v>0.05094681680786957</v>
+        <v>0.05340167339290147</v>
       </c>
       <c r="H757">
-        <v>0.05205236518203923</v>
+        <v>0.05231062430757862</v>
       </c>
       <c r="I757">
-        <v>0.4255483741696615</v>
+        <v>0.4310490853228579</v>
       </c>
       <c r="J757">
-        <v>1.020731165559546</v>
+        <v>1.014732113763807</v>
       </c>
       <c r="K757">
-        <v>23</v>
+        <v>24.55</v>
       </c>
       <c r="L757">
-        <v>27.47</v>
+        <v>28.49</v>
       </c>
       <c r="M757">
-        <v>23.75</v>
+        <v>23.8</v>
       </c>
       <c r="N757">
-        <v>27.81</v>
+        <v>28.16</v>
       </c>
       <c r="O757">
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>186</v>
+        <v>316</v>
       </c>
     </row>
     <row r="758" spans="1:16">
       <c r="A758" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B758" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C758">
-        <v>3.431049885513136</v>
+        <v>3.993183192130434</v>
       </c>
       <c r="D758" t="s">
         <v>318</v>
       </c>
       <c r="E758">
-        <v>3.866598259682796</v>
+        <v>3.567634817960773</v>
       </c>
       <c r="F758">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G758">
-        <v>0.05354895011448686</v>
+        <v>0.05094681680786957</v>
       </c>
       <c r="H758">
-        <v>0.05245340174031721</v>
+        <v>0.05205236518203923</v>
       </c>
       <c r="I758">
-        <v>0.4355483741696595</v>
+        <v>0.4255483741696615</v>
       </c>
       <c r="J758">
         <v>1.020731165559546</v>
       </c>
       <c r="K758">
-        <v>24.55</v>
+        <v>23</v>
       </c>
       <c r="L758">
-        <v>28.49</v>
+        <v>27.47</v>
       </c>
       <c r="M758">
-        <v>23.8</v>
+        <v>23.75</v>
       </c>
       <c r="N758">
-        <v>28.16</v>
+        <v>27.81</v>
       </c>
       <c r="O758">
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="759" spans="1:16">
       <c r="A759" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B759" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C759">
-        <v>3.249078590284071</v>
+        <v>3.431049885513136</v>
       </c>
       <c r="D759" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E759">
-        <v>3.690186168992298</v>
+        <v>3.866598259682796</v>
       </c>
       <c r="F759">
         <v>1</v>
       </c>
       <c r="G759">
-        <v>0.05373092140971593</v>
+        <v>0.05354895011448686</v>
       </c>
       <c r="H759">
-        <v>0.0526298138310077</v>
+        <v>0.05245340174031721</v>
       </c>
       <c r="I759">
-        <v>0.4411075787082268</v>
+        <v>0.4355483741696595</v>
       </c>
       <c r="J759">
-        <v>1.028143438277634</v>
+        <v>1.020731165559546</v>
       </c>
       <c r="K759">
         <v>24.55</v>
@@ -39530,7 +39530,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -39538,31 +39538,31 @@
         <v>0</v>
       </c>
       <c r="B760" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C760">
-        <v>3.14672422434397</v>
+        <v>3.249078590284071</v>
       </c>
       <c r="D760" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E760">
-        <v>3.590958718508617</v>
+        <v>3.690186168992298</v>
       </c>
       <c r="F760">
         <v>1</v>
       </c>
       <c r="G760">
-        <v>0.05383327577565603</v>
+        <v>0.05373092140971593</v>
       </c>
       <c r="H760">
-        <v>0.05272904128149138</v>
+        <v>0.0526298138310077</v>
       </c>
       <c r="I760">
-        <v>0.4442344941646468</v>
+        <v>0.4411075787082268</v>
       </c>
       <c r="J760">
-        <v>1.032312658886193</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K760">
         <v>24.55</v>
@@ -39580,7 +39580,107 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="761" spans="1:16">
+      <c r="A761" s="1">
+        <v>0</v>
+      </c>
+      <c r="B761" t="s">
+        <v>186</v>
+      </c>
+      <c r="C761">
+        <v>3.14672422434397</v>
+      </c>
+      <c r="D761" t="s">
+        <v>317</v>
+      </c>
+      <c r="E761">
+        <v>3.590958718508617</v>
+      </c>
+      <c r="F761">
+        <v>1</v>
+      </c>
+      <c r="G761">
+        <v>0.05383327577565603</v>
+      </c>
+      <c r="H761">
+        <v>0.05272904128149138</v>
+      </c>
+      <c r="I761">
+        <v>0.4442344941646468</v>
+      </c>
+      <c r="J761">
+        <v>1.032312658886193</v>
+      </c>
+      <c r="K761">
+        <v>24.55</v>
+      </c>
+      <c r="L761">
+        <v>28.49</v>
+      </c>
+      <c r="M761">
+        <v>23.8</v>
+      </c>
+      <c r="N761">
+        <v>28.16</v>
+      </c>
+      <c r="O761">
+        <v>1</v>
+      </c>
+      <c r="P761" t="s">
         <v>403</v>
+      </c>
+    </row>
+    <row r="762" spans="1:16">
+      <c r="A762" s="1">
+        <v>0</v>
+      </c>
+      <c r="B762" t="s">
+        <v>186</v>
+      </c>
+      <c r="C762">
+        <v>3.047718597071611</v>
+      </c>
+      <c r="D762" t="s">
+        <v>317</v>
+      </c>
+      <c r="E762">
+        <v>3.494977703067388</v>
+      </c>
+      <c r="F762">
+        <v>1</v>
+      </c>
+      <c r="G762">
+        <v>0.05393228140292838</v>
+      </c>
+      <c r="H762">
+        <v>0.05282502229693262</v>
+      </c>
+      <c r="I762">
+        <v>0.4472591059957765</v>
+      </c>
+      <c r="J762">
+        <v>1.036345474661034</v>
+      </c>
+      <c r="K762">
+        <v>24.55</v>
+      </c>
+      <c r="L762">
+        <v>28.49</v>
+      </c>
+      <c r="M762">
+        <v>23.8</v>
+      </c>
+      <c r="N762">
+        <v>28.16</v>
+      </c>
+      <c r="O762">
+        <v>1</v>
+      </c>
+      <c r="P762" t="s">
+        <v>318</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -574,15 +574,15 @@
     <t>2021-08-26</t>
   </si>
   <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021-09-06</t>
   </si>
   <si>
     <t>2021-08-31</t>
   </si>
   <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
     <t>2016-09-12</t>
   </si>
   <si>
@@ -967,10 +967,10 @@
     <t>2021-08-30</t>
   </si>
   <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
     <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
   </si>
   <si>
     <t>2016-07-29</t>
@@ -39091,40 +39091,40 @@
         <v>186</v>
       </c>
       <c r="C751">
-        <v>4.443664331454439</v>
+        <v>4.941864750446115</v>
       </c>
       <c r="D751" t="s">
         <v>317</v>
       </c>
       <c r="E751">
-        <v>4.848277437418155</v>
+        <v>4.547251644482401</v>
       </c>
       <c r="F751">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G751">
-        <v>0.05253633566854556</v>
+        <v>0.04999813524955388</v>
       </c>
       <c r="H751">
-        <v>0.05147172256258185</v>
+        <v>0.0510727483555176</v>
       </c>
       <c r="I751">
-        <v>0.4046131059637155</v>
+        <v>0.3946131059637139</v>
       </c>
       <c r="J751">
         <v>0.9794841412849514</v>
       </c>
       <c r="K751">
-        <v>24.55</v>
+        <v>23</v>
       </c>
       <c r="L751">
-        <v>28.49</v>
+        <v>27.47</v>
       </c>
       <c r="M751">
-        <v>23.8</v>
+        <v>23.75</v>
       </c>
       <c r="N751">
-        <v>28.16</v>
+        <v>27.81</v>
       </c>
       <c r="O751">
         <v>1</v>
@@ -39135,96 +39135,96 @@
     </row>
     <row r="752" spans="1:16">
       <c r="A752" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B752" t="s">
         <v>187</v>
       </c>
       <c r="C752">
-        <v>4.382704501789181</v>
+        <v>4.443664331454439</v>
       </c>
       <c r="D752" t="s">
         <v>318</v>
       </c>
       <c r="E752">
-        <v>4.041243466552189</v>
+        <v>4.848277437418155</v>
       </c>
       <c r="F752">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G752">
-        <v>0.04821729549821082</v>
+        <v>0.05253633566854556</v>
       </c>
       <c r="H752">
-        <v>0.05157875653344781</v>
+        <v>0.05147172256258185</v>
       </c>
       <c r="I752">
-        <v>0.3414610352369927</v>
+        <v>0.4046131059637155</v>
       </c>
       <c r="J752">
-        <v>1.00078974877675</v>
+        <v>0.9794841412849514</v>
       </c>
       <c r="K752">
-        <v>21.9</v>
+        <v>24.55</v>
       </c>
       <c r="L752">
-        <v>26.3</v>
+        <v>28.49</v>
       </c>
       <c r="M752">
-        <v>23.75</v>
+        <v>23.8</v>
       </c>
       <c r="N752">
-        <v>27.81</v>
+        <v>28.16</v>
       </c>
       <c r="O752">
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>185</v>
+        <v>401</v>
       </c>
     </row>
     <row r="753" spans="1:16">
       <c r="A753" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B753" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C753">
-        <v>3.920611667530789</v>
+        <v>4.382704501789181</v>
       </c>
       <c r="D753" t="s">
         <v>317</v>
       </c>
       <c r="E753">
-        <v>4.341203979113352</v>
+        <v>4.041243466552189</v>
       </c>
       <c r="F753">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G753">
-        <v>0.05305938833246921</v>
+        <v>0.04821729549821082</v>
       </c>
       <c r="H753">
-        <v>0.05197879602088665</v>
+        <v>0.05157875653344781</v>
       </c>
       <c r="I753">
-        <v>0.4205923115825634</v>
+        <v>0.3414610352369927</v>
       </c>
       <c r="J753">
         <v>1.00078974877675</v>
       </c>
       <c r="K753">
-        <v>24.55</v>
+        <v>21.9</v>
       </c>
       <c r="L753">
-        <v>28.49</v>
+        <v>26.3</v>
       </c>
       <c r="M753">
-        <v>23.8</v>
+        <v>23.75</v>
       </c>
       <c r="N753">
-        <v>28.16</v>
+        <v>27.81</v>
       </c>
       <c r="O753">
         <v>1</v>
@@ -39235,96 +39235,96 @@
     </row>
     <row r="754" spans="1:16">
       <c r="A754" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B754" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C754">
-        <v>4.29964997793007</v>
+        <v>3.920611667530789</v>
       </c>
       <c r="D754" t="s">
         <v>318</v>
       </c>
       <c r="E754">
-        <v>3.884095085906051</v>
+        <v>4.341203979113352</v>
       </c>
       <c r="F754">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G754">
-        <v>0.05064035002206992</v>
+        <v>0.05305938833246921</v>
       </c>
       <c r="H754">
-        <v>0.05173590491409395</v>
+        <v>0.05197879602088665</v>
       </c>
       <c r="I754">
-        <v>0.4155548920240193</v>
+        <v>0.4205923115825634</v>
       </c>
       <c r="J754">
-        <v>1.007406522698693</v>
+        <v>1.00078974877675</v>
       </c>
       <c r="K754">
-        <v>23</v>
+        <v>24.55</v>
       </c>
       <c r="L754">
-        <v>27.47</v>
+        <v>28.49</v>
       </c>
       <c r="M754">
-        <v>23.75</v>
+        <v>23.8</v>
       </c>
       <c r="N754">
-        <v>27.81</v>
+        <v>28.16</v>
       </c>
       <c r="O754">
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>402</v>
+        <v>185</v>
       </c>
     </row>
     <row r="755" spans="1:16">
       <c r="A755" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B755" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C755">
-        <v>3.758169867747096</v>
+        <v>4.237797152898636</v>
       </c>
       <c r="D755" t="s">
         <v>317</v>
       </c>
       <c r="E755">
-        <v>4.183724759771117</v>
+        <v>3.884095085906051</v>
       </c>
       <c r="F755">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G755">
-        <v>0.05322183013225291</v>
+        <v>0.04836220284710137</v>
       </c>
       <c r="H755">
-        <v>0.05213627524022888</v>
+        <v>0.05173590491409395</v>
       </c>
       <c r="I755">
-        <v>0.4255548920240209</v>
+        <v>0.3537020669925859</v>
       </c>
       <c r="J755">
         <v>1.007406522698693</v>
       </c>
       <c r="K755">
-        <v>24.55</v>
+        <v>21.9</v>
       </c>
       <c r="L755">
-        <v>28.49</v>
+        <v>26.3</v>
       </c>
       <c r="M755">
-        <v>23.8</v>
+        <v>23.75</v>
       </c>
       <c r="N755">
-        <v>28.16</v>
+        <v>27.81</v>
       </c>
       <c r="O755">
         <v>1</v>
@@ -39335,96 +39335,96 @@
     </row>
     <row r="756" spans="1:16">
       <c r="A756" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B756" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C756">
-        <v>4.131161383432431</v>
+        <v>3.758169867747096</v>
       </c>
       <c r="D756" t="s">
         <v>318</v>
       </c>
       <c r="E756">
-        <v>3.710112298109578</v>
+        <v>4.183724759771117</v>
       </c>
       <c r="F756">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G756">
-        <v>0.05080883861656757</v>
+        <v>0.05322183013225291</v>
       </c>
       <c r="H756">
-        <v>0.05190988770189042</v>
+        <v>0.05213627524022888</v>
       </c>
       <c r="I756">
-        <v>0.4210490853228528</v>
+        <v>0.4255548920240209</v>
       </c>
       <c r="J756">
-        <v>1.014732113763807</v>
+        <v>1.007406522698693</v>
       </c>
       <c r="K756">
-        <v>23</v>
+        <v>24.55</v>
       </c>
       <c r="L756">
-        <v>27.47</v>
+        <v>28.49</v>
       </c>
       <c r="M756">
-        <v>23.75</v>
+        <v>23.8</v>
       </c>
       <c r="N756">
-        <v>27.81</v>
+        <v>28.16</v>
       </c>
       <c r="O756">
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>316</v>
+        <v>402</v>
       </c>
     </row>
     <row r="757" spans="1:16">
       <c r="A757" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B757" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C757">
-        <v>3.578326607098528</v>
+        <v>4.077366708572622</v>
       </c>
       <c r="D757" t="s">
         <v>317</v>
       </c>
       <c r="E757">
-        <v>4.009375692421386</v>
+        <v>3.710112298109578</v>
       </c>
       <c r="F757">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G757">
-        <v>0.05340167339290147</v>
+        <v>0.04852263329142738</v>
       </c>
       <c r="H757">
-        <v>0.05231062430757862</v>
+        <v>0.05190988770189042</v>
       </c>
       <c r="I757">
-        <v>0.4310490853228579</v>
+        <v>0.367254410463044</v>
       </c>
       <c r="J757">
         <v>1.014732113763807</v>
       </c>
       <c r="K757">
-        <v>24.55</v>
+        <v>21.9</v>
       </c>
       <c r="L757">
-        <v>28.49</v>
+        <v>26.3</v>
       </c>
       <c r="M757">
-        <v>23.8</v>
+        <v>23.75</v>
       </c>
       <c r="N757">
-        <v>28.16</v>
+        <v>27.81</v>
       </c>
       <c r="O757">
         <v>1</v>
@@ -39435,66 +39435,66 @@
     </row>
     <row r="758" spans="1:16">
       <c r="A758" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B758" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C758">
-        <v>3.993183192130434</v>
+        <v>3.578326607098528</v>
       </c>
       <c r="D758" t="s">
         <v>318</v>
       </c>
       <c r="E758">
-        <v>3.567634817960773</v>
+        <v>4.009375692421386</v>
       </c>
       <c r="F758">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G758">
-        <v>0.05094681680786957</v>
+        <v>0.05340167339290147</v>
       </c>
       <c r="H758">
-        <v>0.05205236518203923</v>
+        <v>0.05231062430757862</v>
       </c>
       <c r="I758">
-        <v>0.4255483741696615</v>
+        <v>0.4310490853228579</v>
       </c>
       <c r="J758">
-        <v>1.020731165559546</v>
+        <v>1.014732113763807</v>
       </c>
       <c r="K758">
-        <v>23</v>
+        <v>24.55</v>
       </c>
       <c r="L758">
-        <v>27.47</v>
+        <v>28.49</v>
       </c>
       <c r="M758">
-        <v>23.75</v>
+        <v>23.8</v>
       </c>
       <c r="N758">
-        <v>27.81</v>
+        <v>28.16</v>
       </c>
       <c r="O758">
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>187</v>
+        <v>316</v>
       </c>
     </row>
     <row r="759" spans="1:16">
       <c r="A759" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B759" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C759">
         <v>3.431049885513136</v>
       </c>
       <c r="D759" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E759">
         <v>3.866598259682796</v>
@@ -39530,7 +39530,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -39538,13 +39538,13 @@
         <v>0</v>
       </c>
       <c r="B760" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C760">
         <v>3.249078590284071</v>
       </c>
       <c r="D760" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E760">
         <v>3.690186168992298</v>
@@ -39580,7 +39580,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -39588,13 +39588,13 @@
         <v>0</v>
       </c>
       <c r="B761" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C761">
         <v>3.14672422434397</v>
       </c>
       <c r="D761" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E761">
         <v>3.590958718508617</v>
@@ -39638,13 +39638,13 @@
         <v>0</v>
       </c>
       <c r="B762" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C762">
         <v>3.047718597071611</v>
       </c>
       <c r="D762" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E762">
         <v>3.494977703067388</v>
@@ -39680,7 +39680,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2316" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="408">
   <si>
     <t>trade_time</t>
   </si>
@@ -965,6 +965,9 @@
   </si>
   <si>
     <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>2021-09-23</t>
   </si>
   <si>
     <t>2021-09-17</t>
@@ -1592,7 +1595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P768"/>
+  <dimension ref="A1:P767"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1689,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1739,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1789,7 +1792,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1839,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1889,7 +1892,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2139,7 +2142,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2189,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2239,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2289,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2339,7 +2342,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2389,7 +2392,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2439,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2489,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2539,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2589,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2639,7 +2642,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2689,7 +2692,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2739,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2789,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2839,7 +2842,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2889,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2939,7 +2942,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2989,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3039,7 +3042,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3089,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3139,7 +3142,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3189,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3239,7 +3242,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3289,7 +3292,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3339,7 +3342,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3389,7 +3392,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3439,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3489,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3539,7 +3542,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3589,7 +3592,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3639,7 +3642,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3689,7 +3692,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3739,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3789,7 +3792,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3839,7 +3842,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3889,7 +3892,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3939,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3989,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4039,7 +4042,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4089,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4139,7 +4142,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4189,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4239,7 +4242,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4289,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4339,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4389,7 +4392,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4439,7 +4442,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4489,7 +4492,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4539,7 +4542,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4589,7 +4592,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4939,7 +4942,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4989,7 +4992,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5039,7 +5042,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5089,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5139,7 +5142,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5489,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5539,7 +5542,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5589,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5639,7 +5642,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5689,7 +5692,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5739,7 +5742,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5789,7 +5792,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5839,7 +5842,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5889,7 +5892,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5939,7 +5942,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5989,7 +5992,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6039,7 +6042,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6089,7 +6092,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6139,7 +6142,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6189,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6239,7 +6242,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6289,7 +6292,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6339,7 +6342,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6389,7 +6392,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6439,7 +6442,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6489,7 +6492,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6539,7 +6542,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6589,7 +6592,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6639,7 +6642,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6689,7 +6692,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6739,7 +6742,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6789,7 +6792,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6839,7 +6842,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6889,7 +6892,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6939,7 +6942,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6989,7 +6992,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7039,7 +7042,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7089,7 +7092,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7139,7 +7142,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7189,7 +7192,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7239,7 +7242,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7289,7 +7292,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7339,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7389,7 +7392,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7439,7 +7442,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7489,7 +7492,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7539,7 +7542,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7589,7 +7592,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7639,7 +7642,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7689,7 +7692,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7739,7 +7742,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7789,7 +7792,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8189,7 +8192,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8239,7 +8242,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8289,7 +8292,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8339,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8389,7 +8392,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8439,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8489,7 +8492,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8539,7 +8542,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9389,7 +9392,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9439,7 +9442,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9489,7 +9492,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9539,7 +9542,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9589,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9639,7 +9642,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9689,7 +9692,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9739,7 +9742,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10589,7 +10592,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10639,7 +10642,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10689,7 +10692,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10739,7 +10742,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10789,7 +10792,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10839,7 +10842,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10889,7 +10892,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10939,7 +10942,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11389,7 +11392,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11439,7 +11442,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11489,7 +11492,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11539,7 +11542,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11589,7 +11592,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11639,7 +11642,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11689,7 +11692,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11739,7 +11742,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12139,7 +12142,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12189,7 +12192,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12239,7 +12242,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12289,7 +12292,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12339,7 +12342,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12389,7 +12392,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12439,7 +12442,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12489,7 +12492,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12539,7 +12542,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12589,7 +12592,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12639,7 +12642,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12689,7 +12692,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12739,7 +12742,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12789,7 +12792,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12839,7 +12842,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12889,7 +12892,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12939,7 +12942,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12989,7 +12992,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13039,7 +13042,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13089,7 +13092,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13139,7 +13142,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13189,7 +13192,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13239,7 +13242,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13289,7 +13292,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13339,7 +13342,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13389,7 +13392,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13439,7 +13442,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13489,7 +13492,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13539,7 +13542,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13589,7 +13592,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13639,7 +13642,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13689,7 +13692,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13739,7 +13742,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13789,7 +13792,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14139,7 +14142,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14189,7 +14192,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14239,7 +14242,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14289,7 +14292,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14339,7 +14342,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14389,7 +14392,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14439,7 +14442,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14489,7 +14492,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14539,7 +14542,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14589,7 +14592,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14639,7 +14642,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14689,7 +14692,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14739,7 +14742,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14789,7 +14792,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14839,7 +14842,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14889,7 +14892,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14939,7 +14942,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14989,7 +14992,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -16139,7 +16142,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16189,7 +16192,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16239,7 +16242,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16289,7 +16292,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16339,7 +16342,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16389,7 +16392,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16439,7 +16442,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16489,7 +16492,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16539,7 +16542,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16589,7 +16592,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -18239,7 +18242,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18289,7 +18292,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18339,7 +18342,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18389,7 +18392,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18439,7 +18442,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18489,7 +18492,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18689,7 +18692,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18739,7 +18742,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19089,7 +19092,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19139,7 +19142,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19189,7 +19192,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19689,7 +19692,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19739,7 +19742,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19789,7 +19792,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20539,7 +20542,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20589,7 +20592,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20639,7 +20642,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20689,7 +20692,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20739,7 +20742,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20789,7 +20792,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20839,7 +20842,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20889,7 +20892,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20939,7 +20942,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20989,7 +20992,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21039,7 +21042,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21089,7 +21092,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21139,7 +21142,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21189,7 +21192,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21239,7 +21242,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21289,7 +21292,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21339,7 +21342,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21389,7 +21392,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21439,7 +21442,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21489,7 +21492,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21539,7 +21542,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21589,7 +21592,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21639,7 +21642,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21689,7 +21692,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21739,7 +21742,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21789,7 +21792,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21839,7 +21842,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21889,7 +21892,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21939,7 +21942,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21989,7 +21992,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22039,7 +22042,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22089,7 +22092,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22139,7 +22142,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22189,7 +22192,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22239,7 +22242,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22289,7 +22292,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22339,7 +22342,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22839,7 +22842,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22889,7 +22892,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22939,7 +22942,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22989,7 +22992,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23039,7 +23042,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23089,7 +23092,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23139,7 +23142,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23189,7 +23192,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23239,7 +23242,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23289,7 +23292,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23339,7 +23342,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23389,7 +23392,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23439,7 +23442,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23489,7 +23492,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23539,7 +23542,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23589,7 +23592,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23639,7 +23642,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23689,7 +23692,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23739,7 +23742,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23789,7 +23792,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23839,7 +23842,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23889,7 +23892,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23939,7 +23942,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23989,7 +23992,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24039,7 +24042,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24089,7 +24092,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24139,7 +24142,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24189,7 +24192,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24239,7 +24242,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24289,7 +24292,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24339,7 +24342,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24389,7 +24392,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24439,7 +24442,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24489,7 +24492,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24539,7 +24542,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24589,7 +24592,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24639,7 +24642,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24689,7 +24692,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24739,7 +24742,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24789,7 +24792,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25739,7 +25742,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25789,7 +25792,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25839,7 +25842,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25889,7 +25892,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25939,7 +25942,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25989,7 +25992,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26039,7 +26042,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26089,7 +26092,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26139,7 +26142,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26189,7 +26192,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26239,7 +26242,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26289,7 +26292,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26339,7 +26342,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26389,7 +26392,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26439,7 +26442,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26489,7 +26492,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26539,7 +26542,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26589,7 +26592,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26639,7 +26642,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26689,7 +26692,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26739,7 +26742,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26789,7 +26792,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26839,7 +26842,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26889,7 +26892,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26939,7 +26942,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26989,7 +26992,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27039,7 +27042,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27089,7 +27092,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27139,7 +27142,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27189,7 +27192,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27239,7 +27242,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27289,7 +27292,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27339,7 +27342,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27389,7 +27392,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27439,7 +27442,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27489,7 +27492,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27539,7 +27542,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27589,7 +27592,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27639,7 +27642,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27689,7 +27692,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27739,7 +27742,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27789,7 +27792,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27839,7 +27842,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27889,7 +27892,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27939,7 +27942,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27989,7 +27992,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28039,7 +28042,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28089,7 +28092,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28139,7 +28142,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28189,7 +28192,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28239,7 +28242,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28289,7 +28292,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28789,7 +28792,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28839,7 +28842,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28889,7 +28892,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28939,7 +28942,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -28989,7 +28992,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29039,7 +29042,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29089,7 +29092,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29139,7 +29142,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29189,7 +29192,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29239,7 +29242,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29289,7 +29292,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29339,7 +29342,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29389,7 +29392,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29439,7 +29442,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29489,7 +29492,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29539,7 +29542,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29589,7 +29592,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29639,7 +29642,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29689,7 +29692,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29739,7 +29742,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29789,7 +29792,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29839,7 +29842,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29889,7 +29892,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29939,7 +29942,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -29989,7 +29992,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30039,7 +30042,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30089,7 +30092,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30139,7 +30142,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30189,7 +30192,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30239,7 +30242,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30289,7 +30292,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30339,7 +30342,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30389,7 +30392,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30439,7 +30442,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30489,7 +30492,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30539,7 +30542,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30589,7 +30592,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30639,7 +30642,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30689,7 +30692,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30739,7 +30742,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30789,7 +30792,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30839,7 +30842,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30889,7 +30892,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31339,7 +31342,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31389,7 +31392,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31439,7 +31442,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31489,7 +31492,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31539,7 +31542,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31589,7 +31592,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31639,7 +31642,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31689,7 +31692,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31739,7 +31742,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31789,7 +31792,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31839,7 +31842,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -31889,7 +31892,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31939,7 +31942,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -31989,7 +31992,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32039,7 +32042,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32089,7 +32092,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32839,7 +32842,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32889,7 +32892,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32939,7 +32942,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -32989,7 +32992,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33039,7 +33042,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33089,7 +33092,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33139,7 +33142,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33189,7 +33192,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33239,7 +33242,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33289,7 +33292,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33339,7 +33342,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33389,7 +33392,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33439,7 +33442,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33489,7 +33492,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33839,7 +33842,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33889,7 +33892,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33939,7 +33942,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -33989,7 +33992,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34039,7 +34042,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34089,7 +34092,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34389,7 +34392,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34439,7 +34442,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34489,7 +34492,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34539,7 +34542,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34589,7 +34592,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34639,7 +34642,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34689,7 +34692,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34739,7 +34742,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34789,7 +34792,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34839,7 +34842,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34889,7 +34892,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -34939,7 +34942,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -34989,7 +34992,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35039,7 +35042,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35089,7 +35092,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35139,7 +35142,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35189,7 +35192,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35239,7 +35242,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35289,7 +35292,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35639,7 +35642,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35689,7 +35692,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35739,7 +35742,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35789,7 +35792,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35839,7 +35842,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35889,7 +35892,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35939,7 +35942,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -35989,7 +35992,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36039,7 +36042,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36089,7 +36092,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36139,7 +36142,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36189,7 +36192,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36239,7 +36242,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36289,7 +36292,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36339,7 +36342,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36389,7 +36392,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36439,7 +36442,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36489,7 +36492,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36539,7 +36542,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36589,7 +36592,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36639,7 +36642,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36689,7 +36692,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36739,7 +36742,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36789,7 +36792,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36839,7 +36842,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36889,7 +36892,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36939,7 +36942,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -36989,7 +36992,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37039,7 +37042,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37089,7 +37092,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37139,7 +37142,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37189,7 +37192,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37589,7 +37592,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37639,7 +37642,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37689,7 +37692,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37739,7 +37742,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37789,7 +37792,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -37839,7 +37842,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -37889,7 +37892,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38539,7 +38542,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38589,7 +38592,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38639,7 +38642,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38689,7 +38692,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38739,7 +38742,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38789,7 +38792,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38839,7 +38842,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38889,7 +38892,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -38939,7 +38942,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -38989,7 +38992,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39039,7 +39042,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39089,7 +39092,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39139,7 +39142,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39156,7 +39159,7 @@
         <v>317</v>
       </c>
       <c r="E752">
-        <v>4.739813164574617</v>
+        <v>4.767761578703109</v>
       </c>
       <c r="F752">
         <v>-1</v>
@@ -39165,10 +39168,10 @@
         <v>0.05007121262836114</v>
       </c>
       <c r="H752">
-        <v>0.04960018683542539</v>
+        <v>0.0494322384212969</v>
       </c>
       <c r="I752">
-        <v>0.5689742070642438</v>
+        <v>0.541025792935752</v>
       </c>
       <c r="J752">
         <v>0.9794841412849514</v>
@@ -39180,16 +39183,16 @@
         <v>27.69</v>
       </c>
       <c r="M752">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="N752">
-        <v>27.17</v>
+        <v>27.1</v>
       </c>
       <c r="O752">
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39256,7 +39259,7 @@
         <v>317</v>
       </c>
       <c r="E754">
-        <v>4.251914753012432</v>
+        <v>4.281993727890104</v>
       </c>
       <c r="F754">
         <v>-1</v>
@@ -39265,10 +39268,10 @@
         <v>0.05055804575954873</v>
       </c>
       <c r="H754">
-        <v>0.05008808524698757</v>
+        <v>0.0499180062721099</v>
       </c>
       <c r="I754">
-        <v>0.5700394874388337</v>
+        <v>0.5399605125611622</v>
       </c>
       <c r="J754">
         <v>1.00078974877675</v>
@@ -39280,10 +39283,10 @@
         <v>27.69</v>
       </c>
       <c r="M754">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="N754">
-        <v>27.17</v>
+        <v>27.1</v>
       </c>
       <c r="O754">
         <v>1</v>
@@ -39339,7 +39342,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39356,7 +39359,7 @@
         <v>317</v>
       </c>
       <c r="E756">
-        <v>4.100390630199943</v>
+        <v>4.131131282469809</v>
       </c>
       <c r="F756">
         <v>-1</v>
@@ -39365,10 +39368,10 @@
         <v>0.05070923904366513</v>
       </c>
       <c r="H756">
-        <v>0.05023960936980006</v>
+        <v>0.0500688687175302</v>
       </c>
       <c r="I756">
-        <v>0.5703703261349311</v>
+        <v>0.5396296738650648</v>
       </c>
       <c r="J756">
         <v>1.007406522698693</v>
@@ -39380,16 +39383,16 @@
         <v>27.69</v>
       </c>
       <c r="M756">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="N756">
-        <v>27.17</v>
+        <v>27.1</v>
       </c>
       <c r="O756">
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39397,43 +39400,43 @@
         <v>0</v>
       </c>
       <c r="B757" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C757">
-        <v>3.578326607098528</v>
+        <v>4.503371200497003</v>
       </c>
       <c r="D757" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E757">
-        <v>4.009375692421386</v>
+        <v>3.964107806185197</v>
       </c>
       <c r="F757">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G757">
-        <v>0.05340167339290147</v>
+        <v>0.050876628799503</v>
       </c>
       <c r="H757">
-        <v>0.05231062430757862</v>
+        <v>0.05023589219381481</v>
       </c>
       <c r="I757">
-        <v>0.4310490853228579</v>
+        <v>0.5392633943118064</v>
       </c>
       <c r="J757">
         <v>1.014732113763807</v>
       </c>
       <c r="K757">
-        <v>24.55</v>
+        <v>22.85</v>
       </c>
       <c r="L757">
-        <v>28.49</v>
+        <v>27.69</v>
       </c>
       <c r="M757">
-        <v>23.8</v>
+        <v>22.8</v>
       </c>
       <c r="N757">
-        <v>28.16</v>
+        <v>27.1</v>
       </c>
       <c r="O757">
         <v>1</v>
@@ -39444,434 +39447,434 @@
     </row>
     <row r="758" spans="1:16">
       <c r="A758" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B758" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C758">
-        <v>4.503371200497003</v>
+        <v>3.431049885513136</v>
       </c>
       <c r="D758" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E758">
-        <v>3.932634594808817</v>
+        <v>3.866598259682796</v>
       </c>
       <c r="F758">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G758">
-        <v>0.050876628799503</v>
+        <v>0.05354895011448686</v>
       </c>
       <c r="H758">
-        <v>0.05040736540519119</v>
+        <v>0.05245340174031721</v>
       </c>
       <c r="I758">
-        <v>0.570736605688186</v>
+        <v>0.4355483741696595</v>
       </c>
       <c r="J758">
-        <v>1.014732113763807</v>
+        <v>1.020731165559546</v>
       </c>
       <c r="K758">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L758">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M758">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="N758">
-        <v>27.17</v>
+        <v>28.16</v>
       </c>
       <c r="O758">
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>315</v>
+        <v>403</v>
       </c>
     </row>
     <row r="759" spans="1:16">
       <c r="A759" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B759" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C759">
-        <v>3.431049885513136</v>
+        <v>4.366292866964365</v>
       </c>
       <c r="D759" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E759">
-        <v>3.866598259682796</v>
+        <v>3.827329425242343</v>
       </c>
       <c r="F759">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G759">
-        <v>0.05354895011448686</v>
+        <v>0.05101370713303564</v>
       </c>
       <c r="H759">
-        <v>0.05245340174031721</v>
+        <v>0.05037267057475767</v>
       </c>
       <c r="I759">
-        <v>0.4355483741696595</v>
+        <v>0.5389634417220215</v>
       </c>
       <c r="J759">
         <v>1.020731165559546</v>
       </c>
       <c r="K759">
-        <v>24.55</v>
+        <v>22.85</v>
       </c>
       <c r="L759">
-        <v>28.49</v>
+        <v>27.69</v>
       </c>
       <c r="M759">
-        <v>23.8</v>
+        <v>22.8</v>
       </c>
       <c r="N759">
-        <v>28.16</v>
+        <v>27.1</v>
       </c>
       <c r="O759">
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="760" spans="1:16">
       <c r="A760" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B760" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C760">
-        <v>4.366292866964365</v>
+        <v>3.249078590284071</v>
       </c>
       <c r="D760" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E760">
-        <v>3.79525630868639</v>
+        <v>3.690186168992298</v>
       </c>
       <c r="F760">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G760">
-        <v>0.05101370713303564</v>
+        <v>0.05373092140971593</v>
       </c>
       <c r="H760">
-        <v>0.05054474369131361</v>
+        <v>0.0526298138310077</v>
       </c>
       <c r="I760">
-        <v>0.5710365582779744</v>
+        <v>0.4411075787082268</v>
       </c>
       <c r="J760">
-        <v>1.020731165559546</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K760">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L760">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M760">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="N760">
-        <v>27.17</v>
+        <v>28.16</v>
       </c>
       <c r="O760">
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="761" spans="1:16">
       <c r="A761" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B761" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C761">
-        <v>3.249078590284071</v>
+        <v>4.196922435356054</v>
       </c>
       <c r="D761" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E761">
-        <v>3.690186168992298</v>
+        <v>3.658329607269934</v>
       </c>
       <c r="F761">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G761">
-        <v>0.05373092140971593</v>
+        <v>0.05118307756464395</v>
       </c>
       <c r="H761">
-        <v>0.0526298138310077</v>
+        <v>0.05054167039273007</v>
       </c>
       <c r="I761">
-        <v>0.4411075787082268</v>
+        <v>0.5385928280861201</v>
       </c>
       <c r="J761">
         <v>1.028143438277634</v>
       </c>
       <c r="K761">
-        <v>24.55</v>
+        <v>22.85</v>
       </c>
       <c r="L761">
-        <v>28.49</v>
+        <v>27.69</v>
       </c>
       <c r="M761">
-        <v>23.8</v>
+        <v>22.8</v>
       </c>
       <c r="N761">
-        <v>28.16</v>
+        <v>27.1</v>
       </c>
       <c r="O761">
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="762" spans="1:16">
       <c r="A762" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B762" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C762">
-        <v>4.196922435356054</v>
+        <v>3.14672422434397</v>
       </c>
       <c r="D762" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E762">
-        <v>3.625515263442175</v>
+        <v>3.590958718508617</v>
       </c>
       <c r="F762">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G762">
-        <v>0.05118307756464395</v>
+        <v>0.05383327577565603</v>
       </c>
       <c r="H762">
-        <v>0.05071448473655783</v>
+        <v>0.05272904128149138</v>
       </c>
       <c r="I762">
-        <v>0.5714071719138794</v>
+        <v>0.4442344941646468</v>
       </c>
       <c r="J762">
-        <v>1.028143438277634</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K762">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L762">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M762">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="N762">
-        <v>27.17</v>
+        <v>28.16</v>
       </c>
       <c r="O762">
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="763" spans="1:16">
       <c r="A763" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B763" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C763">
-        <v>3.14672422434397</v>
+        <v>4.101655744450497</v>
       </c>
       <c r="D763" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E763">
-        <v>3.590958718508617</v>
+        <v>3.563271377394809</v>
       </c>
       <c r="F763">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G763">
-        <v>0.05383327577565603</v>
+        <v>0.05127834425554951</v>
       </c>
       <c r="H763">
-        <v>0.05272904128149138</v>
+        <v>0.05063672862260519</v>
       </c>
       <c r="I763">
-        <v>0.4442344941646468</v>
+        <v>0.5383843670556878</v>
       </c>
       <c r="J763">
         <v>1.032312658886193</v>
       </c>
       <c r="K763">
-        <v>24.55</v>
+        <v>22.85</v>
       </c>
       <c r="L763">
-        <v>28.49</v>
+        <v>27.69</v>
       </c>
       <c r="M763">
-        <v>23.8</v>
+        <v>22.8</v>
       </c>
       <c r="N763">
-        <v>28.16</v>
+        <v>27.1</v>
       </c>
       <c r="O763">
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="764" spans="1:16">
       <c r="A764" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B764" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C764">
-        <v>4.101655744450497</v>
+        <v>3.047718597071611</v>
       </c>
       <c r="D764" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E764">
-        <v>3.530040111506192</v>
+        <v>3.494977703067388</v>
       </c>
       <c r="F764">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G764">
-        <v>0.05127834425554951</v>
+        <v>0.05393228140292838</v>
       </c>
       <c r="H764">
-        <v>0.05080995988849381</v>
+        <v>0.05282502229693262</v>
       </c>
       <c r="I764">
-        <v>0.5716156329443045</v>
+        <v>0.4472591059957765</v>
       </c>
       <c r="J764">
-        <v>1.032312658886193</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K764">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L764">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M764">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="N764">
-        <v>27.17</v>
+        <v>28.16</v>
       </c>
       <c r="O764">
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="765" spans="1:16">
       <c r="A765" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B765" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C765">
-        <v>3.047718597071611</v>
+        <v>4.009505903995372</v>
       </c>
       <c r="D765" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E765">
-        <v>3.494977703067388</v>
+        <v>3.471323177728422</v>
       </c>
       <c r="F765">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G765">
-        <v>0.05393228140292838</v>
+        <v>0.05137049409600464</v>
       </c>
       <c r="H765">
-        <v>0.05282502229693262</v>
+        <v>0.05072867682227158</v>
       </c>
       <c r="I765">
-        <v>0.4472591059957765</v>
+        <v>0.5381827262669496</v>
       </c>
       <c r="J765">
         <v>1.036345474661034</v>
       </c>
       <c r="K765">
-        <v>24.55</v>
+        <v>22.85</v>
       </c>
       <c r="L765">
-        <v>28.49</v>
+        <v>27.69</v>
       </c>
       <c r="M765">
-        <v>23.8</v>
+        <v>22.8</v>
       </c>
       <c r="N765">
-        <v>28.16</v>
+        <v>27.1</v>
       </c>
       <c r="O765">
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="766" spans="1:16">
       <c r="A766" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B766" t="s">
         <v>187</v>
       </c>
       <c r="C766">
-        <v>4.009505903995372</v>
+        <v>3.923892030831919</v>
       </c>
       <c r="D766" t="s">
         <v>317</v>
       </c>
       <c r="E766">
-        <v>3.437688630262322</v>
+        <v>3.385896643455919</v>
       </c>
       <c r="F766">
         <v>-1</v>
       </c>
       <c r="G766">
-        <v>0.05137049409600464</v>
+        <v>0.05145610796916809</v>
       </c>
       <c r="H766">
-        <v>0.05090231136973768</v>
+        <v>0.05081410335654408</v>
       </c>
       <c r="I766">
-        <v>0.5718172737330498</v>
+        <v>0.5379953873760002</v>
       </c>
       <c r="J766">
-        <v>1.036345474661034</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K766">
         <v>22.85</v>
@@ -39880,16 +39883,16 @@
         <v>27.69</v>
       </c>
       <c r="M766">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="N766">
-        <v>27.17</v>
+        <v>27.1</v>
       </c>
       <c r="O766">
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>405</v>
+        <v>186</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39900,28 +39903,28 @@
         <v>187</v>
       </c>
       <c r="C767">
-        <v>3.923892030831919</v>
+        <v>3.103333239057651</v>
       </c>
       <c r="D767" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E767">
-        <v>3.351887418207919</v>
+        <v>2.529533092972439</v>
       </c>
       <c r="F767">
         <v>-1</v>
       </c>
       <c r="G767">
-        <v>0.05145610796916809</v>
+        <v>0.05227666676094235</v>
       </c>
       <c r="H767">
-        <v>0.05098811258179208</v>
+        <v>0.05181046690702756</v>
       </c>
       <c r="I767">
-        <v>0.5720046126239993</v>
+        <v>0.5738001460852118</v>
       </c>
       <c r="J767">
-        <v>1.040092252480004</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K767">
         <v>22.85</v>
@@ -39939,57 +39942,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="768" spans="1:16">
-      <c r="A768" s="1">
-        <v>0</v>
-      </c>
-      <c r="B768" t="s">
-        <v>187</v>
-      </c>
-      <c r="C768">
-        <v>3.103333239057651</v>
-      </c>
-      <c r="D768" t="s">
-        <v>317</v>
-      </c>
-      <c r="E768">
-        <v>2.529533092972439</v>
-      </c>
-      <c r="F768">
-        <v>-1</v>
-      </c>
-      <c r="G768">
-        <v>0.05227666676094235</v>
-      </c>
-      <c r="H768">
-        <v>0.05181046690702756</v>
-      </c>
-      <c r="I768">
-        <v>0.5738001460852118</v>
-      </c>
-      <c r="J768">
-        <v>1.07600292170426</v>
-      </c>
-      <c r="K768">
-        <v>22.85</v>
-      </c>
-      <c r="L768">
-        <v>27.69</v>
-      </c>
-      <c r="M768">
-        <v>22.9</v>
-      </c>
-      <c r="N768">
-        <v>27.17</v>
-      </c>
-      <c r="O768">
-        <v>1</v>
-      </c>
-      <c r="P768" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="413">
   <si>
     <t>trade_time</t>
   </si>
@@ -979,7 +979,7 @@
     <t>2021-09-17</t>
   </si>
   <si>
-    <t>2021-09-29</t>
+    <t>2021-09-30</t>
   </si>
   <si>
     <t>2021-09-15</t>
@@ -1610,7 +1610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P783"/>
+  <dimension ref="A1:P784"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -39224,7 +39224,7 @@
         <v>321</v>
       </c>
       <c r="E753">
-        <v>5.070071093932135</v>
+        <v>4.464942129253377</v>
       </c>
       <c r="F753">
         <v>-1</v>
@@ -39233,10 +39233,10 @@
         <v>0.05011916104248964</v>
       </c>
       <c r="H753">
-        <v>0.05090992890606786</v>
+        <v>0.04981505787074663</v>
       </c>
       <c r="I753">
-        <v>0.09076786357822897</v>
+        <v>0.6958968282569877</v>
       </c>
       <c r="J753">
         <v>0.9794841412849514</v>
@@ -39248,10 +39248,10 @@
         <v>27.64</v>
       </c>
       <c r="M753">
-        <v>23.4</v>
+        <v>23.15</v>
       </c>
       <c r="N753">
-        <v>27.99</v>
+        <v>27.14</v>
       </c>
       <c r="O753">
         <v>1</v>
@@ -39374,7 +39374,7 @@
         <v>321</v>
       </c>
       <c r="E756">
-        <v>4.571519878624052</v>
+        <v>3.971717315818243</v>
       </c>
       <c r="F756">
         <v>-1</v>
@@ -39383,10 +39383,10 @@
         <v>0.05060812473442641</v>
       </c>
       <c r="H756">
-        <v>0.05140848012137594</v>
+        <v>0.05030828268418176</v>
       </c>
       <c r="I756">
-        <v>0.1003553869495413</v>
+        <v>0.7001579497553507</v>
       </c>
       <c r="J756">
         <v>1.00078974877675</v>
@@ -39398,10 +39398,10 @@
         <v>27.64</v>
       </c>
       <c r="M756">
-        <v>23.4</v>
+        <v>23.15</v>
       </c>
       <c r="N756">
-        <v>27.99</v>
+        <v>27.14</v>
       </c>
       <c r="O756">
         <v>1</v>
@@ -39524,7 +39524,7 @@
         <v>321</v>
       </c>
       <c r="E759">
-        <v>4.416687368850592</v>
+        <v>3.81853899952527</v>
       </c>
       <c r="F759">
         <v>-1</v>
@@ -39533,10 +39533,10 @@
         <v>0.05075997969593499</v>
       </c>
       <c r="H759">
-        <v>0.0515633126311494</v>
+        <v>0.05046146100047473</v>
       </c>
       <c r="I759">
-        <v>0.1033329352144143</v>
+        <v>0.7014813045397368</v>
       </c>
       <c r="J759">
         <v>1.007406522698693</v>
@@ -39548,10 +39548,10 @@
         <v>27.64</v>
       </c>
       <c r="M759">
-        <v>23.4</v>
+        <v>23.15</v>
       </c>
       <c r="N759">
-        <v>27.99</v>
+        <v>27.14</v>
       </c>
       <c r="O759">
         <v>1</v>
@@ -39674,7 +39674,7 @@
         <v>321</v>
       </c>
       <c r="E762">
-        <v>4.245268537926911</v>
+        <v>3.648951566367863</v>
       </c>
       <c r="F762">
         <v>-1</v>
@@ -39683,10 +39683,10 @@
         <v>0.05092810201087937</v>
       </c>
       <c r="H762">
-        <v>0.05173473146207309</v>
+        <v>0.05063104843363214</v>
       </c>
       <c r="I762">
-        <v>0.1066294511937151</v>
+        <v>0.7029464227527633</v>
       </c>
       <c r="J762">
         <v>1.014732113763807</v>
@@ -39698,10 +39698,10 @@
         <v>27.64</v>
       </c>
       <c r="M762">
-        <v>23.4</v>
+        <v>23.15</v>
       </c>
       <c r="N762">
-        <v>27.99</v>
+        <v>27.14</v>
       </c>
       <c r="O762">
         <v>1</v>
@@ -39824,7 +39824,7 @@
         <v>321</v>
       </c>
       <c r="E765">
-        <v>4.104890725906614</v>
+        <v>3.510073517296505</v>
       </c>
       <c r="F765">
         <v>-1</v>
@@ -39833,10 +39833,10 @@
         <v>0.05106578024959159</v>
       </c>
       <c r="H765">
-        <v>0.05187510927409338</v>
+        <v>0.0507699264827035</v>
       </c>
       <c r="I765">
-        <v>0.1093290245017968</v>
+        <v>0.7041462331119064</v>
       </c>
       <c r="J765">
         <v>1.020731165559546</v>
@@ -39848,10 +39848,10 @@
         <v>27.64</v>
       </c>
       <c r="M765">
-        <v>23.4</v>
+        <v>23.15</v>
       </c>
       <c r="N765">
-        <v>27.99</v>
+        <v>27.14</v>
       </c>
       <c r="O765">
         <v>1</v>
@@ -39865,43 +39865,43 @@
         <v>0</v>
       </c>
       <c r="B766" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C766">
-        <v>3.367521621767366</v>
+        <v>3.249078590284071</v>
       </c>
       <c r="D766" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E766">
-        <v>3.770036372389473</v>
+        <v>3.690186168992298</v>
       </c>
       <c r="F766">
         <v>1</v>
       </c>
       <c r="G766">
-        <v>0.05323247837823264</v>
+        <v>0.05373092140971593</v>
       </c>
       <c r="H766">
-        <v>0.05198996362761052</v>
+        <v>0.0526298138310077</v>
       </c>
       <c r="I766">
-        <v>0.4025147506221067</v>
+        <v>0.4411075787082268</v>
       </c>
       <c r="J766">
         <v>1.028143438277634</v>
       </c>
       <c r="K766">
-        <v>24.25</v>
+        <v>24.55</v>
       </c>
       <c r="L766">
-        <v>28.3</v>
+        <v>28.49</v>
       </c>
       <c r="M766">
-        <v>23.45</v>
+        <v>23.8</v>
       </c>
       <c r="N766">
-        <v>27.88</v>
+        <v>28.16</v>
       </c>
       <c r="O766">
         <v>1</v>
@@ -39915,43 +39915,43 @@
         <v>1</v>
       </c>
       <c r="B767" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C767">
-        <v>4.196922435356054</v>
+        <v>3.367521621767366</v>
       </c>
       <c r="D767" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E767">
-        <v>3.625515263442175</v>
+        <v>3.770036372389473</v>
       </c>
       <c r="F767">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G767">
-        <v>0.05118307756464395</v>
+        <v>0.05323247837823264</v>
       </c>
       <c r="H767">
-        <v>0.05071448473655783</v>
+        <v>0.05198996362761052</v>
       </c>
       <c r="I767">
-        <v>0.5714071719138794</v>
+        <v>0.4025147506221067</v>
       </c>
       <c r="J767">
         <v>1.028143438277634</v>
       </c>
       <c r="K767">
-        <v>22.85</v>
+        <v>24.25</v>
       </c>
       <c r="L767">
-        <v>27.69</v>
+        <v>28.3</v>
       </c>
       <c r="M767">
-        <v>22.9</v>
+        <v>23.45</v>
       </c>
       <c r="N767">
-        <v>27.17</v>
+        <v>27.88</v>
       </c>
       <c r="O767">
         <v>1</v>
@@ -39965,43 +39965,43 @@
         <v>2</v>
       </c>
       <c r="B768" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C768">
-        <v>4.04410809152829</v>
+        <v>4.196922435356054</v>
       </c>
       <c r="D768" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E768">
-        <v>3.931443544303352</v>
+        <v>3.625515263442175</v>
       </c>
       <c r="F768">
         <v>-1</v>
       </c>
       <c r="G768">
-        <v>0.05123589190847171</v>
+        <v>0.05118307756464395</v>
       </c>
       <c r="H768">
-        <v>0.05204855645569664</v>
+        <v>0.05071448473655783</v>
       </c>
       <c r="I768">
-        <v>0.1126645472249379</v>
+        <v>0.5714071719138794</v>
       </c>
       <c r="J768">
         <v>1.028143438277634</v>
       </c>
       <c r="K768">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L768">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M768">
-        <v>23.4</v>
+        <v>22.9</v>
       </c>
       <c r="N768">
-        <v>27.99</v>
+        <v>27.17</v>
       </c>
       <c r="O768">
         <v>1</v>
@@ -40012,96 +40012,96 @@
     </row>
     <row r="769" spans="1:16">
       <c r="A769" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B769" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C769">
-        <v>3.26641802200983</v>
+        <v>4.04410809152829</v>
       </c>
       <c r="D769" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E769">
-        <v>3.672268149118782</v>
+        <v>3.338479403872764</v>
       </c>
       <c r="F769">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G769">
-        <v>0.05333358197799017</v>
+        <v>0.05123589190847171</v>
       </c>
       <c r="H769">
-        <v>0.05208773185088121</v>
+        <v>0.05094152059612723</v>
       </c>
       <c r="I769">
-        <v>0.4058501271089519</v>
+        <v>0.7056286876555262</v>
       </c>
       <c r="J769">
-        <v>1.032312658886193</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K769">
-        <v>24.25</v>
+        <v>22.95</v>
       </c>
       <c r="L769">
-        <v>28.3</v>
+        <v>27.64</v>
       </c>
       <c r="M769">
-        <v>23.45</v>
+        <v>23.15</v>
       </c>
       <c r="N769">
-        <v>27.88</v>
+        <v>27.14</v>
       </c>
       <c r="O769">
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="770" spans="1:16">
       <c r="A770" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B770" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C770">
-        <v>4.101655744450497</v>
+        <v>3.14672422434397</v>
       </c>
       <c r="D770" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E770">
-        <v>3.530040111506192</v>
+        <v>3.590958718508617</v>
       </c>
       <c r="F770">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G770">
-        <v>0.05127834425554951</v>
+        <v>0.05383327577565603</v>
       </c>
       <c r="H770">
-        <v>0.05080995988849381</v>
+        <v>0.05272904128149138</v>
       </c>
       <c r="I770">
-        <v>0.5716156329443045</v>
+        <v>0.4442344941646468</v>
       </c>
       <c r="J770">
         <v>1.032312658886193</v>
       </c>
       <c r="K770">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L770">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M770">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="N770">
-        <v>27.17</v>
+        <v>28.16</v>
       </c>
       <c r="O770">
         <v>1</v>
@@ -40112,46 +40112,46 @@
     </row>
     <row r="771" spans="1:16">
       <c r="A771" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B771" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C771">
-        <v>3.948424478561879</v>
+        <v>3.26641802200983</v>
       </c>
       <c r="D771" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E771">
-        <v>3.833883782063094</v>
+        <v>3.672268149118782</v>
       </c>
       <c r="F771">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G771">
-        <v>0.05133157552143813</v>
+        <v>0.05333358197799017</v>
       </c>
       <c r="H771">
-        <v>0.05214611621793691</v>
+        <v>0.05208773185088121</v>
       </c>
       <c r="I771">
-        <v>0.1145406964987856</v>
+        <v>0.4058501271089519</v>
       </c>
       <c r="J771">
         <v>1.032312658886193</v>
       </c>
       <c r="K771">
-        <v>22.95</v>
+        <v>24.25</v>
       </c>
       <c r="L771">
-        <v>27.64</v>
+        <v>28.3</v>
       </c>
       <c r="M771">
-        <v>23.4</v>
+        <v>23.45</v>
       </c>
       <c r="N771">
-        <v>27.99</v>
+        <v>27.88</v>
       </c>
       <c r="O771">
         <v>1</v>
@@ -40162,146 +40162,146 @@
     </row>
     <row r="772" spans="1:16">
       <c r="A772" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B772" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C772">
-        <v>3.047718597071611</v>
+        <v>4.101655744450497</v>
       </c>
       <c r="D772" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E772">
-        <v>3.494977703067388</v>
+        <v>3.530040111506192</v>
       </c>
       <c r="F772">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G772">
-        <v>0.05393228140292838</v>
+        <v>0.05127834425554951</v>
       </c>
       <c r="H772">
-        <v>0.05282502229693262</v>
+        <v>0.05080995988849381</v>
       </c>
       <c r="I772">
-        <v>0.4472591059957765</v>
+        <v>0.5716156329443045</v>
       </c>
       <c r="J772">
-        <v>1.036345474661034</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K772">
-        <v>24.55</v>
+        <v>22.85</v>
       </c>
       <c r="L772">
-        <v>28.49</v>
+        <v>27.69</v>
       </c>
       <c r="M772">
-        <v>23.8</v>
+        <v>22.9</v>
       </c>
       <c r="N772">
-        <v>28.16</v>
+        <v>27.17</v>
       </c>
       <c r="O772">
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="773" spans="1:16">
       <c r="A773" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B773" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C773">
-        <v>3.168622239469922</v>
+        <v>3.948424478561879</v>
       </c>
       <c r="D773" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E773">
-        <v>3.577698619198749</v>
+        <v>3.241961946784642</v>
       </c>
       <c r="F773">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G773">
-        <v>0.05343137776053009</v>
+        <v>0.05133157552143813</v>
       </c>
       <c r="H773">
-        <v>0.05218230138080125</v>
+        <v>0.05103803805321536</v>
       </c>
       <c r="I773">
-        <v>0.4090763797288268</v>
+        <v>0.7064625317772375</v>
       </c>
       <c r="J773">
-        <v>1.036345474661034</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K773">
-        <v>24.25</v>
+        <v>22.95</v>
       </c>
       <c r="L773">
-        <v>28.3</v>
+        <v>27.64</v>
       </c>
       <c r="M773">
-        <v>23.45</v>
+        <v>23.15</v>
       </c>
       <c r="N773">
-        <v>27.88</v>
+        <v>27.14</v>
       </c>
       <c r="O773">
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="774" spans="1:16">
       <c r="A774" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B774" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C774">
-        <v>4.009505903995372</v>
+        <v>3.047718597071611</v>
       </c>
       <c r="D774" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E774">
-        <v>3.437688630262322</v>
+        <v>3.494977703067388</v>
       </c>
       <c r="F774">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G774">
-        <v>0.05137049409600464</v>
+        <v>0.05393228140292838</v>
       </c>
       <c r="H774">
-        <v>0.05090231136973768</v>
+        <v>0.05282502229693262</v>
       </c>
       <c r="I774">
-        <v>0.5718172737330498</v>
+        <v>0.4472591059957765</v>
       </c>
       <c r="J774">
         <v>1.036345474661034</v>
       </c>
       <c r="K774">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L774">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M774">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="N774">
-        <v>27.17</v>
+        <v>28.16</v>
       </c>
       <c r="O774">
         <v>1</v>
@@ -40312,46 +40312,46 @@
     </row>
     <row r="775" spans="1:16">
       <c r="A775" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B775" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C775">
-        <v>3.855871356529267</v>
+        <v>4.009505903995372</v>
       </c>
       <c r="D775" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E775">
-        <v>3.739515892931802</v>
+        <v>3.437688630262322</v>
       </c>
       <c r="F775">
         <v>-1</v>
       </c>
       <c r="G775">
-        <v>0.05142412864347074</v>
+        <v>0.05137049409600464</v>
       </c>
       <c r="H775">
-        <v>0.0522404841070682</v>
+        <v>0.05090231136973768</v>
       </c>
       <c r="I775">
-        <v>0.1163554635974648</v>
+        <v>0.5718172737330498</v>
       </c>
       <c r="J775">
         <v>1.036345474661034</v>
       </c>
       <c r="K775">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L775">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M775">
-        <v>23.4</v>
+        <v>22.9</v>
       </c>
       <c r="N775">
-        <v>27.99</v>
+        <v>27.17</v>
       </c>
       <c r="O775">
         <v>1</v>
@@ -40362,96 +40362,96 @@
     </row>
     <row r="776" spans="1:16">
       <c r="A776" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B776" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C776">
-        <v>3.077762877359913</v>
+        <v>3.855871356529267</v>
       </c>
       <c r="D776" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E776">
-        <v>3.489836679343917</v>
+        <v>3.148602261597063</v>
       </c>
       <c r="F776">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G776">
-        <v>0.05352223712264009</v>
+        <v>0.05142412864347074</v>
       </c>
       <c r="H776">
-        <v>0.05227016332065608</v>
+        <v>0.05113139773840294</v>
       </c>
       <c r="I776">
-        <v>0.412073801984004</v>
+        <v>0.7072690949322045</v>
       </c>
       <c r="J776">
-        <v>1.040092252480004</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K776">
-        <v>24.25</v>
+        <v>22.95</v>
       </c>
       <c r="L776">
-        <v>28.3</v>
+        <v>27.64</v>
       </c>
       <c r="M776">
-        <v>23.45</v>
+        <v>23.15</v>
       </c>
       <c r="N776">
-        <v>27.88</v>
+        <v>27.14</v>
       </c>
       <c r="O776">
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>186</v>
+        <v>410</v>
       </c>
     </row>
     <row r="777" spans="1:16">
       <c r="A777" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B777" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C777">
-        <v>3.923892030831919</v>
+        <v>3.077762877359913</v>
       </c>
       <c r="D777" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E777">
-        <v>3.351887418207919</v>
+        <v>3.489836679343917</v>
       </c>
       <c r="F777">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G777">
-        <v>0.05145610796916809</v>
+        <v>0.05352223712264009</v>
       </c>
       <c r="H777">
-        <v>0.05098811258179208</v>
+        <v>0.05227016332065608</v>
       </c>
       <c r="I777">
-        <v>0.5720046126239993</v>
+        <v>0.412073801984004</v>
       </c>
       <c r="J777">
         <v>1.040092252480004</v>
       </c>
       <c r="K777">
-        <v>22.85</v>
+        <v>24.25</v>
       </c>
       <c r="L777">
-        <v>27.69</v>
+        <v>28.3</v>
       </c>
       <c r="M777">
-        <v>22.9</v>
+        <v>23.45</v>
       </c>
       <c r="N777">
-        <v>27.17</v>
+        <v>27.88</v>
       </c>
       <c r="O777">
         <v>1</v>
@@ -40462,46 +40462,46 @@
     </row>
     <row r="778" spans="1:16">
       <c r="A778" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B778" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C778">
-        <v>3.769882805583919</v>
+        <v>3.923892030831919</v>
       </c>
       <c r="D778" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E778">
-        <v>3.651841291967916</v>
+        <v>3.351887418207919</v>
       </c>
       <c r="F778">
         <v>-1</v>
       </c>
       <c r="G778">
-        <v>0.05151011719441608</v>
+        <v>0.05145610796916809</v>
       </c>
       <c r="H778">
-        <v>0.05232815870803208</v>
+        <v>0.05098811258179208</v>
       </c>
       <c r="I778">
-        <v>0.1180415136160029</v>
+        <v>0.5720046126239993</v>
       </c>
       <c r="J778">
         <v>1.040092252480004</v>
       </c>
       <c r="K778">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L778">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M778">
-        <v>23.4</v>
+        <v>22.9</v>
       </c>
       <c r="N778">
-        <v>27.99</v>
+        <v>27.17</v>
       </c>
       <c r="O778">
         <v>1</v>
@@ -40512,52 +40512,52 @@
     </row>
     <row r="779" spans="1:16">
       <c r="A779" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B779" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C779">
-        <v>3.121932800802011</v>
+        <v>3.769882805583919</v>
       </c>
       <c r="D779" t="s">
         <v>321</v>
       </c>
       <c r="E779">
-        <v>2.811531632120307</v>
+        <v>3.06186435508792</v>
       </c>
       <c r="F779">
         <v>-1</v>
       </c>
       <c r="G779">
-        <v>0.052618067199198</v>
+        <v>0.05151011719441608</v>
       </c>
       <c r="H779">
-        <v>0.05316846836787969</v>
+        <v>0.05121813564491208</v>
       </c>
       <c r="I779">
-        <v>0.3104011686817039</v>
+        <v>0.7080184504959988</v>
       </c>
       <c r="J779">
-        <v>1.07600292170426</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K779">
-        <v>23</v>
+        <v>22.95</v>
       </c>
       <c r="L779">
-        <v>27.87</v>
+        <v>27.64</v>
       </c>
       <c r="M779">
-        <v>23.4</v>
+        <v>23.15</v>
       </c>
       <c r="N779">
-        <v>27.99</v>
+        <v>27.14</v>
       </c>
       <c r="O779">
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -40565,49 +40565,49 @@
         <v>0</v>
       </c>
       <c r="B780" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C780">
-        <v>1.960032246668177</v>
+        <v>3.103333239057651</v>
       </c>
       <c r="D780" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E780">
-        <v>1.629424111827621</v>
+        <v>2.529533092972439</v>
       </c>
       <c r="F780">
         <v>-1</v>
       </c>
       <c r="G780">
-        <v>0.05377996775333183</v>
+        <v>0.05227666676094235</v>
       </c>
       <c r="H780">
-        <v>0.05435057588817237</v>
+        <v>0.05181046690702756</v>
       </c>
       <c r="I780">
-        <v>0.3306081348405563</v>
+        <v>0.5738001460852118</v>
       </c>
       <c r="J780">
-        <v>1.126520337101384</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K780">
-        <v>23</v>
+        <v>22.85</v>
       </c>
       <c r="L780">
-        <v>27.87</v>
+        <v>27.69</v>
       </c>
       <c r="M780">
-        <v>23.4</v>
+        <v>22.9</v>
       </c>
       <c r="N780">
-        <v>27.99</v>
+        <v>27.17</v>
       </c>
       <c r="O780">
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>320</v>
+        <v>189</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -40618,28 +40618,28 @@
         <v>190</v>
       </c>
       <c r="C781">
-        <v>1.520645939861978</v>
+        <v>1.960032246668177</v>
       </c>
       <c r="D781" t="s">
         <v>321</v>
       </c>
       <c r="E781">
-        <v>1.182396304033489</v>
+        <v>1.061054196102969</v>
       </c>
       <c r="F781">
         <v>-1</v>
       </c>
       <c r="G781">
-        <v>0.05421935406013802</v>
+        <v>0.05377996775333183</v>
       </c>
       <c r="H781">
-        <v>0.05479760369596651</v>
+        <v>0.05321894580389703</v>
       </c>
       <c r="I781">
-        <v>0.3382496358284897</v>
+        <v>0.8989780505652085</v>
       </c>
       <c r="J781">
-        <v>1.145624089571218</v>
+        <v>1.126520337101384</v>
       </c>
       <c r="K781">
         <v>23</v>
@@ -40648,16 +40648,16 @@
         <v>27.87</v>
       </c>
       <c r="M781">
-        <v>23.4</v>
+        <v>23.15</v>
       </c>
       <c r="N781">
-        <v>27.99</v>
+        <v>27.14</v>
       </c>
       <c r="O781">
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>411</v>
+        <v>320</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40668,28 +40668,28 @@
         <v>190</v>
       </c>
       <c r="C782">
-        <v>1.004773029933933</v>
+        <v>1.520645939861978</v>
       </c>
       <c r="D782" t="s">
         <v>321</v>
       </c>
       <c r="E782">
-        <v>0.6575516913240875</v>
+        <v>0.6188023264262945</v>
       </c>
       <c r="F782">
         <v>-1</v>
       </c>
       <c r="G782">
-        <v>0.05473522697006607</v>
+        <v>0.05421935406013802</v>
       </c>
       <c r="H782">
-        <v>0.05532244830867591</v>
+        <v>0.05366119767357371</v>
       </c>
       <c r="I782">
-        <v>0.3472213386098453</v>
+        <v>0.901843613435684</v>
       </c>
       <c r="J782">
-        <v>1.168053346524612</v>
+        <v>1.145624089571218</v>
       </c>
       <c r="K782">
         <v>23</v>
@@ -40698,16 +40698,16 @@
         <v>27.87</v>
       </c>
       <c r="M782">
-        <v>23.4</v>
+        <v>23.15</v>
       </c>
       <c r="N782">
-        <v>27.99</v>
+        <v>27.14</v>
       </c>
       <c r="O782">
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40718,28 +40718,28 @@
         <v>190</v>
       </c>
       <c r="C783">
-        <v>0.7502176120988366</v>
+        <v>1.004773029933933</v>
       </c>
       <c r="D783" t="s">
         <v>321</v>
       </c>
       <c r="E783">
-        <v>0.3985692227440332</v>
+        <v>0.09956502795524358</v>
       </c>
       <c r="F783">
         <v>-1</v>
       </c>
       <c r="G783">
-        <v>0.05498978238790116</v>
+        <v>0.05473522697006607</v>
       </c>
       <c r="H783">
-        <v>0.05558143077725596</v>
+        <v>0.05418043497204476</v>
       </c>
       <c r="I783">
-        <v>0.3516483893548035</v>
+        <v>0.9052080019786892</v>
       </c>
       <c r="J783">
-        <v>1.179120973387007</v>
+        <v>1.168053346524612</v>
       </c>
       <c r="K783">
         <v>23</v>
@@ -40748,15 +40748,65 @@
         <v>27.87</v>
       </c>
       <c r="M783">
-        <v>23.4</v>
+        <v>23.15</v>
       </c>
       <c r="N783">
-        <v>27.99</v>
+        <v>27.14</v>
       </c>
       <c r="O783">
         <v>1</v>
       </c>
       <c r="P783" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="784" spans="1:16">
+      <c r="A784" s="1">
+        <v>0</v>
+      </c>
+      <c r="B784" t="s">
+        <v>190</v>
+      </c>
+      <c r="C784">
+        <v>0.7502176120988366</v>
+      </c>
+      <c r="D784" t="s">
+        <v>321</v>
+      </c>
+      <c r="E784">
+        <v>-0.1566505339092146</v>
+      </c>
+      <c r="F784">
+        <v>-1</v>
+      </c>
+      <c r="G784">
+        <v>0.05498978238790116</v>
+      </c>
+      <c r="H784">
+        <v>0.05443665053390922</v>
+      </c>
+      <c r="I784">
+        <v>0.9068681460080512</v>
+      </c>
+      <c r="J784">
+        <v>1.179120973387007</v>
+      </c>
+      <c r="K784">
+        <v>23</v>
+      </c>
+      <c r="L784">
+        <v>27.87</v>
+      </c>
+      <c r="M784">
+        <v>23.15</v>
+      </c>
+      <c r="N784">
+        <v>27.14</v>
+      </c>
+      <c r="O784">
+        <v>1</v>
+      </c>
+      <c r="P784" t="s">
         <v>188</v>
       </c>
     </row>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2367" uniqueCount="413">
   <si>
     <t>trade_time</t>
   </si>
@@ -1610,7 +1610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P784"/>
+  <dimension ref="A1:P785"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -39865,43 +39865,43 @@
         <v>0</v>
       </c>
       <c r="B766" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C766">
-        <v>3.249078590284071</v>
+        <v>3.367521621767366</v>
       </c>
       <c r="D766" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E766">
-        <v>3.690186168992298</v>
+        <v>3.770036372389473</v>
       </c>
       <c r="F766">
         <v>1</v>
       </c>
       <c r="G766">
-        <v>0.05373092140971593</v>
+        <v>0.05323247837823264</v>
       </c>
       <c r="H766">
-        <v>0.0526298138310077</v>
+        <v>0.05198996362761052</v>
       </c>
       <c r="I766">
-        <v>0.4411075787082268</v>
+        <v>0.4025147506221067</v>
       </c>
       <c r="J766">
         <v>1.028143438277634</v>
       </c>
       <c r="K766">
-        <v>24.55</v>
+        <v>24.25</v>
       </c>
       <c r="L766">
-        <v>28.49</v>
+        <v>28.3</v>
       </c>
       <c r="M766">
-        <v>23.8</v>
+        <v>23.45</v>
       </c>
       <c r="N766">
-        <v>28.16</v>
+        <v>27.88</v>
       </c>
       <c r="O766">
         <v>1</v>
@@ -39915,43 +39915,43 @@
         <v>1</v>
       </c>
       <c r="B767" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C767">
-        <v>3.367521621767366</v>
+        <v>4.196922435356054</v>
       </c>
       <c r="D767" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E767">
-        <v>3.770036372389473</v>
+        <v>3.625515263442175</v>
       </c>
       <c r="F767">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G767">
-        <v>0.05323247837823264</v>
+        <v>0.05118307756464395</v>
       </c>
       <c r="H767">
-        <v>0.05198996362761052</v>
+        <v>0.05071448473655783</v>
       </c>
       <c r="I767">
-        <v>0.4025147506221067</v>
+        <v>0.5714071719138794</v>
       </c>
       <c r="J767">
         <v>1.028143438277634</v>
       </c>
       <c r="K767">
-        <v>24.25</v>
+        <v>22.85</v>
       </c>
       <c r="L767">
-        <v>28.3</v>
+        <v>27.69</v>
       </c>
       <c r="M767">
-        <v>23.45</v>
+        <v>22.9</v>
       </c>
       <c r="N767">
-        <v>27.88</v>
+        <v>27.17</v>
       </c>
       <c r="O767">
         <v>1</v>
@@ -39965,43 +39965,43 @@
         <v>2</v>
       </c>
       <c r="B768" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C768">
-        <v>4.196922435356054</v>
+        <v>4.04410809152829</v>
       </c>
       <c r="D768" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E768">
-        <v>3.625515263442175</v>
+        <v>3.338479403872764</v>
       </c>
       <c r="F768">
         <v>-1</v>
       </c>
       <c r="G768">
-        <v>0.05118307756464395</v>
+        <v>0.05123589190847171</v>
       </c>
       <c r="H768">
-        <v>0.05071448473655783</v>
+        <v>0.05094152059612723</v>
       </c>
       <c r="I768">
-        <v>0.5714071719138794</v>
+        <v>0.7056286876555262</v>
       </c>
       <c r="J768">
         <v>1.028143438277634</v>
       </c>
       <c r="K768">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L768">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M768">
-        <v>22.9</v>
+        <v>23.15</v>
       </c>
       <c r="N768">
-        <v>27.17</v>
+        <v>27.14</v>
       </c>
       <c r="O768">
         <v>1</v>
@@ -40012,96 +40012,96 @@
     </row>
     <row r="769" spans="1:16">
       <c r="A769" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B769" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C769">
-        <v>4.04410809152829</v>
+        <v>3.14672422434397</v>
       </c>
       <c r="D769" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E769">
-        <v>3.338479403872764</v>
+        <v>3.590958718508617</v>
       </c>
       <c r="F769">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G769">
-        <v>0.05123589190847171</v>
+        <v>0.05383327577565603</v>
       </c>
       <c r="H769">
-        <v>0.05094152059612723</v>
+        <v>0.05272904128149138</v>
       </c>
       <c r="I769">
-        <v>0.7056286876555262</v>
+        <v>0.4442344941646468</v>
       </c>
       <c r="J769">
-        <v>1.028143438277634</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K769">
-        <v>22.95</v>
+        <v>24.55</v>
       </c>
       <c r="L769">
-        <v>27.64</v>
+        <v>28.49</v>
       </c>
       <c r="M769">
-        <v>23.15</v>
+        <v>23.8</v>
       </c>
       <c r="N769">
-        <v>27.14</v>
+        <v>28.16</v>
       </c>
       <c r="O769">
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="770" spans="1:16">
       <c r="A770" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B770" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C770">
-        <v>3.14672422434397</v>
+        <v>3.26641802200983</v>
       </c>
       <c r="D770" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E770">
-        <v>3.590958718508617</v>
+        <v>3.672268149118782</v>
       </c>
       <c r="F770">
         <v>1</v>
       </c>
       <c r="G770">
-        <v>0.05383327577565603</v>
+        <v>0.05333358197799017</v>
       </c>
       <c r="H770">
-        <v>0.05272904128149138</v>
+        <v>0.05208773185088121</v>
       </c>
       <c r="I770">
-        <v>0.4442344941646468</v>
+        <v>0.4058501271089519</v>
       </c>
       <c r="J770">
         <v>1.032312658886193</v>
       </c>
       <c r="K770">
-        <v>24.55</v>
+        <v>24.25</v>
       </c>
       <c r="L770">
-        <v>28.49</v>
+        <v>28.3</v>
       </c>
       <c r="M770">
-        <v>23.8</v>
+        <v>23.45</v>
       </c>
       <c r="N770">
-        <v>28.16</v>
+        <v>27.88</v>
       </c>
       <c r="O770">
         <v>1</v>
@@ -40112,46 +40112,46 @@
     </row>
     <row r="771" spans="1:16">
       <c r="A771" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B771" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C771">
-        <v>3.26641802200983</v>
+        <v>4.101655744450497</v>
       </c>
       <c r="D771" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E771">
-        <v>3.672268149118782</v>
+        <v>3.530040111506192</v>
       </c>
       <c r="F771">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G771">
-        <v>0.05333358197799017</v>
+        <v>0.05127834425554951</v>
       </c>
       <c r="H771">
-        <v>0.05208773185088121</v>
+        <v>0.05080995988849381</v>
       </c>
       <c r="I771">
-        <v>0.4058501271089519</v>
+        <v>0.5716156329443045</v>
       </c>
       <c r="J771">
         <v>1.032312658886193</v>
       </c>
       <c r="K771">
-        <v>24.25</v>
+        <v>22.85</v>
       </c>
       <c r="L771">
-        <v>28.3</v>
+        <v>27.69</v>
       </c>
       <c r="M771">
-        <v>23.45</v>
+        <v>22.9</v>
       </c>
       <c r="N771">
-        <v>27.88</v>
+        <v>27.17</v>
       </c>
       <c r="O771">
         <v>1</v>
@@ -40162,46 +40162,46 @@
     </row>
     <row r="772" spans="1:16">
       <c r="A772" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B772" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C772">
-        <v>4.101655744450497</v>
+        <v>3.948424478561879</v>
       </c>
       <c r="D772" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E772">
-        <v>3.530040111506192</v>
+        <v>3.241961946784642</v>
       </c>
       <c r="F772">
         <v>-1</v>
       </c>
       <c r="G772">
-        <v>0.05127834425554951</v>
+        <v>0.05133157552143813</v>
       </c>
       <c r="H772">
-        <v>0.05080995988849381</v>
+        <v>0.05103803805321536</v>
       </c>
       <c r="I772">
-        <v>0.5716156329443045</v>
+        <v>0.7064625317772375</v>
       </c>
       <c r="J772">
         <v>1.032312658886193</v>
       </c>
       <c r="K772">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L772">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M772">
-        <v>22.9</v>
+        <v>23.15</v>
       </c>
       <c r="N772">
-        <v>27.17</v>
+        <v>27.14</v>
       </c>
       <c r="O772">
         <v>1</v>
@@ -40212,96 +40212,96 @@
     </row>
     <row r="773" spans="1:16">
       <c r="A773" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B773" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C773">
-        <v>3.948424478561879</v>
+        <v>3.047718597071611</v>
       </c>
       <c r="D773" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E773">
-        <v>3.241961946784642</v>
+        <v>3.494977703067388</v>
       </c>
       <c r="F773">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G773">
-        <v>0.05133157552143813</v>
+        <v>0.05393228140292838</v>
       </c>
       <c r="H773">
-        <v>0.05103803805321536</v>
+        <v>0.05282502229693262</v>
       </c>
       <c r="I773">
-        <v>0.7064625317772375</v>
+        <v>0.4472591059957765</v>
       </c>
       <c r="J773">
-        <v>1.032312658886193</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K773">
-        <v>22.95</v>
+        <v>24.55</v>
       </c>
       <c r="L773">
-        <v>27.64</v>
+        <v>28.49</v>
       </c>
       <c r="M773">
-        <v>23.15</v>
+        <v>23.8</v>
       </c>
       <c r="N773">
-        <v>27.14</v>
+        <v>28.16</v>
       </c>
       <c r="O773">
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="774" spans="1:16">
       <c r="A774" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B774" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C774">
-        <v>3.047718597071611</v>
+        <v>3.168622239469922</v>
       </c>
       <c r="D774" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E774">
-        <v>3.494977703067388</v>
+        <v>3.577698619198749</v>
       </c>
       <c r="F774">
         <v>1</v>
       </c>
       <c r="G774">
-        <v>0.05393228140292838</v>
+        <v>0.05343137776053009</v>
       </c>
       <c r="H774">
-        <v>0.05282502229693262</v>
+        <v>0.05218230138080125</v>
       </c>
       <c r="I774">
-        <v>0.4472591059957765</v>
+        <v>0.4090763797288268</v>
       </c>
       <c r="J774">
         <v>1.036345474661034</v>
       </c>
       <c r="K774">
-        <v>24.55</v>
+        <v>24.25</v>
       </c>
       <c r="L774">
-        <v>28.49</v>
+        <v>28.3</v>
       </c>
       <c r="M774">
-        <v>23.8</v>
+        <v>23.45</v>
       </c>
       <c r="N774">
-        <v>28.16</v>
+        <v>27.88</v>
       </c>
       <c r="O774">
         <v>1</v>
@@ -40312,7 +40312,7 @@
     </row>
     <row r="775" spans="1:16">
       <c r="A775" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B775" t="s">
         <v>187</v>
@@ -40362,7 +40362,7 @@
     </row>
     <row r="776" spans="1:16">
       <c r="A776" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B776" t="s">
         <v>188</v>
@@ -40612,40 +40612,40 @@
     </row>
     <row r="781" spans="1:16">
       <c r="A781" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B781" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C781">
-        <v>1.960032246668177</v>
+        <v>2.945732946887226</v>
       </c>
       <c r="D781" t="s">
         <v>321</v>
       </c>
       <c r="E781">
-        <v>1.061054196102969</v>
+        <v>2.230532362546374</v>
       </c>
       <c r="F781">
         <v>-1</v>
       </c>
       <c r="G781">
-        <v>0.05377996775333183</v>
+        <v>0.05233426705311277</v>
       </c>
       <c r="H781">
-        <v>0.05321894580389703</v>
+        <v>0.05204946763745363</v>
       </c>
       <c r="I781">
-        <v>0.8989780505652085</v>
+        <v>0.7152005843408524</v>
       </c>
       <c r="J781">
-        <v>1.126520337101384</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K781">
-        <v>23</v>
+        <v>22.95</v>
       </c>
       <c r="L781">
-        <v>27.87</v>
+        <v>27.64</v>
       </c>
       <c r="M781">
         <v>23.15</v>
@@ -40657,7 +40657,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>320</v>
+        <v>189</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40665,37 +40665,37 @@
         <v>0</v>
       </c>
       <c r="B782" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C782">
-        <v>1.520645939861978</v>
+        <v>1.786358263523248</v>
       </c>
       <c r="D782" t="s">
         <v>321</v>
       </c>
       <c r="E782">
-        <v>0.6188023264262945</v>
+        <v>1.061054196102969</v>
       </c>
       <c r="F782">
         <v>-1</v>
       </c>
       <c r="G782">
-        <v>0.05421935406013802</v>
+        <v>0.05349364173647676</v>
       </c>
       <c r="H782">
-        <v>0.05366119767357371</v>
+        <v>0.05321894580389703</v>
       </c>
       <c r="I782">
-        <v>0.901843613435684</v>
+        <v>0.7253040674202786</v>
       </c>
       <c r="J782">
-        <v>1.145624089571218</v>
+        <v>1.126520337101384</v>
       </c>
       <c r="K782">
-        <v>23</v>
+        <v>22.95</v>
       </c>
       <c r="L782">
-        <v>27.87</v>
+        <v>27.64</v>
       </c>
       <c r="M782">
         <v>23.15</v>
@@ -40707,7 +40707,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>411</v>
+        <v>320</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40715,37 +40715,37 @@
         <v>0</v>
       </c>
       <c r="B783" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C783">
-        <v>1.004773029933933</v>
+        <v>1.347927144340538</v>
       </c>
       <c r="D783" t="s">
         <v>321</v>
       </c>
       <c r="E783">
-        <v>0.09956502795524358</v>
+        <v>0.6188023264262945</v>
       </c>
       <c r="F783">
         <v>-1</v>
       </c>
       <c r="G783">
-        <v>0.05473522697006607</v>
+        <v>0.05393207285565946</v>
       </c>
       <c r="H783">
-        <v>0.05418043497204476</v>
+        <v>0.05366119767357371</v>
       </c>
       <c r="I783">
-        <v>0.9052080019786892</v>
+        <v>0.7291248179142436</v>
       </c>
       <c r="J783">
-        <v>1.168053346524612</v>
+        <v>1.145624089571218</v>
       </c>
       <c r="K783">
-        <v>23</v>
+        <v>22.95</v>
       </c>
       <c r="L783">
-        <v>27.87</v>
+        <v>27.64</v>
       </c>
       <c r="M783">
         <v>23.15</v>
@@ -40757,7 +40757,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40765,37 +40765,37 @@
         <v>0</v>
       </c>
       <c r="B784" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C784">
-        <v>0.7502176120988366</v>
+        <v>0.8331756972601632</v>
       </c>
       <c r="D784" t="s">
         <v>321</v>
       </c>
       <c r="E784">
-        <v>-0.1566505339092146</v>
+        <v>0.09956502795524358</v>
       </c>
       <c r="F784">
         <v>-1</v>
       </c>
       <c r="G784">
-        <v>0.05498978238790116</v>
+        <v>0.05444682430273984</v>
       </c>
       <c r="H784">
-        <v>0.05443665053390922</v>
+        <v>0.05418043497204476</v>
       </c>
       <c r="I784">
-        <v>0.9068681460080512</v>
+        <v>0.7336106693049196</v>
       </c>
       <c r="J784">
-        <v>1.179120973387007</v>
+        <v>1.168053346524612</v>
       </c>
       <c r="K784">
-        <v>23</v>
+        <v>22.95</v>
       </c>
       <c r="L784">
-        <v>27.87</v>
+        <v>27.64</v>
       </c>
       <c r="M784">
         <v>23.15</v>
@@ -40807,6 +40807,56 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="785" spans="1:16">
+      <c r="A785" s="1">
+        <v>0</v>
+      </c>
+      <c r="B785" t="s">
+        <v>190</v>
+      </c>
+      <c r="C785">
+        <v>0.7502176120988366</v>
+      </c>
+      <c r="D785" t="s">
+        <v>321</v>
+      </c>
+      <c r="E785">
+        <v>-0.1566505339092146</v>
+      </c>
+      <c r="F785">
+        <v>-1</v>
+      </c>
+      <c r="G785">
+        <v>0.05498978238790116</v>
+      </c>
+      <c r="H785">
+        <v>0.05443665053390922</v>
+      </c>
+      <c r="I785">
+        <v>0.9068681460080512</v>
+      </c>
+      <c r="J785">
+        <v>1.179120973387007</v>
+      </c>
+      <c r="K785">
+        <v>23</v>
+      </c>
+      <c r="L785">
+        <v>27.87</v>
+      </c>
+      <c r="M785">
+        <v>23.15</v>
+      </c>
+      <c r="N785">
+        <v>27.14</v>
+      </c>
+      <c r="O785">
+        <v>1</v>
+      </c>
+      <c r="P785" t="s">
         <v>188</v>
       </c>
     </row>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2367" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2376" uniqueCount="415">
   <si>
     <t>trade_time</t>
   </si>
@@ -586,7 +586,7 @@
     <t>2021-09-10</t>
   </si>
   <si>
-    <t>2021-09-28</t>
+    <t>2021-10-11</t>
   </si>
   <si>
     <t>2016-09-12</t>
@@ -985,6 +985,9 @@
     <t>2021-09-15</t>
   </si>
   <si>
+    <t>2021-10-12</t>
+  </si>
+  <si>
     <t>2016-07-29</t>
   </si>
   <si>
@@ -1253,6 +1256,9 @@
   </si>
   <si>
     <t>2021-09-24</t>
+  </si>
+  <si>
+    <t>2021-10-08</t>
   </si>
 </sst>
 </file>
@@ -1610,7 +1616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P785"/>
+  <dimension ref="A1:P788"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1707,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1757,7 +1763,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1807,7 +1813,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1857,7 +1863,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1907,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2157,7 +2163,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2207,7 +2213,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2257,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2307,7 +2313,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2357,7 +2363,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2407,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2457,7 +2463,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2507,7 +2513,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2557,7 +2563,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2607,7 +2613,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2657,7 +2663,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2707,7 +2713,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2757,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2807,7 +2813,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2857,7 +2863,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2907,7 +2913,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2957,7 +2963,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3007,7 +3013,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3057,7 +3063,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3107,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3157,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3207,7 +3213,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3257,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3307,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3357,7 +3363,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3407,7 +3413,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3457,7 +3463,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3507,7 +3513,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3557,7 +3563,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3607,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3657,7 +3663,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3707,7 +3713,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3757,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3807,7 +3813,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3857,7 +3863,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3907,7 +3913,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3957,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4007,7 +4013,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4057,7 +4063,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4107,7 +4113,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4157,7 +4163,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4207,7 +4213,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4257,7 +4263,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4307,7 +4313,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4357,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4407,7 +4413,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4457,7 +4463,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4507,7 +4513,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4557,7 +4563,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4607,7 +4613,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4957,7 +4963,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5007,7 +5013,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5057,7 +5063,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5107,7 +5113,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5157,7 +5163,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5507,7 +5513,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5557,7 +5563,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5607,7 +5613,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5657,7 +5663,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5707,7 +5713,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5757,7 +5763,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5807,7 +5813,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5857,7 +5863,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5907,7 +5913,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5957,7 +5963,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6007,7 +6013,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6057,7 +6063,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6107,7 +6113,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6157,7 +6163,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6207,7 +6213,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6257,7 +6263,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6307,7 +6313,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6357,7 +6363,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6407,7 +6413,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6457,7 +6463,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6507,7 +6513,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6557,7 +6563,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6607,7 +6613,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6657,7 +6663,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6707,7 +6713,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6757,7 +6763,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6807,7 +6813,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6857,7 +6863,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6907,7 +6913,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6957,7 +6963,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7007,7 +7013,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7057,7 +7063,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7107,7 +7113,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7157,7 +7163,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7207,7 +7213,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7257,7 +7263,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7307,7 +7313,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7357,7 +7363,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7407,7 +7413,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7457,7 +7463,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7507,7 +7513,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7557,7 +7563,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7607,7 +7613,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7657,7 +7663,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7707,7 +7713,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7757,7 +7763,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7807,7 +7813,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8207,7 +8213,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8257,7 +8263,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8307,7 +8313,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8357,7 +8363,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8407,7 +8413,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8457,7 +8463,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8507,7 +8513,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8557,7 +8563,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9407,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9457,7 +9463,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9507,7 +9513,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9557,7 +9563,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9607,7 +9613,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9657,7 +9663,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9707,7 +9713,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9757,7 +9763,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10607,7 +10613,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10657,7 +10663,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10707,7 +10713,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10757,7 +10763,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10807,7 +10813,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10857,7 +10863,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10907,7 +10913,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10957,7 +10963,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11407,7 +11413,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11457,7 +11463,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11507,7 +11513,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11557,7 +11563,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11607,7 +11613,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11657,7 +11663,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11707,7 +11713,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11757,7 +11763,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12157,7 +12163,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12207,7 +12213,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12257,7 +12263,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12307,7 +12313,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12357,7 +12363,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12407,7 +12413,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12457,7 +12463,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12507,7 +12513,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12557,7 +12563,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12607,7 +12613,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12657,7 +12663,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12707,7 +12713,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12757,7 +12763,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12807,7 +12813,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12857,7 +12863,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12907,7 +12913,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12957,7 +12963,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13007,7 +13013,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13057,7 +13063,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13107,7 +13113,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13157,7 +13163,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13207,7 +13213,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13257,7 +13263,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13307,7 +13313,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13357,7 +13363,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13407,7 +13413,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13457,7 +13463,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13507,7 +13513,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13557,7 +13563,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13607,7 +13613,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13657,7 +13663,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13707,7 +13713,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13757,7 +13763,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13807,7 +13813,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14157,7 +14163,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14207,7 +14213,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14257,7 +14263,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14307,7 +14313,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14357,7 +14363,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14407,7 +14413,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14457,7 +14463,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14507,7 +14513,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14557,7 +14563,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14607,7 +14613,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14657,7 +14663,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14707,7 +14713,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14757,7 +14763,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14807,7 +14813,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14857,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14907,7 +14913,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14957,7 +14963,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15007,7 +15013,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -16157,7 +16163,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16207,7 +16213,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16257,7 +16263,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16307,7 +16313,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16357,7 +16363,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16407,7 +16413,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16457,7 +16463,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16507,7 +16513,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16557,7 +16563,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16607,7 +16613,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -18257,7 +18263,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18307,7 +18313,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18357,7 +18363,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18407,7 +18413,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18457,7 +18463,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18507,7 +18513,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18707,7 +18713,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18757,7 +18763,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19107,7 +19113,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19157,7 +19163,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19207,7 +19213,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19707,7 +19713,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19757,7 +19763,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19807,7 +19813,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20557,7 +20563,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20607,7 +20613,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20657,7 +20663,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20707,7 +20713,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20757,7 +20763,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20807,7 +20813,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20857,7 +20863,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20907,7 +20913,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20957,7 +20963,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21007,7 +21013,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21057,7 +21063,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21107,7 +21113,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21157,7 +21163,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21207,7 +21213,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21257,7 +21263,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21307,7 +21313,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21357,7 +21363,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21407,7 +21413,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21457,7 +21463,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21507,7 +21513,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21557,7 +21563,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21607,7 +21613,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21657,7 +21663,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21707,7 +21713,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21757,7 +21763,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21807,7 +21813,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21857,7 +21863,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21907,7 +21913,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21957,7 +21963,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22007,7 +22013,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22057,7 +22063,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22107,7 +22113,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22157,7 +22163,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22207,7 +22213,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22257,7 +22263,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22307,7 +22313,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22357,7 +22363,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22857,7 +22863,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22907,7 +22913,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22957,7 +22963,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23007,7 +23013,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23057,7 +23063,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23107,7 +23113,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23157,7 +23163,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23207,7 +23213,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23257,7 +23263,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23307,7 +23313,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23357,7 +23363,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23407,7 +23413,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23457,7 +23463,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23507,7 +23513,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23557,7 +23563,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23607,7 +23613,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23657,7 +23663,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23707,7 +23713,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23757,7 +23763,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23807,7 +23813,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23857,7 +23863,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23907,7 +23913,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23957,7 +23963,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24007,7 +24013,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24057,7 +24063,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24107,7 +24113,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24157,7 +24163,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24207,7 +24213,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24257,7 +24263,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24307,7 +24313,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24357,7 +24363,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24407,7 +24413,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24457,7 +24463,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24507,7 +24513,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24557,7 +24563,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24607,7 +24613,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24657,7 +24663,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24707,7 +24713,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24757,7 +24763,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24807,7 +24813,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25757,7 +25763,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25807,7 +25813,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25857,7 +25863,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25907,7 +25913,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25957,7 +25963,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26007,7 +26013,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26057,7 +26063,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26107,7 +26113,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26157,7 +26163,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26207,7 +26213,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26257,7 +26263,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26307,7 +26313,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26357,7 +26363,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26407,7 +26413,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26457,7 +26463,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26507,7 +26513,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26557,7 +26563,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26607,7 +26613,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26657,7 +26663,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26707,7 +26713,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26757,7 +26763,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26807,7 +26813,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26857,7 +26863,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26907,7 +26913,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26957,7 +26963,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27007,7 +27013,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27057,7 +27063,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27107,7 +27113,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27157,7 +27163,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27207,7 +27213,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27257,7 +27263,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27307,7 +27313,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27357,7 +27363,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27407,7 +27413,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27457,7 +27463,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27507,7 +27513,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27557,7 +27563,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27607,7 +27613,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27657,7 +27663,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27707,7 +27713,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27757,7 +27763,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27807,7 +27813,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27857,7 +27863,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27907,7 +27913,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27957,7 +27963,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28007,7 +28013,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28057,7 +28063,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28107,7 +28113,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28157,7 +28163,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28207,7 +28213,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28257,7 +28263,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28307,7 +28313,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28807,7 +28813,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28857,7 +28863,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28907,7 +28913,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28957,7 +28963,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29007,7 +29013,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29057,7 +29063,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29107,7 +29113,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29157,7 +29163,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29207,7 +29213,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29257,7 +29263,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29307,7 +29313,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29357,7 +29363,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29407,7 +29413,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29457,7 +29463,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29507,7 +29513,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29557,7 +29563,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29607,7 +29613,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29657,7 +29663,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29707,7 +29713,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29757,7 +29763,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29807,7 +29813,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29857,7 +29863,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29907,7 +29913,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29957,7 +29963,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30007,7 +30013,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30057,7 +30063,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30107,7 +30113,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30157,7 +30163,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30207,7 +30213,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30257,7 +30263,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30307,7 +30313,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30357,7 +30363,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30407,7 +30413,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30457,7 +30463,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30507,7 +30513,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30557,7 +30563,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30607,7 +30613,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30657,7 +30663,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30707,7 +30713,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30757,7 +30763,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30807,7 +30813,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30857,7 +30863,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30907,7 +30913,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31357,7 +31363,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31407,7 +31413,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31457,7 +31463,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31507,7 +31513,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31557,7 +31563,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31607,7 +31613,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31657,7 +31663,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31707,7 +31713,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31757,7 +31763,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31807,7 +31813,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31857,7 +31863,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -31907,7 +31913,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31957,7 +31963,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32007,7 +32013,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32057,7 +32063,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32107,7 +32113,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32857,7 +32863,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32907,7 +32913,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32957,7 +32963,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33007,7 +33013,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33057,7 +33063,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33107,7 +33113,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33157,7 +33163,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33207,7 +33213,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33257,7 +33263,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33307,7 +33313,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33357,7 +33363,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33407,7 +33413,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33457,7 +33463,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33507,7 +33513,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33857,7 +33863,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33907,7 +33913,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33957,7 +33963,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34007,7 +34013,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34057,7 +34063,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34107,7 +34113,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34407,7 +34413,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34457,7 +34463,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34507,7 +34513,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34557,7 +34563,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34607,7 +34613,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34657,7 +34663,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34707,7 +34713,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34757,7 +34763,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34807,7 +34813,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34857,7 +34863,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34907,7 +34913,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -34957,7 +34963,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35007,7 +35013,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35057,7 +35063,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35107,7 +35113,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35157,7 +35163,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35207,7 +35213,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35257,7 +35263,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35307,7 +35313,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35657,7 +35663,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35707,7 +35713,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35757,7 +35763,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35807,7 +35813,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35857,7 +35863,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35907,7 +35913,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35957,7 +35963,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36007,7 +36013,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36057,7 +36063,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36107,7 +36113,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36157,7 +36163,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36207,7 +36213,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36257,7 +36263,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36307,7 +36313,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36357,7 +36363,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36407,7 +36413,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36457,7 +36463,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36507,7 +36513,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36557,7 +36563,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36607,7 +36613,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36657,7 +36663,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36707,7 +36713,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36757,7 +36763,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36807,7 +36813,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36857,7 +36863,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36907,7 +36913,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36957,7 +36963,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37007,7 +37013,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37057,7 +37063,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37107,7 +37113,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37157,7 +37163,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37207,7 +37213,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37607,7 +37613,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37657,7 +37663,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37707,7 +37713,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37757,7 +37763,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37807,7 +37813,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -37857,7 +37863,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -37907,7 +37913,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38557,7 +38563,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38607,7 +38613,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38657,7 +38663,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38707,7 +38713,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38757,7 +38763,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38807,7 +38813,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38857,7 +38863,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38907,7 +38913,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -38957,7 +38963,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39007,7 +39013,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39057,7 +39063,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39107,7 +39113,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39157,7 +39163,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39207,7 +39213,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39257,7 +39263,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39315,43 +39321,43 @@
         <v>1</v>
       </c>
       <c r="B755" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C755">
-        <v>4.821954240451266</v>
+        <v>4.030848592163817</v>
       </c>
       <c r="D755" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E755">
-        <v>4.251914753012432</v>
+        <v>4.411480391185215</v>
       </c>
       <c r="F755">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G755">
-        <v>0.05055804575954873</v>
+        <v>0.05256915140783619</v>
       </c>
       <c r="H755">
-        <v>0.05008808524698757</v>
+        <v>0.05134851960881479</v>
       </c>
       <c r="I755">
-        <v>0.5700394874388337</v>
+        <v>0.3806317990213977</v>
       </c>
       <c r="J755">
         <v>1.00078974877675</v>
       </c>
       <c r="K755">
-        <v>22.85</v>
+        <v>24.25</v>
       </c>
       <c r="L755">
-        <v>27.69</v>
+        <v>28.3</v>
       </c>
       <c r="M755">
-        <v>22.9</v>
+        <v>23.45</v>
       </c>
       <c r="N755">
-        <v>27.17</v>
+        <v>27.88</v>
       </c>
       <c r="O755">
         <v>1</v>
@@ -39365,43 +39371,43 @@
         <v>2</v>
       </c>
       <c r="B756" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C756">
-        <v>4.671875265573593</v>
+        <v>4.821954240451266</v>
       </c>
       <c r="D756" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E756">
-        <v>3.971717315818243</v>
+        <v>4.251914753012432</v>
       </c>
       <c r="F756">
         <v>-1</v>
       </c>
       <c r="G756">
-        <v>0.05060812473442641</v>
+        <v>0.05055804575954873</v>
       </c>
       <c r="H756">
-        <v>0.05030828268418176</v>
+        <v>0.05008808524698757</v>
       </c>
       <c r="I756">
-        <v>0.7001579497553507</v>
+        <v>0.5700394874388337</v>
       </c>
       <c r="J756">
         <v>1.00078974877675</v>
       </c>
       <c r="K756">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L756">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M756">
-        <v>23.15</v>
+        <v>22.9</v>
       </c>
       <c r="N756">
-        <v>27.14</v>
+        <v>27.17</v>
       </c>
       <c r="O756">
         <v>1</v>
@@ -39412,196 +39418,196 @@
     </row>
     <row r="757" spans="1:16">
       <c r="A757" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B757" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C757">
-        <v>3.870391824556705</v>
+        <v>4.671875265573593</v>
       </c>
       <c r="D757" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E757">
-        <v>4.256317042715658</v>
+        <v>3.971717315818243</v>
       </c>
       <c r="F757">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G757">
-        <v>0.0527296081754433</v>
+        <v>0.05060812473442641</v>
       </c>
       <c r="H757">
-        <v>0.05150368295728434</v>
+        <v>0.05030828268418176</v>
       </c>
       <c r="I757">
-        <v>0.3859252181589525</v>
+        <v>0.7001579497553507</v>
       </c>
       <c r="J757">
-        <v>1.007406522698693</v>
+        <v>1.00078974877675</v>
       </c>
       <c r="K757">
-        <v>24.25</v>
+        <v>22.95</v>
       </c>
       <c r="L757">
-        <v>28.3</v>
+        <v>27.64</v>
       </c>
       <c r="M757">
-        <v>23.45</v>
+        <v>23.15</v>
       </c>
       <c r="N757">
-        <v>27.88</v>
+        <v>27.14</v>
       </c>
       <c r="O757">
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>406</v>
+        <v>185</v>
       </c>
     </row>
     <row r="758" spans="1:16">
       <c r="A758" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B758" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C758">
-        <v>4.670760956334874</v>
+        <v>3.870391824556705</v>
       </c>
       <c r="D758" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E758">
-        <v>4.100390630199943</v>
+        <v>4.256317042715658</v>
       </c>
       <c r="F758">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G758">
-        <v>0.05070923904366513</v>
+        <v>0.0527296081754433</v>
       </c>
       <c r="H758">
-        <v>0.05023960936980006</v>
+        <v>0.05150368295728434</v>
       </c>
       <c r="I758">
-        <v>0.5703703261349311</v>
+        <v>0.3859252181589525</v>
       </c>
       <c r="J758">
         <v>1.007406522698693</v>
       </c>
       <c r="K758">
-        <v>22.85</v>
+        <v>24.25</v>
       </c>
       <c r="L758">
-        <v>27.69</v>
+        <v>28.3</v>
       </c>
       <c r="M758">
-        <v>22.9</v>
+        <v>23.45</v>
       </c>
       <c r="N758">
-        <v>27.17</v>
+        <v>27.88</v>
       </c>
       <c r="O758">
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="759" spans="1:16">
       <c r="A759" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B759" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C759">
-        <v>4.520020304065007</v>
+        <v>4.670760956334874</v>
       </c>
       <c r="D759" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E759">
-        <v>3.81853899952527</v>
+        <v>4.100390630199943</v>
       </c>
       <c r="F759">
         <v>-1</v>
       </c>
       <c r="G759">
-        <v>0.05075997969593499</v>
+        <v>0.05070923904366513</v>
       </c>
       <c r="H759">
-        <v>0.05046146100047473</v>
+        <v>0.05023960936980006</v>
       </c>
       <c r="I759">
-        <v>0.7014813045397368</v>
+        <v>0.5703703261349311</v>
       </c>
       <c r="J759">
         <v>1.007406522698693</v>
       </c>
       <c r="K759">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L759">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M759">
-        <v>23.15</v>
+        <v>22.9</v>
       </c>
       <c r="N759">
-        <v>27.14</v>
+        <v>27.17</v>
       </c>
       <c r="O759">
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="760" spans="1:16">
       <c r="A760" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B760" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C760">
-        <v>3.692746241227674</v>
+        <v>4.520020304065007</v>
       </c>
       <c r="D760" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E760">
-        <v>4.084531932238722</v>
+        <v>3.81853899952527</v>
       </c>
       <c r="F760">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G760">
-        <v>0.05290725375877233</v>
+        <v>0.05075997969593499</v>
       </c>
       <c r="H760">
-        <v>0.05167546806776127</v>
+        <v>0.05046146100047473</v>
       </c>
       <c r="I760">
-        <v>0.391785691011048</v>
+        <v>0.7014813045397368</v>
       </c>
       <c r="J760">
-        <v>1.014732113763807</v>
+        <v>1.007406522698693</v>
       </c>
       <c r="K760">
-        <v>24.25</v>
+        <v>22.95</v>
       </c>
       <c r="L760">
-        <v>28.3</v>
+        <v>27.64</v>
       </c>
       <c r="M760">
-        <v>23.45</v>
+        <v>23.15</v>
       </c>
       <c r="N760">
-        <v>27.88</v>
+        <v>27.14</v>
       </c>
       <c r="O760">
         <v>1</v>
@@ -39612,196 +39618,196 @@
     </row>
     <row r="761" spans="1:16">
       <c r="A761" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B761" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C761">
-        <v>4.503371200497003</v>
+        <v>3.692746241227674</v>
       </c>
       <c r="D761" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E761">
-        <v>3.932634594808817</v>
+        <v>4.084531932238722</v>
       </c>
       <c r="F761">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G761">
-        <v>0.050876628799503</v>
+        <v>0.05290725375877233</v>
       </c>
       <c r="H761">
-        <v>0.05040736540519119</v>
+        <v>0.05167546806776127</v>
       </c>
       <c r="I761">
-        <v>0.570736605688186</v>
+        <v>0.391785691011048</v>
       </c>
       <c r="J761">
         <v>1.014732113763807</v>
       </c>
       <c r="K761">
-        <v>22.85</v>
+        <v>24.25</v>
       </c>
       <c r="L761">
-        <v>27.69</v>
+        <v>28.3</v>
       </c>
       <c r="M761">
-        <v>22.9</v>
+        <v>23.45</v>
       </c>
       <c r="N761">
-        <v>27.17</v>
+        <v>27.88</v>
       </c>
       <c r="O761">
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="762" spans="1:16">
       <c r="A762" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B762" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C762">
-        <v>4.351897989120626</v>
+        <v>4.503371200497003</v>
       </c>
       <c r="D762" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E762">
-        <v>3.648951566367863</v>
+        <v>3.932634594808817</v>
       </c>
       <c r="F762">
         <v>-1</v>
       </c>
       <c r="G762">
-        <v>0.05092810201087937</v>
+        <v>0.050876628799503</v>
       </c>
       <c r="H762">
-        <v>0.05063104843363214</v>
+        <v>0.05040736540519119</v>
       </c>
       <c r="I762">
-        <v>0.7029464227527633</v>
+        <v>0.570736605688186</v>
       </c>
       <c r="J762">
         <v>1.014732113763807</v>
       </c>
       <c r="K762">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L762">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M762">
-        <v>23.15</v>
+        <v>22.9</v>
       </c>
       <c r="N762">
-        <v>27.14</v>
+        <v>27.17</v>
       </c>
       <c r="O762">
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="763" spans="1:16">
       <c r="A763" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B763" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C763">
-        <v>3.547269235181002</v>
+        <v>4.351897989120626</v>
       </c>
       <c r="D763" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E763">
-        <v>3.943854167628636</v>
+        <v>3.648951566367863</v>
       </c>
       <c r="F763">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G763">
-        <v>0.05305273076481901</v>
+        <v>0.05092810201087937</v>
       </c>
       <c r="H763">
-        <v>0.05181614583237136</v>
+        <v>0.05063104843363214</v>
       </c>
       <c r="I763">
-        <v>0.3965849324476345</v>
+        <v>0.7029464227527633</v>
       </c>
       <c r="J763">
-        <v>1.020731165559546</v>
+        <v>1.014732113763807</v>
       </c>
       <c r="K763">
-        <v>24.25</v>
+        <v>22.95</v>
       </c>
       <c r="L763">
-        <v>28.3</v>
+        <v>27.64</v>
       </c>
       <c r="M763">
-        <v>23.45</v>
+        <v>23.15</v>
       </c>
       <c r="N763">
-        <v>27.88</v>
+        <v>27.14</v>
       </c>
       <c r="O763">
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>318</v>
+        <v>408</v>
       </c>
     </row>
     <row r="764" spans="1:16">
       <c r="A764" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B764" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C764">
-        <v>4.366292866964365</v>
+        <v>3.547269235181002</v>
       </c>
       <c r="D764" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E764">
-        <v>3.79525630868639</v>
+        <v>3.943854167628636</v>
       </c>
       <c r="F764">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G764">
-        <v>0.05101370713303564</v>
+        <v>0.05305273076481901</v>
       </c>
       <c r="H764">
-        <v>0.05054474369131361</v>
+        <v>0.05181614583237136</v>
       </c>
       <c r="I764">
-        <v>0.5710365582779744</v>
+        <v>0.3965849324476345</v>
       </c>
       <c r="J764">
         <v>1.020731165559546</v>
       </c>
       <c r="K764">
-        <v>22.85</v>
+        <v>24.25</v>
       </c>
       <c r="L764">
-        <v>27.69</v>
+        <v>28.3</v>
       </c>
       <c r="M764">
-        <v>22.9</v>
+        <v>23.45</v>
       </c>
       <c r="N764">
-        <v>27.17</v>
+        <v>27.88</v>
       </c>
       <c r="O764">
         <v>1</v>
@@ -39812,46 +39818,46 @@
     </row>
     <row r="765" spans="1:16">
       <c r="A765" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B765" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C765">
-        <v>4.214219750408411</v>
+        <v>4.366292866964365</v>
       </c>
       <c r="D765" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E765">
-        <v>3.510073517296505</v>
+        <v>3.79525630868639</v>
       </c>
       <c r="F765">
         <v>-1</v>
       </c>
       <c r="G765">
-        <v>0.05106578024959159</v>
+        <v>0.05101370713303564</v>
       </c>
       <c r="H765">
-        <v>0.0507699264827035</v>
+        <v>0.05054474369131361</v>
       </c>
       <c r="I765">
-        <v>0.7041462331119064</v>
+        <v>0.5710365582779744</v>
       </c>
       <c r="J765">
         <v>1.020731165559546</v>
       </c>
       <c r="K765">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L765">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M765">
-        <v>23.15</v>
+        <v>22.9</v>
       </c>
       <c r="N765">
-        <v>27.14</v>
+        <v>27.17</v>
       </c>
       <c r="O765">
         <v>1</v>
@@ -39862,196 +39868,196 @@
     </row>
     <row r="766" spans="1:16">
       <c r="A766" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B766" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C766">
-        <v>3.367521621767366</v>
+        <v>4.214219750408411</v>
       </c>
       <c r="D766" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E766">
-        <v>3.770036372389473</v>
+        <v>3.510073517296505</v>
       </c>
       <c r="F766">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G766">
-        <v>0.05323247837823264</v>
+        <v>0.05106578024959159</v>
       </c>
       <c r="H766">
-        <v>0.05198996362761052</v>
+        <v>0.0507699264827035</v>
       </c>
       <c r="I766">
-        <v>0.4025147506221067</v>
+        <v>0.7041462331119064</v>
       </c>
       <c r="J766">
-        <v>1.028143438277634</v>
+        <v>1.020731165559546</v>
       </c>
       <c r="K766">
-        <v>24.25</v>
+        <v>22.95</v>
       </c>
       <c r="L766">
-        <v>28.3</v>
+        <v>27.64</v>
       </c>
       <c r="M766">
-        <v>23.45</v>
+        <v>23.15</v>
       </c>
       <c r="N766">
-        <v>27.88</v>
+        <v>27.14</v>
       </c>
       <c r="O766">
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>408</v>
+        <v>318</v>
       </c>
     </row>
     <row r="767" spans="1:16">
       <c r="A767" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B767" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C767">
-        <v>4.196922435356054</v>
+        <v>3.367521621767366</v>
       </c>
       <c r="D767" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E767">
-        <v>3.625515263442175</v>
+        <v>3.770036372389473</v>
       </c>
       <c r="F767">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G767">
-        <v>0.05118307756464395</v>
+        <v>0.05323247837823264</v>
       </c>
       <c r="H767">
-        <v>0.05071448473655783</v>
+        <v>0.05198996362761052</v>
       </c>
       <c r="I767">
-        <v>0.5714071719138794</v>
+        <v>0.4025147506221067</v>
       </c>
       <c r="J767">
         <v>1.028143438277634</v>
       </c>
       <c r="K767">
-        <v>22.85</v>
+        <v>24.25</v>
       </c>
       <c r="L767">
-        <v>27.69</v>
+        <v>28.3</v>
       </c>
       <c r="M767">
-        <v>22.9</v>
+        <v>23.45</v>
       </c>
       <c r="N767">
-        <v>27.17</v>
+        <v>27.88</v>
       </c>
       <c r="O767">
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="768" spans="1:16">
       <c r="A768" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B768" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C768">
-        <v>4.04410809152829</v>
+        <v>4.196922435356054</v>
       </c>
       <c r="D768" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E768">
-        <v>3.338479403872764</v>
+        <v>3.625515263442175</v>
       </c>
       <c r="F768">
         <v>-1</v>
       </c>
       <c r="G768">
-        <v>0.05123589190847171</v>
+        <v>0.05118307756464395</v>
       </c>
       <c r="H768">
-        <v>0.05094152059612723</v>
+        <v>0.05071448473655783</v>
       </c>
       <c r="I768">
-        <v>0.7056286876555262</v>
+        <v>0.5714071719138794</v>
       </c>
       <c r="J768">
         <v>1.028143438277634</v>
       </c>
       <c r="K768">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L768">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M768">
-        <v>23.15</v>
+        <v>22.9</v>
       </c>
       <c r="N768">
-        <v>27.14</v>
+        <v>27.17</v>
       </c>
       <c r="O768">
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="769" spans="1:16">
       <c r="A769" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B769" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C769">
-        <v>3.14672422434397</v>
+        <v>4.04410809152829</v>
       </c>
       <c r="D769" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E769">
-        <v>3.590958718508617</v>
+        <v>3.338479403872764</v>
       </c>
       <c r="F769">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G769">
-        <v>0.05383327577565603</v>
+        <v>0.05123589190847171</v>
       </c>
       <c r="H769">
-        <v>0.05272904128149138</v>
+        <v>0.05094152059612723</v>
       </c>
       <c r="I769">
-        <v>0.4442344941646468</v>
+        <v>0.7056286876555262</v>
       </c>
       <c r="J769">
-        <v>1.032312658886193</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K769">
-        <v>24.55</v>
+        <v>22.95</v>
       </c>
       <c r="L769">
-        <v>28.49</v>
+        <v>27.64</v>
       </c>
       <c r="M769">
-        <v>23.8</v>
+        <v>23.15</v>
       </c>
       <c r="N769">
-        <v>28.16</v>
+        <v>27.14</v>
       </c>
       <c r="O769">
         <v>1</v>
@@ -40062,7 +40068,7 @@
     </row>
     <row r="770" spans="1:16">
       <c r="A770" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B770" t="s">
         <v>189</v>
@@ -40107,12 +40113,12 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="771" spans="1:16">
       <c r="A771" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B771" t="s">
         <v>187</v>
@@ -40157,12 +40163,12 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="772" spans="1:16">
       <c r="A772" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B772" t="s">
         <v>188</v>
@@ -40207,7 +40213,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40215,49 +40221,49 @@
         <v>0</v>
       </c>
       <c r="B773" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C773">
-        <v>3.047718597071611</v>
+        <v>3.168622239469922</v>
       </c>
       <c r="D773" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E773">
-        <v>3.494977703067388</v>
+        <v>3.577698619198749</v>
       </c>
       <c r="F773">
         <v>1</v>
       </c>
       <c r="G773">
-        <v>0.05393228140292838</v>
+        <v>0.05343137776053009</v>
       </c>
       <c r="H773">
-        <v>0.05282502229693262</v>
+        <v>0.05218230138080125</v>
       </c>
       <c r="I773">
-        <v>0.4472591059957765</v>
+        <v>0.4090763797288268</v>
       </c>
       <c r="J773">
         <v>1.036345474661034</v>
       </c>
       <c r="K773">
-        <v>24.55</v>
+        <v>24.25</v>
       </c>
       <c r="L773">
-        <v>28.49</v>
+        <v>28.3</v>
       </c>
       <c r="M773">
-        <v>23.8</v>
+        <v>23.45</v>
       </c>
       <c r="N773">
-        <v>28.16</v>
+        <v>27.88</v>
       </c>
       <c r="O773">
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40265,49 +40271,49 @@
         <v>1</v>
       </c>
       <c r="B774" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C774">
-        <v>3.168622239469922</v>
+        <v>4.009505903995372</v>
       </c>
       <c r="D774" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E774">
-        <v>3.577698619198749</v>
+        <v>3.437688630262322</v>
       </c>
       <c r="F774">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G774">
-        <v>0.05343137776053009</v>
+        <v>0.05137049409600464</v>
       </c>
       <c r="H774">
-        <v>0.05218230138080125</v>
+        <v>0.05090231136973768</v>
       </c>
       <c r="I774">
-        <v>0.4090763797288268</v>
+        <v>0.5718172737330498</v>
       </c>
       <c r="J774">
         <v>1.036345474661034</v>
       </c>
       <c r="K774">
-        <v>24.25</v>
+        <v>22.85</v>
       </c>
       <c r="L774">
-        <v>28.3</v>
+        <v>27.69</v>
       </c>
       <c r="M774">
-        <v>23.45</v>
+        <v>22.9</v>
       </c>
       <c r="N774">
-        <v>27.88</v>
+        <v>27.17</v>
       </c>
       <c r="O774">
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40315,143 +40321,143 @@
         <v>2</v>
       </c>
       <c r="B775" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C775">
-        <v>4.009505903995372</v>
+        <v>3.855871356529267</v>
       </c>
       <c r="D775" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E775">
-        <v>3.437688630262322</v>
+        <v>3.148602261597063</v>
       </c>
       <c r="F775">
         <v>-1</v>
       </c>
       <c r="G775">
-        <v>0.05137049409600464</v>
+        <v>0.05142412864347074</v>
       </c>
       <c r="H775">
-        <v>0.05090231136973768</v>
+        <v>0.05113139773840294</v>
       </c>
       <c r="I775">
-        <v>0.5718172737330498</v>
+        <v>0.7072690949322045</v>
       </c>
       <c r="J775">
         <v>1.036345474661034</v>
       </c>
       <c r="K775">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L775">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M775">
-        <v>22.9</v>
+        <v>23.15</v>
       </c>
       <c r="N775">
-        <v>27.17</v>
+        <v>27.14</v>
       </c>
       <c r="O775">
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="776" spans="1:16">
       <c r="A776" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B776" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C776">
-        <v>3.855871356529267</v>
+        <v>3.077762877359913</v>
       </c>
       <c r="D776" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E776">
-        <v>3.148602261597063</v>
+        <v>3.489836679343917</v>
       </c>
       <c r="F776">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G776">
-        <v>0.05142412864347074</v>
+        <v>0.05352223712264009</v>
       </c>
       <c r="H776">
-        <v>0.05113139773840294</v>
+        <v>0.05227016332065608</v>
       </c>
       <c r="I776">
-        <v>0.7072690949322045</v>
+        <v>0.412073801984004</v>
       </c>
       <c r="J776">
-        <v>1.036345474661034</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K776">
-        <v>22.95</v>
+        <v>24.25</v>
       </c>
       <c r="L776">
-        <v>27.64</v>
+        <v>28.3</v>
       </c>
       <c r="M776">
-        <v>23.15</v>
+        <v>23.45</v>
       </c>
       <c r="N776">
-        <v>27.14</v>
+        <v>27.88</v>
       </c>
       <c r="O776">
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>410</v>
+        <v>186</v>
       </c>
     </row>
     <row r="777" spans="1:16">
       <c r="A777" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B777" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C777">
-        <v>3.077762877359913</v>
+        <v>3.923892030831919</v>
       </c>
       <c r="D777" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E777">
-        <v>3.489836679343917</v>
+        <v>3.351887418207919</v>
       </c>
       <c r="F777">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G777">
-        <v>0.05352223712264009</v>
+        <v>0.05145610796916809</v>
       </c>
       <c r="H777">
-        <v>0.05227016332065608</v>
+        <v>0.05098811258179208</v>
       </c>
       <c r="I777">
-        <v>0.412073801984004</v>
+        <v>0.5720046126239993</v>
       </c>
       <c r="J777">
         <v>1.040092252480004</v>
       </c>
       <c r="K777">
-        <v>24.25</v>
+        <v>22.85</v>
       </c>
       <c r="L777">
-        <v>28.3</v>
+        <v>27.69</v>
       </c>
       <c r="M777">
-        <v>23.45</v>
+        <v>22.9</v>
       </c>
       <c r="N777">
-        <v>27.88</v>
+        <v>27.17</v>
       </c>
       <c r="O777">
         <v>1</v>
@@ -40462,46 +40468,46 @@
     </row>
     <row r="778" spans="1:16">
       <c r="A778" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B778" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C778">
-        <v>3.923892030831919</v>
+        <v>3.769882805583919</v>
       </c>
       <c r="D778" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E778">
-        <v>3.351887418207919</v>
+        <v>3.06186435508792</v>
       </c>
       <c r="F778">
         <v>-1</v>
       </c>
       <c r="G778">
-        <v>0.05145610796916809</v>
+        <v>0.05151011719441608</v>
       </c>
       <c r="H778">
-        <v>0.05098811258179208</v>
+        <v>0.05121813564491208</v>
       </c>
       <c r="I778">
-        <v>0.5720046126239993</v>
+        <v>0.7080184504959988</v>
       </c>
       <c r="J778">
         <v>1.040092252480004</v>
       </c>
       <c r="K778">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L778">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M778">
-        <v>22.9</v>
+        <v>23.15</v>
       </c>
       <c r="N778">
-        <v>27.17</v>
+        <v>27.14</v>
       </c>
       <c r="O778">
         <v>1</v>
@@ -40512,96 +40518,96 @@
     </row>
     <row r="779" spans="1:16">
       <c r="A779" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B779" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C779">
-        <v>3.769882805583919</v>
+        <v>3.103333239057651</v>
       </c>
       <c r="D779" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E779">
-        <v>3.06186435508792</v>
+        <v>2.529533092972439</v>
       </c>
       <c r="F779">
         <v>-1</v>
       </c>
       <c r="G779">
-        <v>0.05151011719441608</v>
+        <v>0.05227666676094235</v>
       </c>
       <c r="H779">
-        <v>0.05121813564491208</v>
+        <v>0.05181046690702756</v>
       </c>
       <c r="I779">
-        <v>0.7080184504959988</v>
+        <v>0.5738001460852118</v>
       </c>
       <c r="J779">
-        <v>1.040092252480004</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K779">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L779">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M779">
-        <v>23.15</v>
+        <v>22.9</v>
       </c>
       <c r="N779">
-        <v>27.14</v>
+        <v>27.17</v>
       </c>
       <c r="O779">
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="780" spans="1:16">
       <c r="A780" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B780" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C780">
-        <v>3.103333239057651</v>
+        <v>2.945732946887226</v>
       </c>
       <c r="D780" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E780">
-        <v>2.529533092972439</v>
+        <v>2.230532362546374</v>
       </c>
       <c r="F780">
         <v>-1</v>
       </c>
       <c r="G780">
-        <v>0.05227666676094235</v>
+        <v>0.05233426705311277</v>
       </c>
       <c r="H780">
-        <v>0.05181046690702756</v>
+        <v>0.05204946763745363</v>
       </c>
       <c r="I780">
-        <v>0.5738001460852118</v>
+        <v>0.7152005843408524</v>
       </c>
       <c r="J780">
         <v>1.07600292170426</v>
       </c>
       <c r="K780">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L780">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M780">
-        <v>22.9</v>
+        <v>23.15</v>
       </c>
       <c r="N780">
-        <v>27.17</v>
+        <v>27.14</v>
       </c>
       <c r="O780">
         <v>1</v>
@@ -40612,34 +40618,34 @@
     </row>
     <row r="781" spans="1:16">
       <c r="A781" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B781" t="s">
         <v>188</v>
       </c>
       <c r="C781">
-        <v>2.945732946887226</v>
+        <v>1.786358263523248</v>
       </c>
       <c r="D781" t="s">
         <v>321</v>
       </c>
       <c r="E781">
-        <v>2.230532362546374</v>
+        <v>1.061054196102969</v>
       </c>
       <c r="F781">
         <v>-1</v>
       </c>
       <c r="G781">
-        <v>0.05233426705311277</v>
+        <v>0.05349364173647676</v>
       </c>
       <c r="H781">
-        <v>0.05204946763745363</v>
+        <v>0.05321894580389703</v>
       </c>
       <c r="I781">
-        <v>0.7152005843408524</v>
+        <v>0.7253040674202786</v>
       </c>
       <c r="J781">
-        <v>1.07600292170426</v>
+        <v>1.126520337101384</v>
       </c>
       <c r="K781">
         <v>22.95</v>
@@ -40657,51 +40663,51 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>189</v>
+        <v>320</v>
       </c>
     </row>
     <row r="782" spans="1:16">
       <c r="A782" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B782" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C782">
-        <v>1.786358263523248</v>
+        <v>1.179035471334991</v>
       </c>
       <c r="D782" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E782">
-        <v>1.061054196102969</v>
+        <v>1.406991572465408</v>
       </c>
       <c r="F782">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G782">
-        <v>0.05349364173647676</v>
+        <v>0.05818096452866501</v>
       </c>
       <c r="H782">
-        <v>0.05321894580389703</v>
+        <v>0.05773300842753459</v>
       </c>
       <c r="I782">
-        <v>0.7253040674202786</v>
+        <v>0.2279561011304168</v>
       </c>
       <c r="J782">
         <v>1.126520337101384</v>
       </c>
       <c r="K782">
-        <v>22.95</v>
+        <v>25.3</v>
       </c>
       <c r="L782">
-        <v>27.64</v>
+        <v>29.68</v>
       </c>
       <c r="M782">
-        <v>23.15</v>
+        <v>25</v>
       </c>
       <c r="N782">
-        <v>27.14</v>
+        <v>29.57</v>
       </c>
       <c r="O782">
         <v>1</v>
@@ -40757,51 +40763,51 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="784" spans="1:16">
       <c r="A784" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B784" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C784">
-        <v>0.8331756972601632</v>
+        <v>0.6957105338481746</v>
       </c>
       <c r="D784" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E784">
-        <v>0.09956502795524358</v>
+        <v>0.9293977607195387</v>
       </c>
       <c r="F784">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G784">
-        <v>0.05444682430273984</v>
+        <v>0.05866428946615183</v>
       </c>
       <c r="H784">
-        <v>0.05418043497204476</v>
+        <v>0.05821060223928046</v>
       </c>
       <c r="I784">
-        <v>0.7336106693049196</v>
+        <v>0.2336872268713641</v>
       </c>
       <c r="J784">
-        <v>1.168053346524612</v>
+        <v>1.145624089571218</v>
       </c>
       <c r="K784">
-        <v>22.95</v>
+        <v>25.3</v>
       </c>
       <c r="L784">
-        <v>27.64</v>
+        <v>29.68</v>
       </c>
       <c r="M784">
-        <v>23.15</v>
+        <v>25</v>
       </c>
       <c r="N784">
-        <v>27.14</v>
+        <v>29.57</v>
       </c>
       <c r="O784">
         <v>1</v>
@@ -40815,37 +40821,37 @@
         <v>0</v>
       </c>
       <c r="B785" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C785">
-        <v>0.7502176120988366</v>
+        <v>0.8331756972601632</v>
       </c>
       <c r="D785" t="s">
         <v>321</v>
       </c>
       <c r="E785">
-        <v>-0.1566505339092146</v>
+        <v>0.09956502795524358</v>
       </c>
       <c r="F785">
         <v>-1</v>
       </c>
       <c r="G785">
-        <v>0.05498978238790116</v>
+        <v>0.05444682430273984</v>
       </c>
       <c r="H785">
-        <v>0.05443665053390922</v>
+        <v>0.05418043497204476</v>
       </c>
       <c r="I785">
-        <v>0.9068681460080512</v>
+        <v>0.7336106693049196</v>
       </c>
       <c r="J785">
-        <v>1.179120973387007</v>
+        <v>1.168053346524612</v>
       </c>
       <c r="K785">
-        <v>23</v>
+        <v>22.95</v>
       </c>
       <c r="L785">
-        <v>27.87</v>
+        <v>27.64</v>
       </c>
       <c r="M785">
         <v>23.15</v>
@@ -40857,7 +40863,157 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="786" spans="1:16">
+      <c r="A786" s="1">
+        <v>1</v>
+      </c>
+      <c r="B786" t="s">
+        <v>190</v>
+      </c>
+      <c r="C786">
+        <v>0.1282503329273226</v>
+      </c>
+      <c r="D786" t="s">
+        <v>323</v>
+      </c>
+      <c r="E786">
+        <v>0.3686663368847078</v>
+      </c>
+      <c r="F786">
+        <v>1</v>
+      </c>
+      <c r="G786">
+        <v>0.05923174966707268</v>
+      </c>
+      <c r="H786">
+        <v>0.05877133366311529</v>
+      </c>
+      <c r="I786">
+        <v>0.2404160039573853</v>
+      </c>
+      <c r="J786">
+        <v>1.168053346524612</v>
+      </c>
+      <c r="K786">
+        <v>25.3</v>
+      </c>
+      <c r="L786">
+        <v>29.68</v>
+      </c>
+      <c r="M786">
+        <v>25</v>
+      </c>
+      <c r="N786">
+        <v>29.57</v>
+      </c>
+      <c r="O786">
+        <v>1</v>
+      </c>
+      <c r="P786" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="787" spans="1:16">
+      <c r="A787" s="1">
+        <v>0</v>
+      </c>
+      <c r="B787" t="s">
+        <v>190</v>
+      </c>
+      <c r="C787">
+        <v>-0.1517606266912814</v>
+      </c>
+      <c r="D787" t="s">
+        <v>323</v>
+      </c>
+      <c r="E787">
+        <v>0.09197566532482071</v>
+      </c>
+      <c r="F787">
+        <v>1</v>
+      </c>
+      <c r="G787">
+        <v>0.05951176062669129</v>
+      </c>
+      <c r="H787">
+        <v>0.05904802433467518</v>
+      </c>
+      <c r="I787">
+        <v>0.2437362920161021</v>
+      </c>
+      <c r="J787">
+        <v>1.179120973387007</v>
+      </c>
+      <c r="K787">
+        <v>25.3</v>
+      </c>
+      <c r="L787">
+        <v>29.68</v>
+      </c>
+      <c r="M787">
+        <v>25</v>
+      </c>
+      <c r="N787">
+        <v>29.57</v>
+      </c>
+      <c r="O787">
+        <v>1</v>
+      </c>
+      <c r="P787" t="s">
         <v>188</v>
+      </c>
+    </row>
+    <row r="788" spans="1:16">
+      <c r="A788" s="1">
+        <v>0</v>
+      </c>
+      <c r="B788" t="s">
+        <v>190</v>
+      </c>
+      <c r="C788">
+        <v>-0.1984676766040572</v>
+      </c>
+      <c r="D788" t="s">
+        <v>323</v>
+      </c>
+      <c r="E788">
+        <v>0.04582245394855988</v>
+      </c>
+      <c r="F788">
+        <v>1</v>
+      </c>
+      <c r="G788">
+        <v>0.05955846767660405</v>
+      </c>
+      <c r="H788">
+        <v>0.05909417754605144</v>
+      </c>
+      <c r="I788">
+        <v>0.2442901305526171</v>
+      </c>
+      <c r="J788">
+        <v>1.180967101842058</v>
+      </c>
+      <c r="K788">
+        <v>25.3</v>
+      </c>
+      <c r="L788">
+        <v>29.68</v>
+      </c>
+      <c r="M788">
+        <v>25</v>
+      </c>
+      <c r="N788">
+        <v>29.57</v>
+      </c>
+      <c r="O788">
+        <v>1</v>
+      </c>
+      <c r="P788" t="s">
+        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2370" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="415">
   <si>
     <t>trade_time</t>
   </si>
@@ -1616,7 +1616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P786"/>
+  <dimension ref="A1:P787"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -39668,96 +39668,96 @@
     </row>
     <row r="762" spans="1:16">
       <c r="A762" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B762" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C762">
-        <v>3.578326607098528</v>
+        <v>4.384836932532686</v>
       </c>
       <c r="D762" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E762">
-        <v>4.009375692421386</v>
+        <v>3.715577584802556</v>
       </c>
       <c r="F762">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G762">
-        <v>0.05340167339290147</v>
+        <v>0.05475516306746732</v>
       </c>
       <c r="H762">
-        <v>0.05231062430757862</v>
+        <v>0.05388442241519745</v>
       </c>
       <c r="I762">
-        <v>0.4310490853228579</v>
+        <v>0.6692593477301294</v>
       </c>
       <c r="J762">
-        <v>1.014732113763807</v>
+        <v>1.007406522698693</v>
       </c>
       <c r="K762">
-        <v>24.55</v>
+        <v>25</v>
       </c>
       <c r="L762">
-        <v>28.49</v>
+        <v>29.57</v>
       </c>
       <c r="M762">
-        <v>23.8</v>
+        <v>24.9</v>
       </c>
       <c r="N762">
-        <v>28.16</v>
+        <v>28.8</v>
       </c>
       <c r="O762">
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="763" spans="1:16">
       <c r="A763" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B763" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C763">
-        <v>4.503371200497003</v>
+        <v>3.578326607098528</v>
       </c>
       <c r="D763" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E763">
-        <v>3.932634594808817</v>
+        <v>4.009375692421386</v>
       </c>
       <c r="F763">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G763">
-        <v>0.050876628799503</v>
+        <v>0.05340167339290147</v>
       </c>
       <c r="H763">
-        <v>0.05040736540519119</v>
+        <v>0.05231062430757862</v>
       </c>
       <c r="I763">
-        <v>0.570736605688186</v>
+        <v>0.4310490853228579</v>
       </c>
       <c r="J763">
         <v>1.014732113763807</v>
       </c>
       <c r="K763">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L763">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M763">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="N763">
-        <v>27.17</v>
+        <v>28.16</v>
       </c>
       <c r="O763">
         <v>1</v>
@@ -39768,46 +39768,46 @@
     </row>
     <row r="764" spans="1:16">
       <c r="A764" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B764" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C764">
-        <v>4.351897989120626</v>
+        <v>4.503371200497003</v>
       </c>
       <c r="D764" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E764">
-        <v>3.648951566367863</v>
+        <v>3.932634594808817</v>
       </c>
       <c r="F764">
         <v>-1</v>
       </c>
       <c r="G764">
-        <v>0.05092810201087937</v>
+        <v>0.050876628799503</v>
       </c>
       <c r="H764">
-        <v>0.05063104843363214</v>
+        <v>0.05040736540519119</v>
       </c>
       <c r="I764">
-        <v>0.7029464227527633</v>
+        <v>0.570736605688186</v>
       </c>
       <c r="J764">
         <v>1.014732113763807</v>
       </c>
       <c r="K764">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L764">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M764">
-        <v>23.15</v>
+        <v>22.9</v>
       </c>
       <c r="N764">
-        <v>27.14</v>
+        <v>27.17</v>
       </c>
       <c r="O764">
         <v>1</v>
@@ -39818,96 +39818,96 @@
     </row>
     <row r="765" spans="1:16">
       <c r="A765" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B765" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C765">
-        <v>3.431049885513136</v>
+        <v>4.351897989120626</v>
       </c>
       <c r="D765" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E765">
-        <v>3.866598259682796</v>
+        <v>3.648951566367863</v>
       </c>
       <c r="F765">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G765">
-        <v>0.05354895011448686</v>
+        <v>0.05092810201087937</v>
       </c>
       <c r="H765">
-        <v>0.05245340174031721</v>
+        <v>0.05063104843363214</v>
       </c>
       <c r="I765">
-        <v>0.4355483741696595</v>
+        <v>0.7029464227527633</v>
       </c>
       <c r="J765">
-        <v>1.020731165559546</v>
+        <v>1.014732113763807</v>
       </c>
       <c r="K765">
-        <v>24.55</v>
+        <v>22.95</v>
       </c>
       <c r="L765">
-        <v>28.49</v>
+        <v>27.64</v>
       </c>
       <c r="M765">
-        <v>23.8</v>
+        <v>23.15</v>
       </c>
       <c r="N765">
-        <v>28.16</v>
+        <v>27.14</v>
       </c>
       <c r="O765">
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>317</v>
+        <v>406</v>
       </c>
     </row>
     <row r="766" spans="1:16">
       <c r="A766" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B766" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C766">
-        <v>4.366292866964365</v>
+        <v>3.431049885513136</v>
       </c>
       <c r="D766" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E766">
-        <v>3.79525630868639</v>
+        <v>3.866598259682796</v>
       </c>
       <c r="F766">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G766">
-        <v>0.05101370713303564</v>
+        <v>0.05354895011448686</v>
       </c>
       <c r="H766">
-        <v>0.05054474369131361</v>
+        <v>0.05245340174031721</v>
       </c>
       <c r="I766">
-        <v>0.5710365582779744</v>
+        <v>0.4355483741696595</v>
       </c>
       <c r="J766">
         <v>1.020731165559546</v>
       </c>
       <c r="K766">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L766">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M766">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="N766">
-        <v>27.17</v>
+        <v>28.16</v>
       </c>
       <c r="O766">
         <v>1</v>
@@ -39918,46 +39918,46 @@
     </row>
     <row r="767" spans="1:16">
       <c r="A767" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B767" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C767">
-        <v>4.214219750408411</v>
+        <v>4.366292866964365</v>
       </c>
       <c r="D767" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E767">
-        <v>3.510073517296505</v>
+        <v>3.79525630868639</v>
       </c>
       <c r="F767">
         <v>-1</v>
       </c>
       <c r="G767">
-        <v>0.05106578024959159</v>
+        <v>0.05101370713303564</v>
       </c>
       <c r="H767">
-        <v>0.0507699264827035</v>
+        <v>0.05054474369131361</v>
       </c>
       <c r="I767">
-        <v>0.7041462331119064</v>
+        <v>0.5710365582779744</v>
       </c>
       <c r="J767">
         <v>1.020731165559546</v>
       </c>
       <c r="K767">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L767">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M767">
-        <v>23.15</v>
+        <v>22.9</v>
       </c>
       <c r="N767">
-        <v>27.14</v>
+        <v>27.17</v>
       </c>
       <c r="O767">
         <v>1</v>
@@ -39968,96 +39968,96 @@
     </row>
     <row r="768" spans="1:16">
       <c r="A768" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B768" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C768">
-        <v>3.249078590284071</v>
+        <v>4.214219750408411</v>
       </c>
       <c r="D768" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E768">
-        <v>3.690186168992298</v>
+        <v>3.510073517296505</v>
       </c>
       <c r="F768">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G768">
-        <v>0.05373092140971593</v>
+        <v>0.05106578024959159</v>
       </c>
       <c r="H768">
-        <v>0.0526298138310077</v>
+        <v>0.0507699264827035</v>
       </c>
       <c r="I768">
-        <v>0.4411075787082268</v>
+        <v>0.7041462331119064</v>
       </c>
       <c r="J768">
-        <v>1.028143438277634</v>
+        <v>1.020731165559546</v>
       </c>
       <c r="K768">
-        <v>24.55</v>
+        <v>22.95</v>
       </c>
       <c r="L768">
-        <v>28.49</v>
+        <v>27.64</v>
       </c>
       <c r="M768">
-        <v>23.8</v>
+        <v>23.15</v>
       </c>
       <c r="N768">
-        <v>28.16</v>
+        <v>27.14</v>
       </c>
       <c r="O768">
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>407</v>
+        <v>317</v>
       </c>
     </row>
     <row r="769" spans="1:16">
       <c r="A769" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B769" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C769">
-        <v>4.196922435356054</v>
+        <v>3.249078590284071</v>
       </c>
       <c r="D769" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E769">
-        <v>3.625515263442175</v>
+        <v>3.690186168992298</v>
       </c>
       <c r="F769">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G769">
-        <v>0.05118307756464395</v>
+        <v>0.05373092140971593</v>
       </c>
       <c r="H769">
-        <v>0.05071448473655783</v>
+        <v>0.0526298138310077</v>
       </c>
       <c r="I769">
-        <v>0.5714071719138794</v>
+        <v>0.4411075787082268</v>
       </c>
       <c r="J769">
         <v>1.028143438277634</v>
       </c>
       <c r="K769">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L769">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M769">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="N769">
-        <v>27.17</v>
+        <v>28.16</v>
       </c>
       <c r="O769">
         <v>1</v>
@@ -40068,46 +40068,46 @@
     </row>
     <row r="770" spans="1:16">
       <c r="A770" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B770" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C770">
-        <v>4.04410809152829</v>
+        <v>4.196922435356054</v>
       </c>
       <c r="D770" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E770">
-        <v>3.338479403872764</v>
+        <v>3.625515263442175</v>
       </c>
       <c r="F770">
         <v>-1</v>
       </c>
       <c r="G770">
-        <v>0.05123589190847171</v>
+        <v>0.05118307756464395</v>
       </c>
       <c r="H770">
-        <v>0.05094152059612723</v>
+        <v>0.05071448473655783</v>
       </c>
       <c r="I770">
-        <v>0.7056286876555262</v>
+        <v>0.5714071719138794</v>
       </c>
       <c r="J770">
         <v>1.028143438277634</v>
       </c>
       <c r="K770">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L770">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M770">
-        <v>23.15</v>
+        <v>22.9</v>
       </c>
       <c r="N770">
-        <v>27.14</v>
+        <v>27.17</v>
       </c>
       <c r="O770">
         <v>1</v>
@@ -40118,96 +40118,96 @@
     </row>
     <row r="771" spans="1:16">
       <c r="A771" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B771" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C771">
-        <v>3.14672422434397</v>
+        <v>4.04410809152829</v>
       </c>
       <c r="D771" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E771">
-        <v>3.590958718508617</v>
+        <v>3.338479403872764</v>
       </c>
       <c r="F771">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G771">
-        <v>0.05383327577565603</v>
+        <v>0.05123589190847171</v>
       </c>
       <c r="H771">
-        <v>0.05272904128149138</v>
+        <v>0.05094152059612723</v>
       </c>
       <c r="I771">
-        <v>0.4442344941646468</v>
+        <v>0.7056286876555262</v>
       </c>
       <c r="J771">
-        <v>1.032312658886193</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K771">
-        <v>24.55</v>
+        <v>22.95</v>
       </c>
       <c r="L771">
-        <v>28.49</v>
+        <v>27.64</v>
       </c>
       <c r="M771">
-        <v>23.8</v>
+        <v>23.15</v>
       </c>
       <c r="N771">
-        <v>28.16</v>
+        <v>27.14</v>
       </c>
       <c r="O771">
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="772" spans="1:16">
       <c r="A772" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B772" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C772">
-        <v>4.101655744450497</v>
+        <v>3.14672422434397</v>
       </c>
       <c r="D772" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E772">
-        <v>3.241961946784642</v>
+        <v>3.590958718508617</v>
       </c>
       <c r="F772">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G772">
-        <v>0.05127834425554951</v>
+        <v>0.05383327577565603</v>
       </c>
       <c r="H772">
-        <v>0.05103803805321536</v>
+        <v>0.05272904128149138</v>
       </c>
       <c r="I772">
-        <v>0.8596937976658552</v>
+        <v>0.4442344941646468</v>
       </c>
       <c r="J772">
         <v>1.032312658886193</v>
       </c>
       <c r="K772">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L772">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M772">
-        <v>23.15</v>
+        <v>23.8</v>
       </c>
       <c r="N772">
-        <v>27.14</v>
+        <v>28.16</v>
       </c>
       <c r="O772">
         <v>1</v>
@@ -40218,13 +40218,13 @@
     </row>
     <row r="773" spans="1:16">
       <c r="A773" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B773" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C773">
-        <v>3.948424478561879</v>
+        <v>4.101655744450497</v>
       </c>
       <c r="D773" t="s">
         <v>320</v>
@@ -40236,22 +40236,22 @@
         <v>-1</v>
       </c>
       <c r="G773">
-        <v>0.05133157552143813</v>
+        <v>0.05127834425554951</v>
       </c>
       <c r="H773">
         <v>0.05103803805321536</v>
       </c>
       <c r="I773">
-        <v>0.7064625317772375</v>
+        <v>0.8596937976658552</v>
       </c>
       <c r="J773">
         <v>1.032312658886193</v>
       </c>
       <c r="K773">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L773">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M773">
         <v>23.15</v>
@@ -40268,96 +40268,96 @@
     </row>
     <row r="774" spans="1:16">
       <c r="A774" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B774" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C774">
-        <v>3.047718597071611</v>
+        <v>3.948424478561879</v>
       </c>
       <c r="D774" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E774">
-        <v>3.494977703067388</v>
+        <v>3.241961946784642</v>
       </c>
       <c r="F774">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G774">
-        <v>0.05393228140292838</v>
+        <v>0.05133157552143813</v>
       </c>
       <c r="H774">
-        <v>0.05282502229693262</v>
+        <v>0.05103803805321536</v>
       </c>
       <c r="I774">
-        <v>0.4472591059957765</v>
+        <v>0.7064625317772375</v>
       </c>
       <c r="J774">
-        <v>1.036345474661034</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K774">
-        <v>24.55</v>
+        <v>22.95</v>
       </c>
       <c r="L774">
-        <v>28.49</v>
+        <v>27.64</v>
       </c>
       <c r="M774">
-        <v>23.8</v>
+        <v>23.15</v>
       </c>
       <c r="N774">
-        <v>28.16</v>
+        <v>27.14</v>
       </c>
       <c r="O774">
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="775" spans="1:16">
       <c r="A775" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B775" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C775">
-        <v>4.009505903995372</v>
+        <v>3.047718597071611</v>
       </c>
       <c r="D775" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E775">
-        <v>3.148602261597063</v>
+        <v>3.494977703067388</v>
       </c>
       <c r="F775">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G775">
-        <v>0.05137049409600464</v>
+        <v>0.05393228140292838</v>
       </c>
       <c r="H775">
-        <v>0.05113139773840294</v>
+        <v>0.05282502229693262</v>
       </c>
       <c r="I775">
-        <v>0.8609036423983092</v>
+        <v>0.4472591059957765</v>
       </c>
       <c r="J775">
         <v>1.036345474661034</v>
       </c>
       <c r="K775">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L775">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M775">
-        <v>23.15</v>
+        <v>23.8</v>
       </c>
       <c r="N775">
-        <v>27.14</v>
+        <v>28.16</v>
       </c>
       <c r="O775">
         <v>1</v>
@@ -40368,13 +40368,13 @@
     </row>
     <row r="776" spans="1:16">
       <c r="A776" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B776" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C776">
-        <v>3.855871356529267</v>
+        <v>4.009505903995372</v>
       </c>
       <c r="D776" t="s">
         <v>320</v>
@@ -40386,22 +40386,22 @@
         <v>-1</v>
       </c>
       <c r="G776">
-        <v>0.05142412864347074</v>
+        <v>0.05137049409600464</v>
       </c>
       <c r="H776">
         <v>0.05113139773840294</v>
       </c>
       <c r="I776">
-        <v>0.7072690949322045</v>
+        <v>0.8609036423983092</v>
       </c>
       <c r="J776">
         <v>1.036345474661034</v>
       </c>
       <c r="K776">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L776">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M776">
         <v>23.15</v>
@@ -40418,40 +40418,40 @@
     </row>
     <row r="777" spans="1:16">
       <c r="A777" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B777" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C777">
-        <v>3.923892030831919</v>
+        <v>3.855871356529267</v>
       </c>
       <c r="D777" t="s">
         <v>320</v>
       </c>
       <c r="E777">
-        <v>3.06186435508792</v>
+        <v>3.148602261597063</v>
       </c>
       <c r="F777">
         <v>-1</v>
       </c>
       <c r="G777">
-        <v>0.05145610796916809</v>
+        <v>0.05142412864347074</v>
       </c>
       <c r="H777">
-        <v>0.05121813564491208</v>
+        <v>0.05113139773840294</v>
       </c>
       <c r="I777">
-        <v>0.8620276757439989</v>
+        <v>0.7072690949322045</v>
       </c>
       <c r="J777">
-        <v>1.040092252480004</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K777">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L777">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M777">
         <v>23.15</v>
@@ -40463,18 +40463,18 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>186</v>
+        <v>409</v>
       </c>
     </row>
     <row r="778" spans="1:16">
       <c r="A778" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B778" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C778">
-        <v>3.769882805583919</v>
+        <v>3.923892030831919</v>
       </c>
       <c r="D778" t="s">
         <v>320</v>
@@ -40486,22 +40486,22 @@
         <v>-1</v>
       </c>
       <c r="G778">
-        <v>0.05151011719441608</v>
+        <v>0.05145610796916809</v>
       </c>
       <c r="H778">
         <v>0.05121813564491208</v>
       </c>
       <c r="I778">
-        <v>0.7080184504959988</v>
+        <v>0.8620276757439989</v>
       </c>
       <c r="J778">
         <v>1.040092252480004</v>
       </c>
       <c r="K778">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L778">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M778">
         <v>23.15</v>
@@ -40518,63 +40518,63 @@
     </row>
     <row r="779" spans="1:16">
       <c r="A779" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B779" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C779">
-        <v>3.103333239057651</v>
+        <v>3.769882805583919</v>
       </c>
       <c r="D779" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E779">
-        <v>2.529533092972439</v>
+        <v>3.06186435508792</v>
       </c>
       <c r="F779">
         <v>-1</v>
       </c>
       <c r="G779">
-        <v>0.05227666676094235</v>
+        <v>0.05151011719441608</v>
       </c>
       <c r="H779">
-        <v>0.05181046690702756</v>
+        <v>0.05121813564491208</v>
       </c>
       <c r="I779">
-        <v>0.5738001460852118</v>
+        <v>0.7080184504959988</v>
       </c>
       <c r="J779">
-        <v>1.07600292170426</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K779">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L779">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M779">
-        <v>22.9</v>
+        <v>23.15</v>
       </c>
       <c r="N779">
-        <v>27.17</v>
+        <v>27.14</v>
       </c>
       <c r="O779">
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>410</v>
+        <v>186</v>
       </c>
     </row>
     <row r="780" spans="1:16">
       <c r="A780" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B780" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C780">
-        <v>2.945732946887226</v>
+        <v>3.103333239057651</v>
       </c>
       <c r="D780" t="s">
         <v>320</v>
@@ -40586,22 +40586,22 @@
         <v>-1</v>
       </c>
       <c r="G780">
-        <v>0.05233426705311277</v>
+        <v>0.05227666676094235</v>
       </c>
       <c r="H780">
         <v>0.05204946763745363</v>
       </c>
       <c r="I780">
-        <v>0.7152005843408524</v>
+        <v>0.8728008765112776</v>
       </c>
       <c r="J780">
         <v>1.07600292170426</v>
       </c>
       <c r="K780">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L780">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M780">
         <v>23.15</v>
@@ -40618,34 +40618,34 @@
     </row>
     <row r="781" spans="1:16">
       <c r="A781" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B781" t="s">
         <v>188</v>
       </c>
       <c r="C781">
-        <v>1.786358263523248</v>
+        <v>2.945732946887226</v>
       </c>
       <c r="D781" t="s">
         <v>320</v>
       </c>
       <c r="E781">
-        <v>1.061054196102969</v>
+        <v>2.230532362546374</v>
       </c>
       <c r="F781">
         <v>-1</v>
       </c>
       <c r="G781">
-        <v>0.05349364173647676</v>
+        <v>0.05233426705311277</v>
       </c>
       <c r="H781">
-        <v>0.05321894580389703</v>
+        <v>0.05204946763745363</v>
       </c>
       <c r="I781">
-        <v>0.7253040674202786</v>
+        <v>0.7152005843408524</v>
       </c>
       <c r="J781">
-        <v>1.126520337101384</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K781">
         <v>22.95</v>
@@ -40663,7 +40663,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40674,28 +40674,28 @@
         <v>188</v>
       </c>
       <c r="C782">
-        <v>1.347927144340538</v>
+        <v>1.786358263523248</v>
       </c>
       <c r="D782" t="s">
         <v>320</v>
       </c>
       <c r="E782">
-        <v>0.6188023264262945</v>
+        <v>1.061054196102969</v>
       </c>
       <c r="F782">
         <v>-1</v>
       </c>
       <c r="G782">
-        <v>0.05393207285565946</v>
+        <v>0.05349364173647676</v>
       </c>
       <c r="H782">
-        <v>0.05366119767357371</v>
+        <v>0.05321894580389703</v>
       </c>
       <c r="I782">
-        <v>0.7291248179142436</v>
+        <v>0.7253040674202786</v>
       </c>
       <c r="J782">
-        <v>1.145624089571218</v>
+        <v>1.126520337101384</v>
       </c>
       <c r="K782">
         <v>22.95</v>
@@ -40713,7 +40713,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>411</v>
+        <v>319</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40724,28 +40724,28 @@
         <v>188</v>
       </c>
       <c r="C783">
-        <v>0.8331756972601632</v>
+        <v>1.347927144340538</v>
       </c>
       <c r="D783" t="s">
         <v>320</v>
       </c>
       <c r="E783">
-        <v>0.09956502795524358</v>
+        <v>0.6188023264262945</v>
       </c>
       <c r="F783">
         <v>-1</v>
       </c>
       <c r="G783">
-        <v>0.05444682430273984</v>
+        <v>0.05393207285565946</v>
       </c>
       <c r="H783">
-        <v>0.05418043497204476</v>
+        <v>0.05366119767357371</v>
       </c>
       <c r="I783">
-        <v>0.7336106693049196</v>
+        <v>0.7291248179142436</v>
       </c>
       <c r="J783">
-        <v>1.168053346524612</v>
+        <v>1.145624089571218</v>
       </c>
       <c r="K783">
         <v>22.95</v>
@@ -40763,7 +40763,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40771,49 +40771,49 @@
         <v>0</v>
       </c>
       <c r="B784" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C784">
-        <v>-0.02626559060565725</v>
+        <v>0.8331756972601632</v>
       </c>
       <c r="D784" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E784">
-        <v>-0.6778805282432323</v>
+        <v>0.09956502795524358</v>
       </c>
       <c r="F784">
         <v>-1</v>
       </c>
       <c r="G784">
-        <v>0.05916626559060566</v>
+        <v>0.05444682430273984</v>
       </c>
       <c r="H784">
-        <v>0.05827788052824323</v>
+        <v>0.05418043497204476</v>
       </c>
       <c r="I784">
-        <v>0.6516149376375751</v>
+        <v>0.7336106693049196</v>
       </c>
       <c r="J784">
-        <v>1.183850623624226</v>
+        <v>1.168053346524612</v>
       </c>
       <c r="K784">
-        <v>25</v>
+        <v>22.95</v>
       </c>
       <c r="L784">
-        <v>29.57</v>
+        <v>27.64</v>
       </c>
       <c r="M784">
-        <v>24.9</v>
+        <v>23.15</v>
       </c>
       <c r="N784">
-        <v>28.8</v>
+        <v>27.14</v>
       </c>
       <c r="O784">
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>320</v>
+        <v>412</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -40824,28 +40824,28 @@
         <v>189</v>
       </c>
       <c r="C785">
-        <v>0.04582245394855988</v>
+        <v>-0.02626559060565725</v>
       </c>
       <c r="D785" t="s">
         <v>321</v>
       </c>
       <c r="E785">
-        <v>-0.6060808358672318</v>
+        <v>-0.6778805282432323</v>
       </c>
       <c r="F785">
         <v>-1</v>
       </c>
       <c r="G785">
-        <v>0.05909417754605144</v>
+        <v>0.05916626559060566</v>
       </c>
       <c r="H785">
-        <v>0.05820608083586724</v>
+        <v>0.05827788052824323</v>
       </c>
       <c r="I785">
-        <v>0.6519032898157917</v>
+        <v>0.6516149376375751</v>
       </c>
       <c r="J785">
-        <v>1.180967101842058</v>
+        <v>1.183850623624226</v>
       </c>
       <c r="K785">
         <v>25</v>
@@ -40863,7 +40863,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>413</v>
+        <v>320</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -40874,28 +40874,28 @@
         <v>189</v>
       </c>
       <c r="C786">
-        <v>0.05143297331527208</v>
+        <v>0.04582245394855988</v>
       </c>
       <c r="D786" t="s">
         <v>321</v>
       </c>
       <c r="E786">
-        <v>-0.6004927585779853</v>
+        <v>-0.6060808358672318</v>
       </c>
       <c r="F786">
         <v>-1</v>
       </c>
       <c r="G786">
-        <v>0.05908856702668473</v>
+        <v>0.05909417754605144</v>
       </c>
       <c r="H786">
-        <v>0.05820049275857798</v>
+        <v>0.05820608083586724</v>
       </c>
       <c r="I786">
-        <v>0.6519257318932574</v>
+        <v>0.6519032898157917</v>
       </c>
       <c r="J786">
-        <v>1.180742681067389</v>
+        <v>1.180967101842058</v>
       </c>
       <c r="K786">
         <v>25</v>
@@ -40913,6 +40913,56 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="787" spans="1:16">
+      <c r="A787" s="1">
+        <v>0</v>
+      </c>
+      <c r="B787" t="s">
+        <v>189</v>
+      </c>
+      <c r="C787">
+        <v>0.05143297331527208</v>
+      </c>
+      <c r="D787" t="s">
+        <v>321</v>
+      </c>
+      <c r="E787">
+        <v>-0.6004927585779853</v>
+      </c>
+      <c r="F787">
+        <v>-1</v>
+      </c>
+      <c r="G787">
+        <v>0.05908856702668473</v>
+      </c>
+      <c r="H787">
+        <v>0.05820049275857798</v>
+      </c>
+      <c r="I787">
+        <v>0.6519257318932574</v>
+      </c>
+      <c r="J787">
+        <v>1.180742681067389</v>
+      </c>
+      <c r="K787">
+        <v>25</v>
+      </c>
+      <c r="L787">
+        <v>29.57</v>
+      </c>
+      <c r="M787">
+        <v>24.9</v>
+      </c>
+      <c r="N787">
+        <v>28.8</v>
+      </c>
+      <c r="O787">
+        <v>1</v>
+      </c>
+      <c r="P787" t="s">
         <v>414</v>
       </c>
     </row>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2430" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="419">
   <si>
     <t>trade_time</t>
   </si>
@@ -589,7 +589,7 @@
     <t>2021-10-20</t>
   </si>
   <si>
-    <t>2021-10-19</t>
+    <t>2021-10-08</t>
   </si>
   <si>
     <t>2016-09-12</t>
@@ -988,7 +988,7 @@
     <t>2021-10-15</t>
   </si>
   <si>
-    <t>2021-10-21</t>
+    <t>2021-10-25</t>
   </si>
   <si>
     <t>2016-07-29</t>
@@ -1270,13 +1270,7 @@
     <t>2021-09-29</t>
   </si>
   <si>
-    <t>2021-10-08</t>
-  </si>
-  <si>
     <t>2021-10-11</t>
-  </si>
-  <si>
-    <t>2021-10-18</t>
   </si>
 </sst>
 </file>
@@ -1634,7 +1628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P806"/>
+  <dimension ref="A1:P805"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -39348,7 +39342,7 @@
         <v>324</v>
       </c>
       <c r="E755">
-        <v>4.479309154848252</v>
+        <v>4.865973846683474</v>
       </c>
       <c r="F755">
         <v>1</v>
@@ -39357,10 +39351,10 @@
         <v>0.05323607773918804</v>
       </c>
       <c r="H755">
-        <v>0.05502069084515175</v>
+        <v>0.05413402615331653</v>
       </c>
       <c r="I755">
-        <v>0.3153868940362869</v>
+        <v>0.7020515858715086</v>
       </c>
       <c r="J755">
         <v>0.9794841412849514</v>
@@ -39372,10 +39366,10 @@
         <v>28.7</v>
       </c>
       <c r="M755">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N755">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O755">
         <v>1</v>
@@ -39598,7 +39592,7 @@
         <v>324</v>
       </c>
       <c r="E760">
-        <v>3.929624481559852</v>
+        <v>4.330137818264742</v>
       </c>
       <c r="F760">
         <v>1</v>
@@ -39607,10 +39601,10 @@
         <v>0.05376978320685758</v>
       </c>
       <c r="H760">
-        <v>0.05557037551844014</v>
+        <v>0.05466986218173526</v>
       </c>
       <c r="I760">
-        <v>0.299407688417439</v>
+        <v>0.6999210251223289</v>
       </c>
       <c r="J760">
         <v>1.00078974877675</v>
@@ -39622,10 +39616,10 @@
         <v>28.7</v>
       </c>
       <c r="M760">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N760">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O760">
         <v>1</v>
@@ -39848,7 +39842,7 @@
         <v>324</v>
       </c>
       <c r="E765">
-        <v>3.758911714373731</v>
+        <v>4.163725954127884</v>
       </c>
       <c r="F765">
         <v>1</v>
@@ -39857,10 +39851,10 @@
         <v>0.05393553339360225</v>
       </c>
       <c r="H765">
-        <v>0.05574108828562627</v>
+        <v>0.05483627404587212</v>
       </c>
       <c r="I765">
-        <v>0.2944451079759816</v>
+        <v>0.6992593477301341</v>
       </c>
       <c r="J765">
         <v>1.007406522698693</v>
@@ -39872,10 +39866,10 @@
         <v>28.7</v>
       </c>
       <c r="M765">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N765">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O765">
         <v>1</v>
@@ -40048,7 +40042,7 @@
         <v>324</v>
       </c>
       <c r="E769">
-        <v>3.569911464893774</v>
+        <v>3.979487338840251</v>
       </c>
       <c r="F769">
         <v>1</v>
@@ -40057,10 +40051,10 @@
         <v>0.05411903944978337</v>
       </c>
       <c r="H769">
-        <v>0.05593008853510623</v>
+        <v>0.05502051266115975</v>
       </c>
       <c r="I769">
-        <v>0.2889509146771481</v>
+        <v>0.6985267886236244</v>
       </c>
       <c r="J769">
         <v>1.014732113763807</v>
@@ -40072,10 +40066,10 @@
         <v>28.7</v>
       </c>
       <c r="M769">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N769">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O769">
         <v>1</v>
@@ -40248,7 +40242,7 @@
         <v>324</v>
       </c>
       <c r="E773">
-        <v>3.415135928563704</v>
+        <v>3.828611186177412</v>
       </c>
       <c r="F773">
         <v>1</v>
@@ -40257,10 +40251,10 @@
         <v>0.05426931569726664</v>
       </c>
       <c r="H773">
-        <v>0.0560848640714363</v>
+        <v>0.05517138881382259</v>
       </c>
       <c r="I773">
-        <v>0.2844516258303393</v>
+        <v>0.6979268834440475</v>
       </c>
       <c r="J773">
         <v>1.020731165559546</v>
@@ -40272,10 +40266,10 @@
         <v>28.7</v>
       </c>
       <c r="M773">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N773">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O773">
         <v>1</v>
@@ -40448,7 +40442,7 @@
         <v>324</v>
       </c>
       <c r="E777">
-        <v>3.223899292437032</v>
+        <v>3.642192527317494</v>
       </c>
       <c r="F777">
         <v>1</v>
@@ -40457,10 +40451,10 @@
         <v>0.05445499312885474</v>
       </c>
       <c r="H777">
-        <v>0.05627610070756297</v>
+        <v>0.05535780747268251</v>
       </c>
       <c r="I777">
-        <v>0.2788924212917756</v>
+        <v>0.6971856561722376</v>
       </c>
       <c r="J777">
         <v>1.028143438277634</v>
@@ -40472,10 +40466,10 @@
         <v>28.7</v>
       </c>
       <c r="M777">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N777">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O777">
         <v>1</v>
@@ -40648,7 +40642,7 @@
         <v>324</v>
       </c>
       <c r="E781">
-        <v>3.116333400736231</v>
+        <v>3.537336629012259</v>
       </c>
       <c r="F781">
         <v>1</v>
@@ -40657,10 +40651,10 @@
         <v>0.05455943210509912</v>
       </c>
       <c r="H781">
-        <v>0.05638366659926377</v>
+        <v>0.05546266337098774</v>
       </c>
       <c r="I781">
-        <v>0.2757655058353556</v>
+        <v>0.6967687341113837</v>
       </c>
       <c r="J781">
         <v>1.032312658886193</v>
@@ -40672,10 +40666,10 @@
         <v>28.7</v>
       </c>
       <c r="M781">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N781">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O781">
         <v>1</v>
@@ -40848,7 +40842,7 @@
         <v>324</v>
       </c>
       <c r="E785">
-        <v>3.012286753745318</v>
+        <v>3.435911312274992</v>
       </c>
       <c r="F785">
         <v>1</v>
@@ -40857,10 +40851,10 @@
         <v>0.05466045414025891</v>
       </c>
       <c r="H785">
-        <v>0.05648771324625469</v>
+        <v>0.05556408868772501</v>
       </c>
       <c r="I785">
-        <v>0.2727408940042224</v>
+        <v>0.6963654525338967</v>
       </c>
       <c r="J785">
         <v>1.036345474661034</v>
@@ -40872,10 +40866,10 @@
         <v>28.7</v>
       </c>
       <c r="M785">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N785">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O785">
         <v>1</v>
@@ -40998,7 +40992,7 @@
         <v>324</v>
       </c>
       <c r="E788">
-        <v>2.915619886015907</v>
+        <v>3.34167985012791</v>
       </c>
       <c r="F788">
         <v>1</v>
@@ -41007,10 +41001,10 @@
         <v>0.05475431092462409</v>
       </c>
       <c r="H788">
-        <v>0.0565843801139841</v>
+        <v>0.05565832014987209</v>
       </c>
       <c r="I788">
-        <v>0.2699308106399982</v>
+        <v>0.6959907747520013</v>
       </c>
       <c r="J788">
         <v>1.040092252480004</v>
@@ -41022,10 +41016,10 @@
         <v>28.7</v>
       </c>
       <c r="M788">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N788">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O788">
         <v>1</v>
@@ -41148,7 +41142,7 @@
         <v>324</v>
       </c>
       <c r="E791">
-        <v>1.989124620030083</v>
+        <v>2.438526519137852</v>
       </c>
       <c r="F791">
         <v>1</v>
@@ -41157,10 +41151,10 @@
         <v>0.05565387318869172</v>
       </c>
       <c r="H791">
-        <v>0.05751087537996992</v>
+        <v>0.05656147348086215</v>
       </c>
       <c r="I791">
-        <v>0.2429978087218068</v>
+        <v>0.6923997078295763</v>
       </c>
       <c r="J791">
         <v>1.07600292170426</v>
@@ -41172,10 +41166,10 @@
         <v>28.7</v>
       </c>
       <c r="M791">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N791">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O791">
         <v>1</v>
@@ -41248,7 +41242,7 @@
         <v>324</v>
       </c>
       <c r="E793">
-        <v>0.6857753027843003</v>
+        <v>1.168013521900203</v>
       </c>
       <c r="F793">
         <v>1</v>
@@ -41257,10 +41251,10 @@
         <v>0.05691933444438967</v>
       </c>
       <c r="H793">
-        <v>0.0588142246972157</v>
+        <v>0.0578319864780998</v>
       </c>
       <c r="I793">
-        <v>0.2051097471739638</v>
+        <v>0.6873479662898667</v>
       </c>
       <c r="J793">
         <v>1.126520337101384</v>
@@ -41272,10 +41266,10 @@
         <v>28.7</v>
       </c>
       <c r="M793">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N793">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O793">
         <v>1</v>
@@ -41348,7 +41342,7 @@
         <v>324</v>
       </c>
       <c r="E795">
-        <v>0.1928984890625642</v>
+        <v>0.6875541472838584</v>
       </c>
       <c r="F795">
         <v>1</v>
@@ -41357,10 +41351,10 @@
         <v>0.05739788344375902</v>
       </c>
       <c r="H795">
-        <v>0.05930710151093744</v>
+        <v>0.05831244585271614</v>
       </c>
       <c r="I795">
-        <v>0.1907819328215865</v>
+        <v>0.6854375910428807</v>
       </c>
       <c r="J795">
         <v>1.145624089571218</v>
@@ -41372,10 +41366,10 @@
         <v>28.7</v>
       </c>
       <c r="M795">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N795">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O795">
         <v>1</v>
@@ -41448,7 +41442,7 @@
         <v>324</v>
       </c>
       <c r="E797">
-        <v>-0.3857763403349814</v>
+        <v>0.1234583349060188</v>
       </c>
       <c r="F797">
         <v>1</v>
@@ -41457,10 +41451,10 @@
         <v>0.05795973633044153</v>
       </c>
       <c r="H797">
-        <v>0.05988577634033498</v>
+        <v>0.05887654166509398</v>
       </c>
       <c r="I797">
-        <v>0.1739599901065425</v>
+        <v>0.6831946653475427</v>
       </c>
       <c r="J797">
         <v>1.168053346524612</v>
@@ -41472,10 +41466,10 @@
         <v>28.7</v>
       </c>
       <c r="M797">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N797">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O797">
         <v>1</v>
@@ -41498,7 +41492,7 @@
         <v>324</v>
       </c>
       <c r="E798">
-        <v>-0.671321113384785</v>
+        <v>-0.1548924806832268</v>
       </c>
       <c r="F798">
         <v>1</v>
@@ -41507,10 +41501,10 @@
         <v>0.05823698038334453</v>
       </c>
       <c r="H798">
-        <v>0.06017132111338479</v>
+        <v>0.05915489248068323</v>
       </c>
       <c r="I798">
-        <v>0.1656592699597468</v>
+        <v>0.6820879026613049</v>
       </c>
       <c r="J798">
         <v>1.179120973387007</v>
@@ -41522,10 +41516,10 @@
         <v>28.7</v>
       </c>
       <c r="M798">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N798">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O798">
         <v>1</v>
@@ -41548,7 +41542,7 @@
         <v>324</v>
       </c>
       <c r="E799">
-        <v>-0.8924614943403242</v>
+        <v>-0.3704614954519023</v>
       </c>
       <c r="F799">
         <v>1</v>
@@ -41557,10 +41551,10 @@
         <v>0.05845169226485369</v>
       </c>
       <c r="H799">
-        <v>0.06039246149434033</v>
+        <v>0.05937046149545191</v>
       </c>
       <c r="I799">
-        <v>0.1592307705133642</v>
+        <v>0.6812307694017861</v>
       </c>
       <c r="J799">
         <v>1.187692305982183</v>
@@ -41572,10 +41566,10 @@
         <v>28.7</v>
       </c>
       <c r="M799">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N799">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O799">
         <v>1</v>
@@ -41648,7 +41642,7 @@
         <v>324</v>
       </c>
       <c r="E801">
-        <v>-0.7485754576120627</v>
+        <v>-0.230200494532685</v>
       </c>
       <c r="F801">
         <v>1</v>
@@ -41657,10 +41651,10 @@
         <v>0.05831198896175125</v>
       </c>
       <c r="H801">
-        <v>0.06024857545761206</v>
+        <v>0.05923020049453268</v>
       </c>
       <c r="I801">
-        <v>0.1634135041391858</v>
+        <v>0.6817884672185635</v>
       </c>
       <c r="J801">
         <v>1.182115327814421</v>
@@ -41672,10 +41666,10 @@
         <v>28.7</v>
       </c>
       <c r="M801">
-        <v>25.8</v>
+        <v>25.15</v>
       </c>
       <c r="N801">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="O801">
         <v>1</v>
@@ -41689,10 +41683,10 @@
         <v>0</v>
       </c>
       <c r="B802" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C802">
-        <v>-0.02626559060565725</v>
+        <v>-0.1778805282432323</v>
       </c>
       <c r="D802" t="s">
         <v>323</v>
@@ -41704,22 +41698,22 @@
         <v>-1</v>
       </c>
       <c r="G802">
-        <v>0.05916626559060566</v>
+        <v>0.05877788052824323</v>
       </c>
       <c r="H802">
         <v>0.05827788052824323</v>
       </c>
       <c r="I802">
-        <v>0.6516149376375751</v>
+        <v>0.5</v>
       </c>
       <c r="J802">
         <v>1.183850623624226</v>
       </c>
       <c r="K802">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="L802">
-        <v>29.57</v>
+        <v>29.3</v>
       </c>
       <c r="M802">
         <v>24.9</v>
@@ -41736,34 +41730,34 @@
     </row>
     <row r="803" spans="1:16">
       <c r="A803" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B803" t="s">
         <v>189</v>
       </c>
       <c r="C803">
-        <v>0.04582245394855988</v>
+        <v>-0.02626559060565725</v>
       </c>
       <c r="D803" t="s">
         <v>323</v>
       </c>
       <c r="E803">
-        <v>-0.6060808358672318</v>
+        <v>-0.6778805282432323</v>
       </c>
       <c r="F803">
         <v>-1</v>
       </c>
       <c r="G803">
-        <v>0.05909417754605144</v>
+        <v>0.05916626559060566</v>
       </c>
       <c r="H803">
-        <v>0.05820608083586724</v>
+        <v>0.05827788052824323</v>
       </c>
       <c r="I803">
-        <v>0.6519032898157917</v>
+        <v>0.6516149376375751</v>
       </c>
       <c r="J803">
-        <v>1.180967101842058</v>
+        <v>1.183850623624226</v>
       </c>
       <c r="K803">
         <v>25</v>
@@ -41781,7 +41775,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>418</v>
+        <v>322</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41792,28 +41786,28 @@
         <v>189</v>
       </c>
       <c r="C804">
-        <v>0.05143297331527208</v>
+        <v>0.04582245394855988</v>
       </c>
       <c r="D804" t="s">
         <v>323</v>
       </c>
       <c r="E804">
-        <v>-0.6004927585779853</v>
+        <v>-0.6060808358672318</v>
       </c>
       <c r="F804">
         <v>-1</v>
       </c>
       <c r="G804">
-        <v>0.05908856702668473</v>
+        <v>0.05909417754605144</v>
       </c>
       <c r="H804">
-        <v>0.05820049275857798</v>
+        <v>0.05820608083586724</v>
       </c>
       <c r="I804">
-        <v>0.6519257318932574</v>
+        <v>0.6519032898157917</v>
       </c>
       <c r="J804">
-        <v>1.180742681067389</v>
+        <v>1.180967101842058</v>
       </c>
       <c r="K804">
         <v>25</v>
@@ -41831,7 +41825,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>419</v>
+        <v>191</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41839,99 +41833,49 @@
         <v>0</v>
       </c>
       <c r="B805" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C805">
-        <v>-0.2855402577441701</v>
+        <v>0.05143297331527208</v>
       </c>
       <c r="D805" t="s">
-        <v>190</v>
+        <v>323</v>
       </c>
       <c r="E805">
-        <v>-0.843478294849362</v>
+        <v>-0.6004927585779853</v>
       </c>
       <c r="F805">
         <v>-1</v>
       </c>
       <c r="G805">
-        <v>0.05856554025774418</v>
+        <v>0.05908856702668473</v>
       </c>
       <c r="H805">
-        <v>0.05824347829484936</v>
+        <v>0.05820049275857798</v>
       </c>
       <c r="I805">
-        <v>0.5579380371051919</v>
+        <v>0.6519257318932574</v>
       </c>
       <c r="J805">
-        <v>1.179380371051871</v>
+        <v>1.180742681067389</v>
       </c>
       <c r="K805">
-        <v>24.95</v>
+        <v>25</v>
       </c>
       <c r="L805">
-        <v>29.14</v>
+        <v>29.57</v>
       </c>
       <c r="M805">
-        <v>25.05</v>
+        <v>24.9</v>
       </c>
       <c r="N805">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="O805">
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="806" spans="1:16">
-      <c r="A806" s="1">
-        <v>0</v>
-      </c>
-      <c r="B806" t="s">
-        <v>191</v>
-      </c>
-      <c r="C806">
-        <v>-0.3572136305691629</v>
-      </c>
-      <c r="D806" t="s">
-        <v>190</v>
-      </c>
-      <c r="E806">
-        <v>-0.9154389357017081</v>
-      </c>
-      <c r="F806">
-        <v>-1</v>
-      </c>
-      <c r="G806">
-        <v>0.05863721363056917</v>
-      </c>
-      <c r="H806">
-        <v>0.05831543893570171</v>
-      </c>
-      <c r="I806">
-        <v>0.5582253051325452</v>
-      </c>
-      <c r="J806">
-        <v>1.182253051325417</v>
-      </c>
-      <c r="K806">
-        <v>24.95</v>
-      </c>
-      <c r="L806">
-        <v>29.14</v>
-      </c>
-      <c r="M806">
-        <v>25.05</v>
-      </c>
-      <c r="N806">
-        <v>28.7</v>
-      </c>
-      <c r="O806">
-        <v>1</v>
-      </c>
-      <c r="P806" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2430" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2451" uniqueCount="424">
   <si>
     <t>trade_time</t>
   </si>
@@ -589,406 +589,409 @@
     <t>2021-10-20</t>
   </si>
   <si>
+    <t>2021-10-27</t>
+  </si>
+  <si>
+    <t>2016-09-12</t>
+  </si>
+  <si>
+    <t>2016-10-17</t>
+  </si>
+  <si>
+    <t>2016-12-01</t>
+  </si>
+  <si>
+    <t>2016-12-06</t>
+  </si>
+  <si>
+    <t>2016-12-07</t>
+  </si>
+  <si>
+    <t>2016-12-08</t>
+  </si>
+  <si>
+    <t>2016-12-12</t>
+  </si>
+  <si>
+    <t>2017-03-13</t>
+  </si>
+  <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
+    <t>2017-04-28</t>
+  </si>
+  <si>
+    <t>2017-05-05</t>
+  </si>
+  <si>
+    <t>2017-06-12</t>
+  </si>
+  <si>
+    <t>2017-06-09</t>
+  </si>
+  <si>
+    <t>2017-08-17</t>
+  </si>
+  <si>
+    <t>2017-08-18</t>
+  </si>
+  <si>
+    <t>2017-08-03</t>
+  </si>
+  <si>
+    <t>2017-09-04</t>
+  </si>
+  <si>
+    <t>2017-09-06</t>
+  </si>
+  <si>
+    <t>2017-07-28</t>
+  </si>
+  <si>
+    <t>2017-09-08</t>
+  </si>
+  <si>
+    <t>2017-09-11</t>
+  </si>
+  <si>
+    <t>2017-09-13</t>
+  </si>
+  <si>
+    <t>2017-09-14</t>
+  </si>
+  <si>
+    <t>2017-09-18</t>
+  </si>
+  <si>
+    <t>2017-07-19</t>
+  </si>
+  <si>
+    <t>2017-08-29</t>
+  </si>
+  <si>
+    <t>2017-10-10</t>
+  </si>
+  <si>
+    <t>2017-10-17</t>
+  </si>
+  <si>
+    <t>2018-01-17</t>
+  </si>
+  <si>
+    <t>2018-03-01</t>
+  </si>
+  <si>
+    <t>2018-01-18</t>
+  </si>
+  <si>
+    <t>2018-04-23</t>
+  </si>
+  <si>
+    <t>2018-02-05</t>
+  </si>
+  <si>
+    <t>2018-04-24</t>
+  </si>
+  <si>
+    <t>2018-03-02</t>
+  </si>
+  <si>
+    <t>2018-03-13</t>
+  </si>
+  <si>
+    <t>2018-03-26</t>
+  </si>
+  <si>
+    <t>2018-05-14</t>
+  </si>
+  <si>
+    <t>2018-05-07</t>
+  </si>
+  <si>
+    <t>2018-05-17</t>
+  </si>
+  <si>
+    <t>2018-05-18</t>
+  </si>
+  <si>
+    <t>2018-05-04</t>
+  </si>
+  <si>
+    <t>2018-05-21</t>
+  </si>
+  <si>
+    <t>2018-05-24</t>
+  </si>
+  <si>
+    <t>2018-05-03</t>
+  </si>
+  <si>
+    <t>2018-05-25</t>
+  </si>
+  <si>
+    <t>2018-05-31</t>
+  </si>
+  <si>
+    <t>2018-05-29</t>
+  </si>
+  <si>
+    <t>2018-06-13</t>
+  </si>
+  <si>
+    <t>2018-06-12</t>
+  </si>
+  <si>
+    <t>2018-06-20</t>
+  </si>
+  <si>
+    <t>2018-07-10</t>
+  </si>
+  <si>
+    <t>2018-08-23</t>
+  </si>
+  <si>
+    <t>2018-08-27</t>
+  </si>
+  <si>
+    <t>2018-08-28</t>
+  </si>
+  <si>
+    <t>2018-08-29</t>
+  </si>
+  <si>
+    <t>2018-08-30</t>
+  </si>
+  <si>
+    <t>2018-09-04</t>
+  </si>
+  <si>
+    <t>2018-09-10</t>
+  </si>
+  <si>
+    <t>2018-07-26</t>
+  </si>
+  <si>
+    <t>2018-09-21</t>
+  </si>
+  <si>
+    <t>2018-09-27</t>
+  </si>
+  <si>
+    <t>2018-09-28</t>
+  </si>
+  <si>
+    <t>2018-10-09</t>
+  </si>
+  <si>
+    <t>2018-10-10</t>
+  </si>
+  <si>
+    <t>2018-10-11</t>
+  </si>
+  <si>
+    <t>2018-10-12</t>
+  </si>
+  <si>
+    <t>2018-10-15</t>
+  </si>
+  <si>
+    <t>2018-10-16</t>
+  </si>
+  <si>
+    <t>2018-10-18</t>
+  </si>
+  <si>
+    <t>2018-10-19</t>
+  </si>
+  <si>
+    <t>2019-02-20</t>
+  </si>
+  <si>
+    <t>2019-03-12</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2019-06-12</t>
+  </si>
+  <si>
+    <t>2019-07-15</t>
+  </si>
+  <si>
+    <t>2019-07-16</t>
+  </si>
+  <si>
+    <t>2019-05-28</t>
+  </si>
+  <si>
+    <t>2019-06-05</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>2019-07-22</t>
+  </si>
+  <si>
+    <t>2019-08-23</t>
+  </si>
+  <si>
+    <t>2019-09-02</t>
+  </si>
+  <si>
+    <t>2019-09-03</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-09-04</t>
+  </si>
+  <si>
+    <t>2019-08-06</t>
+  </si>
+  <si>
+    <t>2019-09-09</t>
+  </si>
+  <si>
+    <t>2019-09-10</t>
+  </si>
+  <si>
+    <t>2019-09-17</t>
+  </si>
+  <si>
+    <t>2019-09-18</t>
+  </si>
+  <si>
+    <t>2019-12-05</t>
+  </si>
+  <si>
+    <t>2020-02-03</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-04-15</t>
+  </si>
+  <si>
+    <t>2020-04-16</t>
+  </si>
+  <si>
+    <t>2020-04-17</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>2020-04-21</t>
+  </si>
+  <si>
+    <t>2020-04-22</t>
+  </si>
+  <si>
+    <t>2020-04-23</t>
+  </si>
+  <si>
+    <t>2020-03-26</t>
+  </si>
+  <si>
+    <t>2020-05-14</t>
+  </si>
+  <si>
+    <t>2020-06-11</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>2020-07-07</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>2020-07-13</t>
+  </si>
+  <si>
+    <t>2020-07-14</t>
+  </si>
+  <si>
+    <t>2020-07-16</t>
+  </si>
+  <si>
+    <t>2020-07-17</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>2020-07-22</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-24</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>2020-07-28</t>
+  </si>
+  <si>
+    <t>2020-07-29</t>
+  </si>
+  <si>
+    <t>2020-07-30</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>2020-08-04</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>2021-08-31</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>2021-10-15</t>
+  </si>
+  <si>
     <t>2021-10-25</t>
   </si>
   <si>
-    <t>2016-09-12</t>
-  </si>
-  <si>
-    <t>2016-10-17</t>
-  </si>
-  <si>
-    <t>2016-12-01</t>
-  </si>
-  <si>
-    <t>2016-12-06</t>
-  </si>
-  <si>
-    <t>2016-12-07</t>
-  </si>
-  <si>
-    <t>2016-12-08</t>
-  </si>
-  <si>
-    <t>2016-12-12</t>
-  </si>
-  <si>
-    <t>2017-03-13</t>
-  </si>
-  <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
-    <t>2017-04-28</t>
-  </si>
-  <si>
-    <t>2017-05-05</t>
-  </si>
-  <si>
-    <t>2017-06-12</t>
-  </si>
-  <si>
-    <t>2017-06-09</t>
-  </si>
-  <si>
-    <t>2017-08-17</t>
-  </si>
-  <si>
-    <t>2017-08-18</t>
-  </si>
-  <si>
-    <t>2017-08-03</t>
-  </si>
-  <si>
-    <t>2017-09-04</t>
-  </si>
-  <si>
-    <t>2017-09-06</t>
-  </si>
-  <si>
-    <t>2017-07-28</t>
-  </si>
-  <si>
-    <t>2017-09-08</t>
-  </si>
-  <si>
-    <t>2017-09-11</t>
-  </si>
-  <si>
-    <t>2017-09-13</t>
-  </si>
-  <si>
-    <t>2017-09-14</t>
-  </si>
-  <si>
-    <t>2017-09-18</t>
-  </si>
-  <si>
-    <t>2017-07-19</t>
-  </si>
-  <si>
-    <t>2017-08-29</t>
-  </si>
-  <si>
-    <t>2017-10-10</t>
-  </si>
-  <si>
-    <t>2017-10-17</t>
-  </si>
-  <si>
-    <t>2018-01-17</t>
-  </si>
-  <si>
-    <t>2018-03-01</t>
-  </si>
-  <si>
-    <t>2018-01-18</t>
-  </si>
-  <si>
-    <t>2018-04-23</t>
-  </si>
-  <si>
-    <t>2018-02-05</t>
-  </si>
-  <si>
-    <t>2018-04-24</t>
-  </si>
-  <si>
-    <t>2018-03-02</t>
-  </si>
-  <si>
-    <t>2018-03-13</t>
-  </si>
-  <si>
-    <t>2018-03-26</t>
-  </si>
-  <si>
-    <t>2018-05-14</t>
-  </si>
-  <si>
-    <t>2018-05-07</t>
-  </si>
-  <si>
-    <t>2018-05-17</t>
-  </si>
-  <si>
-    <t>2018-05-18</t>
-  </si>
-  <si>
-    <t>2018-05-04</t>
-  </si>
-  <si>
-    <t>2018-05-21</t>
-  </si>
-  <si>
-    <t>2018-05-24</t>
-  </si>
-  <si>
-    <t>2018-05-03</t>
-  </si>
-  <si>
-    <t>2018-05-25</t>
-  </si>
-  <si>
-    <t>2018-05-31</t>
-  </si>
-  <si>
-    <t>2018-05-29</t>
-  </si>
-  <si>
-    <t>2018-06-13</t>
-  </si>
-  <si>
-    <t>2018-06-12</t>
-  </si>
-  <si>
-    <t>2018-06-20</t>
-  </si>
-  <si>
-    <t>2018-07-10</t>
-  </si>
-  <si>
-    <t>2018-08-23</t>
-  </si>
-  <si>
-    <t>2018-08-27</t>
-  </si>
-  <si>
-    <t>2018-08-28</t>
-  </si>
-  <si>
-    <t>2018-08-29</t>
-  </si>
-  <si>
-    <t>2018-08-30</t>
-  </si>
-  <si>
-    <t>2018-09-04</t>
-  </si>
-  <si>
-    <t>2018-09-10</t>
-  </si>
-  <si>
-    <t>2018-07-26</t>
-  </si>
-  <si>
-    <t>2018-09-21</t>
-  </si>
-  <si>
-    <t>2018-09-27</t>
-  </si>
-  <si>
-    <t>2018-09-28</t>
-  </si>
-  <si>
-    <t>2018-10-09</t>
-  </si>
-  <si>
-    <t>2018-10-10</t>
-  </si>
-  <si>
-    <t>2018-10-11</t>
-  </si>
-  <si>
-    <t>2018-10-12</t>
-  </si>
-  <si>
-    <t>2018-10-15</t>
-  </si>
-  <si>
-    <t>2018-10-16</t>
-  </si>
-  <si>
-    <t>2018-10-18</t>
-  </si>
-  <si>
-    <t>2018-10-19</t>
-  </si>
-  <si>
-    <t>2019-02-20</t>
-  </si>
-  <si>
-    <t>2019-03-12</t>
-  </si>
-  <si>
-    <t>2019-05-09</t>
-  </si>
-  <si>
-    <t>2019-06-12</t>
-  </si>
-  <si>
-    <t>2019-07-15</t>
-  </si>
-  <si>
-    <t>2019-07-16</t>
-  </si>
-  <si>
-    <t>2019-05-28</t>
-  </si>
-  <si>
-    <t>2019-06-05</t>
-  </si>
-  <si>
-    <t>2019-06-25</t>
-  </si>
-  <si>
-    <t>2019-07-22</t>
-  </si>
-  <si>
-    <t>2019-08-23</t>
-  </si>
-  <si>
-    <t>2019-09-02</t>
-  </si>
-  <si>
-    <t>2019-09-03</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-09-04</t>
-  </si>
-  <si>
-    <t>2019-08-06</t>
-  </si>
-  <si>
-    <t>2019-09-09</t>
-  </si>
-  <si>
-    <t>2019-09-10</t>
-  </si>
-  <si>
-    <t>2019-09-17</t>
-  </si>
-  <si>
-    <t>2019-09-18</t>
-  </si>
-  <si>
-    <t>2019-12-05</t>
-  </si>
-  <si>
-    <t>2020-02-03</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-04-15</t>
-  </si>
-  <si>
-    <t>2020-04-16</t>
-  </si>
-  <si>
-    <t>2020-04-17</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>2020-04-21</t>
-  </si>
-  <si>
-    <t>2020-04-22</t>
-  </si>
-  <si>
-    <t>2020-04-23</t>
-  </si>
-  <si>
-    <t>2020-03-26</t>
-  </si>
-  <si>
-    <t>2020-05-14</t>
-  </si>
-  <si>
-    <t>2020-06-11</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>2020-07-07</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>2020-07-13</t>
-  </si>
-  <si>
-    <t>2020-07-14</t>
-  </si>
-  <si>
-    <t>2020-07-16</t>
-  </si>
-  <si>
-    <t>2020-07-17</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>2020-07-22</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-24</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>2020-07-28</t>
-  </si>
-  <si>
-    <t>2020-07-29</t>
-  </si>
-  <si>
-    <t>2020-07-30</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>2020-08-04</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>2021-08-31</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>2021-10-15</t>
-  </si>
-  <si>
-    <t>2021-10-27</t>
+    <t>2021-10-28</t>
   </si>
   <si>
     <t>2016-07-29</t>
@@ -1274,6 +1277,15 @@
   </si>
   <si>
     <t>2021-10-11</t>
+  </si>
+  <si>
+    <t>2021-10-18</t>
+  </si>
+  <si>
+    <t>2021-10-19</t>
+  </si>
+  <si>
+    <t>2021-10-21</t>
   </si>
 </sst>
 </file>
@@ -1631,7 +1643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P806"/>
+  <dimension ref="A1:P813"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1728,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1778,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1828,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1878,7 +1890,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1928,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2178,7 +2190,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2228,7 +2240,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2278,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2328,7 +2340,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2378,7 +2390,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2428,7 +2440,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2478,7 +2490,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2528,7 +2540,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2578,7 +2590,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2628,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2678,7 +2690,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2728,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2778,7 +2790,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2828,7 +2840,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2878,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2928,7 +2940,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2978,7 +2990,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3028,7 +3040,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3078,7 +3090,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3128,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3178,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3228,7 +3240,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3278,7 +3290,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3328,7 +3340,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3378,7 +3390,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3428,7 +3440,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3478,7 +3490,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3528,7 +3540,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3578,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3628,7 +3640,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3678,7 +3690,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3728,7 +3740,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3778,7 +3790,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3828,7 +3840,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3878,7 +3890,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3928,7 +3940,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3978,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4028,7 +4040,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4078,7 +4090,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4128,7 +4140,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4178,7 +4190,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4228,7 +4240,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4278,7 +4290,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4328,7 +4340,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4378,7 +4390,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4428,7 +4440,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4478,7 +4490,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4528,7 +4540,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4578,7 +4590,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4628,7 +4640,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4978,7 +4990,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5028,7 +5040,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5078,7 +5090,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5128,7 +5140,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5178,7 +5190,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5528,7 +5540,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5578,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5628,7 +5640,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5678,7 +5690,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5728,7 +5740,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5778,7 +5790,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5828,7 +5840,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5878,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5928,7 +5940,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5978,7 +5990,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6028,7 +6040,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6078,7 +6090,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6128,7 +6140,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6178,7 +6190,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6228,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6278,7 +6290,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6328,7 +6340,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6378,7 +6390,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6428,7 +6440,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6478,7 +6490,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6528,7 +6540,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6578,7 +6590,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6628,7 +6640,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6678,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6728,7 +6740,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6778,7 +6790,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6828,7 +6840,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6878,7 +6890,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6928,7 +6940,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6978,7 +6990,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7028,7 +7040,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7078,7 +7090,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7128,7 +7140,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7178,7 +7190,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7228,7 +7240,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7278,7 +7290,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7328,7 +7340,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7378,7 +7390,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7428,7 +7440,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7478,7 +7490,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7528,7 +7540,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7578,7 +7590,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7628,7 +7640,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7678,7 +7690,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7728,7 +7740,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7778,7 +7790,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7828,7 +7840,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8228,7 +8240,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8278,7 +8290,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8328,7 +8340,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8378,7 +8390,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8428,7 +8440,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8478,7 +8490,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8528,7 +8540,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8578,7 +8590,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9428,7 +9440,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9478,7 +9490,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9528,7 +9540,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9578,7 +9590,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9628,7 +9640,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9678,7 +9690,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9728,7 +9740,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9778,7 +9790,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10628,7 +10640,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10678,7 +10690,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10728,7 +10740,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10778,7 +10790,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10828,7 +10840,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10878,7 +10890,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10928,7 +10940,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10978,7 +10990,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11428,7 +11440,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11478,7 +11490,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11528,7 +11540,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11578,7 +11590,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11628,7 +11640,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11678,7 +11690,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11728,7 +11740,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11778,7 +11790,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12178,7 +12190,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12228,7 +12240,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12278,7 +12290,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12328,7 +12340,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12378,7 +12390,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12428,7 +12440,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12478,7 +12490,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12528,7 +12540,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12578,7 +12590,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12628,7 +12640,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12678,7 +12690,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12728,7 +12740,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12778,7 +12790,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12828,7 +12840,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12878,7 +12890,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12928,7 +12940,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12978,7 +12990,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13028,7 +13040,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13078,7 +13090,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13128,7 +13140,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13178,7 +13190,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13228,7 +13240,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13278,7 +13290,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13328,7 +13340,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13378,7 +13390,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13428,7 +13440,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13478,7 +13490,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13528,7 +13540,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13578,7 +13590,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13628,7 +13640,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13678,7 +13690,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13728,7 +13740,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13778,7 +13790,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13828,7 +13840,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14178,7 +14190,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14228,7 +14240,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14278,7 +14290,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14328,7 +14340,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14378,7 +14390,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14428,7 +14440,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14478,7 +14490,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14528,7 +14540,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14578,7 +14590,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14628,7 +14640,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14678,7 +14690,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14728,7 +14740,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14778,7 +14790,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14828,7 +14840,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14878,7 +14890,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14928,7 +14940,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14978,7 +14990,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15028,7 +15040,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -16178,7 +16190,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16228,7 +16240,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16278,7 +16290,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16328,7 +16340,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16378,7 +16390,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16428,7 +16440,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16478,7 +16490,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16528,7 +16540,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16578,7 +16590,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16628,7 +16640,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -18278,7 +18290,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18328,7 +18340,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18378,7 +18390,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18428,7 +18440,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18478,7 +18490,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18528,7 +18540,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18728,7 +18740,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18778,7 +18790,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19128,7 +19140,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19178,7 +19190,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19228,7 +19240,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19728,7 +19740,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19778,7 +19790,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19828,7 +19840,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20578,7 +20590,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20628,7 +20640,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20678,7 +20690,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20728,7 +20740,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20778,7 +20790,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20828,7 +20840,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20878,7 +20890,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20928,7 +20940,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20978,7 +20990,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21028,7 +21040,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21078,7 +21090,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21128,7 +21140,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21178,7 +21190,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21228,7 +21240,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21278,7 +21290,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21328,7 +21340,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21378,7 +21390,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21428,7 +21440,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21478,7 +21490,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21528,7 +21540,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21578,7 +21590,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21628,7 +21640,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21678,7 +21690,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21728,7 +21740,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21778,7 +21790,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21828,7 +21840,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21878,7 +21890,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21928,7 +21940,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21978,7 +21990,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22028,7 +22040,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22078,7 +22090,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22128,7 +22140,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22178,7 +22190,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22228,7 +22240,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22278,7 +22290,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22328,7 +22340,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22378,7 +22390,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22878,7 +22890,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22928,7 +22940,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22978,7 +22990,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23028,7 +23040,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23078,7 +23090,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23128,7 +23140,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23178,7 +23190,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23228,7 +23240,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23278,7 +23290,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23328,7 +23340,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23378,7 +23390,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23428,7 +23440,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23478,7 +23490,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23528,7 +23540,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23578,7 +23590,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23628,7 +23640,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23678,7 +23690,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23728,7 +23740,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23778,7 +23790,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23828,7 +23840,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23878,7 +23890,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23928,7 +23940,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23978,7 +23990,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24028,7 +24040,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24078,7 +24090,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24128,7 +24140,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24178,7 +24190,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24228,7 +24240,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24278,7 +24290,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24328,7 +24340,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24378,7 +24390,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24428,7 +24440,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24478,7 +24490,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24528,7 +24540,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24578,7 +24590,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24628,7 +24640,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24678,7 +24690,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24728,7 +24740,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24778,7 +24790,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24828,7 +24840,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25778,7 +25790,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25828,7 +25840,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25878,7 +25890,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25928,7 +25940,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25978,7 +25990,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26028,7 +26040,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26078,7 +26090,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26128,7 +26140,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26178,7 +26190,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26228,7 +26240,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26278,7 +26290,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26328,7 +26340,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26378,7 +26390,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26428,7 +26440,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26478,7 +26490,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26528,7 +26540,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26578,7 +26590,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26628,7 +26640,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26678,7 +26690,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26728,7 +26740,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26778,7 +26790,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26828,7 +26840,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26878,7 +26890,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26928,7 +26940,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26978,7 +26990,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27028,7 +27040,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27078,7 +27090,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27128,7 +27140,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27178,7 +27190,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27228,7 +27240,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27278,7 +27290,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27328,7 +27340,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27378,7 +27390,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27428,7 +27440,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27478,7 +27490,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27528,7 +27540,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27578,7 +27590,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27628,7 +27640,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27678,7 +27690,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27728,7 +27740,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27778,7 +27790,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27828,7 +27840,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27878,7 +27890,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27928,7 +27940,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27978,7 +27990,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28028,7 +28040,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28078,7 +28090,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28128,7 +28140,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28178,7 +28190,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28228,7 +28240,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28278,7 +28290,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28328,7 +28340,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28828,7 +28840,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28878,7 +28890,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28928,7 +28940,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28978,7 +28990,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29028,7 +29040,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29078,7 +29090,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29128,7 +29140,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29178,7 +29190,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29228,7 +29240,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29278,7 +29290,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29328,7 +29340,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29378,7 +29390,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29428,7 +29440,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29478,7 +29490,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29528,7 +29540,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29578,7 +29590,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29628,7 +29640,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29678,7 +29690,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29728,7 +29740,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29778,7 +29790,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29828,7 +29840,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29878,7 +29890,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29928,7 +29940,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29978,7 +29990,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30028,7 +30040,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30078,7 +30090,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30128,7 +30140,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30178,7 +30190,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30228,7 +30240,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30278,7 +30290,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30328,7 +30340,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30378,7 +30390,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30428,7 +30440,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30478,7 +30490,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30528,7 +30540,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30578,7 +30590,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30628,7 +30640,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30678,7 +30690,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30728,7 +30740,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30778,7 +30790,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30828,7 +30840,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30878,7 +30890,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30928,7 +30940,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31378,7 +31390,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31428,7 +31440,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31478,7 +31490,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31528,7 +31540,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31578,7 +31590,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31628,7 +31640,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31678,7 +31690,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31728,7 +31740,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31778,7 +31790,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31828,7 +31840,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31878,7 +31890,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -31928,7 +31940,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31978,7 +31990,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32028,7 +32040,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32078,7 +32090,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32128,7 +32140,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32878,7 +32890,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32928,7 +32940,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32978,7 +32990,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33028,7 +33040,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33078,7 +33090,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33128,7 +33140,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33178,7 +33190,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33228,7 +33240,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33278,7 +33290,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33328,7 +33340,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33378,7 +33390,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33428,7 +33440,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33478,7 +33490,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33528,7 +33540,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33878,7 +33890,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33928,7 +33940,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33978,7 +33990,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34028,7 +34040,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34078,7 +34090,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34128,7 +34140,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34428,7 +34440,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34478,7 +34490,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34528,7 +34540,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34578,7 +34590,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34628,7 +34640,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34678,7 +34690,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34728,7 +34740,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34778,7 +34790,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34828,7 +34840,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34878,7 +34890,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34928,7 +34940,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -34978,7 +34990,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35028,7 +35040,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35078,7 +35090,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35128,7 +35140,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35178,7 +35190,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35228,7 +35240,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35278,7 +35290,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35328,7 +35340,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35678,7 +35690,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35728,7 +35740,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35778,7 +35790,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35828,7 +35840,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35878,7 +35890,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35928,7 +35940,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35978,7 +35990,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36028,7 +36040,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36078,7 +36090,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36128,7 +36140,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36178,7 +36190,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36228,7 +36240,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36278,7 +36290,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36328,7 +36340,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36378,7 +36390,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36428,7 +36440,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36478,7 +36490,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36528,7 +36540,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36578,7 +36590,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36628,7 +36640,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36678,7 +36690,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36728,7 +36740,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36778,7 +36790,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36828,7 +36840,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36878,7 +36890,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36928,7 +36940,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36978,7 +36990,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37028,7 +37040,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37078,7 +37090,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37128,7 +37140,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37178,7 +37190,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37228,7 +37240,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37628,7 +37640,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37678,7 +37690,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37728,7 +37740,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37778,7 +37790,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37828,7 +37840,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -37878,7 +37890,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -37928,7 +37940,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38578,7 +38590,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38628,7 +38640,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38678,7 +38690,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38728,7 +38740,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38778,7 +38790,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38828,7 +38840,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38878,7 +38890,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38928,7 +38940,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -38978,7 +38990,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39028,7 +39040,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39078,7 +39090,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39128,7 +39140,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39178,7 +39190,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39228,7 +39240,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39278,7 +39290,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39328,7 +39340,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39342,7 +39354,7 @@
         <v>4.163922260811965</v>
       </c>
       <c r="D755" t="s">
-        <v>191</v>
+        <v>324</v>
       </c>
       <c r="E755">
         <v>4.865973846683474</v>
@@ -39378,7 +39390,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39592,7 +39604,7 @@
         <v>3.630216793142413</v>
       </c>
       <c r="D760" t="s">
-        <v>191</v>
+        <v>324</v>
       </c>
       <c r="E760">
         <v>4.330137818264742</v>
@@ -39678,7 +39690,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -39728,7 +39740,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -39778,7 +39790,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -39828,7 +39840,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -39842,7 +39854,7 @@
         <v>3.46446660639775</v>
       </c>
       <c r="D765" t="s">
-        <v>191</v>
+        <v>324</v>
       </c>
       <c r="E765">
         <v>4.163725954127884</v>
@@ -39878,7 +39890,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -39928,7 +39940,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -39978,7 +39990,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40028,7 +40040,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40078,7 +40090,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40092,7 +40104,7 @@
         <v>3.280960550216626</v>
       </c>
       <c r="D770" t="s">
-        <v>191</v>
+        <v>324</v>
       </c>
       <c r="E770">
         <v>3.979487338840251</v>
@@ -40128,7 +40140,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40286,43 +40298,43 @@
         <v>3</v>
       </c>
       <c r="B774" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C774">
-        <v>3.130684302733364</v>
+        <v>4.05172086101134</v>
       </c>
       <c r="D774" t="s">
-        <v>191</v>
+        <v>323</v>
       </c>
       <c r="E774">
-        <v>3.828611186177412</v>
+        <v>3.383793977567297</v>
       </c>
       <c r="F774">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G774">
-        <v>0.05426931569726664</v>
+        <v>0.05508827913898866</v>
       </c>
       <c r="H774">
-        <v>0.05517138881382259</v>
+        <v>0.0542162060224327</v>
       </c>
       <c r="I774">
-        <v>0.6979268834440475</v>
+        <v>0.6679268834440428</v>
       </c>
       <c r="J774">
         <v>1.020731165559546</v>
       </c>
       <c r="K774">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="L774">
-        <v>28.7</v>
+        <v>29.57</v>
       </c>
       <c r="M774">
-        <v>25.15</v>
+        <v>24.9</v>
       </c>
       <c r="N774">
-        <v>29.5</v>
+        <v>28.8</v>
       </c>
       <c r="O774">
         <v>1</v>
@@ -40333,113 +40345,113 @@
     </row>
     <row r="775" spans="1:16">
       <c r="A775" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B775" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C775">
-        <v>3.249078590284071</v>
+        <v>3.130684302733364</v>
       </c>
       <c r="D775" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E775">
-        <v>3.690186168992298</v>
+        <v>3.828611186177412</v>
       </c>
       <c r="F775">
         <v>1</v>
       </c>
       <c r="G775">
-        <v>0.05373092140971593</v>
+        <v>0.05426931569726664</v>
       </c>
       <c r="H775">
-        <v>0.0526298138310077</v>
+        <v>0.05517138881382259</v>
       </c>
       <c r="I775">
-        <v>0.4411075787082268</v>
+        <v>0.6979268834440475</v>
       </c>
       <c r="J775">
-        <v>1.028143438277634</v>
+        <v>1.020731165559546</v>
       </c>
       <c r="K775">
-        <v>24.55</v>
+        <v>25.05</v>
       </c>
       <c r="L775">
-        <v>28.49</v>
+        <v>28.7</v>
       </c>
       <c r="M775">
-        <v>23.8</v>
+        <v>25.15</v>
       </c>
       <c r="N775">
-        <v>28.16</v>
+        <v>29.5</v>
       </c>
       <c r="O775">
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>410</v>
+        <v>319</v>
       </c>
     </row>
     <row r="776" spans="1:16">
       <c r="A776" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B776" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C776">
-        <v>4.196922435356054</v>
+        <v>3.249078590284071</v>
       </c>
       <c r="D776" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E776">
-        <v>3.338479403872764</v>
+        <v>3.690186168992298</v>
       </c>
       <c r="F776">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G776">
-        <v>0.05118307756464395</v>
+        <v>0.05373092140971593</v>
       </c>
       <c r="H776">
-        <v>0.05094152059612723</v>
+        <v>0.0526298138310077</v>
       </c>
       <c r="I776">
-        <v>0.85844303148329</v>
+        <v>0.4411075787082268</v>
       </c>
       <c r="J776">
         <v>1.028143438277634</v>
       </c>
       <c r="K776">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L776">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M776">
-        <v>23.15</v>
+        <v>23.8</v>
       </c>
       <c r="N776">
-        <v>27.14</v>
+        <v>28.16</v>
       </c>
       <c r="O776">
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="777" spans="1:16">
       <c r="A777" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B777" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C777">
-        <v>4.04410809152829</v>
+        <v>4.196922435356054</v>
       </c>
       <c r="D777" t="s">
         <v>322</v>
@@ -40451,22 +40463,22 @@
         <v>-1</v>
       </c>
       <c r="G777">
-        <v>0.05123589190847171</v>
+        <v>0.05118307756464395</v>
       </c>
       <c r="H777">
         <v>0.05094152059612723</v>
       </c>
       <c r="I777">
-        <v>0.7056286876555262</v>
+        <v>0.85844303148329</v>
       </c>
       <c r="J777">
         <v>1.028143438277634</v>
       </c>
       <c r="K777">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L777">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M777">
         <v>23.15</v>
@@ -40478,101 +40490,101 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="778" spans="1:16">
       <c r="A778" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B778" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C778">
-        <v>2.945006871145257</v>
+        <v>4.04410809152829</v>
       </c>
       <c r="D778" t="s">
-        <v>191</v>
+        <v>322</v>
       </c>
       <c r="E778">
-        <v>3.642192527317494</v>
+        <v>3.338479403872764</v>
       </c>
       <c r="F778">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G778">
-        <v>0.05445499312885474</v>
+        <v>0.05123589190847171</v>
       </c>
       <c r="H778">
-        <v>0.05535780747268251</v>
+        <v>0.05094152059612723</v>
       </c>
       <c r="I778">
-        <v>0.6971856561722376</v>
+        <v>0.7056286876555262</v>
       </c>
       <c r="J778">
         <v>1.028143438277634</v>
       </c>
       <c r="K778">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L778">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M778">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N778">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O778">
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="779" spans="1:16">
       <c r="A779" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B779" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C779">
-        <v>3.14672422434397</v>
+        <v>2.945006871145257</v>
       </c>
       <c r="D779" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E779">
-        <v>3.590958718508617</v>
+        <v>3.642192527317494</v>
       </c>
       <c r="F779">
         <v>1</v>
       </c>
       <c r="G779">
-        <v>0.05383327577565603</v>
+        <v>0.05445499312885474</v>
       </c>
       <c r="H779">
-        <v>0.05272904128149138</v>
+        <v>0.05535780747268251</v>
       </c>
       <c r="I779">
-        <v>0.4442344941646468</v>
+        <v>0.6971856561722376</v>
       </c>
       <c r="J779">
-        <v>1.032312658886193</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K779">
-        <v>24.55</v>
+        <v>25.05</v>
       </c>
       <c r="L779">
-        <v>28.49</v>
+        <v>28.7</v>
       </c>
       <c r="M779">
-        <v>23.8</v>
+        <v>25.15</v>
       </c>
       <c r="N779">
-        <v>28.16</v>
+        <v>29.5</v>
       </c>
       <c r="O779">
         <v>1</v>
@@ -40583,63 +40595,63 @@
     </row>
     <row r="780" spans="1:16">
       <c r="A780" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B780" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C780">
-        <v>4.101655744450497</v>
+        <v>3.14672422434397</v>
       </c>
       <c r="D780" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E780">
-        <v>3.241961946784642</v>
+        <v>3.590958718508617</v>
       </c>
       <c r="F780">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G780">
-        <v>0.05127834425554951</v>
+        <v>0.05383327577565603</v>
       </c>
       <c r="H780">
-        <v>0.05103803805321536</v>
+        <v>0.05272904128149138</v>
       </c>
       <c r="I780">
-        <v>0.8596937976658552</v>
+        <v>0.4442344941646468</v>
       </c>
       <c r="J780">
         <v>1.032312658886193</v>
       </c>
       <c r="K780">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L780">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M780">
-        <v>23.15</v>
+        <v>23.8</v>
       </c>
       <c r="N780">
-        <v>27.14</v>
+        <v>28.16</v>
       </c>
       <c r="O780">
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="781" spans="1:16">
       <c r="A781" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B781" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C781">
-        <v>3.948424478561879</v>
+        <v>4.101655744450497</v>
       </c>
       <c r="D781" t="s">
         <v>322</v>
@@ -40651,22 +40663,22 @@
         <v>-1</v>
       </c>
       <c r="G781">
-        <v>0.05133157552143813</v>
+        <v>0.05127834425554951</v>
       </c>
       <c r="H781">
         <v>0.05103803805321536</v>
       </c>
       <c r="I781">
-        <v>0.7064625317772375</v>
+        <v>0.8596937976658552</v>
       </c>
       <c r="J781">
         <v>1.032312658886193</v>
       </c>
       <c r="K781">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L781">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M781">
         <v>23.15</v>
@@ -40678,101 +40690,101 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="782" spans="1:16">
       <c r="A782" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B782" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C782">
-        <v>2.840567894900875</v>
+        <v>3.948424478561879</v>
       </c>
       <c r="D782" t="s">
-        <v>191</v>
+        <v>322</v>
       </c>
       <c r="E782">
-        <v>3.537336629012259</v>
+        <v>3.241961946784642</v>
       </c>
       <c r="F782">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G782">
-        <v>0.05455943210509912</v>
+        <v>0.05133157552143813</v>
       </c>
       <c r="H782">
-        <v>0.05546266337098774</v>
+        <v>0.05103803805321536</v>
       </c>
       <c r="I782">
-        <v>0.6967687341113837</v>
+        <v>0.7064625317772375</v>
       </c>
       <c r="J782">
         <v>1.032312658886193</v>
       </c>
       <c r="K782">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L782">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M782">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N782">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O782">
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="783" spans="1:16">
       <c r="A783" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B783" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C783">
-        <v>3.047718597071611</v>
+        <v>2.840567894900875</v>
       </c>
       <c r="D783" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E783">
-        <v>3.494977703067388</v>
+        <v>3.537336629012259</v>
       </c>
       <c r="F783">
         <v>1</v>
       </c>
       <c r="G783">
-        <v>0.05393228140292838</v>
+        <v>0.05455943210509912</v>
       </c>
       <c r="H783">
-        <v>0.05282502229693262</v>
+        <v>0.05546266337098774</v>
       </c>
       <c r="I783">
-        <v>0.4472591059957765</v>
+        <v>0.6967687341113837</v>
       </c>
       <c r="J783">
-        <v>1.036345474661034</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K783">
-        <v>24.55</v>
+        <v>25.05</v>
       </c>
       <c r="L783">
-        <v>28.49</v>
+        <v>28.7</v>
       </c>
       <c r="M783">
-        <v>23.8</v>
+        <v>25.15</v>
       </c>
       <c r="N783">
-        <v>28.16</v>
+        <v>29.5</v>
       </c>
       <c r="O783">
         <v>1</v>
@@ -40783,63 +40795,63 @@
     </row>
     <row r="784" spans="1:16">
       <c r="A784" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B784" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C784">
-        <v>4.009505903995372</v>
+        <v>3.047718597071611</v>
       </c>
       <c r="D784" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E784">
-        <v>3.148602261597063</v>
+        <v>3.494977703067388</v>
       </c>
       <c r="F784">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G784">
-        <v>0.05137049409600464</v>
+        <v>0.05393228140292838</v>
       </c>
       <c r="H784">
-        <v>0.05113139773840294</v>
+        <v>0.05282502229693262</v>
       </c>
       <c r="I784">
-        <v>0.8609036423983092</v>
+        <v>0.4472591059957765</v>
       </c>
       <c r="J784">
         <v>1.036345474661034</v>
       </c>
       <c r="K784">
-        <v>22.85</v>
+        <v>24.55</v>
       </c>
       <c r="L784">
-        <v>27.69</v>
+        <v>28.49</v>
       </c>
       <c r="M784">
-        <v>23.15</v>
+        <v>23.8</v>
       </c>
       <c r="N784">
-        <v>27.14</v>
+        <v>28.16</v>
       </c>
       <c r="O784">
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="785" spans="1:16">
       <c r="A785" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B785" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C785">
-        <v>3.855871356529267</v>
+        <v>4.009505903995372</v>
       </c>
       <c r="D785" t="s">
         <v>322</v>
@@ -40851,22 +40863,22 @@
         <v>-1</v>
       </c>
       <c r="G785">
-        <v>0.05142412864347074</v>
+        <v>0.05137049409600464</v>
       </c>
       <c r="H785">
         <v>0.05113139773840294</v>
       </c>
       <c r="I785">
-        <v>0.7072690949322045</v>
+        <v>0.8609036423983092</v>
       </c>
       <c r="J785">
         <v>1.036345474661034</v>
       </c>
       <c r="K785">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L785">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M785">
         <v>23.15</v>
@@ -40878,118 +40890,118 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="786" spans="1:16">
       <c r="A786" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B786" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C786">
-        <v>2.739545859741096</v>
+        <v>3.855871356529267</v>
       </c>
       <c r="D786" t="s">
-        <v>191</v>
+        <v>322</v>
       </c>
       <c r="E786">
-        <v>3.435911312274992</v>
+        <v>3.148602261597063</v>
       </c>
       <c r="F786">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G786">
-        <v>0.05466045414025891</v>
+        <v>0.05142412864347074</v>
       </c>
       <c r="H786">
-        <v>0.05556408868772501</v>
+        <v>0.05113139773840294</v>
       </c>
       <c r="I786">
-        <v>0.6963654525338967</v>
+        <v>0.7072690949322045</v>
       </c>
       <c r="J786">
         <v>1.036345474661034</v>
       </c>
       <c r="K786">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L786">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M786">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N786">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O786">
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="787" spans="1:16">
       <c r="A787" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B787" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C787">
-        <v>3.923892030831919</v>
+        <v>2.739545859741096</v>
       </c>
       <c r="D787" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E787">
-        <v>3.06186435508792</v>
+        <v>3.435911312274992</v>
       </c>
       <c r="F787">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G787">
-        <v>0.05145610796916809</v>
+        <v>0.05466045414025891</v>
       </c>
       <c r="H787">
-        <v>0.05121813564491208</v>
+        <v>0.05556408868772501</v>
       </c>
       <c r="I787">
-        <v>0.8620276757439989</v>
+        <v>0.6963654525338967</v>
       </c>
       <c r="J787">
-        <v>1.040092252480004</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K787">
-        <v>22.85</v>
+        <v>25.05</v>
       </c>
       <c r="L787">
-        <v>27.69</v>
+        <v>28.7</v>
       </c>
       <c r="M787">
-        <v>23.15</v>
+        <v>25.15</v>
       </c>
       <c r="N787">
-        <v>27.14</v>
+        <v>29.5</v>
       </c>
       <c r="O787">
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>186</v>
+        <v>413</v>
       </c>
     </row>
     <row r="788" spans="1:16">
       <c r="A788" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B788" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C788">
-        <v>3.769882805583919</v>
+        <v>3.923892030831919</v>
       </c>
       <c r="D788" t="s">
         <v>322</v>
@@ -41001,22 +41013,22 @@
         <v>-1</v>
       </c>
       <c r="G788">
-        <v>0.05151011719441608</v>
+        <v>0.05145610796916809</v>
       </c>
       <c r="H788">
         <v>0.05121813564491208</v>
       </c>
       <c r="I788">
-        <v>0.7080184504959988</v>
+        <v>0.8620276757439989</v>
       </c>
       <c r="J788">
         <v>1.040092252480004</v>
       </c>
       <c r="K788">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L788">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M788">
         <v>23.15</v>
@@ -41033,46 +41045,46 @@
     </row>
     <row r="789" spans="1:16">
       <c r="A789" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B789" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C789">
-        <v>2.645689075375909</v>
+        <v>3.769882805583919</v>
       </c>
       <c r="D789" t="s">
-        <v>191</v>
+        <v>322</v>
       </c>
       <c r="E789">
-        <v>3.34167985012791</v>
+        <v>3.06186435508792</v>
       </c>
       <c r="F789">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G789">
-        <v>0.05475431092462409</v>
+        <v>0.05151011719441608</v>
       </c>
       <c r="H789">
-        <v>0.05565832014987209</v>
+        <v>0.05121813564491208</v>
       </c>
       <c r="I789">
-        <v>0.6959907747520013</v>
+        <v>0.7080184504959988</v>
       </c>
       <c r="J789">
         <v>1.040092252480004</v>
       </c>
       <c r="K789">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L789">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M789">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N789">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O789">
         <v>1</v>
@@ -41083,63 +41095,63 @@
     </row>
     <row r="790" spans="1:16">
       <c r="A790" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B790" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C790">
-        <v>3.103333239057651</v>
+        <v>2.645689075375909</v>
       </c>
       <c r="D790" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E790">
-        <v>2.230532362546374</v>
+        <v>3.34167985012791</v>
       </c>
       <c r="F790">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G790">
-        <v>0.05227666676094235</v>
+        <v>0.05475431092462409</v>
       </c>
       <c r="H790">
-        <v>0.05204946763745363</v>
+        <v>0.05565832014987209</v>
       </c>
       <c r="I790">
-        <v>0.8728008765112776</v>
+        <v>0.6959907747520013</v>
       </c>
       <c r="J790">
-        <v>1.07600292170426</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K790">
-        <v>22.85</v>
+        <v>25.05</v>
       </c>
       <c r="L790">
-        <v>27.69</v>
+        <v>28.7</v>
       </c>
       <c r="M790">
-        <v>23.15</v>
+        <v>25.15</v>
       </c>
       <c r="N790">
-        <v>27.14</v>
+        <v>29.5</v>
       </c>
       <c r="O790">
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>413</v>
+        <v>186</v>
       </c>
     </row>
     <row r="791" spans="1:16">
       <c r="A791" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B791" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C791">
-        <v>2.945732946887226</v>
+        <v>3.103333239057651</v>
       </c>
       <c r="D791" t="s">
         <v>322</v>
@@ -41151,22 +41163,22 @@
         <v>-1</v>
       </c>
       <c r="G791">
-        <v>0.05233426705311277</v>
+        <v>0.05227666676094235</v>
       </c>
       <c r="H791">
         <v>0.05204946763745363</v>
       </c>
       <c r="I791">
-        <v>0.7152005843408524</v>
+        <v>0.8728008765112776</v>
       </c>
       <c r="J791">
         <v>1.07600292170426</v>
       </c>
       <c r="K791">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L791">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M791">
         <v>23.15</v>
@@ -41178,151 +41190,151 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="792" spans="1:16">
       <c r="A792" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B792" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C792">
-        <v>1.746126811308276</v>
+        <v>2.945732946887226</v>
       </c>
       <c r="D792" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E792">
-        <v>2.495127541734341</v>
+        <v>2.230532362546374</v>
       </c>
       <c r="F792">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G792">
-        <v>0.05565387318869172</v>
+        <v>0.05233426705311277</v>
       </c>
       <c r="H792">
-        <v>0.05586487245826566</v>
+        <v>0.05204946763745363</v>
       </c>
       <c r="I792">
-        <v>0.7490007304260651</v>
+        <v>0.7152005843408524</v>
       </c>
       <c r="J792">
         <v>1.07600292170426</v>
       </c>
       <c r="K792">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L792">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M792">
-        <v>24.8</v>
+        <v>23.15</v>
       </c>
       <c r="N792">
-        <v>29.18</v>
+        <v>27.14</v>
       </c>
       <c r="O792">
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="793" spans="1:16">
       <c r="A793" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B793" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C793">
-        <v>1.786358263523248</v>
+        <v>1.746126811308276</v>
       </c>
       <c r="D793" t="s">
-        <v>322</v>
+        <v>191</v>
       </c>
       <c r="E793">
-        <v>1.061054196102969</v>
+        <v>2.495127541734341</v>
       </c>
       <c r="F793">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G793">
-        <v>0.05349364173647676</v>
+        <v>0.05565387318869172</v>
       </c>
       <c r="H793">
-        <v>0.05321894580389703</v>
+        <v>0.05586487245826566</v>
       </c>
       <c r="I793">
-        <v>0.7253040674202786</v>
+        <v>0.7490007304260651</v>
       </c>
       <c r="J793">
-        <v>1.126520337101384</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K793">
-        <v>22.95</v>
+        <v>25.05</v>
       </c>
       <c r="L793">
-        <v>27.64</v>
+        <v>28.7</v>
       </c>
       <c r="M793">
-        <v>23.15</v>
+        <v>24.8</v>
       </c>
       <c r="N793">
-        <v>27.14</v>
+        <v>29.18</v>
       </c>
       <c r="O793">
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>321</v>
+        <v>414</v>
       </c>
     </row>
     <row r="794" spans="1:16">
       <c r="A794" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B794" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C794">
-        <v>0.4806655556103365</v>
+        <v>1.786358263523248</v>
       </c>
       <c r="D794" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E794">
-        <v>1.242295639885683</v>
+        <v>1.061054196102969</v>
       </c>
       <c r="F794">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G794">
-        <v>0.05691933444438967</v>
+        <v>0.05349364173647676</v>
       </c>
       <c r="H794">
-        <v>0.05711770436011432</v>
+        <v>0.05321894580389703</v>
       </c>
       <c r="I794">
-        <v>0.7616300842753461</v>
+        <v>0.7253040674202786</v>
       </c>
       <c r="J794">
         <v>1.126520337101384</v>
       </c>
       <c r="K794">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L794">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M794">
-        <v>24.8</v>
+        <v>23.15</v>
       </c>
       <c r="N794">
-        <v>29.18</v>
+        <v>27.14</v>
       </c>
       <c r="O794">
         <v>1</v>
@@ -41333,146 +41345,146 @@
     </row>
     <row r="795" spans="1:16">
       <c r="A795" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B795" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C795">
-        <v>1.347927144340538</v>
+        <v>0.4806655556103365</v>
       </c>
       <c r="D795" t="s">
-        <v>322</v>
+        <v>191</v>
       </c>
       <c r="E795">
-        <v>0.6188023264262945</v>
+        <v>1.242295639885683</v>
       </c>
       <c r="F795">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G795">
-        <v>0.05393207285565946</v>
+        <v>0.05691933444438967</v>
       </c>
       <c r="H795">
-        <v>0.05366119767357371</v>
+        <v>0.05711770436011432</v>
       </c>
       <c r="I795">
-        <v>0.7291248179142436</v>
+        <v>0.7616300842753461</v>
       </c>
       <c r="J795">
-        <v>1.145624089571218</v>
+        <v>1.126520337101384</v>
       </c>
       <c r="K795">
-        <v>22.95</v>
+        <v>25.05</v>
       </c>
       <c r="L795">
-        <v>27.64</v>
+        <v>28.7</v>
       </c>
       <c r="M795">
-        <v>23.15</v>
+        <v>24.8</v>
       </c>
       <c r="N795">
-        <v>27.14</v>
+        <v>29.18</v>
       </c>
       <c r="O795">
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>414</v>
+        <v>321</v>
       </c>
     </row>
     <row r="796" spans="1:16">
       <c r="A796" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B796" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C796">
-        <v>0.002116556240977729</v>
+        <v>1.347927144340538</v>
       </c>
       <c r="D796" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E796">
-        <v>0.7685225786337817</v>
+        <v>0.6188023264262945</v>
       </c>
       <c r="F796">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G796">
-        <v>0.05739788344375902</v>
+        <v>0.05393207285565946</v>
       </c>
       <c r="H796">
-        <v>0.05759147742136622</v>
+        <v>0.05366119767357371</v>
       </c>
       <c r="I796">
-        <v>0.766406022392804</v>
+        <v>0.7291248179142436</v>
       </c>
       <c r="J796">
         <v>1.145624089571218</v>
       </c>
       <c r="K796">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L796">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M796">
-        <v>24.8</v>
+        <v>23.15</v>
       </c>
       <c r="N796">
-        <v>29.18</v>
+        <v>27.14</v>
       </c>
       <c r="O796">
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="797" spans="1:16">
       <c r="A797" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B797" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C797">
-        <v>0.8331756972601632</v>
+        <v>0.002116556240977729</v>
       </c>
       <c r="D797" t="s">
-        <v>322</v>
+        <v>191</v>
       </c>
       <c r="E797">
-        <v>0.09956502795524358</v>
+        <v>0.7685225786337817</v>
       </c>
       <c r="F797">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G797">
-        <v>0.05444682430273984</v>
+        <v>0.05739788344375902</v>
       </c>
       <c r="H797">
-        <v>0.05418043497204476</v>
+        <v>0.05759147742136622</v>
       </c>
       <c r="I797">
-        <v>0.7336106693049196</v>
+        <v>0.766406022392804</v>
       </c>
       <c r="J797">
-        <v>1.168053346524612</v>
+        <v>1.145624089571218</v>
       </c>
       <c r="K797">
-        <v>22.95</v>
+        <v>25.05</v>
       </c>
       <c r="L797">
-        <v>27.64</v>
+        <v>28.7</v>
       </c>
       <c r="M797">
-        <v>23.15</v>
+        <v>24.8</v>
       </c>
       <c r="N797">
-        <v>27.14</v>
+        <v>29.18</v>
       </c>
       <c r="O797">
         <v>1</v>
@@ -41483,84 +41495,84 @@
     </row>
     <row r="798" spans="1:16">
       <c r="A798" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B798" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C798">
-        <v>-0.5597363304415239</v>
+        <v>0.8331756972601632</v>
       </c>
       <c r="D798" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E798">
-        <v>0.2122770061896304</v>
+        <v>0.09956502795524358</v>
       </c>
       <c r="F798">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G798">
-        <v>0.05795973633044153</v>
+        <v>0.05444682430273984</v>
       </c>
       <c r="H798">
-        <v>0.05814772299381037</v>
+        <v>0.05418043497204476</v>
       </c>
       <c r="I798">
-        <v>0.7720133366311543</v>
+        <v>0.7336106693049196</v>
       </c>
       <c r="J798">
         <v>1.168053346524612</v>
       </c>
       <c r="K798">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L798">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M798">
-        <v>24.8</v>
+        <v>23.15</v>
       </c>
       <c r="N798">
-        <v>29.18</v>
+        <v>27.14</v>
       </c>
       <c r="O798">
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="799" spans="1:16">
       <c r="A799" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B799" t="s">
         <v>190</v>
       </c>
       <c r="C799">
-        <v>-0.8369803833445317</v>
+        <v>-0.5597363304415239</v>
       </c>
       <c r="D799" t="s">
-        <v>324</v>
+        <v>191</v>
       </c>
       <c r="E799">
-        <v>-0.06220013999777763</v>
+        <v>0.2122770061896304</v>
       </c>
       <c r="F799">
         <v>1</v>
       </c>
       <c r="G799">
-        <v>0.05823698038334453</v>
+        <v>0.05795973633044153</v>
       </c>
       <c r="H799">
-        <v>0.05842220013999778</v>
+        <v>0.05814772299381037</v>
       </c>
       <c r="I799">
-        <v>0.7747802433467541</v>
+        <v>0.7720133366311543</v>
       </c>
       <c r="J799">
-        <v>1.179120973387007</v>
+        <v>1.168053346524612</v>
       </c>
       <c r="K799">
         <v>25.05</v>
@@ -41578,7 +41590,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>188</v>
+        <v>416</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41589,28 +41601,28 @@
         <v>190</v>
       </c>
       <c r="C800">
-        <v>-1.051692264853688</v>
+        <v>-0.8369803833445317</v>
       </c>
       <c r="D800" t="s">
         <v>191</v>
       </c>
       <c r="E800">
-        <v>-0.3704614954519023</v>
+        <v>-0.06220013999777763</v>
       </c>
       <c r="F800">
         <v>1</v>
       </c>
       <c r="G800">
-        <v>0.05845169226485369</v>
+        <v>0.05823698038334453</v>
       </c>
       <c r="H800">
-        <v>0.05937046149545191</v>
+        <v>0.05842220013999778</v>
       </c>
       <c r="I800">
-        <v>0.6812307694017861</v>
+        <v>0.7747802433467541</v>
       </c>
       <c r="J800">
-        <v>1.187692305982183</v>
+        <v>1.179120973387007</v>
       </c>
       <c r="K800">
         <v>25.05</v>
@@ -41619,16 +41631,16 @@
         <v>28.7</v>
       </c>
       <c r="M800">
-        <v>25.15</v>
+        <v>24.8</v>
       </c>
       <c r="N800">
-        <v>29.5</v>
+        <v>29.18</v>
       </c>
       <c r="O800">
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>416</v>
+        <v>188</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41636,43 +41648,43 @@
         <v>0</v>
       </c>
       <c r="B801" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C801">
-        <v>0.01711680463947474</v>
+        <v>-1.051692264853688</v>
       </c>
       <c r="D801" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E801">
-        <v>-0.6346716625790805</v>
+        <v>-0.3704614954519023</v>
       </c>
       <c r="F801">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G801">
-        <v>0.05912288319536053</v>
+        <v>0.05845169226485369</v>
       </c>
       <c r="H801">
-        <v>0.05823467166257908</v>
+        <v>0.05937046149545191</v>
       </c>
       <c r="I801">
-        <v>0.6517884672185552</v>
+        <v>0.6812307694017861</v>
       </c>
       <c r="J801">
-        <v>1.182115327814421</v>
+        <v>1.187692305982183</v>
       </c>
       <c r="K801">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="L801">
-        <v>29.57</v>
+        <v>28.7</v>
       </c>
       <c r="M801">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N801">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O801">
         <v>1</v>
@@ -41683,102 +41695,102 @@
     </row>
     <row r="802" spans="1:16">
       <c r="A802" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B802" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C802">
-        <v>-0.9119889617512484</v>
+        <v>0.01711680463947474</v>
       </c>
       <c r="D802" t="s">
-        <v>191</v>
+        <v>323</v>
       </c>
       <c r="E802">
-        <v>-0.230200494532685</v>
+        <v>-0.6346716625790805</v>
       </c>
       <c r="F802">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G802">
-        <v>0.05831198896175125</v>
+        <v>0.05912288319536053</v>
       </c>
       <c r="H802">
-        <v>0.05923020049453268</v>
+        <v>0.05823467166257908</v>
       </c>
       <c r="I802">
-        <v>0.6817884672185635</v>
+        <v>0.6517884672185552</v>
       </c>
       <c r="J802">
         <v>1.182115327814421</v>
       </c>
       <c r="K802">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="L802">
-        <v>28.7</v>
+        <v>29.57</v>
       </c>
       <c r="M802">
-        <v>25.15</v>
+        <v>24.9</v>
       </c>
       <c r="N802">
-        <v>29.5</v>
+        <v>28.8</v>
       </c>
       <c r="O802">
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="803" spans="1:16">
       <c r="A803" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B803" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C803">
-        <v>-0.02626559060565725</v>
+        <v>-0.9119889617512484</v>
       </c>
       <c r="D803" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E803">
-        <v>-0.6778805282432323</v>
+        <v>-0.230200494532685</v>
       </c>
       <c r="F803">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G803">
-        <v>0.05916626559060566</v>
+        <v>0.05831198896175125</v>
       </c>
       <c r="H803">
-        <v>0.05827788052824323</v>
+        <v>0.05923020049453268</v>
       </c>
       <c r="I803">
-        <v>0.6516149376375751</v>
+        <v>0.6817884672185635</v>
       </c>
       <c r="J803">
-        <v>1.183850623624226</v>
+        <v>1.182115327814421</v>
       </c>
       <c r="K803">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="L803">
-        <v>29.57</v>
+        <v>28.7</v>
       </c>
       <c r="M803">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N803">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O803">
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>322</v>
+        <v>418</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41789,28 +41801,28 @@
         <v>189</v>
       </c>
       <c r="C804">
-        <v>0.04582245394855988</v>
+        <v>-0.02626559060565725</v>
       </c>
       <c r="D804" t="s">
         <v>323</v>
       </c>
       <c r="E804">
-        <v>-0.6060808358672318</v>
+        <v>-0.6778805282432323</v>
       </c>
       <c r="F804">
         <v>-1</v>
       </c>
       <c r="G804">
-        <v>0.05909417754605144</v>
+        <v>0.05916626559060566</v>
       </c>
       <c r="H804">
-        <v>0.05820608083586724</v>
+        <v>0.05827788052824323</v>
       </c>
       <c r="I804">
-        <v>0.6519032898157917</v>
+        <v>0.6516149376375751</v>
       </c>
       <c r="J804">
-        <v>1.180967101842058</v>
+        <v>1.183850623624226</v>
       </c>
       <c r="K804">
         <v>25</v>
@@ -41828,7 +41840,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>418</v>
+        <v>322</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41839,28 +41851,28 @@
         <v>189</v>
       </c>
       <c r="C805">
-        <v>0.05143297331527208</v>
+        <v>0.04582245394855988</v>
       </c>
       <c r="D805" t="s">
         <v>323</v>
       </c>
       <c r="E805">
-        <v>-0.6004927585779853</v>
+        <v>-0.6060808358672318</v>
       </c>
       <c r="F805">
         <v>-1</v>
       </c>
       <c r="G805">
-        <v>0.05908856702668473</v>
+        <v>0.05909417754605144</v>
       </c>
       <c r="H805">
-        <v>0.05820049275857798</v>
+        <v>0.05820608083586724</v>
       </c>
       <c r="I805">
-        <v>0.6519257318932574</v>
+        <v>0.6519032898157917</v>
       </c>
       <c r="J805">
-        <v>1.180742681067389</v>
+        <v>1.180967101842058</v>
       </c>
       <c r="K805">
         <v>25</v>
@@ -41886,49 +41898,399 @@
         <v>0</v>
       </c>
       <c r="B806" t="s">
+        <v>189</v>
+      </c>
+      <c r="C806">
+        <v>0.05143297331527208</v>
+      </c>
+      <c r="D806" t="s">
+        <v>323</v>
+      </c>
+      <c r="E806">
+        <v>-0.6004927585779853</v>
+      </c>
+      <c r="F806">
+        <v>-1</v>
+      </c>
+      <c r="G806">
+        <v>0.05908856702668473</v>
+      </c>
+      <c r="H806">
+        <v>0.05820049275857798</v>
+      </c>
+      <c r="I806">
+        <v>0.6519257318932574</v>
+      </c>
+      <c r="J806">
+        <v>1.180742681067389</v>
+      </c>
+      <c r="K806">
+        <v>25</v>
+      </c>
+      <c r="L806">
+        <v>29.57</v>
+      </c>
+      <c r="M806">
+        <v>24.9</v>
+      </c>
+      <c r="N806">
+        <v>28.8</v>
+      </c>
+      <c r="O806">
+        <v>1</v>
+      </c>
+      <c r="P806" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="807" spans="1:16">
+      <c r="A807" s="1">
+        <v>1</v>
+      </c>
+      <c r="B807" t="s">
         <v>191</v>
       </c>
-      <c r="C806">
-        <v>-0.1614163319545447</v>
-      </c>
-      <c r="D806" t="s">
-        <v>324</v>
-      </c>
-      <c r="E806">
+      <c r="C807">
+        <v>-0.1024184904712513</v>
+      </c>
+      <c r="D807" t="s">
+        <v>325</v>
+      </c>
+      <c r="E807">
+        <v>-0.2214556245246193</v>
+      </c>
+      <c r="F807">
+        <v>-1</v>
+      </c>
+      <c r="G807">
+        <v>0.05846241849047125</v>
+      </c>
+      <c r="H807">
+        <v>0.05846145562452462</v>
+      </c>
+      <c r="I807">
+        <v>0.119037134053368</v>
+      </c>
+      <c r="J807">
+        <v>1.180742681067389</v>
+      </c>
+      <c r="K807">
+        <v>24.8</v>
+      </c>
+      <c r="L807">
+        <v>29.18</v>
+      </c>
+      <c r="M807">
+        <v>24.85</v>
+      </c>
+      <c r="N807">
+        <v>29.12</v>
+      </c>
+      <c r="O807">
+        <v>1</v>
+      </c>
+      <c r="P807" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="808" spans="1:16">
+      <c r="A808" s="1">
+        <v>0</v>
+      </c>
+      <c r="B808" t="s">
+        <v>191</v>
+      </c>
+      <c r="C808">
+        <v>0.004427027548832285</v>
+      </c>
+      <c r="D808" t="s">
+        <v>325</v>
+      </c>
+      <c r="E808">
+        <v>-0.114394692153688</v>
+      </c>
+      <c r="F808">
+        <v>-1</v>
+      </c>
+      <c r="G808">
+        <v>0.05835557297245117</v>
+      </c>
+      <c r="H808">
+        <v>0.05835439469215369</v>
+      </c>
+      <c r="I808">
+        <v>0.1188217197025203</v>
+      </c>
+      <c r="J808">
+        <v>1.17643439405045</v>
+      </c>
+      <c r="K808">
+        <v>24.8</v>
+      </c>
+      <c r="L808">
+        <v>29.18</v>
+      </c>
+      <c r="M808">
+        <v>24.85</v>
+      </c>
+      <c r="N808">
+        <v>29.12</v>
+      </c>
+      <c r="O808">
+        <v>1</v>
+      </c>
+      <c r="P808" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="809" spans="1:16">
+      <c r="A809" s="1">
+        <v>0</v>
+      </c>
+      <c r="B809" t="s">
+        <v>191</v>
+      </c>
+      <c r="C809">
         <v>-0.06863320208639223</v>
       </c>
-      <c r="F806">
-        <v>-1</v>
-      </c>
-      <c r="G806">
-        <v>0.05916141633195454</v>
-      </c>
-      <c r="H806">
+      <c r="D809" t="s">
+        <v>325</v>
+      </c>
+      <c r="E809">
+        <v>-0.1876022206389862</v>
+      </c>
+      <c r="F809">
+        <v>-1</v>
+      </c>
+      <c r="G809">
         <v>0.05842863320208639</v>
       </c>
-      <c r="I806">
-        <v>-0.09278312986815251</v>
-      </c>
-      <c r="J806">
+      <c r="H809">
+        <v>0.05842760222063899</v>
+      </c>
+      <c r="I809">
+        <v>0.118969018552594</v>
+      </c>
+      <c r="J809">
         <v>1.179380371051871</v>
       </c>
-      <c r="K806">
-        <v>25.15</v>
-      </c>
-      <c r="L806">
-        <v>29.5</v>
-      </c>
-      <c r="M806">
+      <c r="K809">
         <v>24.8</v>
       </c>
-      <c r="N806">
+      <c r="L809">
         <v>29.18</v>
       </c>
-      <c r="O806">
-        <v>1</v>
-      </c>
-      <c r="P806" t="s">
+      <c r="M809">
+        <v>24.85</v>
+      </c>
+      <c r="N809">
+        <v>29.12</v>
+      </c>
+      <c r="O809">
+        <v>1</v>
+      </c>
+      <c r="P809" t="s">
         <v>323</v>
+      </c>
+    </row>
+    <row r="810" spans="1:16">
+      <c r="A810" s="1">
+        <v>0</v>
+      </c>
+      <c r="B810" t="s">
+        <v>191</v>
+      </c>
+      <c r="C810">
+        <v>-0.1398756728703532</v>
+      </c>
+      <c r="D810" t="s">
+        <v>325</v>
+      </c>
+      <c r="E810">
+        <v>-0.2589883254366256</v>
+      </c>
+      <c r="F810">
+        <v>-1</v>
+      </c>
+      <c r="G810">
+        <v>0.05849987567287036</v>
+      </c>
+      <c r="H810">
+        <v>0.05849898832543663</v>
+      </c>
+      <c r="I810">
+        <v>0.1191126525662725</v>
+      </c>
+      <c r="J810">
+        <v>1.182253051325417</v>
+      </c>
+      <c r="K810">
+        <v>24.8</v>
+      </c>
+      <c r="L810">
+        <v>29.18</v>
+      </c>
+      <c r="M810">
+        <v>24.85</v>
+      </c>
+      <c r="N810">
+        <v>29.12</v>
+      </c>
+      <c r="O810">
+        <v>1</v>
+      </c>
+      <c r="P810" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="811" spans="1:16">
+      <c r="A811" s="1">
+        <v>0</v>
+      </c>
+      <c r="B811" t="s">
+        <v>191</v>
+      </c>
+      <c r="C811">
+        <v>-0.1618738323455666</v>
+      </c>
+      <c r="D811" t="s">
+        <v>325</v>
+      </c>
+      <c r="E811">
+        <v>-0.281030836039811</v>
+      </c>
+      <c r="F811">
+        <v>-1</v>
+      </c>
+      <c r="G811">
+        <v>0.05852187383234556</v>
+      </c>
+      <c r="H811">
+        <v>0.05852103083603982</v>
+      </c>
+      <c r="I811">
+        <v>0.1191570036942444</v>
+      </c>
+      <c r="J811">
+        <v>1.183140073884902</v>
+      </c>
+      <c r="K811">
+        <v>24.8</v>
+      </c>
+      <c r="L811">
+        <v>29.18</v>
+      </c>
+      <c r="M811">
+        <v>24.85</v>
+      </c>
+      <c r="N811">
+        <v>29.12</v>
+      </c>
+      <c r="O811">
+        <v>1</v>
+      </c>
+      <c r="P811" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="812" spans="1:16">
+      <c r="A812" s="1">
+        <v>0</v>
+      </c>
+      <c r="B812" t="s">
+        <v>191</v>
+      </c>
+      <c r="C812">
+        <v>-0.2777517985715967</v>
+      </c>
+      <c r="D812" t="s">
+        <v>325</v>
+      </c>
+      <c r="E812">
+        <v>-0.3971424271977462</v>
+      </c>
+      <c r="F812">
+        <v>-1</v>
+      </c>
+      <c r="G812">
+        <v>0.0586377517985716</v>
+      </c>
+      <c r="H812">
+        <v>0.05863714242719775</v>
+      </c>
+      <c r="I812">
+        <v>0.1193906286261495</v>
+      </c>
+      <c r="J812">
+        <v>1.187812572523048</v>
+      </c>
+      <c r="K812">
+        <v>24.8</v>
+      </c>
+      <c r="L812">
+        <v>29.18</v>
+      </c>
+      <c r="M812">
+        <v>24.85</v>
+      </c>
+      <c r="N812">
+        <v>29.12</v>
+      </c>
+      <c r="O812">
+        <v>1</v>
+      </c>
+      <c r="P812" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="813" spans="1:16">
+      <c r="A813" s="1">
+        <v>0</v>
+      </c>
+      <c r="B813" t="s">
+        <v>191</v>
+      </c>
+      <c r="C813">
+        <v>-0.678181641571296</v>
+      </c>
+      <c r="D813" t="s">
+        <v>325</v>
+      </c>
+      <c r="E813">
+        <v>-0.7983795884293023</v>
+      </c>
+      <c r="F813">
+        <v>-1</v>
+      </c>
+      <c r="G813">
+        <v>0.0590381816415713</v>
+      </c>
+      <c r="H813">
+        <v>0.05903837958842931</v>
+      </c>
+      <c r="I813">
+        <v>0.1201979468580063</v>
+      </c>
+      <c r="J813">
+        <v>1.203958937160133</v>
+      </c>
+      <c r="K813">
+        <v>24.8</v>
+      </c>
+      <c r="L813">
+        <v>29.18</v>
+      </c>
+      <c r="M813">
+        <v>24.85</v>
+      </c>
+      <c r="N813">
+        <v>29.12</v>
+      </c>
+      <c r="O813">
+        <v>1</v>
+      </c>
+      <c r="P813" t="s">
+        <v>423</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2448" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="425">
   <si>
     <t>trade_time</t>
   </si>
@@ -583,10 +583,10 @@
     <t>2021-10-12</t>
   </si>
   <si>
-    <t>2021-10-20</t>
+    <t>2021-10-18</t>
   </si>
   <si>
-    <t>2021-10-29</t>
+    <t>2021-10-20</t>
   </si>
   <si>
     <t>2021-10-08</t>
@@ -988,7 +988,10 @@
     <t>2021-10-15</t>
   </si>
   <si>
-    <t>2021-11-01</t>
+    <t>2021-10-22</t>
+  </si>
+  <si>
+    <t>2021-10-29</t>
   </si>
   <si>
     <t>2016-07-29</t>
@@ -1277,9 +1280,6 @@
   </si>
   <si>
     <t>2021-10-11</t>
-  </si>
-  <si>
-    <t>2021-10-18</t>
   </si>
   <si>
     <t>2021-10-19</t>
@@ -1646,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P812"/>
+  <dimension ref="A1:P815"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1743,7 +1743,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1793,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1843,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1893,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1943,7 +1943,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2193,7 +2193,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2243,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2293,7 +2293,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2343,7 +2343,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2393,7 +2393,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2443,7 +2443,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2493,7 +2493,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2543,7 +2543,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2593,7 +2593,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2643,7 +2643,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2693,7 +2693,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2743,7 +2743,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2793,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2893,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2943,7 +2943,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2993,7 +2993,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3043,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3093,7 +3093,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3143,7 +3143,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3193,7 +3193,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3243,7 +3243,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3343,7 +3343,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3393,7 +3393,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3443,7 +3443,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3493,7 +3493,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3543,7 +3543,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3593,7 +3593,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3643,7 +3643,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3693,7 +3693,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3743,7 +3743,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3793,7 +3793,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3843,7 +3843,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3893,7 +3893,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3943,7 +3943,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3993,7 +3993,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4043,7 +4043,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4093,7 +4093,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4143,7 +4143,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4193,7 +4193,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4243,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4293,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4343,7 +4343,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4393,7 +4393,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4443,7 +4443,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4493,7 +4493,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4543,7 +4543,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4593,7 +4593,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4643,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4993,7 +4993,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5043,7 +5043,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5093,7 +5093,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5143,7 +5143,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5193,7 +5193,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5543,7 +5543,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5593,7 +5593,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5643,7 +5643,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5693,7 +5693,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5743,7 +5743,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5793,7 +5793,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5843,7 +5843,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5893,7 +5893,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5943,7 +5943,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5993,7 +5993,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6043,7 +6043,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6093,7 +6093,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6193,7 +6193,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6243,7 +6243,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6293,7 +6293,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6343,7 +6343,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6393,7 +6393,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6443,7 +6443,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6493,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6543,7 +6543,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6593,7 +6593,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6643,7 +6643,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6693,7 +6693,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6743,7 +6743,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6793,7 +6793,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6843,7 +6843,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6893,7 +6893,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6943,7 +6943,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6993,7 +6993,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7043,7 +7043,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7093,7 +7093,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7143,7 +7143,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7193,7 +7193,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7243,7 +7243,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7293,7 +7293,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7343,7 +7343,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7393,7 +7393,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7443,7 +7443,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7493,7 +7493,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7543,7 +7543,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7593,7 +7593,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7643,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7693,7 +7693,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7743,7 +7743,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7793,7 +7793,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7843,7 +7843,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8243,7 +8243,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8293,7 +8293,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8343,7 +8343,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8393,7 +8393,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8443,7 +8443,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8493,7 +8493,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8543,7 +8543,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8593,7 +8593,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9443,7 +9443,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9493,7 +9493,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9543,7 +9543,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9593,7 +9593,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9643,7 +9643,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9693,7 +9693,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9743,7 +9743,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9793,7 +9793,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10643,7 +10643,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10693,7 +10693,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10743,7 +10743,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10793,7 +10793,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10843,7 +10843,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10893,7 +10893,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10943,7 +10943,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10993,7 +10993,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11443,7 +11443,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11493,7 +11493,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11543,7 +11543,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11593,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11643,7 +11643,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11693,7 +11693,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11743,7 +11743,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11793,7 +11793,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12193,7 +12193,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12243,7 +12243,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12293,7 +12293,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12343,7 +12343,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12393,7 +12393,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12443,7 +12443,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12493,7 +12493,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12543,7 +12543,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12593,7 +12593,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12643,7 +12643,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12693,7 +12693,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12743,7 +12743,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12793,7 +12793,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12843,7 +12843,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12893,7 +12893,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12943,7 +12943,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12993,7 +12993,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13043,7 +13043,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13093,7 +13093,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13143,7 +13143,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13193,7 +13193,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13243,7 +13243,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13293,7 +13293,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13343,7 +13343,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13393,7 +13393,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13443,7 +13443,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13493,7 +13493,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13543,7 +13543,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13593,7 +13593,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13643,7 +13643,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13693,7 +13693,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13743,7 +13743,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13793,7 +13793,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13843,7 +13843,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14193,7 +14193,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14243,7 +14243,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14293,7 +14293,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14343,7 +14343,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14393,7 +14393,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14443,7 +14443,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14493,7 +14493,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14543,7 +14543,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14593,7 +14593,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14643,7 +14643,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14693,7 +14693,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14743,7 +14743,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14793,7 +14793,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14843,7 +14843,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14893,7 +14893,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14943,7 +14943,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14993,7 +14993,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15043,7 +15043,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -16193,7 +16193,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16243,7 +16243,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16293,7 +16293,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16343,7 +16343,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16393,7 +16393,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16443,7 +16443,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16493,7 +16493,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16543,7 +16543,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16593,7 +16593,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16643,7 +16643,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -18293,7 +18293,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18343,7 +18343,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18393,7 +18393,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18443,7 +18443,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18493,7 +18493,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18543,7 +18543,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18743,7 +18743,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18793,7 +18793,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19143,7 +19143,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19193,7 +19193,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19243,7 +19243,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19743,7 +19743,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19793,7 +19793,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19843,7 +19843,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20593,7 +20593,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20643,7 +20643,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20693,7 +20693,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20743,7 +20743,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20793,7 +20793,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20843,7 +20843,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20893,7 +20893,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20943,7 +20943,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20993,7 +20993,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21043,7 +21043,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21093,7 +21093,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21143,7 +21143,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21193,7 +21193,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21243,7 +21243,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21293,7 +21293,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21343,7 +21343,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21393,7 +21393,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21443,7 +21443,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21493,7 +21493,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21543,7 +21543,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21593,7 +21593,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21643,7 +21643,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21693,7 +21693,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21743,7 +21743,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21793,7 +21793,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21843,7 +21843,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21893,7 +21893,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21943,7 +21943,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21993,7 +21993,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22043,7 +22043,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22093,7 +22093,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22143,7 +22143,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22193,7 +22193,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22243,7 +22243,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22293,7 +22293,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22343,7 +22343,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22393,7 +22393,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22893,7 +22893,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22943,7 +22943,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22993,7 +22993,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23043,7 +23043,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23093,7 +23093,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23143,7 +23143,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23193,7 +23193,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23243,7 +23243,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23293,7 +23293,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23343,7 +23343,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23393,7 +23393,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23443,7 +23443,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23493,7 +23493,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23543,7 +23543,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23593,7 +23593,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23643,7 +23643,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23693,7 +23693,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23743,7 +23743,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23793,7 +23793,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23843,7 +23843,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23893,7 +23893,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23943,7 +23943,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23993,7 +23993,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24043,7 +24043,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24093,7 +24093,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24143,7 +24143,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24193,7 +24193,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24243,7 +24243,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24293,7 +24293,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24343,7 +24343,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24393,7 +24393,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24443,7 +24443,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24493,7 +24493,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24543,7 +24543,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24593,7 +24593,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24643,7 +24643,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24693,7 +24693,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24743,7 +24743,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24793,7 +24793,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24843,7 +24843,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25793,7 +25793,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25843,7 +25843,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25893,7 +25893,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25943,7 +25943,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25993,7 +25993,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26043,7 +26043,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26093,7 +26093,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26143,7 +26143,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26193,7 +26193,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26243,7 +26243,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26293,7 +26293,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26343,7 +26343,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26393,7 +26393,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26443,7 +26443,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26493,7 +26493,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26543,7 +26543,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26593,7 +26593,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26643,7 +26643,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26693,7 +26693,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26743,7 +26743,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26793,7 +26793,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26843,7 +26843,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26893,7 +26893,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26943,7 +26943,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26993,7 +26993,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27043,7 +27043,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27093,7 +27093,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27143,7 +27143,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27193,7 +27193,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27243,7 +27243,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27293,7 +27293,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27343,7 +27343,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27393,7 +27393,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27443,7 +27443,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27493,7 +27493,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27543,7 +27543,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27593,7 +27593,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27643,7 +27643,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27693,7 +27693,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27743,7 +27743,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27793,7 +27793,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27843,7 +27843,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27893,7 +27893,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27943,7 +27943,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27993,7 +27993,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28043,7 +28043,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28093,7 +28093,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28143,7 +28143,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28193,7 +28193,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28243,7 +28243,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28293,7 +28293,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28343,7 +28343,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28843,7 +28843,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28893,7 +28893,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28943,7 +28943,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28993,7 +28993,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29043,7 +29043,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29093,7 +29093,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29143,7 +29143,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29193,7 +29193,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29243,7 +29243,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29293,7 +29293,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29343,7 +29343,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29393,7 +29393,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29443,7 +29443,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29493,7 +29493,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29543,7 +29543,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29593,7 +29593,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29643,7 +29643,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29693,7 +29693,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29743,7 +29743,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29793,7 +29793,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29843,7 +29843,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29893,7 +29893,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29943,7 +29943,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29993,7 +29993,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30043,7 +30043,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30093,7 +30093,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30143,7 +30143,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30193,7 +30193,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30243,7 +30243,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30293,7 +30293,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30343,7 +30343,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30393,7 +30393,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30443,7 +30443,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30493,7 +30493,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30543,7 +30543,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30593,7 +30593,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30643,7 +30643,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30693,7 +30693,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30743,7 +30743,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30793,7 +30793,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30843,7 +30843,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30893,7 +30893,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30943,7 +30943,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31393,7 +31393,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31443,7 +31443,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31493,7 +31493,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31543,7 +31543,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31593,7 +31593,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31643,7 +31643,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31693,7 +31693,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31743,7 +31743,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31793,7 +31793,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31843,7 +31843,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31893,7 +31893,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -31943,7 +31943,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31993,7 +31993,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32043,7 +32043,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32093,7 +32093,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32143,7 +32143,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32893,7 +32893,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32943,7 +32943,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32993,7 +32993,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33043,7 +33043,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33093,7 +33093,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33143,7 +33143,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33193,7 +33193,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33243,7 +33243,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33293,7 +33293,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33343,7 +33343,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33393,7 +33393,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33443,7 +33443,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33493,7 +33493,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33543,7 +33543,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33893,7 +33893,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33943,7 +33943,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33993,7 +33993,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34043,7 +34043,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34093,7 +34093,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34143,7 +34143,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34443,7 +34443,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34493,7 +34493,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34543,7 +34543,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34593,7 +34593,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34643,7 +34643,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34693,7 +34693,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34743,7 +34743,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34793,7 +34793,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34843,7 +34843,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34893,7 +34893,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34943,7 +34943,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -34993,7 +34993,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35043,7 +35043,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35093,7 +35093,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35143,7 +35143,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35193,7 +35193,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35243,7 +35243,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35293,7 +35293,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35343,7 +35343,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35693,7 +35693,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35743,7 +35743,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35793,7 +35793,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35843,7 +35843,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35893,7 +35893,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35943,7 +35943,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35993,7 +35993,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36043,7 +36043,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36093,7 +36093,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36143,7 +36143,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36193,7 +36193,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36243,7 +36243,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36293,7 +36293,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36343,7 +36343,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36393,7 +36393,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36443,7 +36443,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36493,7 +36493,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36543,7 +36543,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36593,7 +36593,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36643,7 +36643,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36693,7 +36693,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36743,7 +36743,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36793,7 +36793,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36843,7 +36843,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36893,7 +36893,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36943,7 +36943,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36993,7 +36993,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37043,7 +37043,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37093,7 +37093,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37143,7 +37143,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37193,7 +37193,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37243,7 +37243,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37643,7 +37643,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37693,7 +37693,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37743,7 +37743,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37793,7 +37793,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37843,7 +37843,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -37893,7 +37893,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -37943,7 +37943,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38593,7 +38593,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38643,7 +38643,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38693,7 +38693,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38743,7 +38743,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38793,7 +38793,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38843,7 +38843,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38893,7 +38893,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38943,7 +38943,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -38993,7 +38993,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39043,7 +39043,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39093,7 +39093,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39143,7 +39143,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39193,7 +39193,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39243,7 +39243,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39293,7 +39293,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39304,107 +39304,107 @@
         <v>189</v>
       </c>
       <c r="C754">
-        <v>4.163922260811965</v>
+        <v>4.375715917325948</v>
       </c>
       <c r="D754" t="s">
-        <v>193</v>
+        <v>324</v>
       </c>
       <c r="E754">
-        <v>4.865973846683474</v>
+        <v>4.716231776040996</v>
       </c>
       <c r="F754">
         <v>1</v>
       </c>
       <c r="G754">
-        <v>0.05323607773918804</v>
+        <v>0.05266428408267405</v>
       </c>
       <c r="H754">
-        <v>0.05413402615331653</v>
+        <v>0.05496376822395901</v>
       </c>
       <c r="I754">
-        <v>0.7020515858715086</v>
+        <v>0.3405158587150474</v>
       </c>
       <c r="J754">
         <v>0.9794841412849514</v>
       </c>
       <c r="K754">
-        <v>25.05</v>
+        <v>24.65</v>
       </c>
       <c r="L754">
-        <v>28.7</v>
+        <v>28.52</v>
       </c>
       <c r="M754">
-        <v>25.15</v>
+        <v>25.65</v>
       </c>
       <c r="N754">
-        <v>29.5</v>
+        <v>29.84</v>
       </c>
       <c r="O754">
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="755" spans="1:16">
       <c r="A755" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B755" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C755">
-        <v>4.821954240451266</v>
+        <v>4.163922260811965</v>
       </c>
       <c r="D755" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E755">
-        <v>3.971717315818243</v>
+        <v>4.716231776040996</v>
       </c>
       <c r="F755">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G755">
-        <v>0.05055804575954873</v>
+        <v>0.05323607773918804</v>
       </c>
       <c r="H755">
-        <v>0.05030828268418176</v>
+        <v>0.05496376822395901</v>
       </c>
       <c r="I755">
-        <v>0.8502369246330232</v>
+        <v>0.5523095152290303</v>
       </c>
       <c r="J755">
-        <v>1.00078974877675</v>
+        <v>0.9794841412849514</v>
       </c>
       <c r="K755">
-        <v>22.85</v>
+        <v>25.05</v>
       </c>
       <c r="L755">
-        <v>27.69</v>
+        <v>28.7</v>
       </c>
       <c r="M755">
-        <v>23.15</v>
+        <v>25.65</v>
       </c>
       <c r="N755">
-        <v>27.14</v>
+        <v>29.84</v>
       </c>
       <c r="O755">
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>185</v>
+        <v>408</v>
       </c>
     </row>
     <row r="756" spans="1:16">
       <c r="A756" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B756" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C756">
-        <v>4.671875265573593</v>
+        <v>4.821954240451266</v>
       </c>
       <c r="D756" t="s">
         <v>322</v>
@@ -39416,22 +39416,22 @@
         <v>-1</v>
       </c>
       <c r="G756">
-        <v>0.05060812473442641</v>
+        <v>0.05055804575954873</v>
       </c>
       <c r="H756">
         <v>0.05030828268418176</v>
       </c>
       <c r="I756">
-        <v>0.7001579497553507</v>
+        <v>0.8502369246330232</v>
       </c>
       <c r="J756">
         <v>1.00078974877675</v>
       </c>
       <c r="K756">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L756">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M756">
         <v>23.15</v>
@@ -39448,46 +39448,46 @@
     </row>
     <row r="757" spans="1:16">
       <c r="A757" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B757" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C757">
-        <v>4.550256280581255</v>
+        <v>4.671875265573593</v>
       </c>
       <c r="D757" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E757">
-        <v>3.880335255458931</v>
+        <v>3.971717315818243</v>
       </c>
       <c r="F757">
         <v>-1</v>
       </c>
       <c r="G757">
-        <v>0.05458974371941875</v>
+        <v>0.05060812473442641</v>
       </c>
       <c r="H757">
-        <v>0.05371966474454107</v>
+        <v>0.05030828268418176</v>
       </c>
       <c r="I757">
-        <v>0.6699210251223242</v>
+        <v>0.7001579497553507</v>
       </c>
       <c r="J757">
         <v>1.00078974877675</v>
       </c>
       <c r="K757">
-        <v>25</v>
+        <v>22.95</v>
       </c>
       <c r="L757">
-        <v>29.57</v>
+        <v>27.64</v>
       </c>
       <c r="M757">
-        <v>24.9</v>
+        <v>23.15</v>
       </c>
       <c r="N757">
-        <v>28.8</v>
+        <v>27.14</v>
       </c>
       <c r="O757">
         <v>1</v>
@@ -39498,46 +39498,46 @@
     </row>
     <row r="758" spans="1:16">
       <c r="A758" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B758" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C758">
-        <v>3.630216793142413</v>
+        <v>4.550256280581255</v>
       </c>
       <c r="D758" t="s">
-        <v>193</v>
+        <v>323</v>
       </c>
       <c r="E758">
-        <v>4.330137818264742</v>
+        <v>3.880335255458931</v>
       </c>
       <c r="F758">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G758">
-        <v>0.05376978320685758</v>
+        <v>0.05458974371941875</v>
       </c>
       <c r="H758">
-        <v>0.05466986218173526</v>
+        <v>0.05371966474454107</v>
       </c>
       <c r="I758">
-        <v>0.6999210251223289</v>
+        <v>0.6699210251223242</v>
       </c>
       <c r="J758">
         <v>1.00078974877675</v>
       </c>
       <c r="K758">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="L758">
-        <v>28.7</v>
+        <v>29.57</v>
       </c>
       <c r="M758">
-        <v>25.15</v>
+        <v>24.9</v>
       </c>
       <c r="N758">
-        <v>29.5</v>
+        <v>28.8</v>
       </c>
       <c r="O758">
         <v>1</v>
@@ -39548,63 +39548,63 @@
     </row>
     <row r="759" spans="1:16">
       <c r="A759" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B759" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C759">
-        <v>4.670760956334874</v>
+        <v>3.630216793142413</v>
       </c>
       <c r="D759" t="s">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="E759">
-        <v>3.81853899952527</v>
+        <v>4.330137818264742</v>
       </c>
       <c r="F759">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G759">
-        <v>0.05070923904366513</v>
+        <v>0.05376978320685758</v>
       </c>
       <c r="H759">
-        <v>0.05046146100047473</v>
+        <v>0.05466986218173526</v>
       </c>
       <c r="I759">
-        <v>0.8522219568096041</v>
+        <v>0.6999210251223289</v>
       </c>
       <c r="J759">
-        <v>1.007406522698693</v>
+        <v>1.00078974877675</v>
       </c>
       <c r="K759">
-        <v>22.85</v>
+        <v>25.05</v>
       </c>
       <c r="L759">
-        <v>27.69</v>
+        <v>28.7</v>
       </c>
       <c r="M759">
-        <v>23.15</v>
+        <v>25.15</v>
       </c>
       <c r="N759">
-        <v>27.14</v>
+        <v>29.5</v>
       </c>
       <c r="O759">
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>408</v>
+        <v>185</v>
       </c>
     </row>
     <row r="760" spans="1:16">
       <c r="A760" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B760" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C760">
-        <v>4.520020304065007</v>
+        <v>4.670760956334874</v>
       </c>
       <c r="D760" t="s">
         <v>322</v>
@@ -39616,22 +39616,22 @@
         <v>-1</v>
       </c>
       <c r="G760">
-        <v>0.05075997969593499</v>
+        <v>0.05070923904366513</v>
       </c>
       <c r="H760">
         <v>0.05046146100047473</v>
       </c>
       <c r="I760">
-        <v>0.7014813045397368</v>
+        <v>0.8522219568096041</v>
       </c>
       <c r="J760">
         <v>1.007406522698693</v>
       </c>
       <c r="K760">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L760">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M760">
         <v>23.15</v>
@@ -39643,168 +39643,168 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="761" spans="1:16">
       <c r="A761" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B761" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C761">
-        <v>4.384836932532686</v>
+        <v>4.520020304065007</v>
       </c>
       <c r="D761" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E761">
-        <v>3.715577584802556</v>
+        <v>3.81853899952527</v>
       </c>
       <c r="F761">
         <v>-1</v>
       </c>
       <c r="G761">
-        <v>0.05475516306746732</v>
+        <v>0.05075997969593499</v>
       </c>
       <c r="H761">
-        <v>0.05388442241519745</v>
+        <v>0.05046146100047473</v>
       </c>
       <c r="I761">
-        <v>0.6692593477301294</v>
+        <v>0.7014813045397368</v>
       </c>
       <c r="J761">
         <v>1.007406522698693</v>
       </c>
       <c r="K761">
-        <v>25</v>
+        <v>22.95</v>
       </c>
       <c r="L761">
-        <v>29.57</v>
+        <v>27.64</v>
       </c>
       <c r="M761">
-        <v>24.9</v>
+        <v>23.15</v>
       </c>
       <c r="N761">
-        <v>28.8</v>
+        <v>27.14</v>
       </c>
       <c r="O761">
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="762" spans="1:16">
       <c r="A762" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B762" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C762">
-        <v>3.46446660639775</v>
+        <v>4.384836932532686</v>
       </c>
       <c r="D762" t="s">
-        <v>193</v>
+        <v>323</v>
       </c>
       <c r="E762">
-        <v>4.163725954127884</v>
+        <v>3.715577584802556</v>
       </c>
       <c r="F762">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G762">
-        <v>0.05393553339360225</v>
+        <v>0.05475516306746732</v>
       </c>
       <c r="H762">
-        <v>0.05483627404587212</v>
+        <v>0.05388442241519745</v>
       </c>
       <c r="I762">
-        <v>0.6992593477301341</v>
+        <v>0.6692593477301294</v>
       </c>
       <c r="J762">
         <v>1.007406522698693</v>
       </c>
       <c r="K762">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="L762">
-        <v>28.7</v>
+        <v>29.57</v>
       </c>
       <c r="M762">
-        <v>25.15</v>
+        <v>24.9</v>
       </c>
       <c r="N762">
-        <v>29.5</v>
+        <v>28.8</v>
       </c>
       <c r="O762">
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="763" spans="1:16">
       <c r="A763" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B763" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C763">
-        <v>4.503371200497003</v>
+        <v>3.46446660639775</v>
       </c>
       <c r="D763" t="s">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="E763">
-        <v>3.648951566367863</v>
+        <v>4.163725954127884</v>
       </c>
       <c r="F763">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G763">
-        <v>0.050876628799503</v>
+        <v>0.05393553339360225</v>
       </c>
       <c r="H763">
-        <v>0.05063104843363214</v>
+        <v>0.05483627404587212</v>
       </c>
       <c r="I763">
-        <v>0.8544196341291403</v>
+        <v>0.6992593477301341</v>
       </c>
       <c r="J763">
-        <v>1.014732113763807</v>
+        <v>1.007406522698693</v>
       </c>
       <c r="K763">
-        <v>22.85</v>
+        <v>25.05</v>
       </c>
       <c r="L763">
-        <v>27.69</v>
+        <v>28.7</v>
       </c>
       <c r="M763">
-        <v>23.15</v>
+        <v>25.15</v>
       </c>
       <c r="N763">
-        <v>27.14</v>
+        <v>29.5</v>
       </c>
       <c r="O763">
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>321</v>
+        <v>409</v>
       </c>
     </row>
     <row r="764" spans="1:16">
       <c r="A764" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B764" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C764">
-        <v>4.351897989120626</v>
+        <v>4.503371200497003</v>
       </c>
       <c r="D764" t="s">
         <v>322</v>
@@ -39816,22 +39816,22 @@
         <v>-1</v>
       </c>
       <c r="G764">
-        <v>0.05092810201087937</v>
+        <v>0.050876628799503</v>
       </c>
       <c r="H764">
         <v>0.05063104843363214</v>
       </c>
       <c r="I764">
-        <v>0.7029464227527633</v>
+        <v>0.8544196341291403</v>
       </c>
       <c r="J764">
         <v>1.014732113763807</v>
       </c>
       <c r="K764">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L764">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M764">
         <v>23.15</v>
@@ -39848,46 +39848,46 @@
     </row>
     <row r="765" spans="1:16">
       <c r="A765" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B765" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C765">
-        <v>4.201697155904821</v>
+        <v>4.351897989120626</v>
       </c>
       <c r="D765" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E765">
-        <v>3.533170367281201</v>
+        <v>3.648951566367863</v>
       </c>
       <c r="F765">
         <v>-1</v>
       </c>
       <c r="G765">
-        <v>0.05493830284409518</v>
+        <v>0.05092810201087937</v>
       </c>
       <c r="H765">
-        <v>0.0540668296327188</v>
+        <v>0.05063104843363214</v>
       </c>
       <c r="I765">
-        <v>0.6685267886236197</v>
+        <v>0.7029464227527633</v>
       </c>
       <c r="J765">
         <v>1.014732113763807</v>
       </c>
       <c r="K765">
-        <v>25</v>
+        <v>22.95</v>
       </c>
       <c r="L765">
-        <v>29.57</v>
+        <v>27.64</v>
       </c>
       <c r="M765">
-        <v>24.9</v>
+        <v>23.15</v>
       </c>
       <c r="N765">
-        <v>28.8</v>
+        <v>27.14</v>
       </c>
       <c r="O765">
         <v>1</v>
@@ -39898,46 +39898,46 @@
     </row>
     <row r="766" spans="1:16">
       <c r="A766" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B766" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C766">
-        <v>3.280960550216626</v>
+        <v>4.201697155904821</v>
       </c>
       <c r="D766" t="s">
-        <v>193</v>
+        <v>323</v>
       </c>
       <c r="E766">
-        <v>3.979487338840251</v>
+        <v>3.533170367281201</v>
       </c>
       <c r="F766">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G766">
-        <v>0.05411903944978337</v>
+        <v>0.05493830284409518</v>
       </c>
       <c r="H766">
-        <v>0.05502051266115975</v>
+        <v>0.0540668296327188</v>
       </c>
       <c r="I766">
-        <v>0.6985267886236244</v>
+        <v>0.6685267886236197</v>
       </c>
       <c r="J766">
         <v>1.014732113763807</v>
       </c>
       <c r="K766">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="L766">
-        <v>28.7</v>
+        <v>29.57</v>
       </c>
       <c r="M766">
-        <v>25.15</v>
+        <v>24.9</v>
       </c>
       <c r="N766">
-        <v>29.5</v>
+        <v>28.8</v>
       </c>
       <c r="O766">
         <v>1</v>
@@ -39948,63 +39948,63 @@
     </row>
     <row r="767" spans="1:16">
       <c r="A767" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B767" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C767">
-        <v>4.366292866964365</v>
+        <v>3.280960550216626</v>
       </c>
       <c r="D767" t="s">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="E767">
-        <v>3.510073517296505</v>
+        <v>3.979487338840251</v>
       </c>
       <c r="F767">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G767">
-        <v>0.05101370713303564</v>
+        <v>0.05411903944978337</v>
       </c>
       <c r="H767">
-        <v>0.0507699264827035</v>
+        <v>0.05502051266115975</v>
       </c>
       <c r="I767">
-        <v>0.8562193496678603</v>
+        <v>0.6985267886236244</v>
       </c>
       <c r="J767">
-        <v>1.020731165559546</v>
+        <v>1.014732113763807</v>
       </c>
       <c r="K767">
-        <v>22.85</v>
+        <v>25.05</v>
       </c>
       <c r="L767">
-        <v>27.69</v>
+        <v>28.7</v>
       </c>
       <c r="M767">
-        <v>23.15</v>
+        <v>25.15</v>
       </c>
       <c r="N767">
-        <v>27.14</v>
+        <v>29.5</v>
       </c>
       <c r="O767">
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>409</v>
+        <v>321</v>
       </c>
     </row>
     <row r="768" spans="1:16">
       <c r="A768" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B768" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C768">
-        <v>4.214219750408411</v>
+        <v>4.366292866964365</v>
       </c>
       <c r="D768" t="s">
         <v>322</v>
@@ -40016,22 +40016,22 @@
         <v>-1</v>
       </c>
       <c r="G768">
-        <v>0.05106578024959159</v>
+        <v>0.05101370713303564</v>
       </c>
       <c r="H768">
         <v>0.0507699264827035</v>
       </c>
       <c r="I768">
-        <v>0.7041462331119064</v>
+        <v>0.8562193496678603</v>
       </c>
       <c r="J768">
         <v>1.020731165559546</v>
       </c>
       <c r="K768">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L768">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M768">
         <v>23.15</v>
@@ -40043,151 +40043,151 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="769" spans="1:16">
       <c r="A769" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B769" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C769">
-        <v>4.05172086101134</v>
+        <v>4.214219750408411</v>
       </c>
       <c r="D769" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E769">
-        <v>3.383793977567297</v>
+        <v>3.510073517296505</v>
       </c>
       <c r="F769">
         <v>-1</v>
       </c>
       <c r="G769">
-        <v>0.05508827913898866</v>
+        <v>0.05106578024959159</v>
       </c>
       <c r="H769">
-        <v>0.0542162060224327</v>
+        <v>0.0507699264827035</v>
       </c>
       <c r="I769">
-        <v>0.6679268834440428</v>
+        <v>0.7041462331119064</v>
       </c>
       <c r="J769">
         <v>1.020731165559546</v>
       </c>
       <c r="K769">
-        <v>25</v>
+        <v>22.95</v>
       </c>
       <c r="L769">
-        <v>29.57</v>
+        <v>27.64</v>
       </c>
       <c r="M769">
-        <v>24.9</v>
+        <v>23.15</v>
       </c>
       <c r="N769">
-        <v>28.8</v>
+        <v>27.14</v>
       </c>
       <c r="O769">
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="770" spans="1:16">
       <c r="A770" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B770" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C770">
-        <v>3.130684302733364</v>
+        <v>4.05172086101134</v>
       </c>
       <c r="D770" t="s">
-        <v>193</v>
+        <v>323</v>
       </c>
       <c r="E770">
-        <v>3.828611186177412</v>
+        <v>3.383793977567297</v>
       </c>
       <c r="F770">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G770">
-        <v>0.05426931569726664</v>
+        <v>0.05508827913898866</v>
       </c>
       <c r="H770">
-        <v>0.05517138881382259</v>
+        <v>0.0542162060224327</v>
       </c>
       <c r="I770">
-        <v>0.6979268834440475</v>
+        <v>0.6679268834440428</v>
       </c>
       <c r="J770">
         <v>1.020731165559546</v>
       </c>
       <c r="K770">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="L770">
-        <v>28.7</v>
+        <v>29.57</v>
       </c>
       <c r="M770">
-        <v>25.15</v>
+        <v>24.9</v>
       </c>
       <c r="N770">
-        <v>29.5</v>
+        <v>28.8</v>
       </c>
       <c r="O770">
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="771" spans="1:16">
       <c r="A771" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B771" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C771">
-        <v>4.196922435356054</v>
+        <v>3.130684302733364</v>
       </c>
       <c r="D771" t="s">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="E771">
-        <v>3.338479403872764</v>
+        <v>3.828611186177412</v>
       </c>
       <c r="F771">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G771">
-        <v>0.05118307756464395</v>
+        <v>0.05426931569726664</v>
       </c>
       <c r="H771">
-        <v>0.05094152059612723</v>
+        <v>0.05517138881382259</v>
       </c>
       <c r="I771">
-        <v>0.85844303148329</v>
+        <v>0.6979268834440475</v>
       </c>
       <c r="J771">
-        <v>1.028143438277634</v>
+        <v>1.020731165559546</v>
       </c>
       <c r="K771">
-        <v>22.85</v>
+        <v>25.05</v>
       </c>
       <c r="L771">
-        <v>27.69</v>
+        <v>28.7</v>
       </c>
       <c r="M771">
-        <v>23.15</v>
+        <v>25.15</v>
       </c>
       <c r="N771">
-        <v>27.14</v>
+        <v>29.5</v>
       </c>
       <c r="O771">
         <v>1</v>
@@ -40198,13 +40198,13 @@
     </row>
     <row r="772" spans="1:16">
       <c r="A772" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B772" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C772">
-        <v>4.04410809152829</v>
+        <v>4.196922435356054</v>
       </c>
       <c r="D772" t="s">
         <v>322</v>
@@ -40216,22 +40216,22 @@
         <v>-1</v>
       </c>
       <c r="G772">
-        <v>0.05123589190847171</v>
+        <v>0.05118307756464395</v>
       </c>
       <c r="H772">
         <v>0.05094152059612723</v>
       </c>
       <c r="I772">
-        <v>0.7056286876555262</v>
+        <v>0.85844303148329</v>
       </c>
       <c r="J772">
         <v>1.028143438277634</v>
       </c>
       <c r="K772">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L772">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M772">
         <v>23.15</v>
@@ -40243,101 +40243,101 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="773" spans="1:16">
       <c r="A773" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B773" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C773">
-        <v>2.945006871145257</v>
+        <v>4.04410809152829</v>
       </c>
       <c r="D773" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="E773">
-        <v>3.642192527317494</v>
+        <v>3.338479403872764</v>
       </c>
       <c r="F773">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G773">
-        <v>0.05445499312885474</v>
+        <v>0.05123589190847171</v>
       </c>
       <c r="H773">
-        <v>0.05535780747268251</v>
+        <v>0.05094152059612723</v>
       </c>
       <c r="I773">
-        <v>0.6971856561722376</v>
+        <v>0.7056286876555262</v>
       </c>
       <c r="J773">
         <v>1.028143438277634</v>
       </c>
       <c r="K773">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L773">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M773">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N773">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O773">
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="774" spans="1:16">
       <c r="A774" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B774" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C774">
-        <v>4.101655744450497</v>
+        <v>3.866414043059141</v>
       </c>
       <c r="D774" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E774">
-        <v>3.241961946784642</v>
+        <v>3.199228386886904</v>
       </c>
       <c r="F774">
         <v>-1</v>
       </c>
       <c r="G774">
-        <v>0.05127834425554951</v>
+        <v>0.05527358595694087</v>
       </c>
       <c r="H774">
-        <v>0.05103803805321536</v>
+        <v>0.0544007716131131</v>
       </c>
       <c r="I774">
-        <v>0.8596937976658552</v>
+        <v>0.6671856561722365</v>
       </c>
       <c r="J774">
-        <v>1.032312658886193</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K774">
-        <v>22.85</v>
+        <v>25</v>
       </c>
       <c r="L774">
-        <v>27.69</v>
+        <v>29.57</v>
       </c>
       <c r="M774">
-        <v>23.15</v>
+        <v>24.9</v>
       </c>
       <c r="N774">
-        <v>27.14</v>
+        <v>28.8</v>
       </c>
       <c r="O774">
         <v>1</v>
@@ -40348,46 +40348,46 @@
     </row>
     <row r="775" spans="1:16">
       <c r="A775" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B775" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C775">
-        <v>3.948424478561879</v>
+        <v>2.945006871145257</v>
       </c>
       <c r="D775" t="s">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="E775">
-        <v>3.241961946784642</v>
+        <v>3.642192527317494</v>
       </c>
       <c r="F775">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G775">
-        <v>0.05133157552143813</v>
+        <v>0.05445499312885474</v>
       </c>
       <c r="H775">
-        <v>0.05103803805321536</v>
+        <v>0.05535780747268251</v>
       </c>
       <c r="I775">
-        <v>0.7064625317772375</v>
+        <v>0.6971856561722376</v>
       </c>
       <c r="J775">
-        <v>1.032312658886193</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K775">
-        <v>22.95</v>
+        <v>25.05</v>
       </c>
       <c r="L775">
-        <v>27.64</v>
+        <v>28.7</v>
       </c>
       <c r="M775">
-        <v>23.15</v>
+        <v>25.15</v>
       </c>
       <c r="N775">
-        <v>27.14</v>
+        <v>29.5</v>
       </c>
       <c r="O775">
         <v>1</v>
@@ -40398,90 +40398,90 @@
     </row>
     <row r="776" spans="1:16">
       <c r="A776" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B776" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C776">
-        <v>2.840567894900875</v>
+        <v>4.101655744450497</v>
       </c>
       <c r="D776" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="E776">
-        <v>3.537336629012259</v>
+        <v>3.241961946784642</v>
       </c>
       <c r="F776">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G776">
-        <v>0.05455943210509912</v>
+        <v>0.05127834425554951</v>
       </c>
       <c r="H776">
-        <v>0.05546266337098774</v>
+        <v>0.05103803805321536</v>
       </c>
       <c r="I776">
-        <v>0.6967687341113837</v>
+        <v>0.8596937976658552</v>
       </c>
       <c r="J776">
         <v>1.032312658886193</v>
       </c>
       <c r="K776">
-        <v>25.05</v>
+        <v>22.85</v>
       </c>
       <c r="L776">
-        <v>28.7</v>
+        <v>27.69</v>
       </c>
       <c r="M776">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N776">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O776">
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="777" spans="1:16">
       <c r="A777" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B777" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C777">
-        <v>4.009505903995372</v>
+        <v>3.948424478561879</v>
       </c>
       <c r="D777" t="s">
         <v>322</v>
       </c>
       <c r="E777">
-        <v>3.148602261597063</v>
+        <v>3.241961946784642</v>
       </c>
       <c r="F777">
         <v>-1</v>
       </c>
       <c r="G777">
-        <v>0.05137049409600464</v>
+        <v>0.05133157552143813</v>
       </c>
       <c r="H777">
-        <v>0.05113139773840294</v>
+        <v>0.05103803805321536</v>
       </c>
       <c r="I777">
-        <v>0.8609036423983092</v>
+        <v>0.7064625317772375</v>
       </c>
       <c r="J777">
-        <v>1.036345474661034</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K777">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L777">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M777">
         <v>23.15</v>
@@ -40498,46 +40498,46 @@
     </row>
     <row r="778" spans="1:16">
       <c r="A778" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B778" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C778">
-        <v>3.855871356529267</v>
+        <v>3.762183527845185</v>
       </c>
       <c r="D778" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E778">
-        <v>3.148602261597063</v>
+        <v>3.095414793733806</v>
       </c>
       <c r="F778">
         <v>-1</v>
       </c>
       <c r="G778">
-        <v>0.05142412864347074</v>
+        <v>0.05537781647215482</v>
       </c>
       <c r="H778">
-        <v>0.05113139773840294</v>
+        <v>0.0545045852062662</v>
       </c>
       <c r="I778">
-        <v>0.7072690949322045</v>
+        <v>0.666768734111379</v>
       </c>
       <c r="J778">
-        <v>1.036345474661034</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K778">
-        <v>22.95</v>
+        <v>25</v>
       </c>
       <c r="L778">
-        <v>27.64</v>
+        <v>29.57</v>
       </c>
       <c r="M778">
-        <v>23.15</v>
+        <v>24.9</v>
       </c>
       <c r="N778">
-        <v>27.14</v>
+        <v>28.8</v>
       </c>
       <c r="O778">
         <v>1</v>
@@ -40548,34 +40548,34 @@
     </row>
     <row r="779" spans="1:16">
       <c r="A779" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B779" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C779">
-        <v>2.739545859741096</v>
+        <v>2.840567894900875</v>
       </c>
       <c r="D779" t="s">
         <v>193</v>
       </c>
       <c r="E779">
-        <v>3.435911312274992</v>
+        <v>3.537336629012259</v>
       </c>
       <c r="F779">
         <v>1</v>
       </c>
       <c r="G779">
-        <v>0.05466045414025891</v>
+        <v>0.05455943210509912</v>
       </c>
       <c r="H779">
-        <v>0.05556408868772501</v>
+        <v>0.05546266337098774</v>
       </c>
       <c r="I779">
-        <v>0.6963654525338967</v>
+        <v>0.6967687341113837</v>
       </c>
       <c r="J779">
-        <v>1.036345474661034</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K779">
         <v>25.05</v>
@@ -40604,28 +40604,28 @@
         <v>186</v>
       </c>
       <c r="C780">
-        <v>3.923892030831919</v>
+        <v>4.009505903995372</v>
       </c>
       <c r="D780" t="s">
         <v>322</v>
       </c>
       <c r="E780">
-        <v>3.06186435508792</v>
+        <v>3.148602261597063</v>
       </c>
       <c r="F780">
         <v>-1</v>
       </c>
       <c r="G780">
-        <v>0.05145610796916809</v>
+        <v>0.05137049409600464</v>
       </c>
       <c r="H780">
-        <v>0.05121813564491208</v>
+        <v>0.05113139773840294</v>
       </c>
       <c r="I780">
-        <v>0.8620276757439989</v>
+        <v>0.8609036423983092</v>
       </c>
       <c r="J780">
-        <v>1.040092252480004</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K780">
         <v>22.85</v>
@@ -40654,28 +40654,28 @@
         <v>187</v>
       </c>
       <c r="C781">
-        <v>3.769882805583919</v>
+        <v>3.855871356529267</v>
       </c>
       <c r="D781" t="s">
         <v>322</v>
       </c>
       <c r="E781">
-        <v>3.06186435508792</v>
+        <v>3.148602261597063</v>
       </c>
       <c r="F781">
         <v>-1</v>
       </c>
       <c r="G781">
-        <v>0.05151011719441608</v>
+        <v>0.05142412864347074</v>
       </c>
       <c r="H781">
-        <v>0.05121813564491208</v>
+        <v>0.05113139773840294</v>
       </c>
       <c r="I781">
-        <v>0.7080184504959988</v>
+        <v>0.7072690949322045</v>
       </c>
       <c r="J781">
-        <v>1.040092252480004</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K781">
         <v>22.95</v>
@@ -40701,43 +40701,43 @@
         <v>2</v>
       </c>
       <c r="B782" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C782">
-        <v>2.645689075375909</v>
+        <v>3.661363133474147</v>
       </c>
       <c r="D782" t="s">
-        <v>193</v>
+        <v>323</v>
       </c>
       <c r="E782">
-        <v>3.34167985012791</v>
+        <v>2.994997680940251</v>
       </c>
       <c r="F782">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G782">
-        <v>0.05475431092462409</v>
+        <v>0.05547863686652586</v>
       </c>
       <c r="H782">
-        <v>0.05565832014987209</v>
+        <v>0.05460500231905975</v>
       </c>
       <c r="I782">
-        <v>0.6959907747520013</v>
+        <v>0.6663654525338956</v>
       </c>
       <c r="J782">
-        <v>1.040092252480004</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K782">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="L782">
-        <v>28.7</v>
+        <v>29.57</v>
       </c>
       <c r="M782">
-        <v>25.15</v>
+        <v>24.9</v>
       </c>
       <c r="N782">
-        <v>29.5</v>
+        <v>28.8</v>
       </c>
       <c r="O782">
         <v>1</v>
@@ -40748,90 +40748,90 @@
     </row>
     <row r="783" spans="1:16">
       <c r="A783" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B783" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C783">
-        <v>3.103333239057651</v>
+        <v>2.739545859741096</v>
       </c>
       <c r="D783" t="s">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="E783">
-        <v>2.230532362546374</v>
+        <v>3.435911312274992</v>
       </c>
       <c r="F783">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G783">
-        <v>0.05227666676094235</v>
+        <v>0.05466045414025891</v>
       </c>
       <c r="H783">
-        <v>0.05204946763745363</v>
+        <v>0.05556408868772501</v>
       </c>
       <c r="I783">
-        <v>0.8728008765112776</v>
+        <v>0.6963654525338967</v>
       </c>
       <c r="J783">
-        <v>1.07600292170426</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K783">
-        <v>22.85</v>
+        <v>25.05</v>
       </c>
       <c r="L783">
-        <v>27.69</v>
+        <v>28.7</v>
       </c>
       <c r="M783">
-        <v>23.15</v>
+        <v>25.15</v>
       </c>
       <c r="N783">
-        <v>27.14</v>
+        <v>29.5</v>
       </c>
       <c r="O783">
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="784" spans="1:16">
       <c r="A784" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B784" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C784">
-        <v>2.945732946887226</v>
+        <v>3.923892030831919</v>
       </c>
       <c r="D784" t="s">
         <v>322</v>
       </c>
       <c r="E784">
-        <v>2.230532362546374</v>
+        <v>3.06186435508792</v>
       </c>
       <c r="F784">
         <v>-1</v>
       </c>
       <c r="G784">
-        <v>0.05233426705311277</v>
+        <v>0.05145610796916809</v>
       </c>
       <c r="H784">
-        <v>0.05204946763745363</v>
+        <v>0.05121813564491208</v>
       </c>
       <c r="I784">
-        <v>0.7152005843408524</v>
+        <v>0.8620276757439989</v>
       </c>
       <c r="J784">
-        <v>1.07600292170426</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K784">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L784">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M784">
         <v>23.15</v>
@@ -40848,46 +40848,46 @@
     </row>
     <row r="785" spans="1:16">
       <c r="A785" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B785" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C785">
-        <v>1.746126811308276</v>
+        <v>3.769882805583919</v>
       </c>
       <c r="D785" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="E785">
-        <v>2.438526519137852</v>
+        <v>3.06186435508792</v>
       </c>
       <c r="F785">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G785">
-        <v>0.05565387318869172</v>
+        <v>0.05151011719441608</v>
       </c>
       <c r="H785">
-        <v>0.05656147348086215</v>
+        <v>0.05121813564491208</v>
       </c>
       <c r="I785">
-        <v>0.6923997078295763</v>
+        <v>0.7080184504959988</v>
       </c>
       <c r="J785">
-        <v>1.07600292170426</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K785">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L785">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M785">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N785">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O785">
         <v>1</v>
@@ -40898,46 +40898,46 @@
     </row>
     <row r="786" spans="1:16">
       <c r="A786" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B786" t="s">
         <v>190</v>
       </c>
       <c r="C786">
-        <v>1.57592987909775</v>
+        <v>2.645689075375909</v>
       </c>
       <c r="D786" t="s">
-        <v>324</v>
+        <v>193</v>
       </c>
       <c r="E786">
-        <v>2.049328856501258</v>
+        <v>3.34167985012791</v>
       </c>
       <c r="F786">
         <v>1</v>
       </c>
       <c r="G786">
-        <v>0.05322407012090225</v>
+        <v>0.05475431092462409</v>
       </c>
       <c r="H786">
-        <v>0.05445067114349874</v>
+        <v>0.05565832014987209</v>
       </c>
       <c r="I786">
-        <v>0.4733989774035088</v>
+        <v>0.6959907747520013</v>
       </c>
       <c r="J786">
-        <v>1.07600292170426</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K786">
-        <v>24</v>
+        <v>25.05</v>
       </c>
       <c r="L786">
-        <v>27.4</v>
+        <v>28.7</v>
       </c>
       <c r="M786">
-        <v>24.35</v>
+        <v>25.15</v>
       </c>
       <c r="N786">
-        <v>28.25</v>
+        <v>29.5</v>
       </c>
       <c r="O786">
         <v>1</v>
@@ -40951,37 +40951,37 @@
         <v>0</v>
       </c>
       <c r="B787" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C787">
-        <v>1.786358263523248</v>
+        <v>3.103333239057651</v>
       </c>
       <c r="D787" t="s">
         <v>322</v>
       </c>
       <c r="E787">
-        <v>1.061054196102969</v>
+        <v>2.230532362546374</v>
       </c>
       <c r="F787">
         <v>-1</v>
       </c>
       <c r="G787">
-        <v>0.05349364173647676</v>
+        <v>0.05227666676094235</v>
       </c>
       <c r="H787">
-        <v>0.05321894580389703</v>
+        <v>0.05204946763745363</v>
       </c>
       <c r="I787">
-        <v>0.7253040674202786</v>
+        <v>0.8728008765112776</v>
       </c>
       <c r="J787">
-        <v>1.126520337101384</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K787">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L787">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M787">
         <v>23.15</v>
@@ -41001,43 +41001,43 @@
         <v>1</v>
       </c>
       <c r="B788" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C788">
-        <v>0.4806655556103365</v>
+        <v>2.945732946887226</v>
       </c>
       <c r="D788" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="E788">
-        <v>1.168013521900203</v>
+        <v>2.230532362546374</v>
       </c>
       <c r="F788">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G788">
-        <v>0.05691933444438967</v>
+        <v>0.05233426705311277</v>
       </c>
       <c r="H788">
-        <v>0.0578319864780998</v>
+        <v>0.05204946763745363</v>
       </c>
       <c r="I788">
-        <v>0.6873479662898667</v>
+        <v>0.7152005843408524</v>
       </c>
       <c r="J788">
-        <v>1.126520337101384</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K788">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L788">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M788">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N788">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O788">
         <v>1</v>
@@ -41054,40 +41054,40 @@
         <v>190</v>
       </c>
       <c r="C789">
-        <v>0.3635119095667889</v>
+        <v>1.746126811308276</v>
       </c>
       <c r="D789" t="s">
-        <v>324</v>
+        <v>193</v>
       </c>
       <c r="E789">
-        <v>0.8192297915813072</v>
+        <v>2.438526519137852</v>
       </c>
       <c r="F789">
         <v>1</v>
       </c>
       <c r="G789">
-        <v>0.05443648809043321</v>
+        <v>0.05565387318869172</v>
       </c>
       <c r="H789">
-        <v>0.0556807702084187</v>
+        <v>0.05656147348086215</v>
       </c>
       <c r="I789">
-        <v>0.4557178820145182</v>
+        <v>0.6923997078295763</v>
       </c>
       <c r="J789">
-        <v>1.126520337101384</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K789">
-        <v>24</v>
+        <v>25.05</v>
       </c>
       <c r="L789">
-        <v>27.4</v>
+        <v>28.7</v>
       </c>
       <c r="M789">
-        <v>24.35</v>
+        <v>25.15</v>
       </c>
       <c r="N789">
-        <v>28.25</v>
+        <v>29.5</v>
       </c>
       <c r="O789">
         <v>1</v>
@@ -41104,28 +41104,28 @@
         <v>187</v>
       </c>
       <c r="C790">
-        <v>1.347927144340538</v>
+        <v>1.786358263523248</v>
       </c>
       <c r="D790" t="s">
         <v>322</v>
       </c>
       <c r="E790">
-        <v>0.6188023264262945</v>
+        <v>1.061054196102969</v>
       </c>
       <c r="F790">
         <v>-1</v>
       </c>
       <c r="G790">
-        <v>0.05393207285565946</v>
+        <v>0.05349364173647676</v>
       </c>
       <c r="H790">
-        <v>0.05366119767357371</v>
+        <v>0.05321894580389703</v>
       </c>
       <c r="I790">
-        <v>0.7291248179142436</v>
+        <v>0.7253040674202786</v>
       </c>
       <c r="J790">
-        <v>1.145624089571218</v>
+        <v>1.126520337101384</v>
       </c>
       <c r="K790">
         <v>22.95</v>
@@ -41151,31 +41151,31 @@
         <v>1</v>
       </c>
       <c r="B791" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C791">
-        <v>0.002116556240977729</v>
+        <v>0.4806655556103365</v>
       </c>
       <c r="D791" t="s">
         <v>193</v>
       </c>
       <c r="E791">
-        <v>0.6875541472838584</v>
+        <v>1.168013521900203</v>
       </c>
       <c r="F791">
         <v>1</v>
       </c>
       <c r="G791">
-        <v>0.05739788344375902</v>
+        <v>0.05691933444438967</v>
       </c>
       <c r="H791">
-        <v>0.05831244585271614</v>
+        <v>0.0578319864780998</v>
       </c>
       <c r="I791">
-        <v>0.6854375910428807</v>
+        <v>0.6873479662898667</v>
       </c>
       <c r="J791">
-        <v>1.145624089571218</v>
+        <v>1.126520337101384</v>
       </c>
       <c r="K791">
         <v>25.05</v>
@@ -41198,84 +41198,84 @@
     </row>
     <row r="792" spans="1:16">
       <c r="A792" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B792" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C792">
-        <v>-0.09497814970924168</v>
+        <v>1.347927144340538</v>
       </c>
       <c r="D792" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E792">
-        <v>0.3540534189408291</v>
+        <v>0.6188023264262945</v>
       </c>
       <c r="F792">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G792">
-        <v>0.05489497814970924</v>
+        <v>0.05393207285565946</v>
       </c>
       <c r="H792">
-        <v>0.05614594658105918</v>
+        <v>0.05366119767357371</v>
       </c>
       <c r="I792">
-        <v>0.4490315686500708</v>
+        <v>0.7291248179142436</v>
       </c>
       <c r="J792">
         <v>1.145624089571218</v>
       </c>
       <c r="K792">
-        <v>24</v>
+        <v>22.95</v>
       </c>
       <c r="L792">
-        <v>27.4</v>
+        <v>27.64</v>
       </c>
       <c r="M792">
-        <v>24.35</v>
+        <v>23.15</v>
       </c>
       <c r="N792">
-        <v>28.25</v>
+        <v>27.14</v>
       </c>
       <c r="O792">
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="793" spans="1:16">
       <c r="A793" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B793" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C793">
-        <v>-0.5597363304415239</v>
+        <v>0.002116556240977729</v>
       </c>
       <c r="D793" t="s">
         <v>193</v>
       </c>
       <c r="E793">
-        <v>0.1234583349060188</v>
+        <v>0.6875541472838584</v>
       </c>
       <c r="F793">
         <v>1</v>
       </c>
       <c r="G793">
-        <v>0.05795973633044153</v>
+        <v>0.05739788344375902</v>
       </c>
       <c r="H793">
-        <v>0.05887654166509398</v>
+        <v>0.05831244585271614</v>
       </c>
       <c r="I793">
-        <v>0.6831946653475427</v>
+        <v>0.6854375910428807</v>
       </c>
       <c r="J793">
-        <v>1.168053346524612</v>
+        <v>1.145624089571218</v>
       </c>
       <c r="K793">
         <v>25.05</v>
@@ -41301,31 +41301,31 @@
         <v>0</v>
       </c>
       <c r="B794" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C794">
-        <v>-0.8369803833445317</v>
+        <v>-0.5597363304415239</v>
       </c>
       <c r="D794" t="s">
         <v>193</v>
       </c>
       <c r="E794">
-        <v>-0.1548924806832268</v>
+        <v>0.1234583349060188</v>
       </c>
       <c r="F794">
         <v>1</v>
       </c>
       <c r="G794">
-        <v>0.05823698038334453</v>
+        <v>0.05795973633044153</v>
       </c>
       <c r="H794">
-        <v>0.05915489248068323</v>
+        <v>0.05887654166509398</v>
       </c>
       <c r="I794">
-        <v>0.6820879026613049</v>
+        <v>0.6831946653475427</v>
       </c>
       <c r="J794">
-        <v>1.179120973387007</v>
+        <v>1.168053346524612</v>
       </c>
       <c r="K794">
         <v>25.05</v>
@@ -41343,7 +41343,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>187</v>
+        <v>418</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41351,31 +41351,31 @@
         <v>0</v>
       </c>
       <c r="B795" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C795">
-        <v>-1.051692264853688</v>
+        <v>-0.8369803833445317</v>
       </c>
       <c r="D795" t="s">
         <v>193</v>
       </c>
       <c r="E795">
-        <v>-0.3704614954519023</v>
+        <v>-0.1548924806832268</v>
       </c>
       <c r="F795">
         <v>1</v>
       </c>
       <c r="G795">
-        <v>0.05845169226485369</v>
+        <v>0.05823698038334453</v>
       </c>
       <c r="H795">
-        <v>0.05937046149545191</v>
+        <v>0.05915489248068323</v>
       </c>
       <c r="I795">
-        <v>0.6812307694017861</v>
+        <v>0.6820879026613049</v>
       </c>
       <c r="J795">
-        <v>1.187692305982183</v>
+        <v>1.179120973387007</v>
       </c>
       <c r="K795">
         <v>25.05</v>
@@ -41393,7 +41393,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>418</v>
+        <v>187</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -41401,43 +41401,43 @@
         <v>0</v>
       </c>
       <c r="B796" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C796">
-        <v>0.01711680463947474</v>
+        <v>-1.051692264853688</v>
       </c>
       <c r="D796" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="E796">
-        <v>-0.6346716625790805</v>
+        <v>-0.3704614954519023</v>
       </c>
       <c r="F796">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G796">
-        <v>0.05912288319536053</v>
+        <v>0.05845169226485369</v>
       </c>
       <c r="H796">
-        <v>0.05823467166257908</v>
+        <v>0.05937046149545191</v>
       </c>
       <c r="I796">
-        <v>0.6517884672185552</v>
+        <v>0.6812307694017861</v>
       </c>
       <c r="J796">
-        <v>1.182115327814421</v>
+        <v>1.187692305982183</v>
       </c>
       <c r="K796">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="L796">
-        <v>29.57</v>
+        <v>28.7</v>
       </c>
       <c r="M796">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N796">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O796">
         <v>1</v>
@@ -41451,37 +41451,37 @@
         <v>0</v>
       </c>
       <c r="B797" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C797">
-        <v>-0.1778805282432323</v>
+        <v>0.01711680463947474</v>
       </c>
       <c r="D797" t="s">
         <v>323</v>
       </c>
       <c r="E797">
-        <v>-0.6778805282432323</v>
+        <v>-0.6346716625790805</v>
       </c>
       <c r="F797">
         <v>-1</v>
       </c>
       <c r="G797">
-        <v>0.05877788052824323</v>
+        <v>0.05912288319536053</v>
       </c>
       <c r="H797">
-        <v>0.05827788052824323</v>
+        <v>0.05823467166257908</v>
       </c>
       <c r="I797">
-        <v>0.5</v>
+        <v>0.6517884672185552</v>
       </c>
       <c r="J797">
-        <v>1.183850623624226</v>
+        <v>1.182115327814421</v>
       </c>
       <c r="K797">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="L797">
-        <v>29.3</v>
+        <v>29.57</v>
       </c>
       <c r="M797">
         <v>24.9</v>
@@ -41493,18 +41493,18 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>322</v>
+        <v>420</v>
       </c>
     </row>
     <row r="798" spans="1:16">
       <c r="A798" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B798" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C798">
-        <v>-0.02626559060565725</v>
+        <v>-0.1778805282432323</v>
       </c>
       <c r="D798" t="s">
         <v>323</v>
@@ -41516,22 +41516,22 @@
         <v>-1</v>
       </c>
       <c r="G798">
-        <v>0.05916626559060566</v>
+        <v>0.05877788052824323</v>
       </c>
       <c r="H798">
         <v>0.05827788052824323</v>
       </c>
       <c r="I798">
-        <v>0.6516149376375751</v>
+        <v>0.5</v>
       </c>
       <c r="J798">
         <v>1.183850623624226</v>
       </c>
       <c r="K798">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="L798">
-        <v>29.57</v>
+        <v>29.3</v>
       </c>
       <c r="M798">
         <v>24.9</v>
@@ -41548,46 +41548,46 @@
     </row>
     <row r="799" spans="1:16">
       <c r="A799" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B799" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C799">
-        <v>-0.1794954658808123</v>
+        <v>-0.02626559060565725</v>
       </c>
       <c r="D799" t="s">
-        <v>190</v>
+        <v>323</v>
       </c>
       <c r="E799">
-        <v>-1.012414966981432</v>
+        <v>-0.6778805282432323</v>
       </c>
       <c r="F799">
         <v>-1</v>
       </c>
       <c r="G799">
-        <v>0.05853949546588081</v>
+        <v>0.05916626559060566</v>
       </c>
       <c r="H799">
-        <v>0.05581241496698143</v>
+        <v>0.05827788052824323</v>
       </c>
       <c r="I799">
-        <v>0.8329195011006192</v>
+        <v>0.6516149376375751</v>
       </c>
       <c r="J799">
         <v>1.183850623624226</v>
       </c>
       <c r="K799">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="L799">
-        <v>29.18</v>
+        <v>29.57</v>
       </c>
       <c r="M799">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="N799">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
       <c r="O799">
         <v>1</v>
@@ -41598,96 +41598,96 @@
     </row>
     <row r="800" spans="1:16">
       <c r="A800" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B800" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C800">
-        <v>0.04582245394855988</v>
+        <v>-0.1794954658808123</v>
       </c>
       <c r="D800" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E800">
-        <v>-0.6060808358672318</v>
+        <v>-1.012414966981432</v>
       </c>
       <c r="F800">
         <v>-1</v>
       </c>
       <c r="G800">
-        <v>0.05909417754605144</v>
+        <v>0.05853949546588081</v>
       </c>
       <c r="H800">
-        <v>0.05820608083586724</v>
+        <v>0.05581241496698143</v>
       </c>
       <c r="I800">
-        <v>0.6519032898157917</v>
+        <v>0.8329195011006192</v>
       </c>
       <c r="J800">
-        <v>1.180967101842058</v>
+        <v>1.183850623624226</v>
       </c>
       <c r="K800">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="L800">
-        <v>29.57</v>
+        <v>29.18</v>
       </c>
       <c r="M800">
-        <v>24.9</v>
+        <v>24</v>
       </c>
       <c r="N800">
-        <v>28.8</v>
+        <v>27.4</v>
       </c>
       <c r="O800">
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>191</v>
+        <v>322</v>
       </c>
     </row>
     <row r="801" spans="1:16">
       <c r="A801" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B801" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C801">
-        <v>-0.1079841256830285</v>
+        <v>0.04582245394855988</v>
       </c>
       <c r="D801" t="s">
-        <v>190</v>
+        <v>323</v>
       </c>
       <c r="E801">
-        <v>-0.9432104442093845</v>
+        <v>-0.6060808358672318</v>
       </c>
       <c r="F801">
         <v>-1</v>
       </c>
       <c r="G801">
-        <v>0.05846798412568303</v>
+        <v>0.05909417754605144</v>
       </c>
       <c r="H801">
-        <v>0.05574321044420939</v>
+        <v>0.05820608083586724</v>
       </c>
       <c r="I801">
-        <v>0.835226318526356</v>
+        <v>0.6519032898157917</v>
       </c>
       <c r="J801">
         <v>1.180967101842058</v>
       </c>
       <c r="K801">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="L801">
-        <v>29.18</v>
+        <v>29.57</v>
       </c>
       <c r="M801">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="N801">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
       <c r="O801">
         <v>1</v>
@@ -41698,134 +41698,134 @@
     </row>
     <row r="802" spans="1:16">
       <c r="A802" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B802" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C802">
-        <v>0.05143297331527208</v>
+        <v>-0.1079841256830285</v>
       </c>
       <c r="D802" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E802">
-        <v>-0.6004927585779853</v>
+        <v>-0.9432104442093845</v>
       </c>
       <c r="F802">
         <v>-1</v>
       </c>
       <c r="G802">
-        <v>0.05908856702668473</v>
+        <v>0.05846798412568303</v>
       </c>
       <c r="H802">
-        <v>0.05820049275857798</v>
+        <v>0.05574321044420939</v>
       </c>
       <c r="I802">
-        <v>0.6519257318932574</v>
+        <v>0.835226318526356</v>
       </c>
       <c r="J802">
-        <v>1.180742681067389</v>
+        <v>1.180967101842058</v>
       </c>
       <c r="K802">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="L802">
-        <v>29.57</v>
+        <v>29.18</v>
       </c>
       <c r="M802">
-        <v>24.9</v>
+        <v>24</v>
       </c>
       <c r="N802">
-        <v>28.8</v>
+        <v>27.4</v>
       </c>
       <c r="O802">
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>420</v>
+        <v>191</v>
       </c>
     </row>
     <row r="803" spans="1:16">
       <c r="A803" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B803" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C803">
-        <v>-0.1024184904712513</v>
+        <v>0.05143297331527208</v>
       </c>
       <c r="D803" t="s">
-        <v>190</v>
+        <v>323</v>
       </c>
       <c r="E803">
-        <v>-0.9378243456173401</v>
+        <v>-0.6004927585779853</v>
       </c>
       <c r="F803">
         <v>-1</v>
       </c>
       <c r="G803">
-        <v>0.05846241849047125</v>
+        <v>0.05908856702668473</v>
       </c>
       <c r="H803">
-        <v>0.05573782434561734</v>
+        <v>0.05820049275857798</v>
       </c>
       <c r="I803">
-        <v>0.8354058551460888</v>
+        <v>0.6519257318932574</v>
       </c>
       <c r="J803">
         <v>1.180742681067389</v>
       </c>
       <c r="K803">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="L803">
-        <v>29.18</v>
+        <v>29.57</v>
       </c>
       <c r="M803">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="N803">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
       <c r="O803">
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="804" spans="1:16">
       <c r="A804" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B804" t="s">
         <v>192</v>
       </c>
       <c r="C804">
-        <v>0.004427027548832285</v>
+        <v>-0.1024184904712513</v>
       </c>
       <c r="D804" t="s">
-        <v>190</v>
+        <v>325</v>
       </c>
       <c r="E804">
-        <v>-0.8344254572108056</v>
+        <v>-0.9378243456173401</v>
       </c>
       <c r="F804">
         <v>-1</v>
       </c>
       <c r="G804">
-        <v>0.05835557297245117</v>
+        <v>0.05846241849047125</v>
       </c>
       <c r="H804">
-        <v>0.05563442545721081</v>
+        <v>0.05573782434561734</v>
       </c>
       <c r="I804">
-        <v>0.8388524847596379</v>
+        <v>0.8354058551460888</v>
       </c>
       <c r="J804">
-        <v>1.17643439405045</v>
+        <v>1.180742681067389</v>
       </c>
       <c r="K804">
         <v>24.8</v>
@@ -41843,7 +41843,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>188</v>
+        <v>421</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -41851,37 +41851,37 @@
         <v>0</v>
       </c>
       <c r="B805" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C805">
-        <v>-0.1614163319545447</v>
+        <v>0.004427027548832285</v>
       </c>
       <c r="D805" t="s">
-        <v>190</v>
+        <v>325</v>
       </c>
       <c r="E805">
-        <v>-0.9051289052448972</v>
+        <v>-0.8344254572108056</v>
       </c>
       <c r="F805">
         <v>-1</v>
       </c>
       <c r="G805">
-        <v>0.05916141633195454</v>
+        <v>0.05835557297245117</v>
       </c>
       <c r="H805">
-        <v>0.05570512890524489</v>
+        <v>0.05563442545721081</v>
       </c>
       <c r="I805">
-        <v>0.7437125732903525</v>
+        <v>0.8388524847596379</v>
       </c>
       <c r="J805">
-        <v>1.179380371051871</v>
+        <v>1.17643439405045</v>
       </c>
       <c r="K805">
-        <v>25.15</v>
+        <v>24.8</v>
       </c>
       <c r="L805">
-        <v>29.5</v>
+        <v>29.18</v>
       </c>
       <c r="M805">
         <v>24</v>
@@ -41893,21 +41893,21 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>323</v>
+        <v>188</v>
       </c>
     </row>
     <row r="806" spans="1:16">
       <c r="A806" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B806" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C806">
-        <v>-0.06863320208639223</v>
+        <v>-0.1614163319545447</v>
       </c>
       <c r="D806" t="s">
-        <v>190</v>
+        <v>325</v>
       </c>
       <c r="E806">
         <v>-0.9051289052448972</v>
@@ -41916,22 +41916,22 @@
         <v>-1</v>
       </c>
       <c r="G806">
-        <v>0.05842863320208639</v>
+        <v>0.05916141633195454</v>
       </c>
       <c r="H806">
         <v>0.05570512890524489</v>
       </c>
       <c r="I806">
-        <v>0.836495703158505</v>
+        <v>0.7437125732903525</v>
       </c>
       <c r="J806">
         <v>1.179380371051871</v>
       </c>
       <c r="K806">
-        <v>24.8</v>
+        <v>25.15</v>
       </c>
       <c r="L806">
-        <v>29.18</v>
+        <v>29.5</v>
       </c>
       <c r="M806">
         <v>24</v>
@@ -41948,40 +41948,40 @@
     </row>
     <row r="807" spans="1:16">
       <c r="A807" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B807" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C807">
-        <v>-0.2336642408342477</v>
+        <v>-0.06863320208639223</v>
       </c>
       <c r="D807" t="s">
-        <v>190</v>
+        <v>325</v>
       </c>
       <c r="E807">
-        <v>-0.9740732318100207</v>
+        <v>-0.9051289052448972</v>
       </c>
       <c r="F807">
         <v>-1</v>
       </c>
       <c r="G807">
-        <v>0.05923366424083425</v>
+        <v>0.05842863320208639</v>
       </c>
       <c r="H807">
-        <v>0.05577407323181002</v>
+        <v>0.05570512890524489</v>
       </c>
       <c r="I807">
-        <v>0.740408990975773</v>
+        <v>0.836495703158505</v>
       </c>
       <c r="J807">
-        <v>1.182253051325417</v>
+        <v>1.179380371051871</v>
       </c>
       <c r="K807">
-        <v>25.15</v>
+        <v>24.8</v>
       </c>
       <c r="L807">
-        <v>29.5</v>
+        <v>29.18</v>
       </c>
       <c r="M807">
         <v>24</v>
@@ -41993,21 +41993,21 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>421</v>
+        <v>323</v>
       </c>
     </row>
     <row r="808" spans="1:16">
       <c r="A808" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B808" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C808">
-        <v>-0.1398756728703532</v>
+        <v>-0.2336642408342477</v>
       </c>
       <c r="D808" t="s">
-        <v>190</v>
+        <v>325</v>
       </c>
       <c r="E808">
         <v>-0.9740732318100207</v>
@@ -42016,22 +42016,22 @@
         <v>-1</v>
       </c>
       <c r="G808">
-        <v>0.05849987567287036</v>
+        <v>0.05923366424083425</v>
       </c>
       <c r="H808">
         <v>0.05577407323181002</v>
       </c>
       <c r="I808">
-        <v>0.8341975589396675</v>
+        <v>0.740408990975773</v>
       </c>
       <c r="J808">
         <v>1.182253051325417</v>
       </c>
       <c r="K808">
-        <v>24.8</v>
+        <v>25.15</v>
       </c>
       <c r="L808">
-        <v>29.18</v>
+        <v>29.5</v>
       </c>
       <c r="M808">
         <v>24</v>
@@ -42043,39 +42043,39 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>421</v>
+        <v>189</v>
       </c>
     </row>
     <row r="809" spans="1:16">
       <c r="A809" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B809" t="s">
         <v>192</v>
       </c>
       <c r="C809">
-        <v>-0.1618738323455666</v>
+        <v>-0.1398756728703532</v>
       </c>
       <c r="D809" t="s">
-        <v>190</v>
+        <v>325</v>
       </c>
       <c r="E809">
-        <v>-0.9953617732376472</v>
+        <v>-0.9740732318100207</v>
       </c>
       <c r="F809">
         <v>-1</v>
       </c>
       <c r="G809">
-        <v>0.05852187383234556</v>
+        <v>0.05849987567287036</v>
       </c>
       <c r="H809">
-        <v>0.05579536177323764</v>
+        <v>0.05577407323181002</v>
       </c>
       <c r="I809">
-        <v>0.8334879408920806</v>
+        <v>0.8341975589396675</v>
       </c>
       <c r="J809">
-        <v>1.183140073884902</v>
+        <v>1.182253051325417</v>
       </c>
       <c r="K809">
         <v>24.8</v>
@@ -42093,7 +42093,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>422</v>
+        <v>189</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42101,37 +42101,37 @@
         <v>0</v>
       </c>
       <c r="B810" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C810">
-        <v>-0.2777517985715967</v>
+        <v>-0.2559728582052792</v>
       </c>
       <c r="D810" t="s">
-        <v>190</v>
+        <v>325</v>
       </c>
       <c r="E810">
-        <v>-1.107501740553158</v>
+        <v>-0.9953617732376472</v>
       </c>
       <c r="F810">
         <v>-1</v>
       </c>
       <c r="G810">
-        <v>0.0586377517985716</v>
+        <v>0.05925597285820528</v>
       </c>
       <c r="H810">
-        <v>0.05590750174055316</v>
+        <v>0.05579536177323764</v>
       </c>
       <c r="I810">
-        <v>0.8297499419815608</v>
+        <v>0.739388915032368</v>
       </c>
       <c r="J810">
-        <v>1.187812572523048</v>
+        <v>1.183140073884902</v>
       </c>
       <c r="K810">
-        <v>24.8</v>
+        <v>25.15</v>
       </c>
       <c r="L810">
-        <v>29.18</v>
+        <v>29.5</v>
       </c>
       <c r="M810">
         <v>24</v>
@@ -42143,39 +42143,39 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>189</v>
+        <v>422</v>
       </c>
     </row>
     <row r="811" spans="1:16">
       <c r="A811" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B811" t="s">
         <v>192</v>
       </c>
       <c r="C811">
-        <v>-0.678181641571296</v>
+        <v>-0.1618738323455666</v>
       </c>
       <c r="D811" t="s">
-        <v>190</v>
+        <v>325</v>
       </c>
       <c r="E811">
-        <v>-1.495014491843193</v>
+        <v>-0.9953617732376472</v>
       </c>
       <c r="F811">
         <v>-1</v>
       </c>
       <c r="G811">
-        <v>0.0590381816415713</v>
+        <v>0.05852187383234556</v>
       </c>
       <c r="H811">
-        <v>0.05629501449184319</v>
+        <v>0.05579536177323764</v>
       </c>
       <c r="I811">
-        <v>0.8168328502718971</v>
+        <v>0.8334879408920806</v>
       </c>
       <c r="J811">
-        <v>1.203958937160133</v>
+        <v>1.183140073884902</v>
       </c>
       <c r="K811">
         <v>24.8</v>
@@ -42193,7 +42193,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42201,37 +42201,37 @@
         <v>0</v>
       </c>
       <c r="B812" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C812">
-        <v>-0.9315019397461235</v>
+        <v>-0.3734861989546587</v>
       </c>
       <c r="D812" t="s">
-        <v>190</v>
+        <v>325</v>
       </c>
       <c r="E812">
-        <v>-1.740163167496249</v>
+        <v>-1.107501740553158</v>
       </c>
       <c r="F812">
         <v>-1</v>
       </c>
       <c r="G812">
-        <v>0.05929150193974612</v>
+        <v>0.05937348619895466</v>
       </c>
       <c r="H812">
-        <v>0.05654016316749625</v>
+        <v>0.05590750174055316</v>
       </c>
       <c r="I812">
-        <v>0.8086612277501253</v>
+        <v>0.7340155415984988</v>
       </c>
       <c r="J812">
-        <v>1.214173465312344</v>
+        <v>1.187812572523048</v>
       </c>
       <c r="K812">
-        <v>24.8</v>
+        <v>25.15</v>
       </c>
       <c r="L812">
-        <v>29.18</v>
+        <v>29.5</v>
       </c>
       <c r="M812">
         <v>24</v>
@@ -42243,6 +42243,156 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="813" spans="1:16">
+      <c r="A813" s="1">
+        <v>1</v>
+      </c>
+      <c r="B813" t="s">
+        <v>192</v>
+      </c>
+      <c r="C813">
+        <v>-0.2777517985715967</v>
+      </c>
+      <c r="D813" t="s">
+        <v>325</v>
+      </c>
+      <c r="E813">
+        <v>-1.107501740553158</v>
+      </c>
+      <c r="F813">
+        <v>-1</v>
+      </c>
+      <c r="G813">
+        <v>0.0586377517985716</v>
+      </c>
+      <c r="H813">
+        <v>0.05590750174055316</v>
+      </c>
+      <c r="I813">
+        <v>0.8297499419815608</v>
+      </c>
+      <c r="J813">
+        <v>1.187812572523048</v>
+      </c>
+      <c r="K813">
+        <v>24.8</v>
+      </c>
+      <c r="L813">
+        <v>29.18</v>
+      </c>
+      <c r="M813">
+        <v>24</v>
+      </c>
+      <c r="N813">
+        <v>27.4</v>
+      </c>
+      <c r="O813">
+        <v>1</v>
+      </c>
+      <c r="P813" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="814" spans="1:16">
+      <c r="A814" s="1">
+        <v>0</v>
+      </c>
+      <c r="B814" t="s">
+        <v>192</v>
+      </c>
+      <c r="C814">
+        <v>-0.678181641571296</v>
+      </c>
+      <c r="D814" t="s">
+        <v>325</v>
+      </c>
+      <c r="E814">
+        <v>-1.495014491843193</v>
+      </c>
+      <c r="F814">
+        <v>-1</v>
+      </c>
+      <c r="G814">
+        <v>0.0590381816415713</v>
+      </c>
+      <c r="H814">
+        <v>0.05629501449184319</v>
+      </c>
+      <c r="I814">
+        <v>0.8168328502718971</v>
+      </c>
+      <c r="J814">
+        <v>1.203958937160133</v>
+      </c>
+      <c r="K814">
+        <v>24.8</v>
+      </c>
+      <c r="L814">
+        <v>29.18</v>
+      </c>
+      <c r="M814">
+        <v>24</v>
+      </c>
+      <c r="N814">
+        <v>27.4</v>
+      </c>
+      <c r="O814">
+        <v>1</v>
+      </c>
+      <c r="P814" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="815" spans="1:16">
+      <c r="A815" s="1">
+        <v>0</v>
+      </c>
+      <c r="B815" t="s">
+        <v>192</v>
+      </c>
+      <c r="C815">
+        <v>-0.9315019397461235</v>
+      </c>
+      <c r="D815" t="s">
+        <v>325</v>
+      </c>
+      <c r="E815">
+        <v>-1.740163167496249</v>
+      </c>
+      <c r="F815">
+        <v>-1</v>
+      </c>
+      <c r="G815">
+        <v>0.05929150193974612</v>
+      </c>
+      <c r="H815">
+        <v>0.05654016316749625</v>
+      </c>
+      <c r="I815">
+        <v>0.8086612277501253</v>
+      </c>
+      <c r="J815">
+        <v>1.214173465312344</v>
+      </c>
+      <c r="K815">
+        <v>24.8</v>
+      </c>
+      <c r="L815">
+        <v>29.18</v>
+      </c>
+      <c r="M815">
+        <v>24</v>
+      </c>
+      <c r="N815">
+        <v>27.4</v>
+      </c>
+      <c r="O815">
+        <v>1</v>
+      </c>
+      <c r="P815" t="s">
         <v>424</v>
       </c>
     </row>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="427">
   <si>
     <t>trade_time</t>
   </si>
@@ -583,703 +583,709 @@
     <t>2021-10-12</t>
   </si>
   <si>
+    <t>2021-10-20</t>
+  </si>
+  <si>
+    <t>2021-11-02</t>
+  </si>
+  <si>
+    <t>2021-10-08</t>
+  </si>
+  <si>
+    <t>2021-10-27</t>
+  </si>
+  <si>
+    <t>2021-10-25</t>
+  </si>
+  <si>
+    <t>2016-09-12</t>
+  </si>
+  <si>
+    <t>2016-10-17</t>
+  </si>
+  <si>
+    <t>2016-12-01</t>
+  </si>
+  <si>
+    <t>2016-12-06</t>
+  </si>
+  <si>
+    <t>2016-12-07</t>
+  </si>
+  <si>
+    <t>2016-12-08</t>
+  </si>
+  <si>
+    <t>2016-12-12</t>
+  </si>
+  <si>
+    <t>2017-03-13</t>
+  </si>
+  <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
+    <t>2017-04-28</t>
+  </si>
+  <si>
+    <t>2017-05-05</t>
+  </si>
+  <si>
+    <t>2017-06-12</t>
+  </si>
+  <si>
+    <t>2017-06-09</t>
+  </si>
+  <si>
+    <t>2017-08-17</t>
+  </si>
+  <si>
+    <t>2017-08-18</t>
+  </si>
+  <si>
+    <t>2017-08-03</t>
+  </si>
+  <si>
+    <t>2017-09-04</t>
+  </si>
+  <si>
+    <t>2017-09-06</t>
+  </si>
+  <si>
+    <t>2017-07-28</t>
+  </si>
+  <si>
+    <t>2017-09-08</t>
+  </si>
+  <si>
+    <t>2017-09-11</t>
+  </si>
+  <si>
+    <t>2017-09-13</t>
+  </si>
+  <si>
+    <t>2017-09-14</t>
+  </si>
+  <si>
+    <t>2017-09-18</t>
+  </si>
+  <si>
+    <t>2017-07-19</t>
+  </si>
+  <si>
+    <t>2017-08-29</t>
+  </si>
+  <si>
+    <t>2017-10-10</t>
+  </si>
+  <si>
+    <t>2017-10-17</t>
+  </si>
+  <si>
+    <t>2018-01-17</t>
+  </si>
+  <si>
+    <t>2018-03-01</t>
+  </si>
+  <si>
+    <t>2018-01-18</t>
+  </si>
+  <si>
+    <t>2018-04-23</t>
+  </si>
+  <si>
+    <t>2018-02-05</t>
+  </si>
+  <si>
+    <t>2018-04-24</t>
+  </si>
+  <si>
+    <t>2018-03-02</t>
+  </si>
+  <si>
+    <t>2018-03-13</t>
+  </si>
+  <si>
+    <t>2018-03-26</t>
+  </si>
+  <si>
+    <t>2018-05-14</t>
+  </si>
+  <si>
+    <t>2018-05-07</t>
+  </si>
+  <si>
+    <t>2018-05-17</t>
+  </si>
+  <si>
+    <t>2018-05-18</t>
+  </si>
+  <si>
+    <t>2018-05-04</t>
+  </si>
+  <si>
+    <t>2018-05-21</t>
+  </si>
+  <si>
+    <t>2018-05-24</t>
+  </si>
+  <si>
+    <t>2018-05-03</t>
+  </si>
+  <si>
+    <t>2018-05-25</t>
+  </si>
+  <si>
+    <t>2018-05-31</t>
+  </si>
+  <si>
+    <t>2018-05-29</t>
+  </si>
+  <si>
+    <t>2018-06-13</t>
+  </si>
+  <si>
+    <t>2018-06-12</t>
+  </si>
+  <si>
+    <t>2018-06-20</t>
+  </si>
+  <si>
+    <t>2018-07-10</t>
+  </si>
+  <si>
+    <t>2018-08-23</t>
+  </si>
+  <si>
+    <t>2018-08-27</t>
+  </si>
+  <si>
+    <t>2018-08-28</t>
+  </si>
+  <si>
+    <t>2018-08-29</t>
+  </si>
+  <si>
+    <t>2018-08-30</t>
+  </si>
+  <si>
+    <t>2018-09-04</t>
+  </si>
+  <si>
+    <t>2018-09-10</t>
+  </si>
+  <si>
+    <t>2018-07-26</t>
+  </si>
+  <si>
+    <t>2018-09-21</t>
+  </si>
+  <si>
+    <t>2018-09-27</t>
+  </si>
+  <si>
+    <t>2018-09-28</t>
+  </si>
+  <si>
+    <t>2018-10-09</t>
+  </si>
+  <si>
+    <t>2018-10-10</t>
+  </si>
+  <si>
+    <t>2018-10-11</t>
+  </si>
+  <si>
+    <t>2018-10-12</t>
+  </si>
+  <si>
+    <t>2018-10-15</t>
+  </si>
+  <si>
+    <t>2018-10-16</t>
+  </si>
+  <si>
+    <t>2018-10-18</t>
+  </si>
+  <si>
+    <t>2018-10-19</t>
+  </si>
+  <si>
+    <t>2019-02-20</t>
+  </si>
+  <si>
+    <t>2019-03-12</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2019-06-12</t>
+  </si>
+  <si>
+    <t>2019-07-15</t>
+  </si>
+  <si>
+    <t>2019-07-16</t>
+  </si>
+  <si>
+    <t>2019-05-28</t>
+  </si>
+  <si>
+    <t>2019-06-05</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>2019-07-22</t>
+  </si>
+  <si>
+    <t>2019-08-23</t>
+  </si>
+  <si>
+    <t>2019-09-02</t>
+  </si>
+  <si>
+    <t>2019-09-03</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-09-04</t>
+  </si>
+  <si>
+    <t>2019-08-06</t>
+  </si>
+  <si>
+    <t>2019-09-09</t>
+  </si>
+  <si>
+    <t>2019-09-10</t>
+  </si>
+  <si>
+    <t>2019-09-17</t>
+  </si>
+  <si>
+    <t>2019-09-18</t>
+  </si>
+  <si>
+    <t>2019-12-05</t>
+  </si>
+  <si>
+    <t>2020-02-03</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-04-15</t>
+  </si>
+  <si>
+    <t>2020-04-16</t>
+  </si>
+  <si>
+    <t>2020-04-17</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>2020-04-21</t>
+  </si>
+  <si>
+    <t>2020-04-22</t>
+  </si>
+  <si>
+    <t>2020-04-23</t>
+  </si>
+  <si>
+    <t>2020-03-26</t>
+  </si>
+  <si>
+    <t>2020-05-14</t>
+  </si>
+  <si>
+    <t>2020-06-11</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>2020-07-07</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>2020-07-13</t>
+  </si>
+  <si>
+    <t>2020-07-14</t>
+  </si>
+  <si>
+    <t>2020-07-16</t>
+  </si>
+  <si>
+    <t>2020-07-17</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>2020-07-22</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-24</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>2020-07-28</t>
+  </si>
+  <si>
+    <t>2020-07-29</t>
+  </si>
+  <si>
+    <t>2020-07-30</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>2020-08-04</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>2021-10-15</t>
+  </si>
+  <si>
+    <t>2021-10-22</t>
+  </si>
+  <si>
+    <t>2021-11-03</t>
+  </si>
+  <si>
+    <t>2021-10-29</t>
+  </si>
+  <si>
+    <t>2016-07-29</t>
+  </si>
+  <si>
+    <t>2016-08-05</t>
+  </si>
+  <si>
+    <t>2016-08-08</t>
+  </si>
+  <si>
+    <t>2016-08-10</t>
+  </si>
+  <si>
+    <t>2017-02-06</t>
+  </si>
+  <si>
+    <t>2017-02-07</t>
+  </si>
+  <si>
+    <t>2017-02-13</t>
+  </si>
+  <si>
+    <t>2017-02-15</t>
+  </si>
+  <si>
+    <t>2017-04-24</t>
+  </si>
+  <si>
+    <t>2017-04-25</t>
+  </si>
+  <si>
+    <t>2017-05-11</t>
+  </si>
+  <si>
+    <t>2017-05-17</t>
+  </si>
+  <si>
+    <t>2017-05-18</t>
+  </si>
+  <si>
+    <t>2017-05-19</t>
+  </si>
+  <si>
+    <t>2017-05-25</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-12-14</t>
+  </si>
+  <si>
+    <t>2017-12-15</t>
+  </si>
+  <si>
+    <t>2017-12-18</t>
+  </si>
+  <si>
+    <t>2017-12-19</t>
+  </si>
+  <si>
+    <t>2017-12-20</t>
+  </si>
+  <si>
+    <t>2018-01-08</t>
+  </si>
+  <si>
+    <t>2018-01-09</t>
+  </si>
+  <si>
+    <t>2018-01-11</t>
+  </si>
+  <si>
+    <t>2018-01-16</t>
+  </si>
+  <si>
+    <t>2018-01-19</t>
+  </si>
+  <si>
+    <t>2018-01-31</t>
+  </si>
+  <si>
+    <t>2018-02-08</t>
+  </si>
+  <si>
+    <t>2018-02-09</t>
+  </si>
+  <si>
+    <t>2018-02-12</t>
+  </si>
+  <si>
+    <t>2018-02-22</t>
+  </si>
+  <si>
+    <t>2018-03-07</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-05-02</t>
+  </si>
+  <si>
+    <t>2018-05-09</t>
+  </si>
+  <si>
+    <t>2018-05-10</t>
+  </si>
+  <si>
+    <t>2018-05-15</t>
+  </si>
+  <si>
+    <t>2018-06-04</t>
+  </si>
+  <si>
+    <t>2018-06-11</t>
+  </si>
+  <si>
+    <t>2019-01-07</t>
+  </si>
+  <si>
+    <t>2019-01-08</t>
+  </si>
+  <si>
+    <t>2019-01-09</t>
+  </si>
+  <si>
+    <t>2019-01-10</t>
+  </si>
+  <si>
+    <t>2019-01-11</t>
+  </si>
+  <si>
+    <t>2019-01-14</t>
+  </si>
+  <si>
+    <t>2019-02-01</t>
+  </si>
+  <si>
+    <t>2019-02-11</t>
+  </si>
+  <si>
+    <t>2019-03-13</t>
+  </si>
+  <si>
+    <t>2019-03-14</t>
+  </si>
+  <si>
+    <t>2019-03-18</t>
+  </si>
+  <si>
+    <t>2019-05-10</t>
+  </si>
+  <si>
+    <t>2019-05-14</t>
+  </si>
+  <si>
+    <t>2019-05-17</t>
+  </si>
+  <si>
+    <t>2019-05-20</t>
+  </si>
+  <si>
+    <t>2019-05-24</t>
+  </si>
+  <si>
+    <t>2019-11-08</t>
+  </si>
+  <si>
+    <t>2019-12-10</t>
+  </si>
+  <si>
+    <t>2019-12-11</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2019-12-13</t>
+  </si>
+  <si>
+    <t>2019-12-16</t>
+  </si>
+  <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
+    <t>2019-12-18</t>
+  </si>
+  <si>
+    <t>2019-12-19</t>
+  </si>
+  <si>
+    <t>2020-02-27</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-09</t>
+  </si>
+  <si>
+    <t>2020-03-11</t>
+  </si>
+  <si>
+    <t>2020-03-13</t>
+  </si>
+  <si>
+    <t>2020-03-16</t>
+  </si>
+  <si>
+    <t>2020-03-17</t>
+  </si>
+  <si>
+    <t>2020-03-19</t>
+  </si>
+  <si>
+    <t>2020-03-20</t>
+  </si>
+  <si>
+    <t>2020-03-23</t>
+  </si>
+  <si>
+    <t>2020-03-24</t>
+  </si>
+  <si>
+    <t>2020-03-25</t>
+  </si>
+  <si>
+    <t>2020-03-27</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>2021-08-23</t>
+  </si>
+  <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
+    <t>2021-08-31</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-09-02</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>2021-09-10</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>2021-09-23</t>
+  </si>
+  <si>
+    <t>2021-09-24</t>
+  </si>
+  <si>
+    <t>2021-09-28</t>
+  </si>
+  <si>
+    <t>2021-09-29</t>
+  </si>
+  <si>
+    <t>2021-10-11</t>
+  </si>
+  <si>
     <t>2021-10-18</t>
-  </si>
-  <si>
-    <t>2021-10-20</t>
-  </si>
-  <si>
-    <t>2021-10-08</t>
-  </si>
-  <si>
-    <t>2021-10-27</t>
-  </si>
-  <si>
-    <t>2021-10-25</t>
-  </si>
-  <si>
-    <t>2016-09-12</t>
-  </si>
-  <si>
-    <t>2016-10-17</t>
-  </si>
-  <si>
-    <t>2016-12-01</t>
-  </si>
-  <si>
-    <t>2016-12-06</t>
-  </si>
-  <si>
-    <t>2016-12-07</t>
-  </si>
-  <si>
-    <t>2016-12-08</t>
-  </si>
-  <si>
-    <t>2016-12-12</t>
-  </si>
-  <si>
-    <t>2017-03-13</t>
-  </si>
-  <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
-    <t>2017-04-28</t>
-  </si>
-  <si>
-    <t>2017-05-05</t>
-  </si>
-  <si>
-    <t>2017-06-12</t>
-  </si>
-  <si>
-    <t>2017-06-09</t>
-  </si>
-  <si>
-    <t>2017-08-17</t>
-  </si>
-  <si>
-    <t>2017-08-18</t>
-  </si>
-  <si>
-    <t>2017-08-03</t>
-  </si>
-  <si>
-    <t>2017-09-04</t>
-  </si>
-  <si>
-    <t>2017-09-06</t>
-  </si>
-  <si>
-    <t>2017-07-28</t>
-  </si>
-  <si>
-    <t>2017-09-08</t>
-  </si>
-  <si>
-    <t>2017-09-11</t>
-  </si>
-  <si>
-    <t>2017-09-13</t>
-  </si>
-  <si>
-    <t>2017-09-14</t>
-  </si>
-  <si>
-    <t>2017-09-18</t>
-  </si>
-  <si>
-    <t>2017-07-19</t>
-  </si>
-  <si>
-    <t>2017-08-29</t>
-  </si>
-  <si>
-    <t>2017-10-10</t>
-  </si>
-  <si>
-    <t>2017-10-17</t>
-  </si>
-  <si>
-    <t>2018-01-17</t>
-  </si>
-  <si>
-    <t>2018-03-01</t>
-  </si>
-  <si>
-    <t>2018-01-18</t>
-  </si>
-  <si>
-    <t>2018-04-23</t>
-  </si>
-  <si>
-    <t>2018-02-05</t>
-  </si>
-  <si>
-    <t>2018-04-24</t>
-  </si>
-  <si>
-    <t>2018-03-02</t>
-  </si>
-  <si>
-    <t>2018-03-13</t>
-  </si>
-  <si>
-    <t>2018-03-26</t>
-  </si>
-  <si>
-    <t>2018-05-14</t>
-  </si>
-  <si>
-    <t>2018-05-07</t>
-  </si>
-  <si>
-    <t>2018-05-17</t>
-  </si>
-  <si>
-    <t>2018-05-18</t>
-  </si>
-  <si>
-    <t>2018-05-04</t>
-  </si>
-  <si>
-    <t>2018-05-21</t>
-  </si>
-  <si>
-    <t>2018-05-24</t>
-  </si>
-  <si>
-    <t>2018-05-03</t>
-  </si>
-  <si>
-    <t>2018-05-25</t>
-  </si>
-  <si>
-    <t>2018-05-31</t>
-  </si>
-  <si>
-    <t>2018-05-29</t>
-  </si>
-  <si>
-    <t>2018-06-13</t>
-  </si>
-  <si>
-    <t>2018-06-12</t>
-  </si>
-  <si>
-    <t>2018-06-20</t>
-  </si>
-  <si>
-    <t>2018-07-10</t>
-  </si>
-  <si>
-    <t>2018-08-23</t>
-  </si>
-  <si>
-    <t>2018-08-27</t>
-  </si>
-  <si>
-    <t>2018-08-28</t>
-  </si>
-  <si>
-    <t>2018-08-29</t>
-  </si>
-  <si>
-    <t>2018-08-30</t>
-  </si>
-  <si>
-    <t>2018-09-04</t>
-  </si>
-  <si>
-    <t>2018-09-10</t>
-  </si>
-  <si>
-    <t>2018-07-26</t>
-  </si>
-  <si>
-    <t>2018-09-21</t>
-  </si>
-  <si>
-    <t>2018-09-27</t>
-  </si>
-  <si>
-    <t>2018-09-28</t>
-  </si>
-  <si>
-    <t>2018-10-09</t>
-  </si>
-  <si>
-    <t>2018-10-10</t>
-  </si>
-  <si>
-    <t>2018-10-11</t>
-  </si>
-  <si>
-    <t>2018-10-12</t>
-  </si>
-  <si>
-    <t>2018-10-15</t>
-  </si>
-  <si>
-    <t>2018-10-16</t>
-  </si>
-  <si>
-    <t>2018-10-18</t>
-  </si>
-  <si>
-    <t>2018-10-19</t>
-  </si>
-  <si>
-    <t>2019-02-20</t>
-  </si>
-  <si>
-    <t>2019-03-12</t>
-  </si>
-  <si>
-    <t>2019-05-09</t>
-  </si>
-  <si>
-    <t>2019-06-12</t>
-  </si>
-  <si>
-    <t>2019-07-15</t>
-  </si>
-  <si>
-    <t>2019-07-16</t>
-  </si>
-  <si>
-    <t>2019-05-28</t>
-  </si>
-  <si>
-    <t>2019-06-05</t>
-  </si>
-  <si>
-    <t>2019-06-25</t>
-  </si>
-  <si>
-    <t>2019-07-22</t>
-  </si>
-  <si>
-    <t>2019-08-23</t>
-  </si>
-  <si>
-    <t>2019-09-02</t>
-  </si>
-  <si>
-    <t>2019-09-03</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-09-04</t>
-  </si>
-  <si>
-    <t>2019-08-06</t>
-  </si>
-  <si>
-    <t>2019-09-09</t>
-  </si>
-  <si>
-    <t>2019-09-10</t>
-  </si>
-  <si>
-    <t>2019-09-17</t>
-  </si>
-  <si>
-    <t>2019-09-18</t>
-  </si>
-  <si>
-    <t>2019-12-05</t>
-  </si>
-  <si>
-    <t>2020-02-03</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-04-15</t>
-  </si>
-  <si>
-    <t>2020-04-16</t>
-  </si>
-  <si>
-    <t>2020-04-17</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>2020-04-21</t>
-  </si>
-  <si>
-    <t>2020-04-22</t>
-  </si>
-  <si>
-    <t>2020-04-23</t>
-  </si>
-  <si>
-    <t>2020-03-26</t>
-  </si>
-  <si>
-    <t>2020-05-14</t>
-  </si>
-  <si>
-    <t>2020-06-11</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>2020-07-07</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>2020-07-13</t>
-  </si>
-  <si>
-    <t>2020-07-14</t>
-  </si>
-  <si>
-    <t>2020-07-16</t>
-  </si>
-  <si>
-    <t>2020-07-17</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>2020-07-22</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-24</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>2020-07-28</t>
-  </si>
-  <si>
-    <t>2020-07-29</t>
-  </si>
-  <si>
-    <t>2020-07-30</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>2020-08-04</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>2021-10-15</t>
-  </si>
-  <si>
-    <t>2021-10-22</t>
-  </si>
-  <si>
-    <t>2021-10-29</t>
-  </si>
-  <si>
-    <t>2016-07-29</t>
-  </si>
-  <si>
-    <t>2016-08-05</t>
-  </si>
-  <si>
-    <t>2016-08-08</t>
-  </si>
-  <si>
-    <t>2016-08-10</t>
-  </si>
-  <si>
-    <t>2017-02-06</t>
-  </si>
-  <si>
-    <t>2017-02-07</t>
-  </si>
-  <si>
-    <t>2017-02-13</t>
-  </si>
-  <si>
-    <t>2017-02-15</t>
-  </si>
-  <si>
-    <t>2017-04-24</t>
-  </si>
-  <si>
-    <t>2017-04-25</t>
-  </si>
-  <si>
-    <t>2017-05-11</t>
-  </si>
-  <si>
-    <t>2017-05-17</t>
-  </si>
-  <si>
-    <t>2017-05-18</t>
-  </si>
-  <si>
-    <t>2017-05-19</t>
-  </si>
-  <si>
-    <t>2017-05-25</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-12-14</t>
-  </si>
-  <si>
-    <t>2017-12-15</t>
-  </si>
-  <si>
-    <t>2017-12-18</t>
-  </si>
-  <si>
-    <t>2017-12-19</t>
-  </si>
-  <si>
-    <t>2017-12-20</t>
-  </si>
-  <si>
-    <t>2018-01-08</t>
-  </si>
-  <si>
-    <t>2018-01-09</t>
-  </si>
-  <si>
-    <t>2018-01-11</t>
-  </si>
-  <si>
-    <t>2018-01-16</t>
-  </si>
-  <si>
-    <t>2018-01-19</t>
-  </si>
-  <si>
-    <t>2018-01-31</t>
-  </si>
-  <si>
-    <t>2018-02-08</t>
-  </si>
-  <si>
-    <t>2018-02-09</t>
-  </si>
-  <si>
-    <t>2018-02-12</t>
-  </si>
-  <si>
-    <t>2018-02-22</t>
-  </si>
-  <si>
-    <t>2018-03-07</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-05-02</t>
-  </si>
-  <si>
-    <t>2018-05-09</t>
-  </si>
-  <si>
-    <t>2018-05-10</t>
-  </si>
-  <si>
-    <t>2018-05-15</t>
-  </si>
-  <si>
-    <t>2018-06-04</t>
-  </si>
-  <si>
-    <t>2018-06-11</t>
-  </si>
-  <si>
-    <t>2019-01-07</t>
-  </si>
-  <si>
-    <t>2019-01-08</t>
-  </si>
-  <si>
-    <t>2019-01-09</t>
-  </si>
-  <si>
-    <t>2019-01-10</t>
-  </si>
-  <si>
-    <t>2019-01-11</t>
-  </si>
-  <si>
-    <t>2019-01-14</t>
-  </si>
-  <si>
-    <t>2019-02-01</t>
-  </si>
-  <si>
-    <t>2019-02-11</t>
-  </si>
-  <si>
-    <t>2019-03-13</t>
-  </si>
-  <si>
-    <t>2019-03-14</t>
-  </si>
-  <si>
-    <t>2019-03-18</t>
-  </si>
-  <si>
-    <t>2019-05-10</t>
-  </si>
-  <si>
-    <t>2019-05-14</t>
-  </si>
-  <si>
-    <t>2019-05-17</t>
-  </si>
-  <si>
-    <t>2019-05-20</t>
-  </si>
-  <si>
-    <t>2019-05-24</t>
-  </si>
-  <si>
-    <t>2019-11-08</t>
-  </si>
-  <si>
-    <t>2019-12-10</t>
-  </si>
-  <si>
-    <t>2019-12-11</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2019-12-13</t>
-  </si>
-  <si>
-    <t>2019-12-16</t>
-  </si>
-  <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
-    <t>2019-12-18</t>
-  </si>
-  <si>
-    <t>2019-12-19</t>
-  </si>
-  <si>
-    <t>2020-02-27</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-09</t>
-  </si>
-  <si>
-    <t>2020-03-11</t>
-  </si>
-  <si>
-    <t>2020-03-13</t>
-  </si>
-  <si>
-    <t>2020-03-16</t>
-  </si>
-  <si>
-    <t>2020-03-17</t>
-  </si>
-  <si>
-    <t>2020-03-19</t>
-  </si>
-  <si>
-    <t>2020-03-20</t>
-  </si>
-  <si>
-    <t>2020-03-23</t>
-  </si>
-  <si>
-    <t>2020-03-24</t>
-  </si>
-  <si>
-    <t>2020-03-25</t>
-  </si>
-  <si>
-    <t>2020-03-27</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>2021-08-23</t>
-  </si>
-  <si>
-    <t>2021-08-27</t>
-  </si>
-  <si>
-    <t>2021-08-31</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
-    <t>2021-09-02</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>2021-09-10</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>2021-09-23</t>
-  </si>
-  <si>
-    <t>2021-09-24</t>
-  </si>
-  <si>
-    <t>2021-09-28</t>
-  </si>
-  <si>
-    <t>2021-09-29</t>
-  </si>
-  <si>
-    <t>2021-10-11</t>
   </si>
   <si>
     <t>2021-10-19</t>
@@ -1743,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1793,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1843,7 +1849,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1893,7 +1899,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1943,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2193,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2243,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2293,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2343,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2393,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2443,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2493,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2543,7 +2549,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2593,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2643,7 +2649,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2693,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2743,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2793,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2843,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2893,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2943,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2993,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3043,7 +3049,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3093,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3143,7 +3149,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3193,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3243,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3293,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3343,7 +3349,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3393,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3443,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3493,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3543,7 +3549,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3593,7 +3599,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3643,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3693,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3743,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3793,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3843,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3893,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3943,7 +3949,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3993,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4043,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4093,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4143,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4193,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4243,7 +4249,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4293,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4343,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4393,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4443,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4493,7 +4499,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4543,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4593,7 +4599,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4643,7 +4649,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4993,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5043,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5093,7 +5099,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5143,7 +5149,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5193,7 +5199,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5543,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5593,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5643,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5693,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5743,7 +5749,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5793,7 +5799,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5843,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5893,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5943,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5993,7 +5999,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6043,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6093,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6143,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6193,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6243,7 +6249,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6293,7 +6299,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6343,7 +6349,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6393,7 +6399,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6443,7 +6449,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6493,7 +6499,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6543,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6593,7 +6599,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6643,7 +6649,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6693,7 +6699,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6743,7 +6749,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6793,7 +6799,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6843,7 +6849,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6893,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6943,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6993,7 +6999,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7043,7 +7049,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7093,7 +7099,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7143,7 +7149,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7193,7 +7199,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7243,7 +7249,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7293,7 +7299,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7343,7 +7349,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7393,7 +7399,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7443,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7493,7 +7499,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7543,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7593,7 +7599,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7643,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7693,7 +7699,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7743,7 +7749,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7793,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7843,7 +7849,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8243,7 +8249,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8293,7 +8299,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8343,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8393,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8443,7 +8449,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8493,7 +8499,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8543,7 +8549,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8593,7 +8599,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9443,7 +9449,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9493,7 +9499,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9543,7 +9549,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9593,7 +9599,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9643,7 +9649,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9693,7 +9699,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9743,7 +9749,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9793,7 +9799,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10643,7 +10649,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10693,7 +10699,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10743,7 +10749,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10793,7 +10799,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10843,7 +10849,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10893,7 +10899,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10943,7 +10949,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10993,7 +10999,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11443,7 +11449,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11493,7 +11499,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11543,7 +11549,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11593,7 +11599,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11643,7 +11649,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11693,7 +11699,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11743,7 +11749,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11793,7 +11799,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12193,7 +12199,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12243,7 +12249,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12293,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12343,7 +12349,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12393,7 +12399,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12443,7 +12449,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12493,7 +12499,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12543,7 +12549,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12593,7 +12599,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12643,7 +12649,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12693,7 +12699,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12743,7 +12749,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12793,7 +12799,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12843,7 +12849,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12893,7 +12899,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12943,7 +12949,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12993,7 +12999,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13043,7 +13049,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13093,7 +13099,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13143,7 +13149,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13193,7 +13199,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13243,7 +13249,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13293,7 +13299,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13343,7 +13349,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13393,7 +13399,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13443,7 +13449,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13493,7 +13499,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13543,7 +13549,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13593,7 +13599,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13643,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13693,7 +13699,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13743,7 +13749,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13793,7 +13799,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13843,7 +13849,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14193,7 +14199,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14243,7 +14249,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14293,7 +14299,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14343,7 +14349,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14393,7 +14399,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14443,7 +14449,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14493,7 +14499,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14543,7 +14549,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14593,7 +14599,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14643,7 +14649,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14693,7 +14699,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14743,7 +14749,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14793,7 +14799,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14843,7 +14849,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14893,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14943,7 +14949,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14993,7 +14999,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15043,7 +15049,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -16193,7 +16199,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16243,7 +16249,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16293,7 +16299,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16343,7 +16349,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16393,7 +16399,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16443,7 +16449,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16493,7 +16499,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16543,7 +16549,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16593,7 +16599,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16643,7 +16649,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -18293,7 +18299,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18343,7 +18349,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18393,7 +18399,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18443,7 +18449,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18493,7 +18499,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18543,7 +18549,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18743,7 +18749,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18793,7 +18799,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19143,7 +19149,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19193,7 +19199,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19243,7 +19249,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19743,7 +19749,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19793,7 +19799,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19843,7 +19849,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20593,7 +20599,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20643,7 +20649,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20693,7 +20699,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20743,7 +20749,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20793,7 +20799,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20843,7 +20849,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20893,7 +20899,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20943,7 +20949,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20993,7 +20999,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21043,7 +21049,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21093,7 +21099,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21143,7 +21149,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21193,7 +21199,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21243,7 +21249,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21293,7 +21299,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21343,7 +21349,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21393,7 +21399,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21443,7 +21449,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21493,7 +21499,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21543,7 +21549,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21593,7 +21599,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21643,7 +21649,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21693,7 +21699,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21743,7 +21749,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21793,7 +21799,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21843,7 +21849,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21893,7 +21899,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21943,7 +21949,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21993,7 +21999,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22043,7 +22049,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22093,7 +22099,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22143,7 +22149,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22193,7 +22199,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22243,7 +22249,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22293,7 +22299,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22343,7 +22349,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22393,7 +22399,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22893,7 +22899,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22943,7 +22949,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22993,7 +22999,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23043,7 +23049,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23093,7 +23099,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23143,7 +23149,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23193,7 +23199,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23243,7 +23249,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23293,7 +23299,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23343,7 +23349,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23393,7 +23399,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23443,7 +23449,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23493,7 +23499,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23543,7 +23549,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23593,7 +23599,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23643,7 +23649,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23693,7 +23699,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23743,7 +23749,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23793,7 +23799,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23843,7 +23849,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23893,7 +23899,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23943,7 +23949,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23993,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24043,7 +24049,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24093,7 +24099,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24143,7 +24149,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24193,7 +24199,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24243,7 +24249,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24293,7 +24299,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24343,7 +24349,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24393,7 +24399,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24443,7 +24449,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24493,7 +24499,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24543,7 +24549,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24593,7 +24599,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24643,7 +24649,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24693,7 +24699,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24743,7 +24749,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24793,7 +24799,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24843,7 +24849,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25793,7 +25799,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25843,7 +25849,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25893,7 +25899,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25943,7 +25949,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25993,7 +25999,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26043,7 +26049,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26093,7 +26099,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26143,7 +26149,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26193,7 +26199,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26243,7 +26249,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26293,7 +26299,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26343,7 +26349,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26393,7 +26399,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26443,7 +26449,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26493,7 +26499,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26543,7 +26549,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26593,7 +26599,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26643,7 +26649,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26693,7 +26699,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26743,7 +26749,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26793,7 +26799,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26843,7 +26849,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26893,7 +26899,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26943,7 +26949,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26993,7 +26999,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27043,7 +27049,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27093,7 +27099,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27143,7 +27149,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27193,7 +27199,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27243,7 +27249,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27293,7 +27299,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27343,7 +27349,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27393,7 +27399,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27443,7 +27449,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27493,7 +27499,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27543,7 +27549,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27593,7 +27599,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27643,7 +27649,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27693,7 +27699,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27743,7 +27749,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27793,7 +27799,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27843,7 +27849,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27893,7 +27899,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27943,7 +27949,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27993,7 +27999,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28043,7 +28049,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28093,7 +28099,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28143,7 +28149,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28193,7 +28199,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28243,7 +28249,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28293,7 +28299,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28343,7 +28349,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28843,7 +28849,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28893,7 +28899,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28943,7 +28949,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28993,7 +28999,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29043,7 +29049,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29093,7 +29099,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29143,7 +29149,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29193,7 +29199,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29243,7 +29249,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29293,7 +29299,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29343,7 +29349,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29393,7 +29399,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29443,7 +29449,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29493,7 +29499,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29543,7 +29549,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29593,7 +29599,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29643,7 +29649,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29693,7 +29699,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29743,7 +29749,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29793,7 +29799,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29843,7 +29849,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29893,7 +29899,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29943,7 +29949,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -29993,7 +29999,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30043,7 +30049,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30093,7 +30099,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30143,7 +30149,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30193,7 +30199,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30243,7 +30249,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30293,7 +30299,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30343,7 +30349,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30393,7 +30399,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30443,7 +30449,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30493,7 +30499,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30543,7 +30549,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30593,7 +30599,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30643,7 +30649,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30693,7 +30699,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30743,7 +30749,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30793,7 +30799,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30843,7 +30849,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30893,7 +30899,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30943,7 +30949,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31393,7 +31399,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31443,7 +31449,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31493,7 +31499,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31543,7 +31549,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31593,7 +31599,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31643,7 +31649,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31693,7 +31699,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31743,7 +31749,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31793,7 +31799,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31843,7 +31849,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31893,7 +31899,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -31943,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -31993,7 +31999,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32043,7 +32049,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32093,7 +32099,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32143,7 +32149,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32893,7 +32899,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32943,7 +32949,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -32993,7 +32999,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33043,7 +33049,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33093,7 +33099,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33143,7 +33149,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33193,7 +33199,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33243,7 +33249,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33293,7 +33299,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33343,7 +33349,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33393,7 +33399,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33443,7 +33449,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33493,7 +33499,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33543,7 +33549,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33893,7 +33899,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33943,7 +33949,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -33993,7 +33999,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34043,7 +34049,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34093,7 +34099,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34143,7 +34149,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34443,7 +34449,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34493,7 +34499,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34543,7 +34549,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34593,7 +34599,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34643,7 +34649,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34693,7 +34699,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34743,7 +34749,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34793,7 +34799,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34843,7 +34849,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34893,7 +34899,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34943,7 +34949,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -34993,7 +34999,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35043,7 +35049,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35093,7 +35099,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35143,7 +35149,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35193,7 +35199,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35243,7 +35249,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35293,7 +35299,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35343,7 +35349,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35693,7 +35699,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35743,7 +35749,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35793,7 +35799,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35843,7 +35849,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35893,7 +35899,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35943,7 +35949,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -35993,7 +35999,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36043,7 +36049,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36093,7 +36099,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36143,7 +36149,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36193,7 +36199,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36243,7 +36249,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36293,7 +36299,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36343,7 +36349,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36393,7 +36399,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36443,7 +36449,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36493,7 +36499,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36543,7 +36549,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36593,7 +36599,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36643,7 +36649,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36693,7 +36699,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36743,7 +36749,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36793,7 +36799,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36843,7 +36849,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36893,7 +36899,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36943,7 +36949,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -36993,7 +36999,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37043,7 +37049,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37093,7 +37099,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37143,7 +37149,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37193,7 +37199,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37243,7 +37249,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37643,7 +37649,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37693,7 +37699,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37743,7 +37749,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37793,7 +37799,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37843,7 +37849,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -37893,7 +37899,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -37943,7 +37949,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38593,7 +38599,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38643,7 +38649,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38693,7 +38699,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38743,7 +38749,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38793,7 +38799,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38843,7 +38849,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38893,7 +38899,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38943,7 +38949,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -38993,7 +38999,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39043,7 +39049,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39093,7 +39099,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39143,7 +39149,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39193,7 +39199,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39243,7 +39249,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39293,7 +39299,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39304,7 +39310,7 @@
         <v>189</v>
       </c>
       <c r="C754">
-        <v>4.375715917325948</v>
+        <v>4.163922260811965</v>
       </c>
       <c r="D754" t="s">
         <v>324</v>
@@ -39316,22 +39322,22 @@
         <v>1</v>
       </c>
       <c r="G754">
-        <v>0.05266428408267405</v>
+        <v>0.05323607773918804</v>
       </c>
       <c r="H754">
         <v>0.05496376822395901</v>
       </c>
       <c r="I754">
-        <v>0.3405158587150474</v>
+        <v>0.5523095152290303</v>
       </c>
       <c r="J754">
         <v>0.9794841412849514</v>
       </c>
       <c r="K754">
-        <v>24.65</v>
+        <v>25.05</v>
       </c>
       <c r="L754">
-        <v>28.52</v>
+        <v>28.7</v>
       </c>
       <c r="M754">
         <v>25.65</v>
@@ -39343,68 +39349,68 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="755" spans="1:16">
       <c r="A755" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B755" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C755">
-        <v>4.163922260811965</v>
+        <v>4.821954240451266</v>
       </c>
       <c r="D755" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E755">
-        <v>4.716231776040996</v>
+        <v>3.971717315818243</v>
       </c>
       <c r="F755">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G755">
-        <v>0.05323607773918804</v>
+        <v>0.05055804575954873</v>
       </c>
       <c r="H755">
-        <v>0.05496376822395901</v>
+        <v>0.05030828268418176</v>
       </c>
       <c r="I755">
-        <v>0.5523095152290303</v>
+        <v>0.8502369246330232</v>
       </c>
       <c r="J755">
-        <v>0.9794841412849514</v>
+        <v>1.00078974877675</v>
       </c>
       <c r="K755">
-        <v>25.05</v>
+        <v>22.85</v>
       </c>
       <c r="L755">
-        <v>28.7</v>
+        <v>27.69</v>
       </c>
       <c r="M755">
-        <v>25.65</v>
+        <v>23.15</v>
       </c>
       <c r="N755">
-        <v>29.84</v>
+        <v>27.14</v>
       </c>
       <c r="O755">
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>408</v>
+        <v>185</v>
       </c>
     </row>
     <row r="756" spans="1:16">
       <c r="A756" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B756" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C756">
-        <v>4.821954240451266</v>
+        <v>4.671875265573593</v>
       </c>
       <c r="D756" t="s">
         <v>322</v>
@@ -39416,22 +39422,22 @@
         <v>-1</v>
       </c>
       <c r="G756">
-        <v>0.05055804575954873</v>
+        <v>0.05060812473442641</v>
       </c>
       <c r="H756">
         <v>0.05030828268418176</v>
       </c>
       <c r="I756">
-        <v>0.8502369246330232</v>
+        <v>0.7001579497553507</v>
       </c>
       <c r="J756">
         <v>1.00078974877675</v>
       </c>
       <c r="K756">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L756">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M756">
         <v>23.15</v>
@@ -39448,46 +39454,46 @@
     </row>
     <row r="757" spans="1:16">
       <c r="A757" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B757" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C757">
-        <v>4.671875265573593</v>
+        <v>4.550256280581255</v>
       </c>
       <c r="D757" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E757">
-        <v>3.971717315818243</v>
+        <v>3.880335255458931</v>
       </c>
       <c r="F757">
         <v>-1</v>
       </c>
       <c r="G757">
-        <v>0.05060812473442641</v>
+        <v>0.05458974371941875</v>
       </c>
       <c r="H757">
-        <v>0.05030828268418176</v>
+        <v>0.05371966474454107</v>
       </c>
       <c r="I757">
-        <v>0.7001579497553507</v>
+        <v>0.6699210251223242</v>
       </c>
       <c r="J757">
         <v>1.00078974877675</v>
       </c>
       <c r="K757">
-        <v>22.95</v>
+        <v>25</v>
       </c>
       <c r="L757">
-        <v>27.64</v>
+        <v>29.57</v>
       </c>
       <c r="M757">
-        <v>23.15</v>
+        <v>24.9</v>
       </c>
       <c r="N757">
-        <v>27.14</v>
+        <v>28.8</v>
       </c>
       <c r="O757">
         <v>1</v>
@@ -39498,46 +39504,46 @@
     </row>
     <row r="758" spans="1:16">
       <c r="A758" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B758" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C758">
-        <v>4.550256280581255</v>
+        <v>3.630216793142413</v>
       </c>
       <c r="D758" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="E758">
-        <v>3.880335255458931</v>
+        <v>4.330137818264742</v>
       </c>
       <c r="F758">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G758">
-        <v>0.05458974371941875</v>
+        <v>0.05376978320685758</v>
       </c>
       <c r="H758">
-        <v>0.05371966474454107</v>
+        <v>0.05466986218173526</v>
       </c>
       <c r="I758">
-        <v>0.6699210251223242</v>
+        <v>0.6999210251223289</v>
       </c>
       <c r="J758">
         <v>1.00078974877675</v>
       </c>
       <c r="K758">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="L758">
-        <v>29.57</v>
+        <v>28.7</v>
       </c>
       <c r="M758">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N758">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O758">
         <v>1</v>
@@ -39548,63 +39554,63 @@
     </row>
     <row r="759" spans="1:16">
       <c r="A759" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B759" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C759">
-        <v>3.630216793142413</v>
+        <v>4.670760956334874</v>
       </c>
       <c r="D759" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="E759">
-        <v>4.330137818264742</v>
+        <v>3.81853899952527</v>
       </c>
       <c r="F759">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G759">
-        <v>0.05376978320685758</v>
+        <v>0.05070923904366513</v>
       </c>
       <c r="H759">
-        <v>0.05466986218173526</v>
+        <v>0.05046146100047473</v>
       </c>
       <c r="I759">
-        <v>0.6999210251223289</v>
+        <v>0.8522219568096041</v>
       </c>
       <c r="J759">
-        <v>1.00078974877675</v>
+        <v>1.007406522698693</v>
       </c>
       <c r="K759">
-        <v>25.05</v>
+        <v>22.85</v>
       </c>
       <c r="L759">
-        <v>28.7</v>
+        <v>27.69</v>
       </c>
       <c r="M759">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N759">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O759">
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>185</v>
+        <v>410</v>
       </c>
     </row>
     <row r="760" spans="1:16">
       <c r="A760" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B760" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C760">
-        <v>4.670760956334874</v>
+        <v>4.520020304065007</v>
       </c>
       <c r="D760" t="s">
         <v>322</v>
@@ -39616,22 +39622,22 @@
         <v>-1</v>
       </c>
       <c r="G760">
-        <v>0.05070923904366513</v>
+        <v>0.05075997969593499</v>
       </c>
       <c r="H760">
         <v>0.05046146100047473</v>
       </c>
       <c r="I760">
-        <v>0.8522219568096041</v>
+        <v>0.7014813045397368</v>
       </c>
       <c r="J760">
         <v>1.007406522698693</v>
       </c>
       <c r="K760">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L760">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M760">
         <v>23.15</v>
@@ -39643,168 +39649,168 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="761" spans="1:16">
       <c r="A761" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B761" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C761">
-        <v>4.520020304065007</v>
+        <v>4.384836932532686</v>
       </c>
       <c r="D761" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E761">
-        <v>3.81853899952527</v>
+        <v>3.715577584802556</v>
       </c>
       <c r="F761">
         <v>-1</v>
       </c>
       <c r="G761">
-        <v>0.05075997969593499</v>
+        <v>0.05475516306746732</v>
       </c>
       <c r="H761">
-        <v>0.05046146100047473</v>
+        <v>0.05388442241519745</v>
       </c>
       <c r="I761">
-        <v>0.7014813045397368</v>
+        <v>0.6692593477301294</v>
       </c>
       <c r="J761">
         <v>1.007406522698693</v>
       </c>
       <c r="K761">
-        <v>22.95</v>
+        <v>25</v>
       </c>
       <c r="L761">
-        <v>27.64</v>
+        <v>29.57</v>
       </c>
       <c r="M761">
-        <v>23.15</v>
+        <v>24.9</v>
       </c>
       <c r="N761">
-        <v>27.14</v>
+        <v>28.8</v>
       </c>
       <c r="O761">
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="762" spans="1:16">
       <c r="A762" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B762" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C762">
-        <v>4.384836932532686</v>
+        <v>3.46446660639775</v>
       </c>
       <c r="D762" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="E762">
-        <v>3.715577584802556</v>
+        <v>4.163725954127884</v>
       </c>
       <c r="F762">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G762">
-        <v>0.05475516306746732</v>
+        <v>0.05393553339360225</v>
       </c>
       <c r="H762">
-        <v>0.05388442241519745</v>
+        <v>0.05483627404587212</v>
       </c>
       <c r="I762">
-        <v>0.6692593477301294</v>
+        <v>0.6992593477301341</v>
       </c>
       <c r="J762">
         <v>1.007406522698693</v>
       </c>
       <c r="K762">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="L762">
-        <v>29.57</v>
+        <v>28.7</v>
       </c>
       <c r="M762">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N762">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O762">
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="763" spans="1:16">
       <c r="A763" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B763" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C763">
-        <v>3.46446660639775</v>
+        <v>4.503371200497003</v>
       </c>
       <c r="D763" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="E763">
-        <v>4.163725954127884</v>
+        <v>3.648951566367863</v>
       </c>
       <c r="F763">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G763">
-        <v>0.05393553339360225</v>
+        <v>0.050876628799503</v>
       </c>
       <c r="H763">
-        <v>0.05483627404587212</v>
+        <v>0.05063104843363214</v>
       </c>
       <c r="I763">
-        <v>0.6992593477301341</v>
+        <v>0.8544196341291403</v>
       </c>
       <c r="J763">
-        <v>1.007406522698693</v>
+        <v>1.014732113763807</v>
       </c>
       <c r="K763">
-        <v>25.05</v>
+        <v>22.85</v>
       </c>
       <c r="L763">
-        <v>28.7</v>
+        <v>27.69</v>
       </c>
       <c r="M763">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N763">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O763">
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>409</v>
+        <v>321</v>
       </c>
     </row>
     <row r="764" spans="1:16">
       <c r="A764" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B764" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C764">
-        <v>4.503371200497003</v>
+        <v>4.351897989120626</v>
       </c>
       <c r="D764" t="s">
         <v>322</v>
@@ -39816,22 +39822,22 @@
         <v>-1</v>
       </c>
       <c r="G764">
-        <v>0.050876628799503</v>
+        <v>0.05092810201087937</v>
       </c>
       <c r="H764">
         <v>0.05063104843363214</v>
       </c>
       <c r="I764">
-        <v>0.8544196341291403</v>
+        <v>0.7029464227527633</v>
       </c>
       <c r="J764">
         <v>1.014732113763807</v>
       </c>
       <c r="K764">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L764">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M764">
         <v>23.15</v>
@@ -39848,46 +39854,46 @@
     </row>
     <row r="765" spans="1:16">
       <c r="A765" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B765" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C765">
-        <v>4.351897989120626</v>
+        <v>4.201697155904821</v>
       </c>
       <c r="D765" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E765">
-        <v>3.648951566367863</v>
+        <v>3.533170367281201</v>
       </c>
       <c r="F765">
         <v>-1</v>
       </c>
       <c r="G765">
-        <v>0.05092810201087937</v>
+        <v>0.05493830284409518</v>
       </c>
       <c r="H765">
-        <v>0.05063104843363214</v>
+        <v>0.0540668296327188</v>
       </c>
       <c r="I765">
-        <v>0.7029464227527633</v>
+        <v>0.6685267886236197</v>
       </c>
       <c r="J765">
         <v>1.014732113763807</v>
       </c>
       <c r="K765">
-        <v>22.95</v>
+        <v>25</v>
       </c>
       <c r="L765">
-        <v>27.64</v>
+        <v>29.57</v>
       </c>
       <c r="M765">
-        <v>23.15</v>
+        <v>24.9</v>
       </c>
       <c r="N765">
-        <v>27.14</v>
+        <v>28.8</v>
       </c>
       <c r="O765">
         <v>1</v>
@@ -39898,46 +39904,46 @@
     </row>
     <row r="766" spans="1:16">
       <c r="A766" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B766" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C766">
-        <v>4.201697155904821</v>
+        <v>3.280960550216626</v>
       </c>
       <c r="D766" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="E766">
-        <v>3.533170367281201</v>
+        <v>3.979487338840251</v>
       </c>
       <c r="F766">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G766">
-        <v>0.05493830284409518</v>
+        <v>0.05411903944978337</v>
       </c>
       <c r="H766">
-        <v>0.0540668296327188</v>
+        <v>0.05502051266115975</v>
       </c>
       <c r="I766">
-        <v>0.6685267886236197</v>
+        <v>0.6985267886236244</v>
       </c>
       <c r="J766">
         <v>1.014732113763807</v>
       </c>
       <c r="K766">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="L766">
-        <v>29.57</v>
+        <v>28.7</v>
       </c>
       <c r="M766">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N766">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O766">
         <v>1</v>
@@ -39948,63 +39954,63 @@
     </row>
     <row r="767" spans="1:16">
       <c r="A767" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B767" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C767">
-        <v>3.280960550216626</v>
+        <v>4.366292866964365</v>
       </c>
       <c r="D767" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="E767">
-        <v>3.979487338840251</v>
+        <v>3.510073517296505</v>
       </c>
       <c r="F767">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G767">
-        <v>0.05411903944978337</v>
+        <v>0.05101370713303564</v>
       </c>
       <c r="H767">
-        <v>0.05502051266115975</v>
+        <v>0.0507699264827035</v>
       </c>
       <c r="I767">
-        <v>0.6985267886236244</v>
+        <v>0.8562193496678603</v>
       </c>
       <c r="J767">
-        <v>1.014732113763807</v>
+        <v>1.020731165559546</v>
       </c>
       <c r="K767">
-        <v>25.05</v>
+        <v>22.85</v>
       </c>
       <c r="L767">
-        <v>28.7</v>
+        <v>27.69</v>
       </c>
       <c r="M767">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N767">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O767">
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>321</v>
+        <v>411</v>
       </c>
     </row>
     <row r="768" spans="1:16">
       <c r="A768" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B768" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C768">
-        <v>4.366292866964365</v>
+        <v>4.214219750408411</v>
       </c>
       <c r="D768" t="s">
         <v>322</v>
@@ -40016,22 +40022,22 @@
         <v>-1</v>
       </c>
       <c r="G768">
-        <v>0.05101370713303564</v>
+        <v>0.05106578024959159</v>
       </c>
       <c r="H768">
         <v>0.0507699264827035</v>
       </c>
       <c r="I768">
-        <v>0.8562193496678603</v>
+        <v>0.7041462331119064</v>
       </c>
       <c r="J768">
         <v>1.020731165559546</v>
       </c>
       <c r="K768">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L768">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M768">
         <v>23.15</v>
@@ -40043,168 +40049,168 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="769" spans="1:16">
       <c r="A769" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B769" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C769">
-        <v>4.214219750408411</v>
+        <v>4.05172086101134</v>
       </c>
       <c r="D769" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E769">
-        <v>3.510073517296505</v>
+        <v>3.383793977567297</v>
       </c>
       <c r="F769">
         <v>-1</v>
       </c>
       <c r="G769">
-        <v>0.05106578024959159</v>
+        <v>0.05508827913898866</v>
       </c>
       <c r="H769">
-        <v>0.0507699264827035</v>
+        <v>0.0542162060224327</v>
       </c>
       <c r="I769">
-        <v>0.7041462331119064</v>
+        <v>0.6679268834440428</v>
       </c>
       <c r="J769">
         <v>1.020731165559546</v>
       </c>
       <c r="K769">
-        <v>22.95</v>
+        <v>25</v>
       </c>
       <c r="L769">
-        <v>27.64</v>
+        <v>29.57</v>
       </c>
       <c r="M769">
-        <v>23.15</v>
+        <v>24.9</v>
       </c>
       <c r="N769">
-        <v>27.14</v>
+        <v>28.8</v>
       </c>
       <c r="O769">
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="770" spans="1:16">
       <c r="A770" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B770" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C770">
-        <v>4.05172086101134</v>
+        <v>3.130684302733364</v>
       </c>
       <c r="D770" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="E770">
-        <v>3.383793977567297</v>
+        <v>3.828611186177412</v>
       </c>
       <c r="F770">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G770">
-        <v>0.05508827913898866</v>
+        <v>0.05426931569726664</v>
       </c>
       <c r="H770">
-        <v>0.0542162060224327</v>
+        <v>0.05517138881382259</v>
       </c>
       <c r="I770">
-        <v>0.6679268834440428</v>
+        <v>0.6979268834440475</v>
       </c>
       <c r="J770">
         <v>1.020731165559546</v>
       </c>
       <c r="K770">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="L770">
-        <v>29.57</v>
+        <v>28.7</v>
       </c>
       <c r="M770">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N770">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O770">
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="771" spans="1:16">
       <c r="A771" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B771" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C771">
-        <v>3.130684302733364</v>
+        <v>4.196922435356054</v>
       </c>
       <c r="D771" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="E771">
-        <v>3.828611186177412</v>
+        <v>3.338479403872764</v>
       </c>
       <c r="F771">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G771">
-        <v>0.05426931569726664</v>
+        <v>0.05118307756464395</v>
       </c>
       <c r="H771">
-        <v>0.05517138881382259</v>
+        <v>0.05094152059612723</v>
       </c>
       <c r="I771">
-        <v>0.6979268834440475</v>
+        <v>0.85844303148329</v>
       </c>
       <c r="J771">
-        <v>1.020731165559546</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K771">
-        <v>25.05</v>
+        <v>22.85</v>
       </c>
       <c r="L771">
-        <v>28.7</v>
+        <v>27.69</v>
       </c>
       <c r="M771">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N771">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O771">
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="772" spans="1:16">
       <c r="A772" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B772" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C772">
-        <v>4.196922435356054</v>
+        <v>4.04410809152829</v>
       </c>
       <c r="D772" t="s">
         <v>322</v>
@@ -40216,22 +40222,22 @@
         <v>-1</v>
       </c>
       <c r="G772">
-        <v>0.05118307756464395</v>
+        <v>0.05123589190847171</v>
       </c>
       <c r="H772">
         <v>0.05094152059612723</v>
       </c>
       <c r="I772">
-        <v>0.85844303148329</v>
+        <v>0.7056286876555262</v>
       </c>
       <c r="J772">
         <v>1.028143438277634</v>
       </c>
       <c r="K772">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L772">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M772">
         <v>23.15</v>
@@ -40243,168 +40249,168 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="773" spans="1:16">
       <c r="A773" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B773" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C773">
-        <v>4.04410809152829</v>
+        <v>3.866414043059141</v>
       </c>
       <c r="D773" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E773">
-        <v>3.338479403872764</v>
+        <v>3.199228386886904</v>
       </c>
       <c r="F773">
         <v>-1</v>
       </c>
       <c r="G773">
-        <v>0.05123589190847171</v>
+        <v>0.05527358595694087</v>
       </c>
       <c r="H773">
-        <v>0.05094152059612723</v>
+        <v>0.0544007716131131</v>
       </c>
       <c r="I773">
-        <v>0.7056286876555262</v>
+        <v>0.6671856561722365</v>
       </c>
       <c r="J773">
         <v>1.028143438277634</v>
       </c>
       <c r="K773">
-        <v>22.95</v>
+        <v>25</v>
       </c>
       <c r="L773">
-        <v>27.64</v>
+        <v>29.57</v>
       </c>
       <c r="M773">
-        <v>23.15</v>
+        <v>24.9</v>
       </c>
       <c r="N773">
-        <v>27.14</v>
+        <v>28.8</v>
       </c>
       <c r="O773">
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="774" spans="1:16">
       <c r="A774" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B774" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C774">
-        <v>3.866414043059141</v>
+        <v>2.945006871145257</v>
       </c>
       <c r="D774" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="E774">
-        <v>3.199228386886904</v>
+        <v>3.642192527317494</v>
       </c>
       <c r="F774">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G774">
-        <v>0.05527358595694087</v>
+        <v>0.05445499312885474</v>
       </c>
       <c r="H774">
-        <v>0.0544007716131131</v>
+        <v>0.05535780747268251</v>
       </c>
       <c r="I774">
-        <v>0.6671856561722365</v>
+        <v>0.6971856561722376</v>
       </c>
       <c r="J774">
         <v>1.028143438277634</v>
       </c>
       <c r="K774">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="L774">
-        <v>29.57</v>
+        <v>28.7</v>
       </c>
       <c r="M774">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N774">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O774">
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="775" spans="1:16">
       <c r="A775" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B775" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C775">
-        <v>2.945006871145257</v>
+        <v>4.101655744450497</v>
       </c>
       <c r="D775" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="E775">
-        <v>3.642192527317494</v>
+        <v>3.241961946784642</v>
       </c>
       <c r="F775">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G775">
-        <v>0.05445499312885474</v>
+        <v>0.05127834425554951</v>
       </c>
       <c r="H775">
-        <v>0.05535780747268251</v>
+        <v>0.05103803805321536</v>
       </c>
       <c r="I775">
-        <v>0.6971856561722376</v>
+        <v>0.8596937976658552</v>
       </c>
       <c r="J775">
-        <v>1.028143438277634</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K775">
-        <v>25.05</v>
+        <v>22.85</v>
       </c>
       <c r="L775">
-        <v>28.7</v>
+        <v>27.69</v>
       </c>
       <c r="M775">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N775">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O775">
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="776" spans="1:16">
       <c r="A776" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B776" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C776">
-        <v>4.101655744450497</v>
+        <v>3.948424478561879</v>
       </c>
       <c r="D776" t="s">
         <v>322</v>
@@ -40416,22 +40422,22 @@
         <v>-1</v>
       </c>
       <c r="G776">
-        <v>0.05127834425554951</v>
+        <v>0.05133157552143813</v>
       </c>
       <c r="H776">
         <v>0.05103803805321536</v>
       </c>
       <c r="I776">
-        <v>0.8596937976658552</v>
+        <v>0.7064625317772375</v>
       </c>
       <c r="J776">
         <v>1.032312658886193</v>
       </c>
       <c r="K776">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L776">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M776">
         <v>23.15</v>
@@ -40443,157 +40449,157 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="777" spans="1:16">
       <c r="A777" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B777" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C777">
-        <v>3.948424478561879</v>
+        <v>3.762183527845185</v>
       </c>
       <c r="D777" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E777">
-        <v>3.241961946784642</v>
+        <v>3.095414793733806</v>
       </c>
       <c r="F777">
         <v>-1</v>
       </c>
       <c r="G777">
-        <v>0.05133157552143813</v>
+        <v>0.05537781647215482</v>
       </c>
       <c r="H777">
-        <v>0.05103803805321536</v>
+        <v>0.0545045852062662</v>
       </c>
       <c r="I777">
-        <v>0.7064625317772375</v>
+        <v>0.666768734111379</v>
       </c>
       <c r="J777">
         <v>1.032312658886193</v>
       </c>
       <c r="K777">
-        <v>22.95</v>
+        <v>25</v>
       </c>
       <c r="L777">
-        <v>27.64</v>
+        <v>29.57</v>
       </c>
       <c r="M777">
-        <v>23.15</v>
+        <v>24.9</v>
       </c>
       <c r="N777">
-        <v>27.14</v>
+        <v>28.8</v>
       </c>
       <c r="O777">
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="778" spans="1:16">
       <c r="A778" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B778" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C778">
-        <v>3.762183527845185</v>
+        <v>2.840567894900875</v>
       </c>
       <c r="D778" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="E778">
-        <v>3.095414793733806</v>
+        <v>3.537336629012259</v>
       </c>
       <c r="F778">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G778">
-        <v>0.05537781647215482</v>
+        <v>0.05455943210509912</v>
       </c>
       <c r="H778">
-        <v>0.0545045852062662</v>
+        <v>0.05546266337098774</v>
       </c>
       <c r="I778">
-        <v>0.666768734111379</v>
+        <v>0.6967687341113837</v>
       </c>
       <c r="J778">
         <v>1.032312658886193</v>
       </c>
       <c r="K778">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="L778">
-        <v>29.57</v>
+        <v>28.7</v>
       </c>
       <c r="M778">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N778">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O778">
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="779" spans="1:16">
       <c r="A779" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B779" t="s">
         <v>190</v>
       </c>
       <c r="C779">
-        <v>2.840567894900875</v>
+        <v>3.021264920842754</v>
       </c>
       <c r="D779" t="s">
-        <v>193</v>
+        <v>325</v>
       </c>
       <c r="E779">
-        <v>3.537336629012259</v>
+        <v>3.417727452619999</v>
       </c>
       <c r="F779">
         <v>1</v>
       </c>
       <c r="G779">
-        <v>0.05455943210509912</v>
+        <v>0.05277873507915724</v>
       </c>
       <c r="H779">
-        <v>0.05546266337098774</v>
+        <v>0.05276227254738</v>
       </c>
       <c r="I779">
-        <v>0.6967687341113837</v>
+        <v>0.3964625317772459</v>
       </c>
       <c r="J779">
         <v>1.032312658886193</v>
       </c>
       <c r="K779">
-        <v>25.05</v>
+        <v>24.1</v>
       </c>
       <c r="L779">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="M779">
-        <v>25.15</v>
+        <v>23.9</v>
       </c>
       <c r="N779">
-        <v>29.5</v>
+        <v>28.09</v>
       </c>
       <c r="O779">
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -40643,7 +40649,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -40693,7 +40699,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40743,7 +40749,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40751,7 +40757,7 @@
         <v>3</v>
       </c>
       <c r="B783" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C783">
         <v>2.739545859741096</v>
@@ -40793,51 +40799,51 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="784" spans="1:16">
       <c r="A784" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B784" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C784">
-        <v>3.923892030831919</v>
+        <v>2.924074060669074</v>
       </c>
       <c r="D784" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E784">
-        <v>3.06186435508792</v>
+        <v>3.321343155601287</v>
       </c>
       <c r="F784">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G784">
-        <v>0.05145610796916809</v>
+        <v>0.05287592593933093</v>
       </c>
       <c r="H784">
-        <v>0.05121813564491208</v>
+        <v>0.05285865684439871</v>
       </c>
       <c r="I784">
-        <v>0.8620276757439989</v>
+        <v>0.3972690949322129</v>
       </c>
       <c r="J784">
-        <v>1.040092252480004</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K784">
-        <v>22.85</v>
+        <v>24.1</v>
       </c>
       <c r="L784">
-        <v>27.69</v>
+        <v>27.9</v>
       </c>
       <c r="M784">
-        <v>23.15</v>
+        <v>23.9</v>
       </c>
       <c r="N784">
-        <v>27.14</v>
+        <v>28.09</v>
       </c>
       <c r="O784">
         <v>1</v>
@@ -40848,13 +40854,13 @@
     </row>
     <row r="785" spans="1:16">
       <c r="A785" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B785" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C785">
-        <v>3.769882805583919</v>
+        <v>3.923892030831919</v>
       </c>
       <c r="D785" t="s">
         <v>322</v>
@@ -40866,22 +40872,22 @@
         <v>-1</v>
       </c>
       <c r="G785">
-        <v>0.05151011719441608</v>
+        <v>0.05145610796916809</v>
       </c>
       <c r="H785">
         <v>0.05121813564491208</v>
       </c>
       <c r="I785">
-        <v>0.7080184504959988</v>
+        <v>0.8620276757439989</v>
       </c>
       <c r="J785">
         <v>1.040092252480004</v>
       </c>
       <c r="K785">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L785">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M785">
         <v>23.15</v>
@@ -40893,101 +40899,101 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="786" spans="1:16">
       <c r="A786" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B786" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C786">
-        <v>2.645689075375909</v>
+        <v>3.769882805583919</v>
       </c>
       <c r="D786" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="E786">
-        <v>3.34167985012791</v>
+        <v>3.06186435508792</v>
       </c>
       <c r="F786">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G786">
-        <v>0.05475431092462409</v>
+        <v>0.05151011719441608</v>
       </c>
       <c r="H786">
-        <v>0.05565832014987209</v>
+        <v>0.05121813564491208</v>
       </c>
       <c r="I786">
-        <v>0.6959907747520013</v>
+        <v>0.7080184504959988</v>
       </c>
       <c r="J786">
         <v>1.040092252480004</v>
       </c>
       <c r="K786">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L786">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M786">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N786">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O786">
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="787" spans="1:16">
       <c r="A787" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B787" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C787">
-        <v>3.103333239057651</v>
+        <v>2.645689075375909</v>
       </c>
       <c r="D787" t="s">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="E787">
-        <v>2.230532362546374</v>
+        <v>3.34167985012791</v>
       </c>
       <c r="F787">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G787">
-        <v>0.05227666676094235</v>
+        <v>0.05475431092462409</v>
       </c>
       <c r="H787">
-        <v>0.05204946763745363</v>
+        <v>0.05565832014987209</v>
       </c>
       <c r="I787">
-        <v>0.8728008765112776</v>
+        <v>0.6959907747520013</v>
       </c>
       <c r="J787">
-        <v>1.07600292170426</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K787">
-        <v>22.85</v>
+        <v>25.05</v>
       </c>
       <c r="L787">
-        <v>27.69</v>
+        <v>28.7</v>
       </c>
       <c r="M787">
-        <v>23.15</v>
+        <v>25.15</v>
       </c>
       <c r="N787">
-        <v>27.14</v>
+        <v>29.5</v>
       </c>
       <c r="O787">
         <v>1</v>
@@ -40998,46 +41004,46 @@
     </row>
     <row r="788" spans="1:16">
       <c r="A788" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B788" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C788">
-        <v>2.945732946887226</v>
+        <v>2.83377671523191</v>
       </c>
       <c r="D788" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E788">
-        <v>2.230532362546374</v>
+        <v>3.231795165727917</v>
       </c>
       <c r="F788">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G788">
-        <v>0.05233426705311277</v>
+        <v>0.05296622328476809</v>
       </c>
       <c r="H788">
-        <v>0.05204946763745363</v>
+        <v>0.05294820483427208</v>
       </c>
       <c r="I788">
-        <v>0.7152005843408524</v>
+        <v>0.3980184504960071</v>
       </c>
       <c r="J788">
-        <v>1.07600292170426</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K788">
-        <v>22.95</v>
+        <v>24.1</v>
       </c>
       <c r="L788">
-        <v>27.64</v>
+        <v>27.9</v>
       </c>
       <c r="M788">
-        <v>23.15</v>
+        <v>23.9</v>
       </c>
       <c r="N788">
-        <v>27.14</v>
+        <v>28.09</v>
       </c>
       <c r="O788">
         <v>1</v>
@@ -41048,84 +41054,84 @@
     </row>
     <row r="789" spans="1:16">
       <c r="A789" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B789" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C789">
-        <v>1.746126811308276</v>
+        <v>3.103333239057651</v>
       </c>
       <c r="D789" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="E789">
-        <v>2.438526519137852</v>
+        <v>2.230532362546374</v>
       </c>
       <c r="F789">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G789">
-        <v>0.05565387318869172</v>
+        <v>0.05227666676094235</v>
       </c>
       <c r="H789">
-        <v>0.05656147348086215</v>
+        <v>0.05204946763745363</v>
       </c>
       <c r="I789">
-        <v>0.6923997078295763</v>
+        <v>0.8728008765112776</v>
       </c>
       <c r="J789">
         <v>1.07600292170426</v>
       </c>
       <c r="K789">
-        <v>25.05</v>
+        <v>22.85</v>
       </c>
       <c r="L789">
-        <v>28.7</v>
+        <v>27.69</v>
       </c>
       <c r="M789">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N789">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O789">
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="790" spans="1:16">
       <c r="A790" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B790" t="s">
         <v>187</v>
       </c>
       <c r="C790">
-        <v>1.786358263523248</v>
+        <v>2.945732946887226</v>
       </c>
       <c r="D790" t="s">
         <v>322</v>
       </c>
       <c r="E790">
-        <v>1.061054196102969</v>
+        <v>2.230532362546374</v>
       </c>
       <c r="F790">
         <v>-1</v>
       </c>
       <c r="G790">
-        <v>0.05349364173647676</v>
+        <v>0.05233426705311277</v>
       </c>
       <c r="H790">
-        <v>0.05321894580389703</v>
+        <v>0.05204946763745363</v>
       </c>
       <c r="I790">
-        <v>0.7253040674202786</v>
+        <v>0.7152005843408524</v>
       </c>
       <c r="J790">
-        <v>1.126520337101384</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K790">
         <v>22.95</v>
@@ -41148,34 +41154,34 @@
     </row>
     <row r="791" spans="1:16">
       <c r="A791" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B791" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C791">
-        <v>0.4806655556103365</v>
+        <v>1.746126811308276</v>
       </c>
       <c r="D791" t="s">
         <v>193</v>
       </c>
       <c r="E791">
-        <v>1.168013521900203</v>
+        <v>2.438526519137852</v>
       </c>
       <c r="F791">
         <v>1</v>
       </c>
       <c r="G791">
-        <v>0.05691933444438967</v>
+        <v>0.05565387318869172</v>
       </c>
       <c r="H791">
-        <v>0.0578319864780998</v>
+        <v>0.05656147348086215</v>
       </c>
       <c r="I791">
-        <v>0.6873479662898667</v>
+        <v>0.6923997078295763</v>
       </c>
       <c r="J791">
-        <v>1.126520337101384</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K791">
         <v>25.05</v>
@@ -41198,96 +41204,96 @@
     </row>
     <row r="792" spans="1:16">
       <c r="A792" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B792" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C792">
-        <v>1.347927144340538</v>
+        <v>1.968329586927322</v>
       </c>
       <c r="D792" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E792">
-        <v>0.6188023264262945</v>
+        <v>2.373530171268179</v>
       </c>
       <c r="F792">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G792">
-        <v>0.05393207285565946</v>
+        <v>0.05383167041307267</v>
       </c>
       <c r="H792">
-        <v>0.05366119767357371</v>
+        <v>0.05380646982873182</v>
       </c>
       <c r="I792">
-        <v>0.7291248179142436</v>
+        <v>0.4052005843408573</v>
       </c>
       <c r="J792">
-        <v>1.145624089571218</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K792">
-        <v>22.95</v>
+        <v>24.1</v>
       </c>
       <c r="L792">
-        <v>27.64</v>
+        <v>27.9</v>
       </c>
       <c r="M792">
-        <v>23.15</v>
+        <v>23.9</v>
       </c>
       <c r="N792">
-        <v>27.14</v>
+        <v>28.09</v>
       </c>
       <c r="O792">
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="793" spans="1:16">
       <c r="A793" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B793" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C793">
-        <v>0.002116556240977729</v>
+        <v>1.786358263523248</v>
       </c>
       <c r="D793" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="E793">
-        <v>0.6875541472838584</v>
+        <v>1.061054196102969</v>
       </c>
       <c r="F793">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G793">
-        <v>0.05739788344375902</v>
+        <v>0.05349364173647676</v>
       </c>
       <c r="H793">
-        <v>0.05831244585271614</v>
+        <v>0.05321894580389703</v>
       </c>
       <c r="I793">
-        <v>0.6854375910428807</v>
+        <v>0.7253040674202786</v>
       </c>
       <c r="J793">
-        <v>1.145624089571218</v>
+        <v>1.126520337101384</v>
       </c>
       <c r="K793">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L793">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M793">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N793">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O793">
         <v>1</v>
@@ -41298,34 +41304,34 @@
     </row>
     <row r="794" spans="1:16">
       <c r="A794" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B794" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C794">
-        <v>-0.5597363304415239</v>
+        <v>0.4806655556103365</v>
       </c>
       <c r="D794" t="s">
         <v>193</v>
       </c>
       <c r="E794">
-        <v>0.1234583349060188</v>
+        <v>1.168013521900203</v>
       </c>
       <c r="F794">
         <v>1</v>
       </c>
       <c r="G794">
-        <v>0.05795973633044153</v>
+        <v>0.05691933444438967</v>
       </c>
       <c r="H794">
-        <v>0.05887654166509398</v>
+        <v>0.0578319864780998</v>
       </c>
       <c r="I794">
-        <v>0.6831946653475427</v>
+        <v>0.6873479662898667</v>
       </c>
       <c r="J794">
-        <v>1.168053346524612</v>
+        <v>1.126520337101384</v>
       </c>
       <c r="K794">
         <v>25.05</v>
@@ -41343,7 +41349,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41351,81 +41357,81 @@
         <v>0</v>
       </c>
       <c r="B795" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C795">
-        <v>-0.8369803833445317</v>
+        <v>1.347927144340538</v>
       </c>
       <c r="D795" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="E795">
-        <v>-0.1548924806832268</v>
+        <v>0.6188023264262945</v>
       </c>
       <c r="F795">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G795">
-        <v>0.05823698038334453</v>
+        <v>0.05393207285565946</v>
       </c>
       <c r="H795">
-        <v>0.05915489248068323</v>
+        <v>0.05366119767357371</v>
       </c>
       <c r="I795">
-        <v>0.6820879026613049</v>
+        <v>0.7291248179142436</v>
       </c>
       <c r="J795">
-        <v>1.179120973387007</v>
+        <v>1.145624089571218</v>
       </c>
       <c r="K795">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L795">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M795">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N795">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O795">
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>187</v>
+        <v>418</v>
       </c>
     </row>
     <row r="796" spans="1:16">
       <c r="A796" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B796" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C796">
-        <v>-1.051692264853688</v>
+        <v>0.002116556240977729</v>
       </c>
       <c r="D796" t="s">
         <v>193</v>
       </c>
       <c r="E796">
-        <v>-0.3704614954519023</v>
+        <v>0.6875541472838584</v>
       </c>
       <c r="F796">
         <v>1</v>
       </c>
       <c r="G796">
-        <v>0.05845169226485369</v>
+        <v>0.05739788344375902</v>
       </c>
       <c r="H796">
-        <v>0.05937046149545191</v>
+        <v>0.05831244585271614</v>
       </c>
       <c r="I796">
-        <v>0.6812307694017861</v>
+        <v>0.6854375910428807</v>
       </c>
       <c r="J796">
-        <v>1.187692305982183</v>
+        <v>1.145624089571218</v>
       </c>
       <c r="K796">
         <v>25.05</v>
@@ -41443,7 +41449,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -41451,49 +41457,49 @@
         <v>0</v>
       </c>
       <c r="B797" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C797">
-        <v>0.01711680463947474</v>
+        <v>-0.5597363304415239</v>
       </c>
       <c r="D797" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="E797">
-        <v>-0.6346716625790805</v>
+        <v>0.1234583349060188</v>
       </c>
       <c r="F797">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G797">
-        <v>0.05912288319536053</v>
+        <v>0.05795973633044153</v>
       </c>
       <c r="H797">
-        <v>0.05823467166257908</v>
+        <v>0.05887654166509398</v>
       </c>
       <c r="I797">
-        <v>0.6517884672185552</v>
+        <v>0.6831946653475427</v>
       </c>
       <c r="J797">
-        <v>1.182115327814421</v>
+        <v>1.168053346524612</v>
       </c>
       <c r="K797">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="L797">
-        <v>29.57</v>
+        <v>28.7</v>
       </c>
       <c r="M797">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N797">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O797">
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -41501,149 +41507,149 @@
         <v>0</v>
       </c>
       <c r="B798" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C798">
-        <v>-0.1778805282432323</v>
+        <v>-0.8369803833445317</v>
       </c>
       <c r="D798" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="E798">
-        <v>-0.6778805282432323</v>
+        <v>-0.1548924806832268</v>
       </c>
       <c r="F798">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G798">
-        <v>0.05877788052824323</v>
+        <v>0.05823698038334453</v>
       </c>
       <c r="H798">
-        <v>0.05827788052824323</v>
+        <v>0.05915489248068323</v>
       </c>
       <c r="I798">
-        <v>0.5</v>
+        <v>0.6820879026613049</v>
       </c>
       <c r="J798">
-        <v>1.183850623624226</v>
+        <v>1.179120973387007</v>
       </c>
       <c r="K798">
-        <v>24.9</v>
+        <v>25.05</v>
       </c>
       <c r="L798">
-        <v>29.3</v>
+        <v>28.7</v>
       </c>
       <c r="M798">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N798">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O798">
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>322</v>
+        <v>187</v>
       </c>
     </row>
     <row r="799" spans="1:16">
       <c r="A799" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B799" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C799">
-        <v>-0.02626559060565725</v>
+        <v>-1.051692264853688</v>
       </c>
       <c r="D799" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="E799">
-        <v>-0.6778805282432323</v>
+        <v>-0.3704614954519023</v>
       </c>
       <c r="F799">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G799">
-        <v>0.05916626559060566</v>
+        <v>0.05845169226485369</v>
       </c>
       <c r="H799">
-        <v>0.05827788052824323</v>
+        <v>0.05937046149545191</v>
       </c>
       <c r="I799">
-        <v>0.6516149376375751</v>
+        <v>0.6812307694017861</v>
       </c>
       <c r="J799">
-        <v>1.183850623624226</v>
+        <v>1.187692305982183</v>
       </c>
       <c r="K799">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="L799">
-        <v>29.57</v>
+        <v>28.7</v>
       </c>
       <c r="M799">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N799">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O799">
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>322</v>
+        <v>420</v>
       </c>
     </row>
     <row r="800" spans="1:16">
       <c r="A800" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B800" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C800">
-        <v>-0.1794954658808123</v>
+        <v>0.01711680463947474</v>
       </c>
       <c r="D800" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E800">
-        <v>-1.012414966981432</v>
+        <v>-0.6346716625790805</v>
       </c>
       <c r="F800">
         <v>-1</v>
       </c>
       <c r="G800">
-        <v>0.05853949546588081</v>
+        <v>0.05912288319536053</v>
       </c>
       <c r="H800">
-        <v>0.05581241496698143</v>
+        <v>0.05823467166257908</v>
       </c>
       <c r="I800">
-        <v>0.8329195011006192</v>
+        <v>0.6517884672185552</v>
       </c>
       <c r="J800">
-        <v>1.183850623624226</v>
+        <v>1.182115327814421</v>
       </c>
       <c r="K800">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="L800">
-        <v>29.18</v>
+        <v>29.57</v>
       </c>
       <c r="M800">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="N800">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
       <c r="O800">
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>322</v>
+        <v>421</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41651,37 +41657,37 @@
         <v>0</v>
       </c>
       <c r="B801" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C801">
-        <v>0.04582245394855988</v>
+        <v>-0.1778805282432323</v>
       </c>
       <c r="D801" t="s">
         <v>323</v>
       </c>
       <c r="E801">
-        <v>-0.6060808358672318</v>
+        <v>-0.6778805282432323</v>
       </c>
       <c r="F801">
         <v>-1</v>
       </c>
       <c r="G801">
-        <v>0.05909417754605144</v>
+        <v>0.05877788052824323</v>
       </c>
       <c r="H801">
-        <v>0.05820608083586724</v>
+        <v>0.05827788052824323</v>
       </c>
       <c r="I801">
-        <v>0.6519032898157917</v>
+        <v>0.5</v>
       </c>
       <c r="J801">
-        <v>1.180967101842058</v>
+        <v>1.183850623624226</v>
       </c>
       <c r="K801">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="L801">
-        <v>29.57</v>
+        <v>29.3</v>
       </c>
       <c r="M801">
         <v>24.9</v>
@@ -41693,7 +41699,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>191</v>
+        <v>322</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41701,181 +41707,181 @@
         <v>1</v>
       </c>
       <c r="B802" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C802">
-        <v>-0.1079841256830285</v>
+        <v>-0.02626559060565725</v>
       </c>
       <c r="D802" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E802">
-        <v>-0.9432104442093845</v>
+        <v>-0.6778805282432323</v>
       </c>
       <c r="F802">
         <v>-1</v>
       </c>
       <c r="G802">
-        <v>0.05846798412568303</v>
+        <v>0.05916626559060566</v>
       </c>
       <c r="H802">
-        <v>0.05574321044420939</v>
+        <v>0.05827788052824323</v>
       </c>
       <c r="I802">
-        <v>0.835226318526356</v>
+        <v>0.6516149376375751</v>
       </c>
       <c r="J802">
-        <v>1.180967101842058</v>
+        <v>1.183850623624226</v>
       </c>
       <c r="K802">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="L802">
-        <v>29.18</v>
+        <v>29.57</v>
       </c>
       <c r="M802">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="N802">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
       <c r="O802">
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>191</v>
+        <v>322</v>
       </c>
     </row>
     <row r="803" spans="1:16">
       <c r="A803" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B803" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C803">
-        <v>0.05143297331527208</v>
+        <v>-0.1794954658808123</v>
       </c>
       <c r="D803" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E803">
-        <v>-0.6004927585779853</v>
+        <v>-1.012414966981432</v>
       </c>
       <c r="F803">
         <v>-1</v>
       </c>
       <c r="G803">
-        <v>0.05908856702668473</v>
+        <v>0.05853949546588081</v>
       </c>
       <c r="H803">
-        <v>0.05820049275857798</v>
+        <v>0.05581241496698143</v>
       </c>
       <c r="I803">
-        <v>0.6519257318932574</v>
+        <v>0.8329195011006192</v>
       </c>
       <c r="J803">
-        <v>1.180742681067389</v>
+        <v>1.183850623624226</v>
       </c>
       <c r="K803">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="L803">
-        <v>29.57</v>
+        <v>29.18</v>
       </c>
       <c r="M803">
-        <v>24.9</v>
+        <v>24</v>
       </c>
       <c r="N803">
-        <v>28.8</v>
+        <v>27.4</v>
       </c>
       <c r="O803">
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>421</v>
+        <v>322</v>
       </c>
     </row>
     <row r="804" spans="1:16">
       <c r="A804" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B804" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C804">
-        <v>-0.1024184904712513</v>
+        <v>0.04582245394855988</v>
       </c>
       <c r="D804" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E804">
-        <v>-0.9378243456173401</v>
+        <v>-0.6060808358672318</v>
       </c>
       <c r="F804">
         <v>-1</v>
       </c>
       <c r="G804">
-        <v>0.05846241849047125</v>
+        <v>0.05909417754605144</v>
       </c>
       <c r="H804">
-        <v>0.05573782434561734</v>
+        <v>0.05820608083586724</v>
       </c>
       <c r="I804">
-        <v>0.8354058551460888</v>
+        <v>0.6519032898157917</v>
       </c>
       <c r="J804">
-        <v>1.180742681067389</v>
+        <v>1.180967101842058</v>
       </c>
       <c r="K804">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="L804">
-        <v>29.18</v>
+        <v>29.57</v>
       </c>
       <c r="M804">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="N804">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
       <c r="O804">
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>421</v>
+        <v>191</v>
       </c>
     </row>
     <row r="805" spans="1:16">
       <c r="A805" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B805" t="s">
         <v>192</v>
       </c>
       <c r="C805">
-        <v>0.004427027548832285</v>
+        <v>-0.1079841256830285</v>
       </c>
       <c r="D805" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E805">
-        <v>-0.8344254572108056</v>
+        <v>-0.9432104442093845</v>
       </c>
       <c r="F805">
         <v>-1</v>
       </c>
       <c r="G805">
-        <v>0.05835557297245117</v>
+        <v>0.05846798412568303</v>
       </c>
       <c r="H805">
-        <v>0.05563442545721081</v>
+        <v>0.05574321044420939</v>
       </c>
       <c r="I805">
-        <v>0.8388524847596379</v>
+        <v>0.835226318526356</v>
       </c>
       <c r="J805">
-        <v>1.17643439405045</v>
+        <v>1.180967101842058</v>
       </c>
       <c r="K805">
         <v>24.8</v>
@@ -41893,7 +41899,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -41901,49 +41907,49 @@
         <v>0</v>
       </c>
       <c r="B806" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C806">
-        <v>-0.1614163319545447</v>
+        <v>0.05143297331527208</v>
       </c>
       <c r="D806" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E806">
-        <v>-0.9051289052448972</v>
+        <v>-0.6004927585779853</v>
       </c>
       <c r="F806">
         <v>-1</v>
       </c>
       <c r="G806">
-        <v>0.05916141633195454</v>
+        <v>0.05908856702668473</v>
       </c>
       <c r="H806">
-        <v>0.05570512890524489</v>
+        <v>0.05820049275857798</v>
       </c>
       <c r="I806">
-        <v>0.7437125732903525</v>
+        <v>0.6519257318932574</v>
       </c>
       <c r="J806">
-        <v>1.179380371051871</v>
+        <v>1.180742681067389</v>
       </c>
       <c r="K806">
-        <v>25.15</v>
+        <v>25</v>
       </c>
       <c r="L806">
-        <v>29.5</v>
+        <v>29.57</v>
       </c>
       <c r="M806">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="N806">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
       <c r="O806">
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>323</v>
+        <v>422</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -41954,28 +41960,28 @@
         <v>192</v>
       </c>
       <c r="C807">
-        <v>-0.06863320208639223</v>
+        <v>-0.1024184904712513</v>
       </c>
       <c r="D807" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E807">
-        <v>-0.9051289052448972</v>
+        <v>-0.9378243456173401</v>
       </c>
       <c r="F807">
         <v>-1</v>
       </c>
       <c r="G807">
-        <v>0.05842863320208639</v>
+        <v>0.05846241849047125</v>
       </c>
       <c r="H807">
-        <v>0.05570512890524489</v>
+        <v>0.05573782434561734</v>
       </c>
       <c r="I807">
-        <v>0.836495703158505</v>
+        <v>0.8354058551460888</v>
       </c>
       <c r="J807">
-        <v>1.179380371051871</v>
+        <v>1.180742681067389</v>
       </c>
       <c r="K807">
         <v>24.8</v>
@@ -41993,7 +41999,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>323</v>
+        <v>422</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42001,37 +42007,37 @@
         <v>0</v>
       </c>
       <c r="B808" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C808">
-        <v>-0.2336642408342477</v>
+        <v>0.004427027548832285</v>
       </c>
       <c r="D808" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E808">
-        <v>-0.9740732318100207</v>
+        <v>-0.8344254572108056</v>
       </c>
       <c r="F808">
         <v>-1</v>
       </c>
       <c r="G808">
-        <v>0.05923366424083425</v>
+        <v>0.05835557297245117</v>
       </c>
       <c r="H808">
-        <v>0.05577407323181002</v>
+        <v>0.05563442545721081</v>
       </c>
       <c r="I808">
-        <v>0.740408990975773</v>
+        <v>0.8388524847596379</v>
       </c>
       <c r="J808">
-        <v>1.182253051325417</v>
+        <v>1.17643439405045</v>
       </c>
       <c r="K808">
-        <v>25.15</v>
+        <v>24.8</v>
       </c>
       <c r="L808">
-        <v>29.5</v>
+        <v>29.18</v>
       </c>
       <c r="M808">
         <v>24</v>
@@ -42043,45 +42049,45 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="809" spans="1:16">
       <c r="A809" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B809" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C809">
-        <v>-0.1398756728703532</v>
+        <v>-0.1614163319545447</v>
       </c>
       <c r="D809" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E809">
-        <v>-0.9740732318100207</v>
+        <v>-0.9051289052448972</v>
       </c>
       <c r="F809">
         <v>-1</v>
       </c>
       <c r="G809">
-        <v>0.05849987567287036</v>
+        <v>0.05916141633195454</v>
       </c>
       <c r="H809">
-        <v>0.05577407323181002</v>
+        <v>0.05570512890524489</v>
       </c>
       <c r="I809">
-        <v>0.8341975589396675</v>
+        <v>0.7437125732903525</v>
       </c>
       <c r="J809">
-        <v>1.182253051325417</v>
+        <v>1.179380371051871</v>
       </c>
       <c r="K809">
-        <v>24.8</v>
+        <v>25.15</v>
       </c>
       <c r="L809">
-        <v>29.18</v>
+        <v>29.5</v>
       </c>
       <c r="M809">
         <v>24</v>
@@ -42093,45 +42099,45 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>189</v>
+        <v>323</v>
       </c>
     </row>
     <row r="810" spans="1:16">
       <c r="A810" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B810" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C810">
-        <v>-0.2559728582052792</v>
+        <v>-0.06863320208639223</v>
       </c>
       <c r="D810" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E810">
-        <v>-0.9953617732376472</v>
+        <v>-0.9051289052448972</v>
       </c>
       <c r="F810">
         <v>-1</v>
       </c>
       <c r="G810">
-        <v>0.05925597285820528</v>
+        <v>0.05842863320208639</v>
       </c>
       <c r="H810">
-        <v>0.05579536177323764</v>
+        <v>0.05570512890524489</v>
       </c>
       <c r="I810">
-        <v>0.739388915032368</v>
+        <v>0.836495703158505</v>
       </c>
       <c r="J810">
-        <v>1.183140073884902</v>
+        <v>1.179380371051871</v>
       </c>
       <c r="K810">
-        <v>25.15</v>
+        <v>24.8</v>
       </c>
       <c r="L810">
-        <v>29.5</v>
+        <v>29.18</v>
       </c>
       <c r="M810">
         <v>24</v>
@@ -42143,39 +42149,39 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>422</v>
+        <v>323</v>
       </c>
     </row>
     <row r="811" spans="1:16">
       <c r="A811" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B811" t="s">
         <v>192</v>
       </c>
       <c r="C811">
-        <v>-0.1618738323455666</v>
+        <v>-0.1398756728703532</v>
       </c>
       <c r="D811" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E811">
-        <v>-0.9953617732376472</v>
+        <v>-0.9740732318100207</v>
       </c>
       <c r="F811">
         <v>-1</v>
       </c>
       <c r="G811">
-        <v>0.05852187383234556</v>
+        <v>0.05849987567287036</v>
       </c>
       <c r="H811">
-        <v>0.05579536177323764</v>
+        <v>0.05577407323181002</v>
       </c>
       <c r="I811">
-        <v>0.8334879408920806</v>
+        <v>0.8341975589396675</v>
       </c>
       <c r="J811">
-        <v>1.183140073884902</v>
+        <v>1.182253051325417</v>
       </c>
       <c r="K811">
         <v>24.8</v>
@@ -42193,7 +42199,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42201,37 +42207,37 @@
         <v>0</v>
       </c>
       <c r="B812" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C812">
-        <v>-0.3734861989546587</v>
+        <v>-0.1618738323455666</v>
       </c>
       <c r="D812" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E812">
-        <v>-1.107501740553158</v>
+        <v>-0.9953617732376472</v>
       </c>
       <c r="F812">
         <v>-1</v>
       </c>
       <c r="G812">
-        <v>0.05937348619895466</v>
+        <v>0.05852187383234556</v>
       </c>
       <c r="H812">
-        <v>0.05590750174055316</v>
+        <v>0.05579536177323764</v>
       </c>
       <c r="I812">
-        <v>0.7340155415984988</v>
+        <v>0.8334879408920806</v>
       </c>
       <c r="J812">
-        <v>1.187812572523048</v>
+        <v>1.183140073884902</v>
       </c>
       <c r="K812">
-        <v>25.15</v>
+        <v>24.8</v>
       </c>
       <c r="L812">
-        <v>29.5</v>
+        <v>29.18</v>
       </c>
       <c r="M812">
         <v>24</v>
@@ -42243,12 +42249,12 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>190</v>
+        <v>424</v>
       </c>
     </row>
     <row r="813" spans="1:16">
       <c r="A813" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B813" t="s">
         <v>192</v>
@@ -42257,7 +42263,7 @@
         <v>-0.2777517985715967</v>
       </c>
       <c r="D813" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E813">
         <v>-1.107501740553158</v>
@@ -42293,7 +42299,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42307,7 +42313,7 @@
         <v>-0.678181641571296</v>
       </c>
       <c r="D814" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E814">
         <v>-1.495014491843193</v>
@@ -42343,7 +42349,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42357,7 +42363,7 @@
         <v>-0.9315019397461235</v>
       </c>
       <c r="D815" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E815">
         <v>-1.740163167496249</v>
@@ -42393,7 +42399,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2523" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2568" uniqueCount="433">
   <si>
     <t>trade_time</t>
   </si>
@@ -589,10 +589,10 @@
     <t>2021-11-09</t>
   </si>
   <si>
-    <t>2021-10-18</t>
+    <t>2021-10-20</t>
   </si>
   <si>
-    <t>2021-10-20</t>
+    <t>2021-11-10</t>
   </si>
   <si>
     <t>2021-09-24</t>
@@ -997,13 +997,10 @@
     <t>2021-10-15</t>
   </si>
   <si>
-    <t>2021-11-10</t>
+    <t>2021-11-03</t>
   </si>
   <si>
-    <t>2021-10-19</t>
-  </si>
-  <si>
-    <t>2021-11-03</t>
+    <t>2021-11-11</t>
   </si>
   <si>
     <t>2021-10-25</t>
@@ -1301,6 +1298,12 @@
   </si>
   <si>
     <t>2021-10-11</t>
+  </si>
+  <si>
+    <t>2021-10-18</t>
+  </si>
+  <si>
+    <t>2021-10-19</t>
   </si>
   <si>
     <t>2021-10-21</t>
@@ -1667,7 +1670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P837"/>
+  <dimension ref="A1:P852"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1764,7 +1767,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1814,7 +1817,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1864,7 +1867,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1914,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1964,7 +1967,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2214,7 +2217,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2264,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2314,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2364,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2414,7 +2417,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2464,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2514,7 +2517,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2564,7 +2567,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2614,7 +2617,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2664,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2714,7 +2717,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2764,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2814,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2864,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2914,7 +2917,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2964,7 +2967,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3014,7 +3017,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3064,7 +3067,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3114,7 +3117,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3164,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3214,7 +3217,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3264,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3314,7 +3317,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3364,7 +3367,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3414,7 +3417,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3464,7 +3467,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3514,7 +3517,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3564,7 +3567,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3614,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3664,7 +3667,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3714,7 +3717,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3764,7 +3767,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3814,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3864,7 +3867,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3914,7 +3917,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3964,7 +3967,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4014,7 +4017,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4064,7 +4067,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4114,7 +4117,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4164,7 +4167,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4214,7 +4217,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4264,7 +4267,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4314,7 +4317,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4364,7 +4367,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4414,7 +4417,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4464,7 +4467,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4514,7 +4517,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4564,7 +4567,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4614,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4664,7 +4667,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5014,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5064,7 +5067,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5114,7 +5117,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5164,7 +5167,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5214,7 +5217,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5564,7 +5567,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5614,7 +5617,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5664,7 +5667,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5714,7 +5717,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5764,7 +5767,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5814,7 +5817,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5864,7 +5867,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5914,7 +5917,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5964,7 +5967,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6014,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6064,7 +6067,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6114,7 +6117,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6164,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6214,7 +6217,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6264,7 +6267,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6314,7 +6317,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6364,7 +6367,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6414,7 +6417,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6464,7 +6467,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6514,7 +6517,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6564,7 +6567,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6614,7 +6617,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6664,7 +6667,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6714,7 +6717,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6764,7 +6767,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6814,7 +6817,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6864,7 +6867,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6914,7 +6917,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6964,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7014,7 +7017,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7064,7 +7067,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7114,7 +7117,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7164,7 +7167,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7214,7 +7217,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7264,7 +7267,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7314,7 +7317,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7364,7 +7367,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7414,7 +7417,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7464,7 +7467,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7514,7 +7517,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7564,7 +7567,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7614,7 +7617,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7664,7 +7667,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7714,7 +7717,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7764,7 +7767,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7814,7 +7817,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7864,7 +7867,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8264,7 +8267,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8314,7 +8317,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8364,7 +8367,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8414,7 +8417,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8464,7 +8467,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8514,7 +8517,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8564,7 +8567,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8614,7 +8617,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9464,7 +9467,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9514,7 +9517,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9564,7 +9567,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9614,7 +9617,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9664,7 +9667,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9714,7 +9717,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9764,7 +9767,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9814,7 +9817,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10664,7 +10667,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10714,7 +10717,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10764,7 +10767,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10814,7 +10817,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10864,7 +10867,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10914,7 +10917,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10964,7 +10967,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11014,7 +11017,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11464,7 +11467,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11514,7 +11517,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11564,7 +11567,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11614,7 +11617,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11664,7 +11667,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11714,7 +11717,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11764,7 +11767,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11814,7 +11817,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12214,7 +12217,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12264,7 +12267,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12314,7 +12317,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12364,7 +12367,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12414,7 +12417,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12464,7 +12467,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12514,7 +12517,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12564,7 +12567,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12614,7 +12617,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12664,7 +12667,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12714,7 +12717,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12764,7 +12767,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12814,7 +12817,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12864,7 +12867,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12914,7 +12917,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12964,7 +12967,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -13014,7 +13017,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13064,7 +13067,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13114,7 +13117,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13164,7 +13167,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13214,7 +13217,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13264,7 +13267,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13314,7 +13317,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13364,7 +13367,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13414,7 +13417,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13464,7 +13467,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13514,7 +13517,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13564,7 +13567,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13614,7 +13617,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13664,7 +13667,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13714,7 +13717,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13764,7 +13767,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13814,7 +13817,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13864,7 +13867,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14214,7 +14217,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14264,7 +14267,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14314,7 +14317,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14364,7 +14367,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14414,7 +14417,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14464,7 +14467,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14514,7 +14517,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14564,7 +14567,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14614,7 +14617,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14664,7 +14667,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14714,7 +14717,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14764,7 +14767,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14814,7 +14817,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14864,7 +14867,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14914,7 +14917,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14964,7 +14967,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15014,7 +15017,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15064,7 +15067,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -16214,7 +16217,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16264,7 +16267,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16314,7 +16317,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16364,7 +16367,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16414,7 +16417,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16464,7 +16467,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16514,7 +16517,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16564,7 +16567,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16614,7 +16617,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16664,7 +16667,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -18314,7 +18317,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18364,7 +18367,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18414,7 +18417,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18464,7 +18467,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18514,7 +18517,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18564,7 +18567,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18764,7 +18767,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18814,7 +18817,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19164,7 +19167,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19214,7 +19217,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19264,7 +19267,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19764,7 +19767,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19814,7 +19817,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19864,7 +19867,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20614,7 +20617,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20664,7 +20667,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20714,7 +20717,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20764,7 +20767,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20814,7 +20817,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20864,7 +20867,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20914,7 +20917,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20964,7 +20967,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21014,7 +21017,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21064,7 +21067,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21114,7 +21117,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21164,7 +21167,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21214,7 +21217,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21264,7 +21267,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21314,7 +21317,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21364,7 +21367,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21414,7 +21417,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21464,7 +21467,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21514,7 +21517,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21564,7 +21567,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21614,7 +21617,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21664,7 +21667,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21714,7 +21717,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21764,7 +21767,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21814,7 +21817,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21864,7 +21867,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21914,7 +21917,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21964,7 +21967,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22014,7 +22017,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22064,7 +22067,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22114,7 +22117,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22164,7 +22167,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22214,7 +22217,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22264,7 +22267,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22314,7 +22317,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22364,7 +22367,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22414,7 +22417,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22914,7 +22917,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22964,7 +22967,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23014,7 +23017,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23064,7 +23067,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23114,7 +23117,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23164,7 +23167,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23214,7 +23217,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23264,7 +23267,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23314,7 +23317,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23364,7 +23367,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23414,7 +23417,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23464,7 +23467,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23514,7 +23517,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23564,7 +23567,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23614,7 +23617,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23664,7 +23667,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23714,7 +23717,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23764,7 +23767,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23814,7 +23817,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23864,7 +23867,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23914,7 +23917,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23964,7 +23967,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24014,7 +24017,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24064,7 +24067,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24114,7 +24117,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24164,7 +24167,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24214,7 +24217,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24264,7 +24267,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24314,7 +24317,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24364,7 +24367,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24414,7 +24417,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24464,7 +24467,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24514,7 +24517,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24564,7 +24567,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24614,7 +24617,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24664,7 +24667,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24714,7 +24717,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24764,7 +24767,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24814,7 +24817,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24864,7 +24867,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25814,7 +25817,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25864,7 +25867,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25914,7 +25917,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25964,7 +25967,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26014,7 +26017,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26064,7 +26067,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26114,7 +26117,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26164,7 +26167,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26214,7 +26217,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26264,7 +26267,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26314,7 +26317,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26364,7 +26367,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26414,7 +26417,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26464,7 +26467,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26514,7 +26517,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26564,7 +26567,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26614,7 +26617,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26664,7 +26667,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26714,7 +26717,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26764,7 +26767,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26814,7 +26817,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26864,7 +26867,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26914,7 +26917,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26964,7 +26967,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27014,7 +27017,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27064,7 +27067,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27114,7 +27117,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27164,7 +27167,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27214,7 +27217,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27264,7 +27267,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27314,7 +27317,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27364,7 +27367,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27414,7 +27417,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27464,7 +27467,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27514,7 +27517,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27564,7 +27567,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27614,7 +27617,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27664,7 +27667,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27714,7 +27717,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27764,7 +27767,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27814,7 +27817,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27864,7 +27867,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27914,7 +27917,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27964,7 +27967,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28014,7 +28017,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28064,7 +28067,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28114,7 +28117,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28164,7 +28167,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28214,7 +28217,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28264,7 +28267,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28314,7 +28317,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28364,7 +28367,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28864,7 +28867,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28914,7 +28917,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28964,7 +28967,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29014,7 +29017,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29064,7 +29067,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29114,7 +29117,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29164,7 +29167,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29214,7 +29217,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29264,7 +29267,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29314,7 +29317,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29364,7 +29367,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29414,7 +29417,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29464,7 +29467,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29514,7 +29517,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29564,7 +29567,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29614,7 +29617,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29664,7 +29667,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29714,7 +29717,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29764,7 +29767,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29814,7 +29817,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -29864,7 +29867,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29914,7 +29917,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -29964,7 +29967,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30014,7 +30017,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30064,7 +30067,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30114,7 +30117,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30164,7 +30167,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30214,7 +30217,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30264,7 +30267,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30314,7 +30317,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30364,7 +30367,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30414,7 +30417,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30464,7 +30467,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30514,7 +30517,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30564,7 +30567,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30614,7 +30617,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30664,7 +30667,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30714,7 +30717,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30764,7 +30767,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30814,7 +30817,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30864,7 +30867,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30914,7 +30917,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -30964,7 +30967,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31414,7 +31417,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31464,7 +31467,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31514,7 +31517,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -31564,7 +31567,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31614,7 +31617,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31664,7 +31667,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -31714,7 +31717,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31764,7 +31767,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31814,7 +31817,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31864,7 +31867,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -31914,7 +31917,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -31964,7 +31967,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32014,7 +32017,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32064,7 +32067,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32114,7 +32117,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32164,7 +32167,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32914,7 +32917,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -32964,7 +32967,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33014,7 +33017,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33064,7 +33067,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33114,7 +33117,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33164,7 +33167,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33214,7 +33217,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33264,7 +33267,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33314,7 +33317,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33364,7 +33367,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33414,7 +33417,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33464,7 +33467,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33514,7 +33517,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33564,7 +33567,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33914,7 +33917,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -33964,7 +33967,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34014,7 +34017,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34064,7 +34067,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34114,7 +34117,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34164,7 +34167,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34464,7 +34467,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34514,7 +34517,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34564,7 +34567,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34614,7 +34617,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34664,7 +34667,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34714,7 +34717,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34764,7 +34767,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34814,7 +34817,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34864,7 +34867,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -34914,7 +34917,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -34964,7 +34967,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35014,7 +35017,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35064,7 +35067,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35114,7 +35117,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35164,7 +35167,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35214,7 +35217,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35264,7 +35267,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35314,7 +35317,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35364,7 +35367,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35714,7 +35717,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35764,7 +35767,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35814,7 +35817,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35864,7 +35867,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -35914,7 +35917,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -35964,7 +35967,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36014,7 +36017,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36064,7 +36067,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36114,7 +36117,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36164,7 +36167,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36214,7 +36217,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36264,7 +36267,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36314,7 +36317,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36364,7 +36367,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36414,7 +36417,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36464,7 +36467,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36514,7 +36517,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36564,7 +36567,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36614,7 +36617,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36664,7 +36667,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36714,7 +36717,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36764,7 +36767,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36814,7 +36817,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36864,7 +36867,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -36914,7 +36917,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -36964,7 +36967,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37014,7 +37017,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37064,7 +37067,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37114,7 +37117,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37164,7 +37167,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37214,7 +37217,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37264,7 +37267,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37664,7 +37667,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37714,7 +37717,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37764,7 +37767,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37814,7 +37817,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37864,7 +37867,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -37914,7 +37917,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -37964,7 +37967,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38614,7 +38617,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38664,7 +38667,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38714,7 +38717,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38764,7 +38767,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38814,7 +38817,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38864,7 +38867,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -38914,7 +38917,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -38964,7 +38967,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39014,7 +39017,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39064,7 +39067,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39114,7 +39117,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39164,7 +39167,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39214,7 +39217,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39264,7 +39267,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39314,7 +39317,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39328,10 +39331,10 @@
         <v>4.294432195032666</v>
       </c>
       <c r="D754" t="s">
-        <v>195</v>
+        <v>327</v>
       </c>
       <c r="E754">
-        <v>4.729303230353906</v>
+        <v>4.680329023289662</v>
       </c>
       <c r="F754">
         <v>1</v>
@@ -39340,10 +39343,10 @@
         <v>0.05150556780496733</v>
       </c>
       <c r="H754">
-        <v>0.05145069676964609</v>
+        <v>0.05149967097671034</v>
       </c>
       <c r="I754">
-        <v>0.4348710353212404</v>
+        <v>0.3858968282569961</v>
       </c>
       <c r="J754">
         <v>0.9794841412849514</v>
@@ -39355,7 +39358,7 @@
         <v>27.9</v>
       </c>
       <c r="M754">
-        <v>23.85</v>
+        <v>23.9</v>
       </c>
       <c r="N754">
         <v>28.09</v>
@@ -39364,7 +39367,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39378,10 +39381,10 @@
         <v>4.330329023289661</v>
       </c>
       <c r="D755" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E755">
-        <v>3.921354816225413</v>
+        <v>3.96187067494046</v>
       </c>
       <c r="F755">
         <v>1</v>
@@ -39390,10 +39393,10 @@
         <v>0.05114967097671034</v>
       </c>
       <c r="H755">
-        <v>0.05083864518377459</v>
+        <v>0.05283812932505954</v>
       </c>
       <c r="I755">
-        <v>-0.4089742070642473</v>
+        <v>-0.3684583483492005</v>
       </c>
       <c r="J755">
         <v>0.9794841412849514</v>
@@ -39405,16 +39408,16 @@
         <v>27.74</v>
       </c>
       <c r="M755">
-        <v>23.95</v>
+        <v>24.95</v>
       </c>
       <c r="N755">
-        <v>27.38</v>
+        <v>28.4</v>
       </c>
       <c r="O755">
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39572,43 +39575,43 @@
         <v>3</v>
       </c>
       <c r="B759" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C759">
-        <v>3.850532692653118</v>
+        <v>3.780967054480325</v>
       </c>
       <c r="D759" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E759">
-        <v>4.170295768020093</v>
+        <v>4.17112500423568</v>
       </c>
       <c r="F759">
         <v>1</v>
       </c>
       <c r="G759">
-        <v>0.05318946730734688</v>
+        <v>0.05201903294551967</v>
       </c>
       <c r="H759">
-        <v>0.0541097042319799</v>
+        <v>0.05200887499576431</v>
       </c>
       <c r="I759">
-        <v>0.3197630753669749</v>
+        <v>0.3901579497553556</v>
       </c>
       <c r="J759">
         <v>1.00078974877675</v>
       </c>
       <c r="K759">
-        <v>24.65</v>
+        <v>24.1</v>
       </c>
       <c r="L759">
-        <v>28.52</v>
+        <v>27.9</v>
       </c>
       <c r="M759">
-        <v>24.95</v>
+        <v>23.9</v>
       </c>
       <c r="N759">
-        <v>29.14</v>
+        <v>28.09</v>
       </c>
       <c r="O759">
         <v>1</v>
@@ -39622,43 +39625,43 @@
         <v>4</v>
       </c>
       <c r="B760" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C760">
-        <v>3.780967054480325</v>
+        <v>3.821125004235679</v>
       </c>
       <c r="D760" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E760">
-        <v>4.17112500423568</v>
+        <v>3.430295768020091</v>
       </c>
       <c r="F760">
         <v>1</v>
       </c>
       <c r="G760">
-        <v>0.05201903294551967</v>
+        <v>0.05165887499576433</v>
       </c>
       <c r="H760">
-        <v>0.05200887499576431</v>
+        <v>0.05336970423197991</v>
       </c>
       <c r="I760">
-        <v>0.3901579497553556</v>
+        <v>-0.3908292362155876</v>
       </c>
       <c r="J760">
         <v>1.00078974877675</v>
       </c>
       <c r="K760">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="L760">
-        <v>27.9</v>
+        <v>27.74</v>
       </c>
       <c r="M760">
-        <v>23.9</v>
+        <v>24.95</v>
       </c>
       <c r="N760">
-        <v>28.09</v>
+        <v>28.4</v>
       </c>
       <c r="O760">
         <v>1</v>
@@ -39669,63 +39672,63 @@
     </row>
     <row r="761" spans="1:16">
       <c r="A761" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B761" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C761">
-        <v>3.821125004235679</v>
+        <v>4.670760956334874</v>
       </c>
       <c r="D761" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E761">
-        <v>3.411085516796842</v>
+        <v>3.81853899952527</v>
       </c>
       <c r="F761">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G761">
-        <v>0.05165887499576433</v>
+        <v>0.05070923904366513</v>
       </c>
       <c r="H761">
-        <v>0.05134891448320316</v>
+        <v>0.05046146100047473</v>
       </c>
       <c r="I761">
-        <v>-0.4100394874388371</v>
+        <v>0.8522219568096041</v>
       </c>
       <c r="J761">
-        <v>1.00078974877675</v>
+        <v>1.007406522698693</v>
       </c>
       <c r="K761">
-        <v>23.9</v>
+        <v>22.85</v>
       </c>
       <c r="L761">
-        <v>27.74</v>
+        <v>27.69</v>
       </c>
       <c r="M761">
-        <v>23.95</v>
+        <v>23.15</v>
       </c>
       <c r="N761">
-        <v>27.38</v>
+        <v>27.14</v>
       </c>
       <c r="O761">
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>185</v>
+        <v>415</v>
       </c>
     </row>
     <row r="762" spans="1:16">
       <c r="A762" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B762" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C762">
-        <v>4.670760956334874</v>
+        <v>4.520020304065007</v>
       </c>
       <c r="D762" t="s">
         <v>325</v>
@@ -39737,22 +39740,22 @@
         <v>-1</v>
       </c>
       <c r="G762">
-        <v>0.05070923904366513</v>
+        <v>0.05075997969593499</v>
       </c>
       <c r="H762">
         <v>0.05046146100047473</v>
       </c>
       <c r="I762">
-        <v>0.8522219568096041</v>
+        <v>0.7014813045397368</v>
       </c>
       <c r="J762">
         <v>1.007406522698693</v>
       </c>
       <c r="K762">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L762">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M762">
         <v>23.15</v>
@@ -39764,351 +39767,351 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="763" spans="1:16">
       <c r="A763" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B763" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C763">
-        <v>4.520020304065007</v>
+        <v>4.384836932532686</v>
       </c>
       <c r="D763" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E763">
-        <v>3.81853899952527</v>
+        <v>3.715577584802556</v>
       </c>
       <c r="F763">
         <v>-1</v>
       </c>
       <c r="G763">
-        <v>0.05075997969593499</v>
+        <v>0.05475516306746732</v>
       </c>
       <c r="H763">
-        <v>0.05046146100047473</v>
+        <v>0.05388442241519745</v>
       </c>
       <c r="I763">
-        <v>0.7014813045397368</v>
+        <v>0.6692593477301294</v>
       </c>
       <c r="J763">
         <v>1.007406522698693</v>
       </c>
       <c r="K763">
-        <v>22.95</v>
+        <v>25</v>
       </c>
       <c r="L763">
-        <v>27.64</v>
+        <v>29.57</v>
       </c>
       <c r="M763">
-        <v>23.15</v>
+        <v>24.9</v>
       </c>
       <c r="N763">
-        <v>27.14</v>
+        <v>28.8</v>
       </c>
       <c r="O763">
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="764" spans="1:16">
       <c r="A764" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B764" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C764">
-        <v>4.384836932532686</v>
+        <v>3.621502802961505</v>
       </c>
       <c r="D764" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E764">
-        <v>3.715577584802556</v>
+        <v>4.01298410750125</v>
       </c>
       <c r="F764">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G764">
-        <v>0.05475516306746732</v>
+        <v>0.05217849719703849</v>
       </c>
       <c r="H764">
-        <v>0.05388442241519745</v>
+        <v>0.05216701589249875</v>
       </c>
       <c r="I764">
-        <v>0.6692593477301294</v>
+        <v>0.3914813045397452</v>
       </c>
       <c r="J764">
         <v>1.007406522698693</v>
       </c>
       <c r="K764">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="L764">
-        <v>29.57</v>
+        <v>27.9</v>
       </c>
       <c r="M764">
-        <v>24.9</v>
+        <v>23.9</v>
       </c>
       <c r="N764">
-        <v>28.8</v>
+        <v>28.09</v>
       </c>
       <c r="O764">
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="765" spans="1:16">
       <c r="A765" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B765" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C765">
-        <v>3.687429215477231</v>
+        <v>3.662984107501249</v>
       </c>
       <c r="D765" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E765">
-        <v>4.163725954127884</v>
+        <v>3.265207258667619</v>
       </c>
       <c r="F765">
         <v>1</v>
       </c>
       <c r="G765">
-        <v>0.05335257078452277</v>
+        <v>0.05181701589249874</v>
       </c>
       <c r="H765">
-        <v>0.05483627404587212</v>
+        <v>0.05353479274133238</v>
       </c>
       <c r="I765">
-        <v>0.4762967386506531</v>
+        <v>-0.3977768488336295</v>
       </c>
       <c r="J765">
         <v>1.007406522698693</v>
       </c>
       <c r="K765">
-        <v>24.65</v>
+        <v>23.9</v>
       </c>
       <c r="L765">
-        <v>28.52</v>
+        <v>27.74</v>
       </c>
       <c r="M765">
-        <v>25.15</v>
+        <v>24.95</v>
       </c>
       <c r="N765">
-        <v>29.5</v>
+        <v>28.4</v>
       </c>
       <c r="O765">
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="766" spans="1:16">
       <c r="A766" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B766" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C766">
-        <v>3.46446660639775</v>
+        <v>4.503371200497003</v>
       </c>
       <c r="D766" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E766">
-        <v>4.163725954127884</v>
+        <v>3.648951566367863</v>
       </c>
       <c r="F766">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G766">
-        <v>0.05393553339360225</v>
+        <v>0.050876628799503</v>
       </c>
       <c r="H766">
-        <v>0.05483627404587212</v>
+        <v>0.05063104843363214</v>
       </c>
       <c r="I766">
-        <v>0.6992593477301341</v>
+        <v>0.8544196341291403</v>
       </c>
       <c r="J766">
-        <v>1.007406522698693</v>
+        <v>1.014732113763807</v>
       </c>
       <c r="K766">
-        <v>25.05</v>
+        <v>22.85</v>
       </c>
       <c r="L766">
-        <v>28.7</v>
+        <v>27.69</v>
       </c>
       <c r="M766">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N766">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O766">
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>416</v>
+        <v>324</v>
       </c>
     </row>
     <row r="767" spans="1:16">
       <c r="A767" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B767" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C767">
-        <v>3.621502802961505</v>
+        <v>4.351897989120626</v>
       </c>
       <c r="D767" t="s">
-        <v>195</v>
+        <v>325</v>
       </c>
       <c r="E767">
-        <v>4.063354433636182</v>
+        <v>3.648951566367863</v>
       </c>
       <c r="F767">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G767">
-        <v>0.05217849719703849</v>
+        <v>0.05092810201087937</v>
       </c>
       <c r="H767">
-        <v>0.05211664556636381</v>
+        <v>0.05063104843363214</v>
       </c>
       <c r="I767">
-        <v>0.4418516306746767</v>
+        <v>0.7029464227527633</v>
       </c>
       <c r="J767">
-        <v>1.007406522698693</v>
+        <v>1.014732113763807</v>
       </c>
       <c r="K767">
-        <v>24.1</v>
+        <v>22.95</v>
       </c>
       <c r="L767">
-        <v>27.9</v>
+        <v>27.64</v>
       </c>
       <c r="M767">
-        <v>23.85</v>
+        <v>23.15</v>
       </c>
       <c r="N767">
-        <v>28.09</v>
+        <v>27.14</v>
       </c>
       <c r="O767">
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>416</v>
+        <v>324</v>
       </c>
     </row>
     <row r="768" spans="1:16">
       <c r="A768" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B768" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C768">
-        <v>3.662984107501249</v>
+        <v>4.201697155904821</v>
       </c>
       <c r="D768" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E768">
-        <v>3.252613781366314</v>
+        <v>3.533170367281201</v>
       </c>
       <c r="F768">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G768">
-        <v>0.05181701589249874</v>
+        <v>0.05493830284409518</v>
       </c>
       <c r="H768">
-        <v>0.05150738621863368</v>
+        <v>0.0540668296327188</v>
       </c>
       <c r="I768">
-        <v>-0.4103703261349345</v>
+        <v>0.6685267886236197</v>
       </c>
       <c r="J768">
-        <v>1.007406522698693</v>
+        <v>1.014732113763807</v>
       </c>
       <c r="K768">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="L768">
-        <v>27.74</v>
+        <v>29.57</v>
       </c>
       <c r="M768">
-        <v>23.95</v>
+        <v>24.9</v>
       </c>
       <c r="N768">
-        <v>27.38</v>
+        <v>28.8</v>
       </c>
       <c r="O768">
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>416</v>
+        <v>324</v>
       </c>
     </row>
     <row r="769" spans="1:16">
       <c r="A769" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B769" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C769">
-        <v>4.503371200497003</v>
+        <v>3.280960550216626</v>
       </c>
       <c r="D769" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E769">
-        <v>3.648951566367863</v>
+        <v>3.979487338840251</v>
       </c>
       <c r="F769">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G769">
-        <v>0.050876628799503</v>
+        <v>0.05411903944978337</v>
       </c>
       <c r="H769">
-        <v>0.05063104843363214</v>
+        <v>0.05502051266115975</v>
       </c>
       <c r="I769">
-        <v>0.8544196341291403</v>
+        <v>0.6985267886236244</v>
       </c>
       <c r="J769">
         <v>1.014732113763807</v>
       </c>
       <c r="K769">
-        <v>22.85</v>
+        <v>25.05</v>
       </c>
       <c r="L769">
-        <v>27.69</v>
+        <v>28.7</v>
       </c>
       <c r="M769">
-        <v>23.15</v>
+        <v>25.15</v>
       </c>
       <c r="N769">
-        <v>27.14</v>
+        <v>29.5</v>
       </c>
       <c r="O769">
         <v>1</v>
@@ -40119,46 +40122,46 @@
     </row>
     <row r="770" spans="1:16">
       <c r="A770" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B770" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C770">
-        <v>4.351897989120626</v>
+        <v>3.444956058292242</v>
       </c>
       <c r="D770" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E770">
-        <v>3.648951566367863</v>
+        <v>3.83790248104501</v>
       </c>
       <c r="F770">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G770">
-        <v>0.05092810201087937</v>
+        <v>0.05235504394170776</v>
       </c>
       <c r="H770">
-        <v>0.05063104843363214</v>
+        <v>0.05234209751895499</v>
       </c>
       <c r="I770">
-        <v>0.7029464227527633</v>
+        <v>0.3929464227527681</v>
       </c>
       <c r="J770">
         <v>1.014732113763807</v>
       </c>
       <c r="K770">
-        <v>22.95</v>
+        <v>24.1</v>
       </c>
       <c r="L770">
-        <v>27.64</v>
+        <v>27.9</v>
       </c>
       <c r="M770">
-        <v>23.15</v>
+        <v>23.9</v>
       </c>
       <c r="N770">
-        <v>27.14</v>
+        <v>28.09</v>
       </c>
       <c r="O770">
         <v>1</v>
@@ -40169,46 +40172,46 @@
     </row>
     <row r="771" spans="1:16">
       <c r="A771" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B771" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C771">
-        <v>4.201697155904821</v>
+        <v>3.487902481045008</v>
       </c>
       <c r="D771" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E771">
-        <v>3.533170367281201</v>
+        <v>3.082433761593009</v>
       </c>
       <c r="F771">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G771">
-        <v>0.05493830284409518</v>
+        <v>0.05199209751895499</v>
       </c>
       <c r="H771">
-        <v>0.0540668296327188</v>
+        <v>0.05371756623840699</v>
       </c>
       <c r="I771">
-        <v>0.6685267886236197</v>
+        <v>-0.4054687194519992</v>
       </c>
       <c r="J771">
         <v>1.014732113763807</v>
       </c>
       <c r="K771">
-        <v>25</v>
+        <v>23.9</v>
       </c>
       <c r="L771">
-        <v>29.57</v>
+        <v>27.74</v>
       </c>
       <c r="M771">
-        <v>24.9</v>
+        <v>24.95</v>
       </c>
       <c r="N771">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="O771">
         <v>1</v>
@@ -40219,346 +40222,346 @@
     </row>
     <row r="772" spans="1:16">
       <c r="A772" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B772" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C772">
-        <v>3.506853395722153</v>
+        <v>4.366292866964365</v>
       </c>
       <c r="D772" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E772">
-        <v>3.979487338840251</v>
+        <v>3.510073517296505</v>
       </c>
       <c r="F772">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G772">
-        <v>0.05353314660427785</v>
+        <v>0.05101370713303564</v>
       </c>
       <c r="H772">
-        <v>0.05502051266115975</v>
+        <v>0.0507699264827035</v>
       </c>
       <c r="I772">
-        <v>0.4726339431180975</v>
+        <v>0.8562193496678603</v>
       </c>
       <c r="J772">
-        <v>1.014732113763807</v>
+        <v>1.020731165559546</v>
       </c>
       <c r="K772">
-        <v>24.65</v>
+        <v>22.85</v>
       </c>
       <c r="L772">
-        <v>28.52</v>
+        <v>27.69</v>
       </c>
       <c r="M772">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N772">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O772">
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>324</v>
+        <v>416</v>
       </c>
     </row>
     <row r="773" spans="1:16">
       <c r="A773" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B773" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C773">
-        <v>3.280960550216626</v>
+        <v>4.214219750408411</v>
       </c>
       <c r="D773" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E773">
-        <v>3.979487338840251</v>
+        <v>3.510073517296505</v>
       </c>
       <c r="F773">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G773">
-        <v>0.05411903944978337</v>
+        <v>0.05106578024959159</v>
       </c>
       <c r="H773">
-        <v>0.05502051266115975</v>
+        <v>0.0507699264827035</v>
       </c>
       <c r="I773">
-        <v>0.6985267886236244</v>
+        <v>0.7041462331119064</v>
       </c>
       <c r="J773">
-        <v>1.014732113763807</v>
+        <v>1.020731165559546</v>
       </c>
       <c r="K773">
-        <v>25.05</v>
+        <v>22.95</v>
       </c>
       <c r="L773">
-        <v>28.7</v>
+        <v>27.64</v>
       </c>
       <c r="M773">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N773">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O773">
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>324</v>
+        <v>416</v>
       </c>
     </row>
     <row r="774" spans="1:16">
       <c r="A774" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B774" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C774">
-        <v>3.444956058292242</v>
+        <v>4.05172086101134</v>
       </c>
       <c r="D774" t="s">
-        <v>195</v>
+        <v>326</v>
       </c>
       <c r="E774">
-        <v>3.888639086733196</v>
+        <v>3.383793977567297</v>
       </c>
       <c r="F774">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G774">
-        <v>0.05235504394170776</v>
+        <v>0.05508827913898866</v>
       </c>
       <c r="H774">
-        <v>0.0522913609132668</v>
+        <v>0.0542162060224327</v>
       </c>
       <c r="I774">
-        <v>0.4436830284409545</v>
+        <v>0.6679268834440428</v>
       </c>
       <c r="J774">
-        <v>1.014732113763807</v>
+        <v>1.020731165559546</v>
       </c>
       <c r="K774">
-        <v>24.1</v>
+        <v>25</v>
       </c>
       <c r="L774">
-        <v>27.9</v>
+        <v>29.57</v>
       </c>
       <c r="M774">
-        <v>23.85</v>
+        <v>24.9</v>
       </c>
       <c r="N774">
-        <v>28.09</v>
+        <v>28.8</v>
       </c>
       <c r="O774">
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>324</v>
+        <v>416</v>
       </c>
     </row>
     <row r="775" spans="1:16">
       <c r="A775" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B775" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C775">
-        <v>3.487902481045008</v>
+        <v>3.130684302733364</v>
       </c>
       <c r="D775" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E775">
-        <v>3.077165875356815</v>
+        <v>3.828611186177412</v>
       </c>
       <c r="F775">
         <v>1</v>
       </c>
       <c r="G775">
-        <v>0.05199209751895499</v>
+        <v>0.05426931569726664</v>
       </c>
       <c r="H775">
-        <v>0.05168283412464318</v>
+        <v>0.05517138881382259</v>
       </c>
       <c r="I775">
-        <v>-0.4107366056881929</v>
+        <v>0.6979268834440475</v>
       </c>
       <c r="J775">
-        <v>1.014732113763807</v>
+        <v>1.020731165559546</v>
       </c>
       <c r="K775">
-        <v>23.9</v>
+        <v>25.05</v>
       </c>
       <c r="L775">
-        <v>27.74</v>
+        <v>28.7</v>
       </c>
       <c r="M775">
-        <v>23.95</v>
+        <v>25.15</v>
       </c>
       <c r="N775">
-        <v>27.38</v>
+        <v>29.5</v>
       </c>
       <c r="O775">
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>324</v>
+        <v>416</v>
       </c>
     </row>
     <row r="776" spans="1:16">
       <c r="A776" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B776" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C776">
-        <v>4.366292866964365</v>
+        <v>3.300378910014931</v>
       </c>
       <c r="D776" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E776">
-        <v>3.510073517296505</v>
+        <v>3.694525143126842</v>
       </c>
       <c r="F776">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G776">
-        <v>0.05101370713303564</v>
+        <v>0.05249962108998507</v>
       </c>
       <c r="H776">
-        <v>0.0507699264827035</v>
+        <v>0.05248547485687315</v>
       </c>
       <c r="I776">
-        <v>0.8562193496678603</v>
+        <v>0.3941462331119112</v>
       </c>
       <c r="J776">
         <v>1.020731165559546</v>
       </c>
       <c r="K776">
-        <v>22.85</v>
+        <v>24.1</v>
       </c>
       <c r="L776">
-        <v>27.69</v>
+        <v>27.9</v>
       </c>
       <c r="M776">
-        <v>23.15</v>
+        <v>23.9</v>
       </c>
       <c r="N776">
-        <v>27.14</v>
+        <v>28.09</v>
       </c>
       <c r="O776">
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="777" spans="1:16">
       <c r="A777" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B777" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C777">
-        <v>4.214219750408411</v>
+        <v>2.933488584848863</v>
       </c>
       <c r="D777" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E777">
-        <v>3.510073517296505</v>
+        <v>2.932757419289317</v>
       </c>
       <c r="F777">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G777">
-        <v>0.05106578024959159</v>
+        <v>0.05182651141515113</v>
       </c>
       <c r="H777">
-        <v>0.0507699264827035</v>
+        <v>0.05386724258071068</v>
       </c>
       <c r="I777">
-        <v>0.7041462331119064</v>
+        <v>-0.0007311655595465538</v>
       </c>
       <c r="J777">
         <v>1.020731165559546</v>
       </c>
       <c r="K777">
-        <v>22.95</v>
+        <v>23.95</v>
       </c>
       <c r="L777">
-        <v>27.64</v>
+        <v>27.38</v>
       </c>
       <c r="M777">
-        <v>23.15</v>
+        <v>24.95</v>
       </c>
       <c r="N777">
-        <v>27.14</v>
+        <v>28.4</v>
       </c>
       <c r="O777">
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="778" spans="1:16">
       <c r="A778" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B778" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C778">
-        <v>4.05172086101134</v>
+        <v>4.196922435356054</v>
       </c>
       <c r="D778" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E778">
-        <v>3.383793977567297</v>
+        <v>3.338479403872764</v>
       </c>
       <c r="F778">
         <v>-1</v>
       </c>
       <c r="G778">
-        <v>0.05508827913898866</v>
+        <v>0.05118307756464395</v>
       </c>
       <c r="H778">
-        <v>0.0542162060224327</v>
+        <v>0.05094152059612723</v>
       </c>
       <c r="I778">
-        <v>0.6679268834440428</v>
+        <v>0.85844303148329</v>
       </c>
       <c r="J778">
-        <v>1.020731165559546</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K778">
-        <v>25</v>
+        <v>22.85</v>
       </c>
       <c r="L778">
-        <v>29.57</v>
+        <v>27.69</v>
       </c>
       <c r="M778">
-        <v>24.9</v>
+        <v>23.15</v>
       </c>
       <c r="N778">
-        <v>28.8</v>
+        <v>27.14</v>
       </c>
       <c r="O778">
         <v>1</v>
@@ -40569,46 +40572,46 @@
     </row>
     <row r="779" spans="1:16">
       <c r="A779" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B779" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C779">
-        <v>3.358976768957184</v>
+        <v>4.04410809152829</v>
       </c>
       <c r="D779" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E779">
-        <v>3.828611186177412</v>
+        <v>3.338479403872764</v>
       </c>
       <c r="F779">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G779">
-        <v>0.05368102323104282</v>
+        <v>0.05123589190847171</v>
       </c>
       <c r="H779">
-        <v>0.05517138881382259</v>
+        <v>0.05094152059612723</v>
       </c>
       <c r="I779">
-        <v>0.4696344172202274</v>
+        <v>0.7056286876555262</v>
       </c>
       <c r="J779">
-        <v>1.020731165559546</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K779">
-        <v>24.65</v>
+        <v>22.95</v>
       </c>
       <c r="L779">
-        <v>28.52</v>
+        <v>27.64</v>
       </c>
       <c r="M779">
-        <v>25.15</v>
+        <v>23.15</v>
       </c>
       <c r="N779">
-        <v>29.5</v>
+        <v>27.14</v>
       </c>
       <c r="O779">
         <v>1</v>
@@ -40619,46 +40622,46 @@
     </row>
     <row r="780" spans="1:16">
       <c r="A780" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B780" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C780">
-        <v>3.130684302733364</v>
+        <v>3.866414043059141</v>
       </c>
       <c r="D780" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E780">
-        <v>3.828611186177412</v>
+        <v>3.199228386886904</v>
       </c>
       <c r="F780">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G780">
-        <v>0.05426931569726664</v>
+        <v>0.05527358595694087</v>
       </c>
       <c r="H780">
-        <v>0.05517138881382259</v>
+        <v>0.0544007716131131</v>
       </c>
       <c r="I780">
-        <v>0.6979268834440475</v>
+        <v>0.6671856561722365</v>
       </c>
       <c r="J780">
-        <v>1.020731165559546</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K780">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="L780">
-        <v>28.7</v>
+        <v>29.57</v>
       </c>
       <c r="M780">
-        <v>25.15</v>
+        <v>24.9</v>
       </c>
       <c r="N780">
-        <v>29.5</v>
+        <v>28.8</v>
       </c>
       <c r="O780">
         <v>1</v>
@@ -40669,46 +40672,46 @@
     </row>
     <row r="781" spans="1:16">
       <c r="A781" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B781" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C781">
-        <v>3.300378910014931</v>
+        <v>2.945006871145257</v>
       </c>
       <c r="D781" t="s">
-        <v>195</v>
+        <v>329</v>
       </c>
       <c r="E781">
-        <v>3.745561701404817</v>
+        <v>3.642192527317494</v>
       </c>
       <c r="F781">
         <v>1</v>
       </c>
       <c r="G781">
-        <v>0.05249962108998507</v>
+        <v>0.05445499312885474</v>
       </c>
       <c r="H781">
-        <v>0.05243443829859518</v>
+        <v>0.05535780747268251</v>
       </c>
       <c r="I781">
-        <v>0.445182791389886</v>
+        <v>0.6971856561722376</v>
       </c>
       <c r="J781">
-        <v>1.020731165559546</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K781">
-        <v>24.1</v>
+        <v>25.05</v>
       </c>
       <c r="L781">
-        <v>27.9</v>
+        <v>28.7</v>
       </c>
       <c r="M781">
-        <v>23.85</v>
+        <v>25.15</v>
       </c>
       <c r="N781">
-        <v>28.09</v>
+        <v>29.5</v>
       </c>
       <c r="O781">
         <v>1</v>
@@ -40719,46 +40722,46 @@
     </row>
     <row r="782" spans="1:16">
       <c r="A782" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B782" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C782">
-        <v>3.344525143126841</v>
+        <v>3.121743137509007</v>
       </c>
       <c r="D782" t="s">
         <v>327</v>
       </c>
       <c r="E782">
-        <v>2.933488584848863</v>
+        <v>3.517371825164538</v>
       </c>
       <c r="F782">
         <v>1</v>
       </c>
       <c r="G782">
-        <v>0.05213547485687316</v>
+        <v>0.05267825686249099</v>
       </c>
       <c r="H782">
-        <v>0.05182651141515113</v>
+        <v>0.05266262817483546</v>
       </c>
       <c r="I782">
-        <v>-0.4110365582779778</v>
+        <v>0.3956286876555311</v>
       </c>
       <c r="J782">
-        <v>1.020731165559546</v>
+        <v>1.028143438277634</v>
       </c>
       <c r="K782">
+        <v>24.1</v>
+      </c>
+      <c r="L782">
+        <v>27.9</v>
+      </c>
+      <c r="M782">
         <v>23.9</v>
       </c>
-      <c r="L782">
-        <v>27.74</v>
-      </c>
-      <c r="M782">
-        <v>23.95</v>
-      </c>
       <c r="N782">
-        <v>27.38</v>
+        <v>28.09</v>
       </c>
       <c r="O782">
         <v>1</v>
@@ -40769,90 +40772,90 @@
     </row>
     <row r="783" spans="1:16">
       <c r="A783" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B783" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C783">
-        <v>4.196922435356054</v>
+        <v>2.755964653250654</v>
       </c>
       <c r="D783" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E783">
-        <v>3.338479403872764</v>
+        <v>2.747821214973019</v>
       </c>
       <c r="F783">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G783">
-        <v>0.05118307756464395</v>
+        <v>0.05200403534674935</v>
       </c>
       <c r="H783">
-        <v>0.05094152059612723</v>
+        <v>0.05405217878502698</v>
       </c>
       <c r="I783">
-        <v>0.85844303148329</v>
+        <v>-0.008143438277635084</v>
       </c>
       <c r="J783">
         <v>1.028143438277634</v>
       </c>
       <c r="K783">
-        <v>22.85</v>
+        <v>23.95</v>
       </c>
       <c r="L783">
-        <v>27.69</v>
+        <v>27.38</v>
       </c>
       <c r="M783">
-        <v>23.15</v>
+        <v>24.95</v>
       </c>
       <c r="N783">
-        <v>27.14</v>
+        <v>28.4</v>
       </c>
       <c r="O783">
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="784" spans="1:16">
       <c r="A784" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B784" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C784">
-        <v>4.04410809152829</v>
+        <v>4.101655744450497</v>
       </c>
       <c r="D784" t="s">
         <v>325</v>
       </c>
       <c r="E784">
-        <v>3.338479403872764</v>
+        <v>3.241961946784642</v>
       </c>
       <c r="F784">
         <v>-1</v>
       </c>
       <c r="G784">
-        <v>0.05123589190847171</v>
+        <v>0.05127834425554951</v>
       </c>
       <c r="H784">
-        <v>0.05094152059612723</v>
+        <v>0.05103803805321536</v>
       </c>
       <c r="I784">
-        <v>0.7056286876555262</v>
+        <v>0.8596937976658552</v>
       </c>
       <c r="J784">
-        <v>1.028143438277634</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K784">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="L784">
-        <v>27.64</v>
+        <v>27.69</v>
       </c>
       <c r="M784">
         <v>23.15</v>
@@ -40869,46 +40872,46 @@
     </row>
     <row r="785" spans="1:16">
       <c r="A785" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B785" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C785">
-        <v>3.866414043059141</v>
+        <v>3.948424478561879</v>
       </c>
       <c r="D785" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E785">
-        <v>3.199228386886904</v>
+        <v>3.241961946784642</v>
       </c>
       <c r="F785">
         <v>-1</v>
       </c>
       <c r="G785">
-        <v>0.05527358595694087</v>
+        <v>0.05133157552143813</v>
       </c>
       <c r="H785">
-        <v>0.0544007716131131</v>
+        <v>0.05103803805321536</v>
       </c>
       <c r="I785">
-        <v>0.6671856561722365</v>
+        <v>0.7064625317772375</v>
       </c>
       <c r="J785">
-        <v>1.028143438277634</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K785">
-        <v>25</v>
+        <v>22.95</v>
       </c>
       <c r="L785">
-        <v>29.57</v>
+        <v>27.64</v>
       </c>
       <c r="M785">
-        <v>24.9</v>
+        <v>23.15</v>
       </c>
       <c r="N785">
-        <v>28.8</v>
+        <v>27.14</v>
       </c>
       <c r="O785">
         <v>1</v>
@@ -40919,46 +40922,46 @@
     </row>
     <row r="786" spans="1:16">
       <c r="A786" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B786" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C786">
-        <v>3.176264246456313</v>
+        <v>3.762183527845185</v>
       </c>
       <c r="D786" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E786">
-        <v>3.642192527317494</v>
+        <v>3.095414793733806</v>
       </c>
       <c r="F786">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G786">
-        <v>0.05386373575354369</v>
+        <v>0.05537781647215482</v>
       </c>
       <c r="H786">
-        <v>0.05535780747268251</v>
+        <v>0.0545045852062662</v>
       </c>
       <c r="I786">
-        <v>0.4659282808611813</v>
+        <v>0.666768734111379</v>
       </c>
       <c r="J786">
-        <v>1.028143438277634</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K786">
-        <v>24.65</v>
+        <v>25</v>
       </c>
       <c r="L786">
-        <v>28.52</v>
+        <v>29.57</v>
       </c>
       <c r="M786">
-        <v>25.15</v>
+        <v>24.9</v>
       </c>
       <c r="N786">
-        <v>29.5</v>
+        <v>28.8</v>
       </c>
       <c r="O786">
         <v>1</v>
@@ -40969,34 +40972,34 @@
     </row>
     <row r="787" spans="1:16">
       <c r="A787" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B787" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C787">
-        <v>2.945006871145257</v>
+        <v>2.840567894900875</v>
       </c>
       <c r="D787" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E787">
-        <v>3.642192527317494</v>
+        <v>3.537336629012259</v>
       </c>
       <c r="F787">
         <v>1</v>
       </c>
       <c r="G787">
-        <v>0.05445499312885474</v>
+        <v>0.05455943210509912</v>
       </c>
       <c r="H787">
-        <v>0.05535780747268251</v>
+        <v>0.05546266337098774</v>
       </c>
       <c r="I787">
-        <v>0.6971856561722376</v>
+        <v>0.6967687341113837</v>
       </c>
       <c r="J787">
-        <v>1.028143438277634</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K787">
         <v>25.05</v>
@@ -41019,34 +41022,34 @@
     </row>
     <row r="788" spans="1:16">
       <c r="A788" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B788" t="s">
         <v>189</v>
       </c>
       <c r="C788">
-        <v>3.121743137509007</v>
+        <v>3.021264920842754</v>
       </c>
       <c r="D788" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E788">
-        <v>3.517371825164538</v>
+        <v>3.417727452619999</v>
       </c>
       <c r="F788">
         <v>1</v>
       </c>
       <c r="G788">
-        <v>0.05267825686249099</v>
+        <v>0.05277873507915724</v>
       </c>
       <c r="H788">
-        <v>0.05266262817483546</v>
+        <v>0.05276227254738</v>
       </c>
       <c r="I788">
-        <v>0.3956286876555311</v>
+        <v>0.3964625317772459</v>
       </c>
       <c r="J788">
-        <v>1.028143438277634</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K788">
         <v>24.1</v>
@@ -41069,46 +41072,46 @@
     </row>
     <row r="789" spans="1:16">
       <c r="A789" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B789" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C789">
-        <v>3.167371825164537</v>
+        <v>2.656111819675687</v>
       </c>
       <c r="D789" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E789">
-        <v>2.755964653250654</v>
+        <v>2.643799160789495</v>
       </c>
       <c r="F789">
         <v>1</v>
       </c>
       <c r="G789">
-        <v>0.05231262817483546</v>
+        <v>0.05210388818032431</v>
       </c>
       <c r="H789">
-        <v>0.05200403534674935</v>
+        <v>0.0541562008392105</v>
       </c>
       <c r="I789">
-        <v>-0.4114071719138828</v>
+        <v>-0.01231265888619149</v>
       </c>
       <c r="J789">
-        <v>1.028143438277634</v>
+        <v>1.032312658886193</v>
       </c>
       <c r="K789">
-        <v>23.9</v>
+        <v>23.95</v>
       </c>
       <c r="L789">
-        <v>27.74</v>
+        <v>27.38</v>
       </c>
       <c r="M789">
-        <v>23.95</v>
+        <v>24.95</v>
       </c>
       <c r="N789">
-        <v>27.38</v>
+        <v>28.4</v>
       </c>
       <c r="O789">
         <v>1</v>
@@ -41125,28 +41128,28 @@
         <v>186</v>
       </c>
       <c r="C790">
-        <v>4.101655744450497</v>
+        <v>4.009505903995372</v>
       </c>
       <c r="D790" t="s">
         <v>325</v>
       </c>
       <c r="E790">
-        <v>3.241961946784642</v>
+        <v>3.148602261597063</v>
       </c>
       <c r="F790">
         <v>-1</v>
       </c>
       <c r="G790">
-        <v>0.05127834425554951</v>
+        <v>0.05137049409600464</v>
       </c>
       <c r="H790">
-        <v>0.05103803805321536</v>
+        <v>0.05113139773840294</v>
       </c>
       <c r="I790">
-        <v>0.8596937976658552</v>
+        <v>0.8609036423983092</v>
       </c>
       <c r="J790">
-        <v>1.032312658886193</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K790">
         <v>22.85</v>
@@ -41175,28 +41178,28 @@
         <v>187</v>
       </c>
       <c r="C791">
-        <v>3.948424478561879</v>
+        <v>3.855871356529267</v>
       </c>
       <c r="D791" t="s">
         <v>325</v>
       </c>
       <c r="E791">
-        <v>3.241961946784642</v>
+        <v>3.148602261597063</v>
       </c>
       <c r="F791">
         <v>-1</v>
       </c>
       <c r="G791">
-        <v>0.05133157552143813</v>
+        <v>0.05142412864347074</v>
       </c>
       <c r="H791">
-        <v>0.05103803805321536</v>
+        <v>0.05113139773840294</v>
       </c>
       <c r="I791">
-        <v>0.7064625317772375</v>
+        <v>0.7072690949322045</v>
       </c>
       <c r="J791">
-        <v>1.032312658886193</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K791">
         <v>22.95</v>
@@ -41225,28 +41228,28 @@
         <v>188</v>
       </c>
       <c r="C792">
-        <v>3.762183527845185</v>
+        <v>3.661363133474147</v>
       </c>
       <c r="D792" t="s">
         <v>326</v>
       </c>
       <c r="E792">
-        <v>3.095414793733806</v>
+        <v>2.994997680940251</v>
       </c>
       <c r="F792">
         <v>-1</v>
       </c>
       <c r="G792">
-        <v>0.05537781647215482</v>
+        <v>0.05547863686652586</v>
       </c>
       <c r="H792">
-        <v>0.0545045852062662</v>
+        <v>0.05460500231905975</v>
       </c>
       <c r="I792">
-        <v>0.666768734111379</v>
+        <v>0.6663654525338956</v>
       </c>
       <c r="J792">
-        <v>1.032312658886193</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K792">
         <v>25</v>
@@ -41272,43 +41275,43 @@
         <v>3</v>
       </c>
       <c r="B793" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C793">
-        <v>2.840567894900875</v>
+        <v>2.924074060669074</v>
       </c>
       <c r="D793" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E793">
-        <v>3.537336629012259</v>
+        <v>3.321343155601287</v>
       </c>
       <c r="F793">
         <v>1</v>
       </c>
       <c r="G793">
-        <v>0.05455943210509912</v>
+        <v>0.05287592593933093</v>
       </c>
       <c r="H793">
-        <v>0.05546266337098774</v>
+        <v>0.05285865684439871</v>
       </c>
       <c r="I793">
-        <v>0.6967687341113837</v>
+        <v>0.3972690949322129</v>
       </c>
       <c r="J793">
-        <v>1.032312658886193</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K793">
-        <v>25.05</v>
+        <v>24.1</v>
       </c>
       <c r="L793">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="M793">
-        <v>25.15</v>
+        <v>23.9</v>
       </c>
       <c r="N793">
-        <v>29.5</v>
+        <v>28.09</v>
       </c>
       <c r="O793">
         <v>1</v>
@@ -41322,43 +41325,43 @@
         <v>4</v>
       </c>
       <c r="B794" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C794">
-        <v>3.021264920842754</v>
+        <v>2.559525881868232</v>
       </c>
       <c r="D794" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E794">
-        <v>3.417727452619999</v>
+        <v>2.543180407207199</v>
       </c>
       <c r="F794">
         <v>1</v>
       </c>
       <c r="G794">
-        <v>0.05277873507915724</v>
+        <v>0.05220047411813176</v>
       </c>
       <c r="H794">
-        <v>0.05276227254738</v>
+        <v>0.0542568195927928</v>
       </c>
       <c r="I794">
-        <v>0.3964625317772459</v>
+        <v>-0.01634547466103342</v>
       </c>
       <c r="J794">
-        <v>1.032312658886193</v>
+        <v>1.036345474661034</v>
       </c>
       <c r="K794">
-        <v>24.1</v>
+        <v>23.95</v>
       </c>
       <c r="L794">
-        <v>27.9</v>
+        <v>27.38</v>
       </c>
       <c r="M794">
-        <v>23.9</v>
+        <v>24.95</v>
       </c>
       <c r="N794">
-        <v>28.09</v>
+        <v>28.4</v>
       </c>
       <c r="O794">
         <v>1</v>
@@ -41369,90 +41372,90 @@
     </row>
     <row r="795" spans="1:16">
       <c r="A795" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B795" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C795">
-        <v>3.067727452619998</v>
+        <v>3.923892030831919</v>
       </c>
       <c r="D795" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E795">
-        <v>2.656111819675687</v>
+        <v>3.06186435508792</v>
       </c>
       <c r="F795">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G795">
-        <v>0.05241227254738</v>
+        <v>0.05145610796916809</v>
       </c>
       <c r="H795">
-        <v>0.05210388818032431</v>
+        <v>0.05121813564491208</v>
       </c>
       <c r="I795">
-        <v>-0.4116156329443115</v>
+        <v>0.8620276757439989</v>
       </c>
       <c r="J795">
-        <v>1.032312658886193</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K795">
-        <v>23.9</v>
+        <v>22.85</v>
       </c>
       <c r="L795">
-        <v>27.74</v>
+        <v>27.69</v>
       </c>
       <c r="M795">
-        <v>23.95</v>
+        <v>23.15</v>
       </c>
       <c r="N795">
-        <v>27.38</v>
+        <v>27.14</v>
       </c>
       <c r="O795">
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="796" spans="1:16">
       <c r="A796" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B796" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C796">
-        <v>4.009505903995372</v>
+        <v>3.769882805583919</v>
       </c>
       <c r="D796" t="s">
         <v>325</v>
       </c>
       <c r="E796">
-        <v>3.148602261597063</v>
+        <v>3.06186435508792</v>
       </c>
       <c r="F796">
         <v>-1</v>
       </c>
       <c r="G796">
-        <v>0.05137049409600464</v>
+        <v>0.05151011719441608</v>
       </c>
       <c r="H796">
-        <v>0.05113139773840294</v>
+        <v>0.05121813564491208</v>
       </c>
       <c r="I796">
-        <v>0.8609036423983092</v>
+        <v>0.7080184504959988</v>
       </c>
       <c r="J796">
-        <v>1.036345474661034</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K796">
-        <v>22.85</v>
+        <v>22.95</v>
       </c>
       <c r="L796">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="M796">
         <v>23.15</v>
@@ -41469,46 +41472,46 @@
     </row>
     <row r="797" spans="1:16">
       <c r="A797" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B797" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C797">
-        <v>3.855871356529267</v>
+        <v>3.56769368799991</v>
       </c>
       <c r="D797" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E797">
-        <v>3.148602261597063</v>
+        <v>2.901702913247913</v>
       </c>
       <c r="F797">
         <v>-1</v>
       </c>
       <c r="G797">
-        <v>0.05142412864347074</v>
+        <v>0.05557230631200009</v>
       </c>
       <c r="H797">
-        <v>0.05113139773840294</v>
+        <v>0.05469829708675209</v>
       </c>
       <c r="I797">
-        <v>0.7072690949322045</v>
+        <v>0.6659907747519966</v>
       </c>
       <c r="J797">
-        <v>1.036345474661034</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K797">
-        <v>22.95</v>
+        <v>25</v>
       </c>
       <c r="L797">
-        <v>27.64</v>
+        <v>29.57</v>
       </c>
       <c r="M797">
-        <v>23.15</v>
+        <v>24.9</v>
       </c>
       <c r="N797">
-        <v>27.14</v>
+        <v>28.8</v>
       </c>
       <c r="O797">
         <v>1</v>
@@ -41519,46 +41522,46 @@
     </row>
     <row r="798" spans="1:16">
       <c r="A798" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B798" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C798">
-        <v>3.661363133474147</v>
+        <v>2.645689075375909</v>
       </c>
       <c r="D798" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E798">
-        <v>2.994997680940251</v>
+        <v>3.34167985012791</v>
       </c>
       <c r="F798">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G798">
-        <v>0.05547863686652586</v>
+        <v>0.05475431092462409</v>
       </c>
       <c r="H798">
-        <v>0.05460500231905975</v>
+        <v>0.05565832014987209</v>
       </c>
       <c r="I798">
-        <v>0.6663654525338956</v>
+        <v>0.6959907747520013</v>
       </c>
       <c r="J798">
-        <v>1.036345474661034</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K798">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="L798">
-        <v>29.57</v>
+        <v>28.7</v>
       </c>
       <c r="M798">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N798">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O798">
         <v>1</v>
@@ -41569,46 +41572,46 @@
     </row>
     <row r="799" spans="1:16">
       <c r="A799" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B799" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C799">
-        <v>2.739545859741096</v>
+        <v>2.83377671523191</v>
       </c>
       <c r="D799" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E799">
-        <v>3.435911312274992</v>
+        <v>3.231795165727917</v>
       </c>
       <c r="F799">
         <v>1</v>
       </c>
       <c r="G799">
-        <v>0.05466045414025891</v>
+        <v>0.05296622328476809</v>
       </c>
       <c r="H799">
-        <v>0.05556408868772501</v>
+        <v>0.05294820483427208</v>
       </c>
       <c r="I799">
-        <v>0.6963654525338967</v>
+        <v>0.3980184504960071</v>
       </c>
       <c r="J799">
-        <v>1.036345474661034</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K799">
-        <v>25.05</v>
+        <v>24.1</v>
       </c>
       <c r="L799">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="M799">
-        <v>25.15</v>
+        <v>23.9</v>
       </c>
       <c r="N799">
-        <v>29.5</v>
+        <v>28.09</v>
       </c>
       <c r="O799">
         <v>1</v>
@@ -41619,46 +41622,46 @@
     </row>
     <row r="800" spans="1:16">
       <c r="A800" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B800" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C800">
-        <v>2.924074060669074</v>
+        <v>2.469790553103913</v>
       </c>
       <c r="D800" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E800">
-        <v>3.321343155601287</v>
+        <v>2.449698300623911</v>
       </c>
       <c r="F800">
         <v>1</v>
       </c>
       <c r="G800">
-        <v>0.05287592593933093</v>
+        <v>0.05229020944689609</v>
       </c>
       <c r="H800">
-        <v>0.05285865684439871</v>
+        <v>0.05435030169937609</v>
       </c>
       <c r="I800">
-        <v>0.3972690949322129</v>
+        <v>-0.02009225248000135</v>
       </c>
       <c r="J800">
-        <v>1.036345474661034</v>
+        <v>1.040092252480004</v>
       </c>
       <c r="K800">
-        <v>24.1</v>
+        <v>23.95</v>
       </c>
       <c r="L800">
-        <v>27.9</v>
+        <v>27.38</v>
       </c>
       <c r="M800">
-        <v>23.9</v>
+        <v>24.95</v>
       </c>
       <c r="N800">
-        <v>28.09</v>
+        <v>28.4</v>
       </c>
       <c r="O800">
         <v>1</v>
@@ -41675,28 +41678,28 @@
         <v>186</v>
       </c>
       <c r="C801">
-        <v>3.923892030831919</v>
+        <v>3.103333239057651</v>
       </c>
       <c r="D801" t="s">
         <v>325</v>
       </c>
       <c r="E801">
-        <v>3.06186435508792</v>
+        <v>2.230532362546374</v>
       </c>
       <c r="F801">
         <v>-1</v>
       </c>
       <c r="G801">
-        <v>0.05145610796916809</v>
+        <v>0.05227666676094235</v>
       </c>
       <c r="H801">
-        <v>0.05121813564491208</v>
+        <v>0.05204946763745363</v>
       </c>
       <c r="I801">
-        <v>0.8620276757439989</v>
+        <v>0.8728008765112776</v>
       </c>
       <c r="J801">
-        <v>1.040092252480004</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K801">
         <v>22.85</v>
@@ -41725,28 +41728,28 @@
         <v>187</v>
       </c>
       <c r="C802">
-        <v>3.769882805583919</v>
+        <v>2.945732946887226</v>
       </c>
       <c r="D802" t="s">
         <v>325</v>
       </c>
       <c r="E802">
-        <v>3.06186435508792</v>
+        <v>2.230532362546374</v>
       </c>
       <c r="F802">
         <v>-1</v>
       </c>
       <c r="G802">
-        <v>0.05151011719441608</v>
+        <v>0.05233426705311277</v>
       </c>
       <c r="H802">
-        <v>0.05121813564491208</v>
+        <v>0.05204946763745363</v>
       </c>
       <c r="I802">
-        <v>0.7080184504959988</v>
+        <v>0.7152005843408524</v>
       </c>
       <c r="J802">
-        <v>1.040092252480004</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K802">
         <v>22.95</v>
@@ -41772,43 +41775,43 @@
         <v>2</v>
       </c>
       <c r="B803" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C803">
-        <v>3.56769368799991</v>
+        <v>1.746126811308276</v>
       </c>
       <c r="D803" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E803">
-        <v>2.901702913247913</v>
+        <v>2.438526519137852</v>
       </c>
       <c r="F803">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G803">
-        <v>0.05557230631200009</v>
+        <v>0.05565387318869172</v>
       </c>
       <c r="H803">
-        <v>0.05469829708675209</v>
+        <v>0.05656147348086215</v>
       </c>
       <c r="I803">
-        <v>0.6659907747519966</v>
+        <v>0.6923997078295763</v>
       </c>
       <c r="J803">
-        <v>1.040092252480004</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K803">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="L803">
-        <v>29.57</v>
+        <v>28.7</v>
       </c>
       <c r="M803">
-        <v>24.9</v>
+        <v>25.15</v>
       </c>
       <c r="N803">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="O803">
         <v>1</v>
@@ -41825,40 +41828,40 @@
         <v>192</v>
       </c>
       <c r="C804">
-        <v>2.645689075375909</v>
+        <v>1.609730025182962</v>
       </c>
       <c r="D804" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E804">
-        <v>3.34167985012791</v>
+        <v>1.553727103478703</v>
       </c>
       <c r="F804">
         <v>1</v>
       </c>
       <c r="G804">
-        <v>0.05475431092462409</v>
+        <v>0.05315026997481704</v>
       </c>
       <c r="H804">
-        <v>0.05565832014987209</v>
+        <v>0.05524627289652129</v>
       </c>
       <c r="I804">
-        <v>0.6959907747520013</v>
+        <v>-0.05600292170425902</v>
       </c>
       <c r="J804">
-        <v>1.040092252480004</v>
+        <v>1.07600292170426</v>
       </c>
       <c r="K804">
-        <v>25.05</v>
+        <v>23.95</v>
       </c>
       <c r="L804">
-        <v>28.7</v>
+        <v>27.38</v>
       </c>
       <c r="M804">
-        <v>25.15</v>
+        <v>24.95</v>
       </c>
       <c r="N804">
-        <v>29.5</v>
+        <v>28.4</v>
       </c>
       <c r="O804">
         <v>1</v>
@@ -41869,96 +41872,96 @@
     </row>
     <row r="805" spans="1:16">
       <c r="A805" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B805" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C805">
-        <v>2.83377671523191</v>
+        <v>1.471662330943524</v>
       </c>
       <c r="D805" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E805">
-        <v>3.231795165727917</v>
+        <v>1.061054196102969</v>
       </c>
       <c r="F805">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G805">
-        <v>0.05296622328476809</v>
+        <v>0.05272833766905648</v>
       </c>
       <c r="H805">
-        <v>0.05294820483427208</v>
+        <v>0.05321894580389703</v>
       </c>
       <c r="I805">
-        <v>0.3980184504960071</v>
+        <v>0.4106081348405546</v>
       </c>
       <c r="J805">
-        <v>1.040092252480004</v>
+        <v>1.126520337101384</v>
       </c>
       <c r="K805">
-        <v>24.1</v>
+        <v>22.75</v>
       </c>
       <c r="L805">
-        <v>27.9</v>
+        <v>27.1</v>
       </c>
       <c r="M805">
-        <v>23.9</v>
+        <v>23.15</v>
       </c>
       <c r="N805">
-        <v>28.09</v>
+        <v>27.14</v>
       </c>
       <c r="O805">
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="806" spans="1:16">
       <c r="A806" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B806" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C806">
-        <v>3.103333239057651</v>
+        <v>0.4806655556103365</v>
       </c>
       <c r="D806" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E806">
-        <v>2.230532362546374</v>
+        <v>1.168013521900203</v>
       </c>
       <c r="F806">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G806">
-        <v>0.05227666676094235</v>
+        <v>0.05691933444438967</v>
       </c>
       <c r="H806">
-        <v>0.05204946763745363</v>
+        <v>0.0578319864780998</v>
       </c>
       <c r="I806">
-        <v>0.8728008765112776</v>
+        <v>0.6873479662898667</v>
       </c>
       <c r="J806">
-        <v>1.07600292170426</v>
+        <v>1.126520337101384</v>
       </c>
       <c r="K806">
-        <v>22.85</v>
+        <v>25.05</v>
       </c>
       <c r="L806">
-        <v>27.69</v>
+        <v>28.7</v>
       </c>
       <c r="M806">
-        <v>23.15</v>
+        <v>25.15</v>
       </c>
       <c r="N806">
-        <v>27.14</v>
+        <v>29.5</v>
       </c>
       <c r="O806">
         <v>1</v>
@@ -41969,46 +41972,46 @@
     </row>
     <row r="807" spans="1:16">
       <c r="A807" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B807" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C807">
-        <v>2.945732946887226</v>
+        <v>0.3998379264218599</v>
       </c>
       <c r="D807" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E807">
-        <v>2.230532362546374</v>
+        <v>0.2933175893204769</v>
       </c>
       <c r="F807">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G807">
-        <v>0.05233426705311277</v>
+        <v>0.05436016207357814</v>
       </c>
       <c r="H807">
-        <v>0.05204946763745363</v>
+        <v>0.05650668241067952</v>
       </c>
       <c r="I807">
-        <v>0.7152005843408524</v>
+        <v>-0.106520337101383</v>
       </c>
       <c r="J807">
-        <v>1.07600292170426</v>
+        <v>1.126520337101384</v>
       </c>
       <c r="K807">
-        <v>22.95</v>
+        <v>23.95</v>
       </c>
       <c r="L807">
-        <v>27.64</v>
+        <v>27.38</v>
       </c>
       <c r="M807">
-        <v>23.15</v>
+        <v>24.95</v>
       </c>
       <c r="N807">
-        <v>27.14</v>
+        <v>28.4</v>
       </c>
       <c r="O807">
         <v>1</v>
@@ -42019,146 +42022,146 @@
     </row>
     <row r="808" spans="1:16">
       <c r="A808" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B808" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C808">
-        <v>1.746126811308276</v>
+        <v>1.037051962254782</v>
       </c>
       <c r="D808" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E808">
-        <v>2.438526519137852</v>
+        <v>0.2739601696766627</v>
       </c>
       <c r="F808">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G808">
-        <v>0.05565387318869172</v>
+        <v>0.05316294803774523</v>
       </c>
       <c r="H808">
-        <v>0.05656147348086215</v>
+        <v>0.05732603983032334</v>
       </c>
       <c r="I808">
-        <v>0.6923997078295763</v>
+        <v>0.7630917925781198</v>
       </c>
       <c r="J808">
-        <v>1.07600292170426</v>
+        <v>1.145624089571218</v>
       </c>
       <c r="K808">
-        <v>25.05</v>
+        <v>22.75</v>
       </c>
       <c r="L808">
-        <v>28.7</v>
+        <v>27.1</v>
       </c>
       <c r="M808">
-        <v>25.15</v>
+        <v>24.9</v>
       </c>
       <c r="N808">
-        <v>29.5</v>
+        <v>28.8</v>
       </c>
       <c r="O808">
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="809" spans="1:16">
       <c r="A809" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B809" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C809">
-        <v>1.968329586927322</v>
+        <v>0.002116556240977729</v>
       </c>
       <c r="D809" t="s">
         <v>329</v>
       </c>
       <c r="E809">
-        <v>2.373530171268179</v>
+        <v>0.6875541472838584</v>
       </c>
       <c r="F809">
         <v>1</v>
       </c>
       <c r="G809">
-        <v>0.05383167041307267</v>
+        <v>0.05739788344375902</v>
       </c>
       <c r="H809">
-        <v>0.05380646982873182</v>
+        <v>0.05831244585271614</v>
       </c>
       <c r="I809">
-        <v>0.4052005843408573</v>
+        <v>0.6854375910428807</v>
       </c>
       <c r="J809">
-        <v>1.07600292170426</v>
+        <v>1.145624089571218</v>
       </c>
       <c r="K809">
-        <v>24.1</v>
+        <v>25.05</v>
       </c>
       <c r="L809">
-        <v>27.9</v>
+        <v>28.7</v>
       </c>
       <c r="M809">
-        <v>23.9</v>
+        <v>25.15</v>
       </c>
       <c r="N809">
-        <v>28.09</v>
+        <v>29.5</v>
       </c>
       <c r="O809">
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="810" spans="1:16">
       <c r="A810" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B810" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C810">
-        <v>1.786358263523248</v>
+        <v>-0.05769694523068125</v>
       </c>
       <c r="D810" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E810">
-        <v>1.061054196102969</v>
+        <v>-0.1833210348018994</v>
       </c>
       <c r="F810">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G810">
-        <v>0.05349364173647676</v>
+        <v>0.05481769694523068</v>
       </c>
       <c r="H810">
-        <v>0.05321894580389703</v>
+        <v>0.0569833210348019</v>
       </c>
       <c r="I810">
-        <v>0.7253040674202786</v>
+        <v>-0.1256240895712182</v>
       </c>
       <c r="J810">
-        <v>1.126520337101384</v>
+        <v>1.145624089571218</v>
       </c>
       <c r="K810">
-        <v>22.95</v>
+        <v>23.95</v>
       </c>
       <c r="L810">
-        <v>27.64</v>
+        <v>27.38</v>
       </c>
       <c r="M810">
-        <v>23.15</v>
+        <v>24.95</v>
       </c>
       <c r="N810">
-        <v>27.14</v>
+        <v>28.4</v>
       </c>
       <c r="O810">
         <v>1</v>
@@ -42169,34 +42172,34 @@
     </row>
     <row r="811" spans="1:16">
       <c r="A811" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B811" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C811">
-        <v>0.4806655556103365</v>
+        <v>-0.5597363304415239</v>
       </c>
       <c r="D811" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E811">
-        <v>1.168013521900203</v>
+        <v>0.1234583349060188</v>
       </c>
       <c r="F811">
         <v>1</v>
       </c>
       <c r="G811">
-        <v>0.05691933444438967</v>
+        <v>0.05795973633044153</v>
       </c>
       <c r="H811">
-        <v>0.0578319864780998</v>
+        <v>0.05887654166509398</v>
       </c>
       <c r="I811">
-        <v>0.6873479662898667</v>
+        <v>0.6831946653475427</v>
       </c>
       <c r="J811">
-        <v>1.126520337101384</v>
+        <v>1.168053346524612</v>
       </c>
       <c r="K811">
         <v>25.05</v>
@@ -42214,89 +42217,89 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>423</v>
+        <v>193</v>
       </c>
     </row>
     <row r="812" spans="1:16">
       <c r="A812" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B812" t="s">
+        <v>192</v>
+      </c>
+      <c r="C812">
+        <v>-0.5948776492644505</v>
+      </c>
+      <c r="D812" t="s">
+        <v>328</v>
+      </c>
+      <c r="E812">
+        <v>-0.7429309957890631</v>
+      </c>
+      <c r="F812">
+        <v>1</v>
+      </c>
+      <c r="G812">
+        <v>0.05535487764926445</v>
+      </c>
+      <c r="H812">
+        <v>0.05754293099578907</v>
+      </c>
+      <c r="I812">
+        <v>-0.1480533465246126</v>
+      </c>
+      <c r="J812">
+        <v>1.168053346524612</v>
+      </c>
+      <c r="K812">
+        <v>23.95</v>
+      </c>
+      <c r="L812">
+        <v>27.38</v>
+      </c>
+      <c r="M812">
+        <v>24.95</v>
+      </c>
+      <c r="N812">
+        <v>28.4</v>
+      </c>
+      <c r="O812">
+        <v>1</v>
+      </c>
+      <c r="P812" t="s">
         <v>193</v>
-      </c>
-      <c r="C812">
-        <v>1.037051962254782</v>
-      </c>
-      <c r="D812" t="s">
-        <v>325</v>
-      </c>
-      <c r="E812">
-        <v>0.6188023264262945</v>
-      </c>
-      <c r="F812">
-        <v>-1</v>
-      </c>
-      <c r="G812">
-        <v>0.05316294803774523</v>
-      </c>
-      <c r="H812">
-        <v>0.05366119767357371</v>
-      </c>
-      <c r="I812">
-        <v>0.418249635828488</v>
-      </c>
-      <c r="J812">
-        <v>1.145624089571218</v>
-      </c>
-      <c r="K812">
-        <v>22.75</v>
-      </c>
-      <c r="L812">
-        <v>27.1</v>
-      </c>
-      <c r="M812">
-        <v>23.15</v>
-      </c>
-      <c r="N812">
-        <v>27.14</v>
-      </c>
-      <c r="O812">
-        <v>1</v>
-      </c>
-      <c r="P812" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="813" spans="1:16">
       <c r="A813" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B813" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C813">
-        <v>0.002116556240977729</v>
+        <v>-0.8369803833445317</v>
       </c>
       <c r="D813" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E813">
-        <v>0.6875541472838584</v>
+        <v>-0.1548924806832268</v>
       </c>
       <c r="F813">
         <v>1</v>
       </c>
       <c r="G813">
-        <v>0.05739788344375902</v>
+        <v>0.05823698038334453</v>
       </c>
       <c r="H813">
-        <v>0.05831244585271614</v>
+        <v>0.05915489248068323</v>
       </c>
       <c r="I813">
-        <v>0.6854375910428807</v>
+        <v>0.6820879026613049</v>
       </c>
       <c r="J813">
-        <v>1.145624089571218</v>
+        <v>1.179120973387007</v>
       </c>
       <c r="K813">
         <v>25.05</v>
@@ -42314,101 +42317,101 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>424</v>
+        <v>187</v>
       </c>
     </row>
     <row r="814" spans="1:16">
       <c r="A814" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B814" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C814">
-        <v>-0.5597363304415239</v>
+        <v>0.1937889793972793</v>
       </c>
       <c r="D814" t="s">
         <v>330</v>
       </c>
       <c r="E814">
-        <v>0.1234583349060188</v>
+        <v>-0.3168154586268734</v>
       </c>
       <c r="F814">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G814">
-        <v>0.05795973633044153</v>
+        <v>0.05596621102060272</v>
       </c>
       <c r="H814">
-        <v>0.05887654166509398</v>
+        <v>0.05651681545862688</v>
       </c>
       <c r="I814">
-        <v>0.6831946653475427</v>
+        <v>0.5106044380241528</v>
       </c>
       <c r="J814">
-        <v>1.168053346524612</v>
+        <v>1.179120973387007</v>
       </c>
       <c r="K814">
-        <v>25.05</v>
+        <v>23.65</v>
       </c>
       <c r="L814">
-        <v>28.7</v>
+        <v>28.08</v>
       </c>
       <c r="M814">
-        <v>25.15</v>
+        <v>24.1</v>
       </c>
       <c r="N814">
-        <v>29.5</v>
+        <v>28.1</v>
       </c>
       <c r="O814">
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="815" spans="1:16">
       <c r="A815" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B815" t="s">
         <v>192</v>
       </c>
       <c r="C815">
-        <v>-0.8369803833445317</v>
+        <v>-0.8599473126188215</v>
       </c>
       <c r="D815" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E815">
-        <v>-0.1548924806832268</v>
+        <v>-1.01906828600583</v>
       </c>
       <c r="F815">
         <v>1</v>
       </c>
       <c r="G815">
-        <v>0.05823698038334453</v>
+        <v>0.05561994731261882</v>
       </c>
       <c r="H815">
-        <v>0.05915489248068323</v>
+        <v>0.05781906828600583</v>
       </c>
       <c r="I815">
-        <v>0.6820879026613049</v>
+        <v>-0.159120973387008</v>
       </c>
       <c r="J815">
         <v>1.179120973387007</v>
       </c>
       <c r="K815">
-        <v>25.05</v>
+        <v>23.95</v>
       </c>
       <c r="L815">
-        <v>28.7</v>
+        <v>27.38</v>
       </c>
       <c r="M815">
-        <v>25.15</v>
+        <v>24.95</v>
       </c>
       <c r="N815">
-        <v>29.5</v>
+        <v>28.4</v>
       </c>
       <c r="O815">
         <v>1</v>
@@ -42419,34 +42422,34 @@
     </row>
     <row r="816" spans="1:16">
       <c r="A816" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B816" t="s">
         <v>194</v>
       </c>
       <c r="C816">
-        <v>0.1937889793972793</v>
+        <v>-0.008923036478631019</v>
       </c>
       <c r="D816" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E816">
-        <v>-0.3168154586268734</v>
+        <v>-0.5233845741706133</v>
       </c>
       <c r="F816">
         <v>-1</v>
       </c>
       <c r="G816">
-        <v>0.05596621102060272</v>
+        <v>0.05616892303647864</v>
       </c>
       <c r="H816">
-        <v>0.05651681545862688</v>
+        <v>0.05672338457417062</v>
       </c>
       <c r="I816">
-        <v>0.5106044380241528</v>
+        <v>0.5144615376919823</v>
       </c>
       <c r="J816">
-        <v>1.179120973387007</v>
+        <v>1.187692305982183</v>
       </c>
       <c r="K816">
         <v>23.65</v>
@@ -42464,101 +42467,101 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>187</v>
+        <v>424</v>
       </c>
     </row>
     <row r="817" spans="1:16">
       <c r="A817" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B817" t="s">
         <v>192</v>
       </c>
       <c r="C817">
-        <v>-1.051692264853688</v>
+        <v>-1.065230728273285</v>
       </c>
       <c r="D817" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E817">
-        <v>-0.3704614954519023</v>
+        <v>-1.232923034255471</v>
       </c>
       <c r="F817">
         <v>1</v>
       </c>
       <c r="G817">
-        <v>0.05845169226485369</v>
+        <v>0.05582523072827329</v>
       </c>
       <c r="H817">
-        <v>0.05937046149545191</v>
+        <v>0.05803292303425547</v>
       </c>
       <c r="I817">
-        <v>0.6812307694017861</v>
+        <v>-0.167692305982186</v>
       </c>
       <c r="J817">
         <v>1.187692305982183</v>
       </c>
       <c r="K817">
-        <v>25.05</v>
+        <v>23.95</v>
       </c>
       <c r="L817">
-        <v>28.7</v>
+        <v>27.38</v>
       </c>
       <c r="M817">
-        <v>25.15</v>
+        <v>24.95</v>
       </c>
       <c r="N817">
-        <v>29.5</v>
+        <v>28.4</v>
       </c>
       <c r="O817">
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="818" spans="1:16">
       <c r="A818" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B818" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C818">
-        <v>-0.008923036478631019</v>
+        <v>0.01711680463947474</v>
       </c>
       <c r="D818" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E818">
-        <v>-0.5233845741706133</v>
+        <v>-0.6346716625790805</v>
       </c>
       <c r="F818">
         <v>-1</v>
       </c>
       <c r="G818">
-        <v>0.05616892303647864</v>
+        <v>0.05912288319536053</v>
       </c>
       <c r="H818">
-        <v>0.05672338457417062</v>
+        <v>0.05823467166257908</v>
       </c>
       <c r="I818">
-        <v>0.5144615376919823</v>
+        <v>0.6517884672185552</v>
       </c>
       <c r="J818">
-        <v>1.187692305982183</v>
+        <v>1.182115327814421</v>
       </c>
       <c r="K818">
-        <v>23.65</v>
+        <v>25</v>
       </c>
       <c r="L818">
-        <v>28.08</v>
+        <v>29.57</v>
       </c>
       <c r="M818">
-        <v>24.1</v>
+        <v>24.9</v>
       </c>
       <c r="N818">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="O818">
         <v>1</v>
@@ -42569,102 +42572,102 @@
     </row>
     <row r="819" spans="1:16">
       <c r="A819" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B819" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C819">
-        <v>0.01711680463947474</v>
+        <v>0.1229724971889432</v>
       </c>
       <c r="D819" t="s">
-        <v>326</v>
+        <v>190</v>
       </c>
       <c r="E819">
-        <v>-0.6346716625790805</v>
+        <v>-0.5125563347646604</v>
       </c>
       <c r="F819">
         <v>-1</v>
       </c>
       <c r="G819">
-        <v>0.05912288319536053</v>
+        <v>0.05603702750281106</v>
       </c>
       <c r="H819">
-        <v>0.05823467166257908</v>
+        <v>0.05599255633476466</v>
       </c>
       <c r="I819">
-        <v>0.6517884672185552</v>
+        <v>0.6355288319536037</v>
       </c>
       <c r="J819">
         <v>1.182115327814421</v>
       </c>
       <c r="K819">
-        <v>25</v>
+        <v>23.65</v>
       </c>
       <c r="L819">
-        <v>29.57</v>
+        <v>28.08</v>
       </c>
       <c r="M819">
-        <v>24.9</v>
+        <v>23.9</v>
       </c>
       <c r="N819">
-        <v>28.8</v>
+        <v>27.74</v>
       </c>
       <c r="O819">
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="820" spans="1:16">
       <c r="A820" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B820" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C820">
-        <v>0.1229724971889432</v>
+        <v>-0.9316621011553821</v>
       </c>
       <c r="D820" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E820">
-        <v>-0.3889794003275462</v>
+        <v>-1.093777428969805</v>
       </c>
       <c r="F820">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G820">
-        <v>0.05603702750281106</v>
+        <v>0.05569166210115538</v>
       </c>
       <c r="H820">
-        <v>0.05658897940032755</v>
+        <v>0.0578937774289698</v>
       </c>
       <c r="I820">
-        <v>0.5119518975164894</v>
+        <v>-0.1621153278144227</v>
       </c>
       <c r="J820">
         <v>1.182115327814421</v>
       </c>
       <c r="K820">
-        <v>23.65</v>
+        <v>23.95</v>
       </c>
       <c r="L820">
-        <v>28.08</v>
+        <v>27.38</v>
       </c>
       <c r="M820">
-        <v>24.1</v>
+        <v>24.95</v>
       </c>
       <c r="N820">
-        <v>28.1</v>
+        <v>28.4</v>
       </c>
       <c r="O820">
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -42769,202 +42772,202 @@
     </row>
     <row r="823" spans="1:16">
       <c r="A823" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B823" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C823">
-        <v>0.04582245394855988</v>
+        <v>-0.9732224358002206</v>
       </c>
       <c r="D823" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E823">
-        <v>-0.6060808358672318</v>
+        <v>-1.137073059424448</v>
       </c>
       <c r="F823">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G823">
-        <v>0.05909417754605144</v>
+        <v>0.05573322243580021</v>
       </c>
       <c r="H823">
-        <v>0.05820608083586724</v>
+        <v>0.05793707305942445</v>
       </c>
       <c r="I823">
-        <v>0.6519032898157917</v>
+        <v>-0.1638506236242279</v>
       </c>
       <c r="J823">
-        <v>1.180967101842058</v>
+        <v>1.183850623624226</v>
       </c>
       <c r="K823">
-        <v>25</v>
+        <v>23.95</v>
       </c>
       <c r="L823">
-        <v>29.57</v>
+        <v>27.38</v>
       </c>
       <c r="M823">
-        <v>24.9</v>
+        <v>24.95</v>
       </c>
       <c r="N823">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="O823">
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>427</v>
+        <v>325</v>
       </c>
     </row>
     <row r="824" spans="1:16">
       <c r="A824" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B824" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C824">
-        <v>-0.07606537893307319</v>
+        <v>0.04582245394855988</v>
       </c>
       <c r="D824" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="E824">
-        <v>-0.4851137340251768</v>
+        <v>-0.6060808358672318</v>
       </c>
       <c r="F824">
         <v>-1</v>
       </c>
       <c r="G824">
-        <v>0.05625606537893307</v>
+        <v>0.05909417754605144</v>
       </c>
       <c r="H824">
-        <v>0.05596511373402518</v>
+        <v>0.05820608083586724</v>
       </c>
       <c r="I824">
-        <v>0.4090483550921036</v>
+        <v>0.6519032898157917</v>
       </c>
       <c r="J824">
         <v>1.180967101842058</v>
       </c>
       <c r="K824">
-        <v>23.85</v>
+        <v>25</v>
       </c>
       <c r="L824">
-        <v>28.09</v>
+        <v>29.57</v>
       </c>
       <c r="M824">
-        <v>23.9</v>
+        <v>24.9</v>
       </c>
       <c r="N824">
-        <v>27.74</v>
+        <v>28.8</v>
       </c>
       <c r="O824">
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="825" spans="1:16">
       <c r="A825" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B825" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C825">
-        <v>0.05143297331527208</v>
+        <v>-0.07606537893307319</v>
       </c>
       <c r="D825" t="s">
-        <v>326</v>
+        <v>190</v>
       </c>
       <c r="E825">
-        <v>-0.6004927585779853</v>
+        <v>-0.4851137340251768</v>
       </c>
       <c r="F825">
         <v>-1</v>
       </c>
       <c r="G825">
-        <v>0.05908856702668473</v>
+        <v>0.05625606537893307</v>
       </c>
       <c r="H825">
-        <v>0.05820049275857798</v>
+        <v>0.05596511373402518</v>
       </c>
       <c r="I825">
-        <v>0.6519257318932574</v>
+        <v>0.4090483550921036</v>
       </c>
       <c r="J825">
-        <v>1.180742681067389</v>
+        <v>1.180967101842058</v>
       </c>
       <c r="K825">
-        <v>25</v>
+        <v>23.85</v>
       </c>
       <c r="L825">
-        <v>29.57</v>
+        <v>28.09</v>
       </c>
       <c r="M825">
-        <v>24.9</v>
+        <v>23.9</v>
       </c>
       <c r="N825">
-        <v>28.8</v>
+        <v>27.74</v>
       </c>
       <c r="O825">
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="826" spans="1:16">
       <c r="A826" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B826" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C826">
-        <v>-0.07071294345723089</v>
+        <v>-0.9041620891172784</v>
       </c>
       <c r="D826" t="s">
-        <v>190</v>
+        <v>328</v>
       </c>
       <c r="E826">
-        <v>-0.4797500775105981</v>
+        <v>-1.065129190959336</v>
       </c>
       <c r="F826">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G826">
-        <v>0.05625071294345723</v>
+        <v>0.05566416208911728</v>
       </c>
       <c r="H826">
-        <v>0.05595975007751059</v>
+        <v>0.05786512919095934</v>
       </c>
       <c r="I826">
-        <v>0.4090371340533672</v>
+        <v>-0.1609671018420578</v>
       </c>
       <c r="J826">
-        <v>1.180742681067389</v>
+        <v>1.180967101842058</v>
       </c>
       <c r="K826">
-        <v>23.85</v>
+        <v>23.95</v>
       </c>
       <c r="L826">
-        <v>28.09</v>
+        <v>27.38</v>
       </c>
       <c r="M826">
-        <v>23.9</v>
+        <v>24.95</v>
       </c>
       <c r="N826">
-        <v>27.74</v>
+        <v>28.4</v>
       </c>
       <c r="O826">
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -42972,231 +42975,231 @@
         <v>0</v>
       </c>
       <c r="B827" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C827">
-        <v>0.03203970189676042</v>
+        <v>0.05143297331527208</v>
       </c>
       <c r="D827" t="s">
-        <v>190</v>
+        <v>326</v>
       </c>
       <c r="E827">
-        <v>-0.3767820178057626</v>
+        <v>-0.6004927585779853</v>
       </c>
       <c r="F827">
         <v>-1</v>
       </c>
       <c r="G827">
-        <v>0.05614796029810325</v>
+        <v>0.05908856702668473</v>
       </c>
       <c r="H827">
-        <v>0.05585678201780576</v>
+        <v>0.05820049275857798</v>
       </c>
       <c r="I827">
-        <v>0.408821719702523</v>
+        <v>0.6519257318932574</v>
       </c>
       <c r="J827">
-        <v>1.17643439405045</v>
+        <v>1.180742681067389</v>
       </c>
       <c r="K827">
-        <v>23.85</v>
+        <v>25</v>
       </c>
       <c r="L827">
-        <v>28.09</v>
+        <v>29.57</v>
       </c>
       <c r="M827">
-        <v>23.9</v>
+        <v>24.9</v>
       </c>
       <c r="N827">
-        <v>27.74</v>
+        <v>28.8</v>
       </c>
       <c r="O827">
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>188</v>
+        <v>427</v>
       </c>
     </row>
     <row r="828" spans="1:16">
       <c r="A828" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B828" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C828">
-        <v>-0.06863320208639223</v>
+        <v>-0.07071294345723089</v>
       </c>
       <c r="D828" t="s">
-        <v>332</v>
+        <v>190</v>
       </c>
       <c r="E828">
-        <v>-0.9051289052448972</v>
+        <v>-0.4797500775105981</v>
       </c>
       <c r="F828">
         <v>-1</v>
       </c>
       <c r="G828">
-        <v>0.05842863320208639</v>
+        <v>0.05625071294345723</v>
       </c>
       <c r="H828">
-        <v>0.05570512890524489</v>
+        <v>0.05595975007751059</v>
       </c>
       <c r="I828">
-        <v>0.836495703158505</v>
+        <v>0.4090371340533672</v>
       </c>
       <c r="J828">
-        <v>1.179380371051871</v>
+        <v>1.180742681067389</v>
       </c>
       <c r="K828">
-        <v>24.8</v>
+        <v>23.85</v>
       </c>
       <c r="L828">
-        <v>29.18</v>
+        <v>28.09</v>
       </c>
       <c r="M828">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="N828">
-        <v>27.4</v>
+        <v>27.74</v>
       </c>
       <c r="O828">
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>326</v>
+        <v>427</v>
       </c>
     </row>
     <row r="829" spans="1:16">
       <c r="A829" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B829" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C829">
-        <v>-0.1398756728703532</v>
+        <v>-0.8987872115639703</v>
       </c>
       <c r="D829" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E829">
-        <v>-0.9740732318100207</v>
+        <v>-1.05952989263136</v>
       </c>
       <c r="F829">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G829">
-        <v>0.05849987567287036</v>
+        <v>0.05565878721156397</v>
       </c>
       <c r="H829">
-        <v>0.05577407323181002</v>
+        <v>0.05785952989263136</v>
       </c>
       <c r="I829">
-        <v>0.8341975589396675</v>
+        <v>-0.16074268106739</v>
       </c>
       <c r="J829">
-        <v>1.182253051325417</v>
+        <v>1.180742681067389</v>
       </c>
       <c r="K829">
-        <v>24.8</v>
+        <v>23.95</v>
       </c>
       <c r="L829">
-        <v>29.18</v>
+        <v>27.38</v>
       </c>
       <c r="M829">
-        <v>24</v>
+        <v>24.95</v>
       </c>
       <c r="N829">
-        <v>27.4</v>
+        <v>28.4</v>
       </c>
       <c r="O829">
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>191</v>
+        <v>427</v>
       </c>
     </row>
     <row r="830" spans="1:16">
       <c r="A830" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B830" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C830">
-        <v>-0.1067352741112089</v>
+        <v>0.004427027548832285</v>
       </c>
       <c r="D830" t="s">
-        <v>190</v>
+        <v>331</v>
       </c>
       <c r="E830">
-        <v>-0.5158479266774769</v>
+        <v>-0.8344254572108056</v>
       </c>
       <c r="F830">
         <v>-1</v>
       </c>
       <c r="G830">
-        <v>0.05628673527411121</v>
+        <v>0.05835557297245117</v>
       </c>
       <c r="H830">
-        <v>0.05599584792667747</v>
+        <v>0.05563442545721081</v>
       </c>
       <c r="I830">
-        <v>0.4091126525662681</v>
+        <v>0.8388524847596379</v>
       </c>
       <c r="J830">
-        <v>1.182253051325417</v>
+        <v>1.17643439405045</v>
       </c>
       <c r="K830">
-        <v>23.85</v>
+        <v>24.8</v>
       </c>
       <c r="L830">
-        <v>28.09</v>
+        <v>29.18</v>
       </c>
       <c r="M830">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="N830">
-        <v>27.74</v>
+        <v>27.4</v>
       </c>
       <c r="O830">
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="831" spans="1:16">
       <c r="A831" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B831" t="s">
         <v>195</v>
       </c>
       <c r="C831">
-        <v>-0.1278907621549088</v>
+        <v>0.03203970189676042</v>
       </c>
       <c r="D831" t="s">
         <v>190</v>
       </c>
       <c r="E831">
-        <v>-0.5370477658491524</v>
+        <v>-0.3767820178057626</v>
       </c>
       <c r="F831">
         <v>-1</v>
       </c>
       <c r="G831">
-        <v>0.05630789076215491</v>
+        <v>0.05614796029810325</v>
       </c>
       <c r="H831">
-        <v>0.05601704776584915</v>
+        <v>0.05585678201780576</v>
       </c>
       <c r="I831">
-        <v>0.4091570036942436</v>
+        <v>0.408821719702523</v>
       </c>
       <c r="J831">
-        <v>1.183140073884902</v>
+        <v>1.17643439405045</v>
       </c>
       <c r="K831">
         <v>23.85</v>
@@ -43214,57 +43217,57 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>328</v>
+        <v>188</v>
       </c>
     </row>
     <row r="832" spans="1:16">
       <c r="A832" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B832" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C832">
-        <v>-0.2393298546747005</v>
+        <v>-0.7956037375082836</v>
       </c>
       <c r="D832" t="s">
-        <v>190</v>
+        <v>328</v>
       </c>
       <c r="E832">
-        <v>-0.6487204833008526</v>
+        <v>-0.9520381315587336</v>
       </c>
       <c r="F832">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G832">
-        <v>0.0564193298546747</v>
+        <v>0.05555560373750828</v>
       </c>
       <c r="H832">
-        <v>0.05612872048330086</v>
+        <v>0.05775203813155873</v>
       </c>
       <c r="I832">
-        <v>0.4093906286261522</v>
+        <v>-0.15643439405045</v>
       </c>
       <c r="J832">
-        <v>1.187812572523048</v>
+        <v>1.17643439405045</v>
       </c>
       <c r="K832">
-        <v>23.85</v>
+        <v>23.95</v>
       </c>
       <c r="L832">
-        <v>28.09</v>
+        <v>27.38</v>
       </c>
       <c r="M832">
-        <v>23.9</v>
+        <v>24.95</v>
       </c>
       <c r="N832">
-        <v>27.74</v>
+        <v>28.4</v>
       </c>
       <c r="O832">
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43272,99 +43275,99 @@
         <v>0</v>
       </c>
       <c r="B833" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C833">
-        <v>-0.6244206512691726</v>
+        <v>-0.06863320208639223</v>
       </c>
       <c r="D833" t="s">
-        <v>190</v>
+        <v>331</v>
       </c>
       <c r="E833">
-        <v>-1.034618598127178</v>
+        <v>-0.9051289052448972</v>
       </c>
       <c r="F833">
         <v>-1</v>
       </c>
       <c r="G833">
-        <v>0.05680442065126917</v>
+        <v>0.05842863320208639</v>
       </c>
       <c r="H833">
-        <v>0.05651461859812718</v>
+        <v>0.05570512890524489</v>
       </c>
       <c r="I833">
-        <v>0.4101979468580055</v>
+        <v>0.836495703158505</v>
       </c>
       <c r="J833">
-        <v>1.203958937160133</v>
+        <v>1.179380371051871</v>
       </c>
       <c r="K833">
-        <v>23.85</v>
+        <v>24.8</v>
       </c>
       <c r="L833">
-        <v>28.09</v>
+        <v>29.18</v>
       </c>
       <c r="M833">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="N833">
-        <v>27.74</v>
+        <v>27.4</v>
       </c>
       <c r="O833">
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>429</v>
+        <v>326</v>
       </c>
     </row>
     <row r="834" spans="1:16">
       <c r="A834" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B834" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C834">
-        <v>-0.6352024546369286</v>
+        <v>-0.8661598866923015</v>
       </c>
       <c r="D834" t="s">
-        <v>190</v>
+        <v>328</v>
       </c>
       <c r="E834">
-        <v>-1.278745820965014</v>
+        <v>-1.025540257744172</v>
       </c>
       <c r="F834">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G834">
-        <v>0.05679520245463692</v>
+        <v>0.0556261598866923</v>
       </c>
       <c r="H834">
-        <v>0.05675874582096501</v>
+        <v>0.05782554025774417</v>
       </c>
       <c r="I834">
-        <v>0.6435433663280854</v>
+        <v>-0.1593803710518706</v>
       </c>
       <c r="J834">
-        <v>1.214173465312344</v>
+        <v>1.179380371051871</v>
       </c>
       <c r="K834">
-        <v>23.65</v>
+        <v>23.95</v>
       </c>
       <c r="L834">
-        <v>28.08</v>
+        <v>27.38</v>
       </c>
       <c r="M834">
-        <v>23.9</v>
+        <v>24.95</v>
       </c>
       <c r="N834">
-        <v>27.74</v>
+        <v>28.4</v>
       </c>
       <c r="O834">
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>430</v>
+        <v>326</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43372,81 +43375,81 @@
         <v>0</v>
       </c>
       <c r="B835" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C835">
-        <v>-0.4183504845900821</v>
+        <v>-0.1398756728703532</v>
       </c>
       <c r="D835" t="s">
-        <v>190</v>
+        <v>331</v>
       </c>
       <c r="E835">
-        <v>-1.059601546795051</v>
+        <v>-0.9740732318100207</v>
       </c>
       <c r="F835">
         <v>-1</v>
       </c>
       <c r="G835">
-        <v>0.05657835048459008</v>
+        <v>0.05849987567287036</v>
       </c>
       <c r="H835">
-        <v>0.05653960154679505</v>
+        <v>0.05577407323181002</v>
       </c>
       <c r="I835">
-        <v>0.6412510622049687</v>
+        <v>0.8341975589396675</v>
       </c>
       <c r="J835">
-        <v>1.205004248819877</v>
+        <v>1.182253051325417</v>
       </c>
       <c r="K835">
-        <v>23.65</v>
+        <v>24.8</v>
       </c>
       <c r="L835">
-        <v>28.08</v>
+        <v>29.18</v>
       </c>
       <c r="M835">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="N835">
-        <v>27.74</v>
+        <v>27.4</v>
       </c>
       <c r="O835">
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>196</v>
+        <v>428</v>
       </c>
     </row>
     <row r="836" spans="1:16">
       <c r="A836" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B836" t="s">
         <v>195</v>
       </c>
       <c r="C836">
-        <v>-0.5811865552738134</v>
+        <v>-0.1067352741112089</v>
       </c>
       <c r="D836" t="s">
         <v>190</v>
       </c>
       <c r="E836">
-        <v>-0.9912938646140077</v>
+        <v>-0.5158479266774769</v>
       </c>
       <c r="F836">
         <v>-1</v>
       </c>
       <c r="G836">
-        <v>0.05676118655527381</v>
+        <v>0.05628673527411121</v>
       </c>
       <c r="H836">
-        <v>0.056471293864614</v>
+        <v>0.05599584792667747</v>
       </c>
       <c r="I836">
-        <v>0.4101073093401943</v>
+        <v>0.4091126525662681</v>
       </c>
       <c r="J836">
-        <v>1.202146186803933</v>
+        <v>1.182253051325417</v>
       </c>
       <c r="K836">
         <v>23.85</v>
@@ -43464,57 +43467,807 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="837" spans="1:16">
       <c r="A837" s="1">
+        <v>2</v>
+      </c>
+      <c r="B837" t="s">
+        <v>192</v>
+      </c>
+      <c r="C837">
+        <v>-0.9349605792437501</v>
+      </c>
+      <c r="D837" t="s">
+        <v>328</v>
+      </c>
+      <c r="E837">
+        <v>-1.097213630569165</v>
+      </c>
+      <c r="F837">
+        <v>1</v>
+      </c>
+      <c r="G837">
+        <v>0.05569496057924375</v>
+      </c>
+      <c r="H837">
+        <v>0.05789721363056916</v>
+      </c>
+      <c r="I837">
+        <v>-0.1622530513254148</v>
+      </c>
+      <c r="J837">
+        <v>1.182253051325417</v>
+      </c>
+      <c r="K837">
+        <v>23.95</v>
+      </c>
+      <c r="L837">
+        <v>27.38</v>
+      </c>
+      <c r="M837">
+        <v>24.95</v>
+      </c>
+      <c r="N837">
+        <v>28.4</v>
+      </c>
+      <c r="O837">
+        <v>1</v>
+      </c>
+      <c r="P837" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="838" spans="1:16">
+      <c r="A838" s="1">
         <v>0</v>
       </c>
-      <c r="B837" t="s">
+      <c r="B838" t="s">
+        <v>196</v>
+      </c>
+      <c r="C838">
+        <v>-0.1618738323455666</v>
+      </c>
+      <c r="D838" t="s">
+        <v>331</v>
+      </c>
+      <c r="E838">
+        <v>-0.9953617732376472</v>
+      </c>
+      <c r="F838">
+        <v>-1</v>
+      </c>
+      <c r="G838">
+        <v>0.05852187383234556</v>
+      </c>
+      <c r="H838">
+        <v>0.05579536177323764</v>
+      </c>
+      <c r="I838">
+        <v>0.8334879408920806</v>
+      </c>
+      <c r="J838">
+        <v>1.183140073884902</v>
+      </c>
+      <c r="K838">
+        <v>24.8</v>
+      </c>
+      <c r="L838">
+        <v>29.18</v>
+      </c>
+      <c r="M838">
+        <v>24</v>
+      </c>
+      <c r="N838">
+        <v>27.4</v>
+      </c>
+      <c r="O838">
+        <v>1</v>
+      </c>
+      <c r="P838" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="839" spans="1:16">
+      <c r="A839" s="1">
+        <v>1</v>
+      </c>
+      <c r="B839" t="s">
         <v>195</v>
       </c>
-      <c r="C837">
+      <c r="C839">
+        <v>-0.1278907621549088</v>
+      </c>
+      <c r="D839" t="s">
+        <v>190</v>
+      </c>
+      <c r="E839">
+        <v>-0.5370477658491524</v>
+      </c>
+      <c r="F839">
+        <v>-1</v>
+      </c>
+      <c r="G839">
+        <v>0.05630789076215491</v>
+      </c>
+      <c r="H839">
+        <v>0.05601704776584915</v>
+      </c>
+      <c r="I839">
+        <v>0.4091570036942436</v>
+      </c>
+      <c r="J839">
+        <v>1.183140073884902</v>
+      </c>
+      <c r="K839">
+        <v>23.85</v>
+      </c>
+      <c r="L839">
+        <v>28.09</v>
+      </c>
+      <c r="M839">
+        <v>23.9</v>
+      </c>
+      <c r="N839">
+        <v>27.74</v>
+      </c>
+      <c r="O839">
+        <v>1</v>
+      </c>
+      <c r="P839" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="840" spans="1:16">
+      <c r="A840" s="1">
+        <v>2</v>
+      </c>
+      <c r="B840" t="s">
+        <v>192</v>
+      </c>
+      <c r="C840">
+        <v>-0.9562047695433975</v>
+      </c>
+      <c r="D840" t="s">
+        <v>328</v>
+      </c>
+      <c r="E840">
+        <v>-1.119344843428301</v>
+      </c>
+      <c r="F840">
+        <v>1</v>
+      </c>
+      <c r="G840">
+        <v>0.0557162047695434</v>
+      </c>
+      <c r="H840">
+        <v>0.0579193448434283</v>
+      </c>
+      <c r="I840">
+        <v>-0.1631400738849038</v>
+      </c>
+      <c r="J840">
+        <v>1.183140073884902</v>
+      </c>
+      <c r="K840">
+        <v>23.95</v>
+      </c>
+      <c r="L840">
+        <v>27.38</v>
+      </c>
+      <c r="M840">
+        <v>24.95</v>
+      </c>
+      <c r="N840">
+        <v>28.4</v>
+      </c>
+      <c r="O840">
+        <v>1</v>
+      </c>
+      <c r="P840" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="841" spans="1:16">
+      <c r="A841" s="1">
+        <v>0</v>
+      </c>
+      <c r="B841" t="s">
+        <v>196</v>
+      </c>
+      <c r="C841">
+        <v>-0.2777517985715967</v>
+      </c>
+      <c r="D841" t="s">
+        <v>331</v>
+      </c>
+      <c r="E841">
+        <v>-1.107501740553158</v>
+      </c>
+      <c r="F841">
+        <v>-1</v>
+      </c>
+      <c r="G841">
+        <v>0.0586377517985716</v>
+      </c>
+      <c r="H841">
+        <v>0.05590750174055316</v>
+      </c>
+      <c r="I841">
+        <v>0.8297499419815608</v>
+      </c>
+      <c r="J841">
+        <v>1.187812572523048</v>
+      </c>
+      <c r="K841">
+        <v>24.8</v>
+      </c>
+      <c r="L841">
+        <v>29.18</v>
+      </c>
+      <c r="M841">
+        <v>24</v>
+      </c>
+      <c r="N841">
+        <v>27.4</v>
+      </c>
+      <c r="O841">
+        <v>1</v>
+      </c>
+      <c r="P841" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="842" spans="1:16">
+      <c r="A842" s="1">
+        <v>1</v>
+      </c>
+      <c r="B842" t="s">
+        <v>195</v>
+      </c>
+      <c r="C842">
+        <v>-0.2393298546747005</v>
+      </c>
+      <c r="D842" t="s">
+        <v>190</v>
+      </c>
+      <c r="E842">
+        <v>-0.6487204833008526</v>
+      </c>
+      <c r="F842">
+        <v>-1</v>
+      </c>
+      <c r="G842">
+        <v>0.0564193298546747</v>
+      </c>
+      <c r="H842">
+        <v>0.05612872048330086</v>
+      </c>
+      <c r="I842">
+        <v>0.4093906286261522</v>
+      </c>
+      <c r="J842">
+        <v>1.187812572523048</v>
+      </c>
+      <c r="K842">
+        <v>23.85</v>
+      </c>
+      <c r="L842">
+        <v>28.09</v>
+      </c>
+      <c r="M842">
+        <v>23.9</v>
+      </c>
+      <c r="N842">
+        <v>27.74</v>
+      </c>
+      <c r="O842">
+        <v>1</v>
+      </c>
+      <c r="P842" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="843" spans="1:16">
+      <c r="A843" s="1">
+        <v>2</v>
+      </c>
+      <c r="B843" t="s">
+        <v>192</v>
+      </c>
+      <c r="C843">
+        <v>-1.068111111927003</v>
+      </c>
+      <c r="D843" t="s">
+        <v>328</v>
+      </c>
+      <c r="E843">
+        <v>-1.235923684450054</v>
+      </c>
+      <c r="F843">
+        <v>1</v>
+      </c>
+      <c r="G843">
+        <v>0.055828111111927</v>
+      </c>
+      <c r="H843">
+        <v>0.05803592368445006</v>
+      </c>
+      <c r="I843">
+        <v>-0.1678125725230508</v>
+      </c>
+      <c r="J843">
+        <v>1.187812572523048</v>
+      </c>
+      <c r="K843">
+        <v>23.95</v>
+      </c>
+      <c r="L843">
+        <v>27.38</v>
+      </c>
+      <c r="M843">
+        <v>24.95</v>
+      </c>
+      <c r="N843">
+        <v>28.4</v>
+      </c>
+      <c r="O843">
+        <v>1</v>
+      </c>
+      <c r="P843" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="844" spans="1:16">
+      <c r="A844" s="1">
+        <v>0</v>
+      </c>
+      <c r="B844" t="s">
+        <v>195</v>
+      </c>
+      <c r="C844">
+        <v>-0.6244206512691726</v>
+      </c>
+      <c r="D844" t="s">
+        <v>190</v>
+      </c>
+      <c r="E844">
+        <v>-1.034618598127178</v>
+      </c>
+      <c r="F844">
+        <v>-1</v>
+      </c>
+      <c r="G844">
+        <v>0.05680442065126917</v>
+      </c>
+      <c r="H844">
+        <v>0.05651461859812718</v>
+      </c>
+      <c r="I844">
+        <v>0.4101979468580055</v>
+      </c>
+      <c r="J844">
+        <v>1.203958937160133</v>
+      </c>
+      <c r="K844">
+        <v>23.85</v>
+      </c>
+      <c r="L844">
+        <v>28.09</v>
+      </c>
+      <c r="M844">
+        <v>23.9</v>
+      </c>
+      <c r="N844">
+        <v>27.74</v>
+      </c>
+      <c r="O844">
+        <v>1</v>
+      </c>
+      <c r="P844" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="845" spans="1:16">
+      <c r="A845" s="1">
+        <v>1</v>
+      </c>
+      <c r="B845" t="s">
+        <v>192</v>
+      </c>
+      <c r="C845">
+        <v>-1.454816544985185</v>
+      </c>
+      <c r="D845" t="s">
+        <v>328</v>
+      </c>
+      <c r="E845">
+        <v>-1.638775482145316</v>
+      </c>
+      <c r="F845">
+        <v>1</v>
+      </c>
+      <c r="G845">
+        <v>0.05621481654498518</v>
+      </c>
+      <c r="H845">
+        <v>0.05843877548214532</v>
+      </c>
+      <c r="I845">
+        <v>-0.1839589371601313</v>
+      </c>
+      <c r="J845">
+        <v>1.203958937160133</v>
+      </c>
+      <c r="K845">
+        <v>23.95</v>
+      </c>
+      <c r="L845">
+        <v>27.38</v>
+      </c>
+      <c r="M845">
+        <v>24.95</v>
+      </c>
+      <c r="N845">
+        <v>28.4</v>
+      </c>
+      <c r="O845">
+        <v>1</v>
+      </c>
+      <c r="P845" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="846" spans="1:16">
+      <c r="A846" s="1">
+        <v>0</v>
+      </c>
+      <c r="B846" t="s">
+        <v>195</v>
+      </c>
+      <c r="C846">
+        <v>-0.8680371476994004</v>
+      </c>
+      <c r="D846" t="s">
+        <v>190</v>
+      </c>
+      <c r="E846">
+        <v>-1.278745820965014</v>
+      </c>
+      <c r="F846">
+        <v>-1</v>
+      </c>
+      <c r="G846">
+        <v>0.0570480371476994</v>
+      </c>
+      <c r="H846">
+        <v>0.05675874582096501</v>
+      </c>
+      <c r="I846">
+        <v>0.4107086732656136</v>
+      </c>
+      <c r="J846">
+        <v>1.214173465312344</v>
+      </c>
+      <c r="K846">
+        <v>23.85</v>
+      </c>
+      <c r="L846">
+        <v>28.09</v>
+      </c>
+      <c r="M846">
+        <v>23.9</v>
+      </c>
+      <c r="N846">
+        <v>27.74</v>
+      </c>
+      <c r="O846">
+        <v>1</v>
+      </c>
+      <c r="P846" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="847" spans="1:16">
+      <c r="A847" s="1">
+        <v>1</v>
+      </c>
+      <c r="B847" t="s">
+        <v>192</v>
+      </c>
+      <c r="C847">
+        <v>-1.699454494230633</v>
+      </c>
+      <c r="D847" t="s">
+        <v>328</v>
+      </c>
+      <c r="E847">
+        <v>-1.893627959542975</v>
+      </c>
+      <c r="F847">
+        <v>1</v>
+      </c>
+      <c r="G847">
+        <v>0.05645945449423063</v>
+      </c>
+      <c r="H847">
+        <v>0.05869362795954297</v>
+      </c>
+      <c r="I847">
+        <v>-0.1941734653123426</v>
+      </c>
+      <c r="J847">
+        <v>1.214173465312344</v>
+      </c>
+      <c r="K847">
+        <v>23.95</v>
+      </c>
+      <c r="L847">
+        <v>27.38</v>
+      </c>
+      <c r="M847">
+        <v>24.95</v>
+      </c>
+      <c r="N847">
+        <v>28.4</v>
+      </c>
+      <c r="O847">
+        <v>1</v>
+      </c>
+      <c r="P847" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="848" spans="1:16">
+      <c r="A848" s="1">
+        <v>0</v>
+      </c>
+      <c r="B848" t="s">
+        <v>194</v>
+      </c>
+      <c r="C848">
+        <v>-0.4183504845900821</v>
+      </c>
+      <c r="D848" t="s">
+        <v>190</v>
+      </c>
+      <c r="E848">
+        <v>-1.059601546795051</v>
+      </c>
+      <c r="F848">
+        <v>-1</v>
+      </c>
+      <c r="G848">
+        <v>0.05657835048459008</v>
+      </c>
+      <c r="H848">
+        <v>0.05653960154679505</v>
+      </c>
+      <c r="I848">
+        <v>0.6412510622049687</v>
+      </c>
+      <c r="J848">
+        <v>1.205004248819877</v>
+      </c>
+      <c r="K848">
+        <v>23.65</v>
+      </c>
+      <c r="L848">
+        <v>28.08</v>
+      </c>
+      <c r="M848">
+        <v>23.9</v>
+      </c>
+      <c r="N848">
+        <v>27.74</v>
+      </c>
+      <c r="O848">
+        <v>1</v>
+      </c>
+      <c r="P848" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="849" spans="1:16">
+      <c r="A849" s="1">
+        <v>1</v>
+      </c>
+      <c r="B849" t="s">
+        <v>192</v>
+      </c>
+      <c r="C849">
+        <v>-1.479851759236045</v>
+      </c>
+      <c r="D849" t="s">
+        <v>328</v>
+      </c>
+      <c r="E849">
+        <v>-1.664856008055924</v>
+      </c>
+      <c r="F849">
+        <v>1</v>
+      </c>
+      <c r="G849">
+        <v>0.05623985175923605</v>
+      </c>
+      <c r="H849">
+        <v>0.05846485600805592</v>
+      </c>
+      <c r="I849">
+        <v>-0.1850042488198795</v>
+      </c>
+      <c r="J849">
+        <v>1.205004248819877</v>
+      </c>
+      <c r="K849">
+        <v>23.95</v>
+      </c>
+      <c r="L849">
+        <v>27.38</v>
+      </c>
+      <c r="M849">
+        <v>24.95</v>
+      </c>
+      <c r="N849">
+        <v>28.4</v>
+      </c>
+      <c r="O849">
+        <v>1</v>
+      </c>
+      <c r="P849" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="850" spans="1:16">
+      <c r="A850" s="1">
+        <v>0</v>
+      </c>
+      <c r="B850" t="s">
+        <v>195</v>
+      </c>
+      <c r="C850">
+        <v>-0.5811865552738134</v>
+      </c>
+      <c r="D850" t="s">
+        <v>190</v>
+      </c>
+      <c r="E850">
+        <v>-0.9912938646140077</v>
+      </c>
+      <c r="F850">
+        <v>-1</v>
+      </c>
+      <c r="G850">
+        <v>0.05676118655527381</v>
+      </c>
+      <c r="H850">
+        <v>0.056471293864614</v>
+      </c>
+      <c r="I850">
+        <v>0.4101073093401943</v>
+      </c>
+      <c r="J850">
+        <v>1.202146186803933</v>
+      </c>
+      <c r="K850">
+        <v>23.85</v>
+      </c>
+      <c r="L850">
+        <v>28.09</v>
+      </c>
+      <c r="M850">
+        <v>23.9</v>
+      </c>
+      <c r="N850">
+        <v>27.74</v>
+      </c>
+      <c r="O850">
+        <v>1</v>
+      </c>
+      <c r="P850" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="851" spans="1:16">
+      <c r="A851" s="1">
+        <v>1</v>
+      </c>
+      <c r="B851" t="s">
+        <v>192</v>
+      </c>
+      <c r="C851">
+        <v>-1.411401173954204</v>
+      </c>
+      <c r="D851" t="s">
+        <v>328</v>
+      </c>
+      <c r="E851">
+        <v>-1.593547360758137</v>
+      </c>
+      <c r="F851">
+        <v>1</v>
+      </c>
+      <c r="G851">
+        <v>0.0561714011739542</v>
+      </c>
+      <c r="H851">
+        <v>0.05839354736075814</v>
+      </c>
+      <c r="I851">
+        <v>-0.1821461868039336</v>
+      </c>
+      <c r="J851">
+        <v>1.202146186803933</v>
+      </c>
+      <c r="K851">
+        <v>23.95</v>
+      </c>
+      <c r="L851">
+        <v>27.38</v>
+      </c>
+      <c r="M851">
+        <v>24.95</v>
+      </c>
+      <c r="N851">
+        <v>28.4</v>
+      </c>
+      <c r="O851">
+        <v>1</v>
+      </c>
+      <c r="P851" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="852" spans="1:16">
+      <c r="A852" s="1">
+        <v>0</v>
+      </c>
+      <c r="B852" t="s">
+        <v>195</v>
+      </c>
+      <c r="C852">
         <v>-0.5785545596828676</v>
       </c>
-      <c r="D837" t="s">
-        <v>190</v>
-      </c>
-      <c r="E837">
-        <v>-0.988656351212601</v>
-      </c>
-      <c r="F837">
-        <v>-1</v>
-      </c>
-      <c r="G837">
+      <c r="D852" t="s">
+        <v>192</v>
+      </c>
+      <c r="E852">
+        <v>-1.408758142742332</v>
+      </c>
+      <c r="F852">
+        <v>-1</v>
+      </c>
+      <c r="G852">
         <v>0.05675855455968287</v>
       </c>
-      <c r="H837">
-        <v>0.0564686563512126</v>
-      </c>
-      <c r="I837">
-        <v>0.4101017915297334</v>
-      </c>
-      <c r="J837">
+      <c r="H852">
+        <v>0.05616875814274234</v>
+      </c>
+      <c r="I852">
+        <v>0.8302035830594647</v>
+      </c>
+      <c r="J852">
         <v>1.202035830594669</v>
       </c>
-      <c r="K837">
+      <c r="K852">
         <v>23.85</v>
       </c>
-      <c r="L837">
+      <c r="L852">
         <v>28.09</v>
       </c>
-      <c r="M837">
-        <v>23.9</v>
-      </c>
-      <c r="N837">
-        <v>27.74</v>
-      </c>
-      <c r="O837">
-        <v>1</v>
-      </c>
-      <c r="P837" t="s">
-        <v>332</v>
+      <c r="M852">
+        <v>23.95</v>
+      </c>
+      <c r="N852">
+        <v>27.38</v>
+      </c>
+      <c r="O852">
+        <v>1</v>
+      </c>
+      <c r="P852" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02601-601601.xlsx
+++ b/s60_signal/position-02601-601601.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="433">
   <si>
     <t>trade_time</t>
   </si>
@@ -592,10 +592,10 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-11-04</t>
+    <t>2021-10-27</t>
   </si>
   <si>
-    <t>2021-10-27</t>
+    <t>2021-11-04</t>
   </si>
   <si>
     <t>2021-11-11</t>
@@ -994,7 +994,7 @@
     <t>2021-10-15</t>
   </si>
   <si>
-    <t>2021-11-16</t>
+    <t>2021-11-17</t>
   </si>
   <si>
     <t>2021-11-08</t>
@@ -1670,7 +1670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P832"/>
+  <dimension ref="A1:P838"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -39284,7 +39284,7 @@
         <v>326</v>
       </c>
       <c r="E753">
-        <v>4.132896467876215</v>
+        <v>4.082896467876214</v>
       </c>
       <c r="F753">
         <v>1</v>
@@ -39293,10 +39293,10 @@
         <v>0.05083864518377459</v>
       </c>
       <c r="H753">
-        <v>0.05310710353212379</v>
+        <v>0.05305710353212379</v>
       </c>
       <c r="I753">
-        <v>0.2115416516508013</v>
+        <v>0.1615416516508006</v>
       </c>
       <c r="J753">
         <v>0.9794841412849514</v>
@@ -39311,7 +39311,7 @@
         <v>25</v>
       </c>
       <c r="N753">
-        <v>28.62</v>
+        <v>28.57</v>
       </c>
       <c r="O753">
         <v>1</v>
@@ -39484,7 +39484,7 @@
         <v>326</v>
       </c>
       <c r="E757">
-        <v>3.600256280581256</v>
+        <v>3.550256280581255</v>
       </c>
       <c r="F757">
         <v>1</v>
@@ -39493,10 +39493,10 @@
         <v>0.05134891448320316</v>
       </c>
       <c r="H757">
-        <v>0.05363974371941875</v>
+        <v>0.05358974371941875</v>
       </c>
       <c r="I757">
-        <v>0.1891707637844142</v>
+        <v>0.1391707637844135</v>
       </c>
       <c r="J757">
         <v>1.00078974877675</v>
@@ -39511,7 +39511,7 @@
         <v>25</v>
       </c>
       <c r="N757">
-        <v>28.62</v>
+        <v>28.57</v>
       </c>
       <c r="O757">
         <v>1</v>
@@ -39684,7 +39684,7 @@
         <v>326</v>
       </c>
       <c r="E761">
-        <v>3.434836932532686</v>
+        <v>3.384836932532686</v>
       </c>
       <c r="F761">
         <v>1</v>
@@ -39693,10 +39693,10 @@
         <v>0.05150738621863368</v>
       </c>
       <c r="H761">
-        <v>0.05380516306746732</v>
+        <v>0.05375516306746732</v>
       </c>
       <c r="I761">
-        <v>0.1822231511663723</v>
+        <v>0.1322231511663716</v>
       </c>
       <c r="J761">
         <v>1.007406522698693</v>
@@ -39711,7 +39711,7 @@
         <v>25</v>
       </c>
       <c r="N761">
-        <v>28.62</v>
+        <v>28.57</v>
       </c>
       <c r="O761">
         <v>1</v>
@@ -39884,7 +39884,7 @@
         <v>326</v>
       </c>
       <c r="E765">
-        <v>3.251697155904822</v>
+        <v>3.201697155904821</v>
       </c>
       <c r="F765">
         <v>1</v>
@@ -39893,10 +39893,10 @@
         <v>0.05168283412464318</v>
       </c>
       <c r="H765">
-        <v>0.05398830284409518</v>
+        <v>0.05393830284409518</v>
       </c>
       <c r="I765">
-        <v>0.1745312805480062</v>
+        <v>0.1245312805480054</v>
       </c>
       <c r="J765">
         <v>1.014732113763807</v>
@@ -39911,7 +39911,7 @@
         <v>25</v>
       </c>
       <c r="N765">
-        <v>28.62</v>
+        <v>28.57</v>
       </c>
       <c r="O765">
         <v>1</v>
@@ -40084,7 +40084,7 @@
         <v>326</v>
       </c>
       <c r="E769">
-        <v>3.101720861011341</v>
+        <v>3.05172086101134</v>
       </c>
       <c r="F769">
         <v>1</v>
@@ -40093,10 +40093,10 @@
         <v>0.05182651141515113</v>
       </c>
       <c r="H769">
-        <v>0.05413827913898867</v>
+        <v>0.05408827913898866</v>
       </c>
       <c r="I769">
-        <v>0.1682322761624775</v>
+        <v>0.1182322761624768</v>
       </c>
       <c r="J769">
         <v>1.020731165559546</v>
@@ -40111,7 +40111,7 @@
         <v>25</v>
       </c>
       <c r="N769">
-        <v>28.62</v>
+        <v>28.57</v>
       </c>
       <c r="O769">
         <v>1</v>
@@ -40284,7 +40284,7 @@
         <v>326</v>
       </c>
       <c r="E773">
-        <v>2.916414043059142</v>
+        <v>2.866414043059141</v>
       </c>
       <c r="F773">
         <v>1</v>
@@ -40293,10 +40293,10 @@
         <v>0.05200403534674935</v>
       </c>
       <c r="H773">
-        <v>0.05432358595694086</v>
+        <v>0.05427358595694087</v>
       </c>
       <c r="I773">
-        <v>0.1604493898084876</v>
+        <v>0.1104493898084868</v>
       </c>
       <c r="J773">
         <v>1.028143438277634</v>
@@ -40311,7 +40311,7 @@
         <v>25</v>
       </c>
       <c r="N773">
-        <v>28.62</v>
+        <v>28.57</v>
       </c>
       <c r="O773">
         <v>1</v>
@@ -40484,7 +40484,7 @@
         <v>326</v>
       </c>
       <c r="E777">
-        <v>2.812183527845185</v>
+        <v>2.762183527845185</v>
       </c>
       <c r="F777">
         <v>1</v>
@@ -40493,10 +40493,10 @@
         <v>0.05210388818032431</v>
       </c>
       <c r="H777">
-        <v>0.05442781647215482</v>
+        <v>0.05437781647215482</v>
       </c>
       <c r="I777">
-        <v>0.1560717081694989</v>
+        <v>0.1060717081694982</v>
       </c>
       <c r="J777">
         <v>1.032312658886193</v>
@@ -40511,7 +40511,7 @@
         <v>25</v>
       </c>
       <c r="N777">
-        <v>28.62</v>
+        <v>28.57</v>
       </c>
       <c r="O777">
         <v>1</v>
@@ -40684,7 +40684,7 @@
         <v>326</v>
       </c>
       <c r="E781">
-        <v>2.711363133474148</v>
+        <v>2.661363133474147</v>
       </c>
       <c r="F781">
         <v>1</v>
@@ -40693,10 +40693,10 @@
         <v>0.05220047411813176</v>
       </c>
       <c r="H781">
-        <v>0.05452863686652586</v>
+        <v>0.05447863686652585</v>
       </c>
       <c r="I781">
-        <v>0.1518372516059152</v>
+        <v>0.1018372516059145</v>
       </c>
       <c r="J781">
         <v>1.036345474661034</v>
@@ -40711,7 +40711,7 @@
         <v>25</v>
       </c>
       <c r="N781">
-        <v>28.62</v>
+        <v>28.57</v>
       </c>
       <c r="O781">
         <v>1</v>
@@ -40884,7 +40884,7 @@
         <v>326</v>
       </c>
       <c r="E785">
-        <v>2.61769368799991</v>
+        <v>2.56769368799991</v>
       </c>
       <c r="F785">
         <v>1</v>
@@ -40893,10 +40893,10 @@
         <v>0.05229020944689609</v>
       </c>
       <c r="H785">
-        <v>0.05462230631200009</v>
+        <v>0.05457230631200009</v>
       </c>
       <c r="I785">
-        <v>0.1479031348959978</v>
+        <v>0.09790313489599711</v>
       </c>
       <c r="J785">
         <v>1.040092252480004</v>
@@ -40911,7 +40911,7 @@
         <v>25</v>
       </c>
       <c r="N785">
-        <v>28.62</v>
+        <v>28.57</v>
       </c>
       <c r="O785">
         <v>1</v>
@@ -41034,7 +41034,7 @@
         <v>326</v>
       </c>
       <c r="E788">
-        <v>1.719926957393493</v>
+        <v>1.669926957393493</v>
       </c>
       <c r="F788">
         <v>1</v>
@@ -41043,10 +41043,10 @@
         <v>0.05315026997481704</v>
       </c>
       <c r="H788">
-        <v>0.05552007304260651</v>
+        <v>0.05547007304260651</v>
       </c>
       <c r="I788">
-        <v>0.1101969322105312</v>
+        <v>0.06019693221053046</v>
       </c>
       <c r="J788">
         <v>1.07600292170426</v>
@@ -41061,7 +41061,7 @@
         <v>25</v>
       </c>
       <c r="N788">
-        <v>28.62</v>
+        <v>28.57</v>
       </c>
       <c r="O788">
         <v>1</v>
@@ -41125,43 +41125,43 @@
         <v>1</v>
       </c>
       <c r="B790" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C790">
-        <v>0.3998379264218599</v>
+        <v>1.437794027552275</v>
       </c>
       <c r="D790" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E790">
-        <v>0.4569915724654088</v>
+        <v>0.9508598758566542</v>
       </c>
       <c r="F790">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G790">
-        <v>0.05436016207357814</v>
+        <v>0.05472220597244772</v>
       </c>
       <c r="H790">
-        <v>0.0567830084275346</v>
+        <v>0.05524914012414335</v>
       </c>
       <c r="I790">
-        <v>0.05715364604354889</v>
+        <v>0.4869341516956212</v>
       </c>
       <c r="J790">
         <v>1.126520337101384</v>
       </c>
       <c r="K790">
-        <v>23.95</v>
+        <v>23.65</v>
       </c>
       <c r="L790">
-        <v>27.38</v>
+        <v>28.08</v>
       </c>
       <c r="M790">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="N790">
-        <v>28.62</v>
+        <v>28.1</v>
       </c>
       <c r="O790">
         <v>1</v>
@@ -41172,96 +41172,96 @@
     </row>
     <row r="791" spans="1:16">
       <c r="A791" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B791" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C791">
-        <v>0.9859902816406851</v>
+        <v>0.3998379264218599</v>
       </c>
       <c r="D791" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E791">
-        <v>0.4904594413336376</v>
+        <v>0.4069915724654081</v>
       </c>
       <c r="F791">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G791">
-        <v>0.05517400971835932</v>
+        <v>0.05436016207357814</v>
       </c>
       <c r="H791">
-        <v>0.05570954055866637</v>
+        <v>0.05673300842753459</v>
       </c>
       <c r="I791">
-        <v>0.4955308403070475</v>
+        <v>0.007153646043548179</v>
       </c>
       <c r="J791">
-        <v>1.145624089571218</v>
+        <v>1.126520337101384</v>
       </c>
       <c r="K791">
-        <v>23.65</v>
+        <v>23.95</v>
       </c>
       <c r="L791">
-        <v>28.08</v>
+        <v>27.38</v>
       </c>
       <c r="M791">
-        <v>24.1</v>
+        <v>25</v>
       </c>
       <c r="N791">
-        <v>28.1</v>
+        <v>28.57</v>
       </c>
       <c r="O791">
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="792" spans="1:16">
       <c r="A792" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B792" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C792">
-        <v>-0.05769694523068125</v>
+        <v>0.9859902816406851</v>
       </c>
       <c r="D792" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E792">
-        <v>-0.02060223928046057</v>
+        <v>0.4904594413336376</v>
       </c>
       <c r="F792">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G792">
-        <v>0.05481769694523068</v>
+        <v>0.05517400971835932</v>
       </c>
       <c r="H792">
-        <v>0.05726060223928046</v>
+        <v>0.05570954055866637</v>
       </c>
       <c r="I792">
-        <v>0.03709470595022069</v>
+        <v>0.4955308403070475</v>
       </c>
       <c r="J792">
         <v>1.145624089571218</v>
       </c>
       <c r="K792">
-        <v>23.95</v>
+        <v>23.65</v>
       </c>
       <c r="L792">
-        <v>27.38</v>
+        <v>28.08</v>
       </c>
       <c r="M792">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="N792">
-        <v>28.62</v>
+        <v>28.1</v>
       </c>
       <c r="O792">
         <v>1</v>
@@ -41272,96 +41272,96 @@
     </row>
     <row r="793" spans="1:16">
       <c r="A793" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B793" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C793">
-        <v>0.4555383546929335</v>
+        <v>-0.05769694523068125</v>
       </c>
       <c r="D793" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E793">
-        <v>-0.05008565124314046</v>
+        <v>-0.07060223928046128</v>
       </c>
       <c r="F793">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G793">
-        <v>0.05570446164530706</v>
+        <v>0.05481769694523068</v>
       </c>
       <c r="H793">
-        <v>0.05625008565124314</v>
+        <v>0.05721060223928046</v>
       </c>
       <c r="I793">
-        <v>0.5056240059360739</v>
+        <v>-0.01290529404978003</v>
       </c>
       <c r="J793">
-        <v>1.168053346524612</v>
+        <v>1.145624089571218</v>
       </c>
       <c r="K793">
-        <v>23.65</v>
+        <v>23.95</v>
       </c>
       <c r="L793">
-        <v>28.08</v>
+        <v>27.38</v>
       </c>
       <c r="M793">
-        <v>24.1</v>
+        <v>25</v>
       </c>
       <c r="N793">
-        <v>28.1</v>
+        <v>28.57</v>
       </c>
       <c r="O793">
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>189</v>
+        <v>423</v>
       </c>
     </row>
     <row r="794" spans="1:16">
       <c r="A794" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B794" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C794">
-        <v>-0.5948776492644505</v>
+        <v>0.4555383546929335</v>
       </c>
       <c r="D794" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E794">
-        <v>-0.5813336631152914</v>
+        <v>-0.1764749819382203</v>
       </c>
       <c r="F794">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G794">
-        <v>0.05535487764926445</v>
+        <v>0.05570446164530706</v>
       </c>
       <c r="H794">
-        <v>0.0578213336631153</v>
+        <v>0.05565647498193822</v>
       </c>
       <c r="I794">
-        <v>0.01354398614915908</v>
+        <v>0.6320133366311538</v>
       </c>
       <c r="J794">
         <v>1.168053346524612</v>
       </c>
       <c r="K794">
-        <v>23.95</v>
+        <v>23.65</v>
       </c>
       <c r="L794">
-        <v>27.38</v>
+        <v>28.08</v>
       </c>
       <c r="M794">
-        <v>25</v>
+        <v>23.9</v>
       </c>
       <c r="N794">
-        <v>28.62</v>
+        <v>27.74</v>
       </c>
       <c r="O794">
         <v>1</v>
@@ -41372,96 +41372,96 @@
     </row>
     <row r="795" spans="1:16">
       <c r="A795" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B795" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C795">
-        <v>0.1937889793972793</v>
+        <v>-0.5948776492644505</v>
       </c>
       <c r="D795" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E795">
-        <v>-0.4409912639494706</v>
+        <v>-0.6313336631152922</v>
       </c>
       <c r="F795">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G795">
-        <v>0.05596621102060272</v>
+        <v>0.05535487764926445</v>
       </c>
       <c r="H795">
-        <v>0.05592099126394947</v>
+        <v>0.05777133366311529</v>
       </c>
       <c r="I795">
-        <v>0.63478024334675</v>
+        <v>-0.03645601385084163</v>
       </c>
       <c r="J795">
-        <v>1.179120973387007</v>
+        <v>1.168053346524612</v>
       </c>
       <c r="K795">
-        <v>23.65</v>
+        <v>23.95</v>
       </c>
       <c r="L795">
-        <v>28.08</v>
+        <v>27.38</v>
       </c>
       <c r="M795">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="N795">
-        <v>27.74</v>
+        <v>28.57</v>
       </c>
       <c r="O795">
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="796" spans="1:16">
       <c r="A796" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B796" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C796">
-        <v>-0.8599473126188215</v>
+        <v>0.1937889793972793</v>
       </c>
       <c r="D796" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E796">
-        <v>-0.8580243346751786</v>
+        <v>-0.4409912639494706</v>
       </c>
       <c r="F796">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G796">
-        <v>0.05561994731261882</v>
+        <v>0.05596621102060272</v>
       </c>
       <c r="H796">
-        <v>0.05809802433467518</v>
+        <v>0.05592099126394947</v>
       </c>
       <c r="I796">
-        <v>0.001922977943642934</v>
+        <v>0.63478024334675</v>
       </c>
       <c r="J796">
         <v>1.179120973387007</v>
       </c>
       <c r="K796">
-        <v>23.95</v>
+        <v>23.65</v>
       </c>
       <c r="L796">
-        <v>27.38</v>
+        <v>28.08</v>
       </c>
       <c r="M796">
-        <v>25</v>
+        <v>23.9</v>
       </c>
       <c r="N796">
-        <v>28.62</v>
+        <v>27.74</v>
       </c>
       <c r="O796">
         <v>1</v>
@@ -41472,96 +41472,96 @@
     </row>
     <row r="797" spans="1:16">
       <c r="A797" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B797" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C797">
-        <v>-0.1223076495545783</v>
+        <v>-0.8599473126188215</v>
       </c>
       <c r="D797" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E797">
-        <v>-0.7735384189563561</v>
+        <v>-0.9080243346751793</v>
       </c>
       <c r="F797">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G797">
-        <v>0.05926230764955458</v>
+        <v>0.05561994731261882</v>
       </c>
       <c r="H797">
-        <v>0.05837353841895636</v>
+        <v>0.05804802433467518</v>
       </c>
       <c r="I797">
-        <v>0.6512307694017778</v>
+        <v>-0.04807702205635778</v>
       </c>
       <c r="J797">
-        <v>1.187692305982183</v>
+        <v>1.179120973387007</v>
       </c>
       <c r="K797">
+        <v>23.95</v>
+      </c>
+      <c r="L797">
+        <v>27.38</v>
+      </c>
+      <c r="M797">
         <v>25</v>
       </c>
-      <c r="L797">
-        <v>29.57</v>
-      </c>
-      <c r="M797">
-        <v>24.9</v>
-      </c>
       <c r="N797">
-        <v>28.8</v>
+        <v>28.57</v>
       </c>
       <c r="O797">
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>424</v>
+        <v>186</v>
       </c>
     </row>
     <row r="798" spans="1:16">
       <c r="A798" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B798" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C798">
-        <v>-0.008923036478631019</v>
+        <v>-0.1223076495545783</v>
       </c>
       <c r="D798" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E798">
-        <v>-0.6458461129741764</v>
+        <v>-0.7735384189563561</v>
       </c>
       <c r="F798">
         <v>-1</v>
       </c>
       <c r="G798">
-        <v>0.05616892303647864</v>
+        <v>0.05926230764955458</v>
       </c>
       <c r="H798">
-        <v>0.05612584611297417</v>
+        <v>0.05837353841895636</v>
       </c>
       <c r="I798">
-        <v>0.6369230764955454</v>
+        <v>0.6512307694017778</v>
       </c>
       <c r="J798">
         <v>1.187692305982183</v>
       </c>
       <c r="K798">
-        <v>23.65</v>
+        <v>25</v>
       </c>
       <c r="L798">
-        <v>28.08</v>
+        <v>29.57</v>
       </c>
       <c r="M798">
-        <v>23.9</v>
+        <v>24.9</v>
       </c>
       <c r="N798">
-        <v>27.74</v>
+        <v>28.8</v>
       </c>
       <c r="O798">
         <v>1</v>
@@ -41572,46 +41572,46 @@
     </row>
     <row r="799" spans="1:16">
       <c r="A799" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B799" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C799">
-        <v>-1.065230728273285</v>
+        <v>-0.008923036478631019</v>
       </c>
       <c r="D799" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E799">
-        <v>-1.072307649554578</v>
+        <v>-0.6458461129741764</v>
       </c>
       <c r="F799">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G799">
-        <v>0.05582523072827329</v>
+        <v>0.05616892303647864</v>
       </c>
       <c r="H799">
-        <v>0.05831230764955458</v>
+        <v>0.05612584611297417</v>
       </c>
       <c r="I799">
-        <v>-0.00707692128129267</v>
+        <v>0.6369230764955454</v>
       </c>
       <c r="J799">
         <v>1.187692305982183</v>
       </c>
       <c r="K799">
-        <v>23.95</v>
+        <v>23.65</v>
       </c>
       <c r="L799">
-        <v>27.38</v>
+        <v>28.08</v>
       </c>
       <c r="M799">
-        <v>25</v>
+        <v>23.9</v>
       </c>
       <c r="N799">
-        <v>28.62</v>
+        <v>27.74</v>
       </c>
       <c r="O799">
         <v>1</v>
@@ -41622,96 +41622,96 @@
     </row>
     <row r="800" spans="1:16">
       <c r="A800" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B800" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C800">
-        <v>0.01711680463947474</v>
+        <v>-1.065230728273285</v>
       </c>
       <c r="D800" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E800">
-        <v>-0.6346716625790805</v>
+        <v>-1.122307649554578</v>
       </c>
       <c r="F800">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G800">
-        <v>0.05912288319536053</v>
+        <v>0.05582523072827329</v>
       </c>
       <c r="H800">
-        <v>0.05823467166257908</v>
+        <v>0.05826230764955458</v>
       </c>
       <c r="I800">
-        <v>0.6517884672185552</v>
+        <v>-0.05707692128129338</v>
       </c>
       <c r="J800">
-        <v>1.182115327814421</v>
+        <v>1.187692305982183</v>
       </c>
       <c r="K800">
+        <v>23.95</v>
+      </c>
+      <c r="L800">
+        <v>27.38</v>
+      </c>
+      <c r="M800">
         <v>25</v>
       </c>
-      <c r="L800">
-        <v>29.57</v>
-      </c>
-      <c r="M800">
-        <v>24.9</v>
-      </c>
       <c r="N800">
-        <v>28.8</v>
+        <v>28.57</v>
       </c>
       <c r="O800">
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="801" spans="1:16">
       <c r="A801" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B801" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C801">
-        <v>0.1229724971889432</v>
+        <v>0.01711680463947474</v>
       </c>
       <c r="D801" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E801">
-        <v>-0.5125563347646604</v>
+        <v>-0.6346716625790805</v>
       </c>
       <c r="F801">
         <v>-1</v>
       </c>
       <c r="G801">
-        <v>0.05603702750281106</v>
+        <v>0.05912288319536053</v>
       </c>
       <c r="H801">
-        <v>0.05599255633476466</v>
+        <v>0.05823467166257908</v>
       </c>
       <c r="I801">
-        <v>0.6355288319536037</v>
+        <v>0.6517884672185552</v>
       </c>
       <c r="J801">
         <v>1.182115327814421</v>
       </c>
       <c r="K801">
-        <v>23.65</v>
+        <v>25</v>
       </c>
       <c r="L801">
-        <v>28.08</v>
+        <v>29.57</v>
       </c>
       <c r="M801">
-        <v>23.9</v>
+        <v>24.9</v>
       </c>
       <c r="N801">
-        <v>27.74</v>
+        <v>28.8</v>
       </c>
       <c r="O801">
         <v>1</v>
@@ -41722,46 +41722,46 @@
     </row>
     <row r="802" spans="1:16">
       <c r="A802" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B802" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C802">
-        <v>-0.9316621011553821</v>
+        <v>0.1229724971889432</v>
       </c>
       <c r="D802" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E802">
-        <v>-0.9328831953605246</v>
+        <v>-0.5125563347646604</v>
       </c>
       <c r="F802">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G802">
-        <v>0.05569166210115538</v>
+        <v>0.05603702750281106</v>
       </c>
       <c r="H802">
-        <v>0.05817288319536053</v>
+        <v>0.05599255633476466</v>
       </c>
       <c r="I802">
-        <v>-0.001221094205142492</v>
+        <v>0.6355288319536037</v>
       </c>
       <c r="J802">
         <v>1.182115327814421</v>
       </c>
       <c r="K802">
-        <v>23.95</v>
+        <v>23.65</v>
       </c>
       <c r="L802">
-        <v>27.38</v>
+        <v>28.08</v>
       </c>
       <c r="M802">
-        <v>25</v>
+        <v>23.9</v>
       </c>
       <c r="N802">
-        <v>28.62</v>
+        <v>27.74</v>
       </c>
       <c r="O802">
         <v>1</v>
@@ -41772,63 +41772,63 @@
     </row>
     <row r="803" spans="1:16">
       <c r="A803" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B803" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C803">
-        <v>-0.1778805282432323</v>
+        <v>-0.9316621011553821</v>
       </c>
       <c r="D803" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E803">
-        <v>-0.6778805282432323</v>
+        <v>-0.9828831953605253</v>
       </c>
       <c r="F803">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G803">
-        <v>0.05877788052824323</v>
+        <v>0.05569166210115538</v>
       </c>
       <c r="H803">
-        <v>0.05827788052824323</v>
+        <v>0.05812288319536053</v>
       </c>
       <c r="I803">
-        <v>0.5</v>
+        <v>-0.0512210942051432</v>
       </c>
       <c r="J803">
-        <v>1.183850623624226</v>
+        <v>1.182115327814421</v>
       </c>
       <c r="K803">
-        <v>24.9</v>
+        <v>23.95</v>
       </c>
       <c r="L803">
-        <v>29.3</v>
+        <v>27.38</v>
       </c>
       <c r="M803">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="N803">
-        <v>28.8</v>
+        <v>28.57</v>
       </c>
       <c r="O803">
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>324</v>
+        <v>425</v>
       </c>
     </row>
     <row r="804" spans="1:16">
       <c r="A804" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B804" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C804">
-        <v>-0.02626559060565725</v>
+        <v>-0.1778805282432323</v>
       </c>
       <c r="D804" t="s">
         <v>325</v>
@@ -41840,22 +41840,22 @@
         <v>-1</v>
       </c>
       <c r="G804">
-        <v>0.05916626559060566</v>
+        <v>0.05877788052824323</v>
       </c>
       <c r="H804">
         <v>0.05827788052824323</v>
       </c>
       <c r="I804">
-        <v>0.6516149376375751</v>
+        <v>0.5</v>
       </c>
       <c r="J804">
         <v>1.183850623624226</v>
       </c>
       <c r="K804">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="L804">
-        <v>29.57</v>
+        <v>29.3</v>
       </c>
       <c r="M804">
         <v>24.9</v>
@@ -41872,46 +41872,46 @@
     </row>
     <row r="805" spans="1:16">
       <c r="A805" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B805" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C805">
-        <v>-0.1448373734377988</v>
+        <v>-0.02626559060565725</v>
       </c>
       <c r="D805" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E805">
-        <v>-0.5540299046190107</v>
+        <v>-0.6778805282432323</v>
       </c>
       <c r="F805">
         <v>-1</v>
       </c>
       <c r="G805">
-        <v>0.0563248373734378</v>
+        <v>0.05916626559060566</v>
       </c>
       <c r="H805">
-        <v>0.056034029904619</v>
+        <v>0.05827788052824323</v>
       </c>
       <c r="I805">
-        <v>0.4091925311812119</v>
+        <v>0.6516149376375751</v>
       </c>
       <c r="J805">
         <v>1.183850623624226</v>
       </c>
       <c r="K805">
-        <v>23.85</v>
+        <v>25</v>
       </c>
       <c r="L805">
-        <v>28.09</v>
+        <v>29.57</v>
       </c>
       <c r="M805">
-        <v>23.9</v>
+        <v>24.9</v>
       </c>
       <c r="N805">
-        <v>27.74</v>
+        <v>28.8</v>
       </c>
       <c r="O805">
         <v>1</v>
@@ -41922,46 +41922,46 @@
     </row>
     <row r="806" spans="1:16">
       <c r="A806" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B806" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C806">
-        <v>-0.9732224358002206</v>
+        <v>-0.1794954658808123</v>
       </c>
       <c r="D806" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E806">
-        <v>-0.9762655906056565</v>
+        <v>-1.012414966981432</v>
       </c>
       <c r="F806">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G806">
-        <v>0.05573322243580021</v>
+        <v>0.05853949546588081</v>
       </c>
       <c r="H806">
-        <v>0.05821626559060566</v>
+        <v>0.05581241496698143</v>
       </c>
       <c r="I806">
-        <v>-0.003043154805435933</v>
+        <v>0.8329195011006192</v>
       </c>
       <c r="J806">
         <v>1.183850623624226</v>
       </c>
       <c r="K806">
-        <v>23.95</v>
+        <v>24.8</v>
       </c>
       <c r="L806">
-        <v>27.38</v>
+        <v>29.18</v>
       </c>
       <c r="M806">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N806">
-        <v>28.62</v>
+        <v>27.4</v>
       </c>
       <c r="O806">
         <v>1</v>
@@ -41972,96 +41972,96 @@
     </row>
     <row r="807" spans="1:16">
       <c r="A807" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B807" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C807">
-        <v>0.04582245394855988</v>
+        <v>-0.1448373734377988</v>
       </c>
       <c r="D807" t="s">
-        <v>325</v>
+        <v>188</v>
       </c>
       <c r="E807">
-        <v>-0.6060808358672318</v>
+        <v>-0.9732224358002206</v>
       </c>
       <c r="F807">
         <v>-1</v>
       </c>
       <c r="G807">
-        <v>0.05909417754605144</v>
+        <v>0.0563248373734378</v>
       </c>
       <c r="H807">
-        <v>0.05820608083586724</v>
+        <v>0.05573322243580021</v>
       </c>
       <c r="I807">
-        <v>0.6519032898157917</v>
+        <v>0.8283850623624218</v>
       </c>
       <c r="J807">
-        <v>1.180967101842058</v>
+        <v>1.183850623624226</v>
       </c>
       <c r="K807">
-        <v>25</v>
+        <v>23.85</v>
       </c>
       <c r="L807">
-        <v>29.57</v>
+        <v>28.09</v>
       </c>
       <c r="M807">
-        <v>24.9</v>
+        <v>23.95</v>
       </c>
       <c r="N807">
-        <v>28.8</v>
+        <v>27.38</v>
       </c>
       <c r="O807">
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>191</v>
+        <v>324</v>
       </c>
     </row>
     <row r="808" spans="1:16">
       <c r="A808" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B808" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C808">
-        <v>-0.1079841256830285</v>
+        <v>0.04582245394855988</v>
       </c>
       <c r="D808" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E808">
-        <v>-0.9432104442093845</v>
+        <v>-0.6060808358672318</v>
       </c>
       <c r="F808">
         <v>-1</v>
       </c>
       <c r="G808">
-        <v>0.05846798412568303</v>
+        <v>0.05909417754605144</v>
       </c>
       <c r="H808">
-        <v>0.05574321044420939</v>
+        <v>0.05820608083586724</v>
       </c>
       <c r="I808">
-        <v>0.835226318526356</v>
+        <v>0.6519032898157917</v>
       </c>
       <c r="J808">
         <v>1.180967101842058</v>
       </c>
       <c r="K808">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="L808">
-        <v>29.18</v>
+        <v>29.57</v>
       </c>
       <c r="M808">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="N808">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
       <c r="O808">
         <v>1</v>
@@ -42072,46 +42072,46 @@
     </row>
     <row r="809" spans="1:16">
       <c r="A809" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B809" t="s">
         <v>192</v>
       </c>
       <c r="C809">
-        <v>-0.07606537893307319</v>
+        <v>-0.1079841256830285</v>
       </c>
       <c r="D809" t="s">
-        <v>188</v>
+        <v>329</v>
       </c>
       <c r="E809">
-        <v>-0.9041620891172784</v>
+        <v>-0.9432104442093845</v>
       </c>
       <c r="F809">
         <v>-1</v>
       </c>
       <c r="G809">
-        <v>0.05625606537893307</v>
+        <v>0.05846798412568303</v>
       </c>
       <c r="H809">
-        <v>0.05566416208911728</v>
+        <v>0.05574321044420939</v>
       </c>
       <c r="I809">
-        <v>0.8280967101842052</v>
+        <v>0.835226318526356</v>
       </c>
       <c r="J809">
         <v>1.180967101842058</v>
       </c>
       <c r="K809">
-        <v>23.85</v>
+        <v>24.8</v>
       </c>
       <c r="L809">
-        <v>28.09</v>
+        <v>29.18</v>
       </c>
       <c r="M809">
-        <v>23.95</v>
+        <v>24</v>
       </c>
       <c r="N809">
-        <v>27.38</v>
+        <v>27.4</v>
       </c>
       <c r="O809">
         <v>1</v>
@@ -42122,96 +42122,96 @@
     </row>
     <row r="810" spans="1:16">
       <c r="A810" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B810" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C810">
-        <v>0.05143297331527208</v>
+        <v>-0.07606537893307319</v>
       </c>
       <c r="D810" t="s">
-        <v>325</v>
+        <v>188</v>
       </c>
       <c r="E810">
-        <v>-0.6004927585779853</v>
+        <v>-0.9041620891172784</v>
       </c>
       <c r="F810">
         <v>-1</v>
       </c>
       <c r="G810">
-        <v>0.05908856702668473</v>
+        <v>0.05625606537893307</v>
       </c>
       <c r="H810">
-        <v>0.05820049275857798</v>
+        <v>0.05566416208911728</v>
       </c>
       <c r="I810">
-        <v>0.6519257318932574</v>
+        <v>0.8280967101842052</v>
       </c>
       <c r="J810">
-        <v>1.180742681067389</v>
+        <v>1.180967101842058</v>
       </c>
       <c r="K810">
-        <v>25</v>
+        <v>23.85</v>
       </c>
       <c r="L810">
-        <v>29.57</v>
+        <v>28.09</v>
       </c>
       <c r="M810">
-        <v>24.9</v>
+        <v>23.95</v>
       </c>
       <c r="N810">
-        <v>28.8</v>
+        <v>27.38</v>
       </c>
       <c r="O810">
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>426</v>
+        <v>191</v>
       </c>
     </row>
     <row r="811" spans="1:16">
       <c r="A811" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B811" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C811">
-        <v>-0.1024184904712513</v>
+        <v>0.05143297331527208</v>
       </c>
       <c r="D811" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E811">
-        <v>-0.9378243456173401</v>
+        <v>-0.6004927585779853</v>
       </c>
       <c r="F811">
         <v>-1</v>
       </c>
       <c r="G811">
-        <v>0.05846241849047125</v>
+        <v>0.05908856702668473</v>
       </c>
       <c r="H811">
-        <v>0.05573782434561734</v>
+        <v>0.05820049275857798</v>
       </c>
       <c r="I811">
-        <v>0.8354058551460888</v>
+        <v>0.6519257318932574</v>
       </c>
       <c r="J811">
         <v>1.180742681067389</v>
       </c>
       <c r="K811">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="L811">
-        <v>29.18</v>
+        <v>29.57</v>
       </c>
       <c r="M811">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="N811">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
       <c r="O811">
         <v>1</v>
@@ -42222,46 +42222,46 @@
     </row>
     <row r="812" spans="1:16">
       <c r="A812" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B812" t="s">
         <v>192</v>
       </c>
       <c r="C812">
-        <v>-0.07071294345723089</v>
+        <v>-0.1024184904712513</v>
       </c>
       <c r="D812" t="s">
-        <v>188</v>
+        <v>329</v>
       </c>
       <c r="E812">
-        <v>-0.8987872115639703</v>
+        <v>-0.9378243456173401</v>
       </c>
       <c r="F812">
         <v>-1</v>
       </c>
       <c r="G812">
-        <v>0.05625071294345723</v>
+        <v>0.05846241849047125</v>
       </c>
       <c r="H812">
-        <v>0.05565878721156397</v>
+        <v>0.05573782434561734</v>
       </c>
       <c r="I812">
-        <v>0.8280742681067395</v>
+        <v>0.8354058551460888</v>
       </c>
       <c r="J812">
         <v>1.180742681067389</v>
       </c>
       <c r="K812">
-        <v>23.85</v>
+        <v>24.8</v>
       </c>
       <c r="L812">
-        <v>28.09</v>
+        <v>29.18</v>
       </c>
       <c r="M812">
-        <v>23.95</v>
+        <v>24</v>
       </c>
       <c r="N812">
-        <v>27.38</v>
+        <v>27.4</v>
       </c>
       <c r="O812">
         <v>1</v>
@@ -42275,7 +42275,7 @@
         <v>0</v>
       </c>
       <c r="B813" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C813">
         <v>0.004427027548832285</v>
@@ -42322,96 +42322,96 @@
     </row>
     <row r="814" spans="1:16">
       <c r="A814" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B814" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C814">
-        <v>-0.06863320208639223</v>
+        <v>-0.9520381315587336</v>
       </c>
       <c r="D814" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E814">
-        <v>-0.9051289052448972</v>
+        <v>-0.8408598512612571</v>
       </c>
       <c r="F814">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G814">
-        <v>0.05842863320208639</v>
+        <v>0.05775203813155873</v>
       </c>
       <c r="H814">
-        <v>0.05570512890524489</v>
+        <v>0.05798085985126126</v>
       </c>
       <c r="I814">
-        <v>0.836495703158505</v>
+        <v>0.1111782802974766</v>
       </c>
       <c r="J814">
-        <v>1.179380371051871</v>
+        <v>1.17643439405045</v>
       </c>
       <c r="K814">
-        <v>24.8</v>
+        <v>24.95</v>
       </c>
       <c r="L814">
-        <v>29.18</v>
+        <v>28.4</v>
       </c>
       <c r="M814">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N814">
-        <v>27.4</v>
+        <v>28.57</v>
       </c>
       <c r="O814">
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>325</v>
+        <v>187</v>
       </c>
     </row>
     <row r="815" spans="1:16">
       <c r="A815" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B815" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C815">
-        <v>-1.025540257744172</v>
+        <v>-0.06863320208639223</v>
       </c>
       <c r="D815" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E815">
-        <v>-0.864509276296765</v>
+        <v>-0.9051289052448972</v>
       </c>
       <c r="F815">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G815">
-        <v>0.05782554025774417</v>
+        <v>0.05842863320208639</v>
       </c>
       <c r="H815">
-        <v>0.05810450927629677</v>
+        <v>0.05570512890524489</v>
       </c>
       <c r="I815">
-        <v>0.1610309814474071</v>
+        <v>0.836495703158505</v>
       </c>
       <c r="J815">
         <v>1.179380371051871</v>
       </c>
       <c r="K815">
-        <v>24.95</v>
+        <v>24.8</v>
       </c>
       <c r="L815">
-        <v>28.4</v>
+        <v>29.18</v>
       </c>
       <c r="M815">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N815">
-        <v>28.62</v>
+        <v>27.4</v>
       </c>
       <c r="O815">
         <v>1</v>
@@ -42422,84 +42422,84 @@
     </row>
     <row r="816" spans="1:16">
       <c r="A816" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B816" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C816">
-        <v>-0.1398756728703532</v>
+        <v>-0.0971908681397089</v>
       </c>
       <c r="D816" t="s">
-        <v>329</v>
+        <v>188</v>
       </c>
       <c r="E816">
-        <v>-0.9740732318100207</v>
+        <v>-0.8661598866923015</v>
       </c>
       <c r="F816">
         <v>-1</v>
       </c>
       <c r="G816">
-        <v>0.05849987567287036</v>
+        <v>0.05627719086813971</v>
       </c>
       <c r="H816">
-        <v>0.05577407323181002</v>
+        <v>0.0556261598866923</v>
       </c>
       <c r="I816">
-        <v>0.8341975589396675</v>
+        <v>0.7689690185525926</v>
       </c>
       <c r="J816">
-        <v>1.182253051325417</v>
+        <v>1.179380371051871</v>
       </c>
       <c r="K816">
-        <v>24.8</v>
+        <v>23.9</v>
       </c>
       <c r="L816">
-        <v>29.18</v>
+        <v>28.09</v>
       </c>
       <c r="M816">
-        <v>24</v>
+        <v>23.95</v>
       </c>
       <c r="N816">
-        <v>27.4</v>
+        <v>27.38</v>
       </c>
       <c r="O816">
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>427</v>
+        <v>325</v>
       </c>
     </row>
     <row r="817" spans="1:16">
       <c r="A817" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B817" t="s">
         <v>194</v>
       </c>
       <c r="C817">
-        <v>-1.097213630569165</v>
+        <v>-1.025540257744172</v>
       </c>
       <c r="D817" t="s">
         <v>326</v>
       </c>
       <c r="E817">
-        <v>-0.9363262831354362</v>
+        <v>-0.9145092762967657</v>
       </c>
       <c r="F817">
         <v>1</v>
       </c>
       <c r="G817">
-        <v>0.05789721363056916</v>
+        <v>0.05782554025774417</v>
       </c>
       <c r="H817">
-        <v>0.05817632628313544</v>
+        <v>0.05805450927629677</v>
       </c>
       <c r="I817">
-        <v>0.1608873474337287</v>
+        <v>0.1110309814474064</v>
       </c>
       <c r="J817">
-        <v>1.182253051325417</v>
+        <v>1.179380371051871</v>
       </c>
       <c r="K817">
         <v>24.95</v>
@@ -42511,13 +42511,13 @@
         <v>25</v>
       </c>
       <c r="N817">
-        <v>28.62</v>
+        <v>28.57</v>
       </c>
       <c r="O817">
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>427</v>
+        <v>325</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42525,31 +42525,31 @@
         <v>0</v>
       </c>
       <c r="B818" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C818">
-        <v>-0.1618738323455666</v>
+        <v>-0.1398756728703532</v>
       </c>
       <c r="D818" t="s">
         <v>329</v>
       </c>
       <c r="E818">
-        <v>-0.9953617732376472</v>
+        <v>-0.9740732318100207</v>
       </c>
       <c r="F818">
         <v>-1</v>
       </c>
       <c r="G818">
-        <v>0.05852187383234556</v>
+        <v>0.05849987567287036</v>
       </c>
       <c r="H818">
-        <v>0.05579536177323764</v>
+        <v>0.05577407323181002</v>
       </c>
       <c r="I818">
-        <v>0.8334879408920806</v>
+        <v>0.8341975589396675</v>
       </c>
       <c r="J818">
-        <v>1.183140073884902</v>
+        <v>1.182253051325417</v>
       </c>
       <c r="K818">
         <v>24.8</v>
@@ -42567,7 +42567,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -42575,331 +42575,331 @@
         <v>1</v>
       </c>
       <c r="B819" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C819">
-        <v>-1.119344843428301</v>
+        <v>-0.1658479266774755</v>
       </c>
       <c r="D819" t="s">
-        <v>326</v>
+        <v>188</v>
       </c>
       <c r="E819">
-        <v>-0.9585018471225446</v>
+        <v>-0.9349605792437501</v>
       </c>
       <c r="F819">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G819">
-        <v>0.0579193448434283</v>
+        <v>0.05634584792667748</v>
       </c>
       <c r="H819">
-        <v>0.05819850184712255</v>
+        <v>0.05569496057924375</v>
       </c>
       <c r="I819">
-        <v>0.1608429963057567</v>
+        <v>0.7691126525662746</v>
       </c>
       <c r="J819">
-        <v>1.183140073884902</v>
+        <v>1.182253051325417</v>
       </c>
       <c r="K819">
-        <v>24.95</v>
+        <v>23.9</v>
       </c>
       <c r="L819">
-        <v>28.4</v>
+        <v>28.09</v>
       </c>
       <c r="M819">
-        <v>25</v>
+        <v>23.95</v>
       </c>
       <c r="N819">
-        <v>28.62</v>
+        <v>27.38</v>
       </c>
       <c r="O819">
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="820" spans="1:16">
       <c r="A820" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B820" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C820">
-        <v>-0.2777517985715967</v>
+        <v>-1.097213630569165</v>
       </c>
       <c r="D820" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E820">
-        <v>-1.107501740553158</v>
+        <v>-0.9863262831354369</v>
       </c>
       <c r="F820">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G820">
-        <v>0.0586377517985716</v>
+        <v>0.05789721363056916</v>
       </c>
       <c r="H820">
-        <v>0.05590750174055316</v>
+        <v>0.05812632628313544</v>
       </c>
       <c r="I820">
-        <v>0.8297499419815608</v>
+        <v>0.110887347433728</v>
       </c>
       <c r="J820">
-        <v>1.187812572523048</v>
+        <v>1.182253051325417</v>
       </c>
       <c r="K820">
-        <v>24.8</v>
+        <v>24.95</v>
       </c>
       <c r="L820">
-        <v>29.18</v>
+        <v>28.4</v>
       </c>
       <c r="M820">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N820">
-        <v>27.4</v>
+        <v>28.57</v>
       </c>
       <c r="O820">
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="821" spans="1:16">
       <c r="A821" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B821" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C821">
-        <v>-1.235923684450054</v>
+        <v>-0.1618738323455666</v>
       </c>
       <c r="D821" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E821">
-        <v>-1.075314313076202</v>
+        <v>-0.9953617732376472</v>
       </c>
       <c r="F821">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G821">
-        <v>0.05803592368445006</v>
+        <v>0.05852187383234556</v>
       </c>
       <c r="H821">
-        <v>0.0583153143130762</v>
+        <v>0.05579536177323764</v>
       </c>
       <c r="I821">
-        <v>0.1606093713738517</v>
+        <v>0.8334879408920806</v>
       </c>
       <c r="J821">
-        <v>1.187812572523048</v>
+        <v>1.183140073884902</v>
       </c>
       <c r="K821">
-        <v>24.95</v>
+        <v>24.8</v>
       </c>
       <c r="L821">
-        <v>28.4</v>
+        <v>29.18</v>
       </c>
       <c r="M821">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N821">
-        <v>28.62</v>
+        <v>27.4</v>
       </c>
       <c r="O821">
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="822" spans="1:16">
       <c r="A822" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B822" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C822">
-        <v>-0.678181641571296</v>
+        <v>-1.119344843428301</v>
       </c>
       <c r="D822" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E822">
-        <v>-1.495014491843193</v>
+        <v>-1.008501847122545</v>
       </c>
       <c r="F822">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G822">
-        <v>0.0590381816415713</v>
+        <v>0.0579193448434283</v>
       </c>
       <c r="H822">
-        <v>0.05629501449184319</v>
+        <v>0.05814850184712254</v>
       </c>
       <c r="I822">
-        <v>0.8168328502718971</v>
+        <v>0.110842996305756</v>
       </c>
       <c r="J822">
-        <v>1.203958937160133</v>
+        <v>1.183140073884902</v>
       </c>
       <c r="K822">
-        <v>24.8</v>
+        <v>24.95</v>
       </c>
       <c r="L822">
-        <v>29.18</v>
+        <v>28.4</v>
       </c>
       <c r="M822">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N822">
-        <v>27.4</v>
+        <v>28.57</v>
       </c>
       <c r="O822">
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="823" spans="1:16">
       <c r="A823" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B823" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C823">
-        <v>-1.638775482145316</v>
+        <v>-0.2777517985715967</v>
       </c>
       <c r="D823" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E823">
-        <v>-1.478973429003322</v>
+        <v>-1.107501740553158</v>
       </c>
       <c r="F823">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G823">
-        <v>0.05843877548214532</v>
+        <v>0.0586377517985716</v>
       </c>
       <c r="H823">
-        <v>0.05871897342900333</v>
+        <v>0.05590750174055316</v>
       </c>
       <c r="I823">
-        <v>0.1598020531419948</v>
+        <v>0.8297499419815608</v>
       </c>
       <c r="J823">
-        <v>1.203958937160133</v>
+        <v>1.187812572523048</v>
       </c>
       <c r="K823">
-        <v>24.95</v>
+        <v>24.8</v>
       </c>
       <c r="L823">
-        <v>28.4</v>
+        <v>29.18</v>
       </c>
       <c r="M823">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N823">
-        <v>28.62</v>
+        <v>27.4</v>
       </c>
       <c r="O823">
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="824" spans="1:16">
       <c r="A824" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B824" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C824">
-        <v>-0.9315019397461235</v>
+        <v>-0.2987204833008512</v>
       </c>
       <c r="D824" t="s">
-        <v>329</v>
+        <v>188</v>
       </c>
       <c r="E824">
-        <v>-1.740163167496249</v>
+        <v>-1.068111111927003</v>
       </c>
       <c r="F824">
         <v>-1</v>
       </c>
       <c r="G824">
-        <v>0.05929150193974612</v>
+        <v>0.05647872048330085</v>
       </c>
       <c r="H824">
-        <v>0.05654016316749625</v>
+        <v>0.055828111111927</v>
       </c>
       <c r="I824">
-        <v>0.8086612277501253</v>
+        <v>0.7693906286261516</v>
       </c>
       <c r="J824">
-        <v>1.214173465312344</v>
+        <v>1.187812572523048</v>
       </c>
       <c r="K824">
-        <v>24.8</v>
+        <v>23.9</v>
       </c>
       <c r="L824">
-        <v>29.18</v>
+        <v>28.09</v>
       </c>
       <c r="M824">
-        <v>24</v>
+        <v>23.95</v>
       </c>
       <c r="N824">
-        <v>27.4</v>
+        <v>27.38</v>
       </c>
       <c r="O824">
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="825" spans="1:16">
       <c r="A825" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B825" t="s">
         <v>194</v>
       </c>
       <c r="C825">
-        <v>-1.893627959542975</v>
+        <v>-1.235923684450054</v>
       </c>
       <c r="D825" t="s">
         <v>326</v>
       </c>
       <c r="E825">
-        <v>-1.734336632808592</v>
+        <v>-1.125314313076203</v>
       </c>
       <c r="F825">
         <v>1</v>
       </c>
       <c r="G825">
-        <v>0.05869362795954297</v>
+        <v>0.05803592368445006</v>
       </c>
       <c r="H825">
-        <v>0.05897433663280859</v>
+        <v>0.0582653143130762</v>
       </c>
       <c r="I825">
-        <v>0.1592913267343832</v>
+        <v>0.110609371373851</v>
       </c>
       <c r="J825">
-        <v>1.214173465312344</v>
+        <v>1.187812572523048</v>
       </c>
       <c r="K825">
         <v>24.95</v>
@@ -42911,13 +42911,13 @@
         <v>25</v>
       </c>
       <c r="N825">
-        <v>28.62</v>
+        <v>28.57</v>
       </c>
       <c r="O825">
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -42925,49 +42925,49 @@
         <v>0</v>
       </c>
       <c r="B826" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C826">
-        <v>-0.7096015467950494</v>
+        <v>-0.678181641571296</v>
       </c>
       <c r="D826" t="s">
-        <v>188</v>
+        <v>329</v>
       </c>
       <c r="E826">
-        <v>-1.479851759236045</v>
+        <v>-1.495014491843193</v>
       </c>
       <c r="F826">
         <v>-1</v>
       </c>
       <c r="G826">
-        <v>0.05688960154679505</v>
+        <v>0.0590381816415713</v>
       </c>
       <c r="H826">
-        <v>0.05623985175923605</v>
+        <v>0.05629501449184319</v>
       </c>
       <c r="I826">
-        <v>0.7702502124409953</v>
+        <v>0.8168328502718971</v>
       </c>
       <c r="J826">
-        <v>1.205004248819877</v>
+        <v>1.203958937160133</v>
       </c>
       <c r="K826">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
       <c r="L826">
-        <v>28.09</v>
+        <v>29.18</v>
       </c>
       <c r="M826">
-        <v>23.95</v>
+        <v>24</v>
       </c>
       <c r="N826">
-        <v>27.38</v>
+        <v>27.4</v>
       </c>
       <c r="O826">
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>193</v>
+        <v>430</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -42975,181 +42975,181 @@
         <v>1</v>
       </c>
       <c r="B827" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C827">
-        <v>-1.664856008055924</v>
+        <v>-0.6846185981271766</v>
       </c>
       <c r="D827" t="s">
-        <v>326</v>
+        <v>188</v>
       </c>
       <c r="E827">
-        <v>-1.505106220496916</v>
+        <v>-1.454816544985185</v>
       </c>
       <c r="F827">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G827">
-        <v>0.05846485600805592</v>
+        <v>0.05686461859812718</v>
       </c>
       <c r="H827">
-        <v>0.05874510622049692</v>
+        <v>0.05621481654498518</v>
       </c>
       <c r="I827">
-        <v>0.1597497875590079</v>
+        <v>0.7701979468580085</v>
       </c>
       <c r="J827">
-        <v>1.205004248819877</v>
+        <v>1.203958937160133</v>
       </c>
       <c r="K827">
-        <v>24.95</v>
+        <v>23.9</v>
       </c>
       <c r="L827">
-        <v>28.4</v>
+        <v>28.09</v>
       </c>
       <c r="M827">
-        <v>25</v>
+        <v>23.95</v>
       </c>
       <c r="N827">
-        <v>28.62</v>
+        <v>27.38</v>
       </c>
       <c r="O827">
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>193</v>
+        <v>430</v>
       </c>
     </row>
     <row r="828" spans="1:16">
       <c r="A828" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B828" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C828">
-        <v>-0.6412938646140063</v>
+        <v>-1.638775482145316</v>
       </c>
       <c r="D828" t="s">
-        <v>188</v>
+        <v>326</v>
       </c>
       <c r="E828">
-        <v>-1.411401173954204</v>
+        <v>-1.528973429003322</v>
       </c>
       <c r="F828">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G828">
-        <v>0.05682129386461401</v>
+        <v>0.05843877548214532</v>
       </c>
       <c r="H828">
-        <v>0.0561714011739542</v>
+        <v>0.05866897342900333</v>
       </c>
       <c r="I828">
-        <v>0.7701073093401973</v>
+        <v>0.1098020531419941</v>
       </c>
       <c r="J828">
-        <v>1.202146186803933</v>
+        <v>1.203958937160133</v>
       </c>
       <c r="K828">
-        <v>23.9</v>
+        <v>24.95</v>
       </c>
       <c r="L828">
-        <v>28.09</v>
+        <v>28.4</v>
       </c>
       <c r="M828">
-        <v>23.95</v>
+        <v>25</v>
       </c>
       <c r="N828">
-        <v>27.38</v>
+        <v>28.57</v>
       </c>
       <c r="O828">
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="829" spans="1:16">
       <c r="A829" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B829" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C829">
-        <v>-1.593547360758137</v>
+        <v>-0.9315019397461235</v>
       </c>
       <c r="D829" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E829">
-        <v>-1.433654670098335</v>
+        <v>-1.740163167496249</v>
       </c>
       <c r="F829">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G829">
-        <v>0.05839354736075814</v>
+        <v>0.05929150193974612</v>
       </c>
       <c r="H829">
-        <v>0.05867365467009834</v>
+        <v>0.05654016316749625</v>
       </c>
       <c r="I829">
-        <v>0.1598926906598024</v>
+        <v>0.8086612277501253</v>
       </c>
       <c r="J829">
-        <v>1.202146186803933</v>
+        <v>1.214173465312344</v>
       </c>
       <c r="K829">
-        <v>24.95</v>
+        <v>24.8</v>
       </c>
       <c r="L829">
-        <v>28.4</v>
+        <v>29.18</v>
       </c>
       <c r="M829">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N829">
-        <v>28.62</v>
+        <v>27.4</v>
       </c>
       <c r="O829">
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="830" spans="1:16">
       <c r="A830" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B830" t="s">
         <v>195</v>
       </c>
       <c r="C830">
-        <v>-0.6386563512125996</v>
+        <v>-0.9287458209650126</v>
       </c>
       <c r="D830" t="s">
         <v>188</v>
       </c>
       <c r="E830">
-        <v>-1.408758142742332</v>
+        <v>-1.699454494230633</v>
       </c>
       <c r="F830">
         <v>-1</v>
       </c>
       <c r="G830">
-        <v>0.0568186563512126</v>
+        <v>0.05710874582096501</v>
       </c>
       <c r="H830">
-        <v>0.05616875814274234</v>
+        <v>0.05645945449423063</v>
       </c>
       <c r="I830">
-        <v>0.7701017915297328</v>
+        <v>0.7707086732656201</v>
       </c>
       <c r="J830">
-        <v>1.202035830594669</v>
+        <v>1.214173465312344</v>
       </c>
       <c r="K830">
         <v>23.9</v>
@@ -43167,39 +43167,39 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>329</v>
+        <v>431</v>
       </c>
     </row>
     <row r="831" spans="1:16">
       <c r="A831" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B831" t="s">
         <v>194</v>
       </c>
       <c r="C831">
-        <v>-1.590793973337004</v>
+        <v>-1.893627959542975</v>
       </c>
       <c r="D831" t="s">
         <v>326</v>
       </c>
       <c r="E831">
-        <v>-1.430895764866737</v>
+        <v>-1.784336632808593</v>
       </c>
       <c r="F831">
         <v>1</v>
       </c>
       <c r="G831">
-        <v>0.058390793973337</v>
+        <v>0.05869362795954297</v>
       </c>
       <c r="H831">
-        <v>0.05867089576486674</v>
+        <v>0.05892433663280859</v>
       </c>
       <c r="I831">
-        <v>0.1598982084702669</v>
+        <v>0.1092913267343825</v>
       </c>
       <c r="J831">
-        <v>1.202035830594669</v>
+        <v>1.214173465312344</v>
       </c>
       <c r="K831">
         <v>24.95</v>
@@ -43211,13 +43211,13 @@
         <v>25</v>
       </c>
       <c r="N831">
-        <v>28.62</v>
+        <v>28.57</v>
       </c>
       <c r="O831">
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>329</v>
+        <v>431</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43225,48 +43225,348 @@
         <v>0</v>
       </c>
       <c r="B832" t="s">
+        <v>195</v>
+      </c>
+      <c r="C832">
+        <v>-0.7096015467950494</v>
+      </c>
+      <c r="D832" t="s">
+        <v>188</v>
+      </c>
+      <c r="E832">
+        <v>-1.479851759236045</v>
+      </c>
+      <c r="F832">
+        <v>-1</v>
+      </c>
+      <c r="G832">
+        <v>0.05688960154679505</v>
+      </c>
+      <c r="H832">
+        <v>0.05623985175923605</v>
+      </c>
+      <c r="I832">
+        <v>0.7702502124409953</v>
+      </c>
+      <c r="J832">
+        <v>1.205004248819877</v>
+      </c>
+      <c r="K832">
+        <v>23.9</v>
+      </c>
+      <c r="L832">
+        <v>28.09</v>
+      </c>
+      <c r="M832">
+        <v>23.95</v>
+      </c>
+      <c r="N832">
+        <v>27.38</v>
+      </c>
+      <c r="O832">
+        <v>1</v>
+      </c>
+      <c r="P832" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="833" spans="1:16">
+      <c r="A833" s="1">
+        <v>1</v>
+      </c>
+      <c r="B833" t="s">
+        <v>194</v>
+      </c>
+      <c r="C833">
+        <v>-1.664856008055924</v>
+      </c>
+      <c r="D833" t="s">
+        <v>326</v>
+      </c>
+      <c r="E833">
+        <v>-1.555106220496917</v>
+      </c>
+      <c r="F833">
+        <v>1</v>
+      </c>
+      <c r="G833">
+        <v>0.05846485600805592</v>
+      </c>
+      <c r="H833">
+        <v>0.05869510622049692</v>
+      </c>
+      <c r="I833">
+        <v>0.1097497875590072</v>
+      </c>
+      <c r="J833">
+        <v>1.205004248819877</v>
+      </c>
+      <c r="K833">
+        <v>24.95</v>
+      </c>
+      <c r="L833">
+        <v>28.4</v>
+      </c>
+      <c r="M833">
+        <v>25</v>
+      </c>
+      <c r="N833">
+        <v>28.57</v>
+      </c>
+      <c r="O833">
+        <v>1</v>
+      </c>
+      <c r="P833" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="834" spans="1:16">
+      <c r="A834" s="1">
+        <v>0</v>
+      </c>
+      <c r="B834" t="s">
+        <v>195</v>
+      </c>
+      <c r="C834">
+        <v>-0.6412938646140063</v>
+      </c>
+      <c r="D834" t="s">
+        <v>188</v>
+      </c>
+      <c r="E834">
+        <v>-1.411401173954204</v>
+      </c>
+      <c r="F834">
+        <v>-1</v>
+      </c>
+      <c r="G834">
+        <v>0.05682129386461401</v>
+      </c>
+      <c r="H834">
+        <v>0.0561714011739542</v>
+      </c>
+      <c r="I834">
+        <v>0.7701073093401973</v>
+      </c>
+      <c r="J834">
+        <v>1.202146186803933</v>
+      </c>
+      <c r="K834">
+        <v>23.9</v>
+      </c>
+      <c r="L834">
+        <v>28.09</v>
+      </c>
+      <c r="M834">
+        <v>23.95</v>
+      </c>
+      <c r="N834">
+        <v>27.38</v>
+      </c>
+      <c r="O834">
+        <v>1</v>
+      </c>
+      <c r="P834" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="835" spans="1:16">
+      <c r="A835" s="1">
+        <v>1</v>
+      </c>
+      <c r="B835" t="s">
+        <v>194</v>
+      </c>
+      <c r="C835">
+        <v>-1.593547360758137</v>
+      </c>
+      <c r="D835" t="s">
+        <v>326</v>
+      </c>
+      <c r="E835">
+        <v>-1.483654670098336</v>
+      </c>
+      <c r="F835">
+        <v>1</v>
+      </c>
+      <c r="G835">
+        <v>0.05839354736075814</v>
+      </c>
+      <c r="H835">
+        <v>0.05862365467009834</v>
+      </c>
+      <c r="I835">
+        <v>0.1098926906598017</v>
+      </c>
+      <c r="J835">
+        <v>1.202146186803933</v>
+      </c>
+      <c r="K835">
+        <v>24.95</v>
+      </c>
+      <c r="L835">
+        <v>28.4</v>
+      </c>
+      <c r="M835">
+        <v>25</v>
+      </c>
+      <c r="N835">
+        <v>28.57</v>
+      </c>
+      <c r="O835">
+        <v>1</v>
+      </c>
+      <c r="P835" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="836" spans="1:16">
+      <c r="A836" s="1">
+        <v>0</v>
+      </c>
+      <c r="B836" t="s">
+        <v>195</v>
+      </c>
+      <c r="C836">
+        <v>-0.6386563512125996</v>
+      </c>
+      <c r="D836" t="s">
+        <v>188</v>
+      </c>
+      <c r="E836">
+        <v>-1.408758142742332</v>
+      </c>
+      <c r="F836">
+        <v>-1</v>
+      </c>
+      <c r="G836">
+        <v>0.0568186563512126</v>
+      </c>
+      <c r="H836">
+        <v>0.05616875814274234</v>
+      </c>
+      <c r="I836">
+        <v>0.7701017915297328</v>
+      </c>
+      <c r="J836">
+        <v>1.202035830594669</v>
+      </c>
+      <c r="K836">
+        <v>23.9</v>
+      </c>
+      <c r="L836">
+        <v>28.09</v>
+      </c>
+      <c r="M836">
+        <v>23.95</v>
+      </c>
+      <c r="N836">
+        <v>27.38</v>
+      </c>
+      <c r="O836">
+        <v>1</v>
+      </c>
+      <c r="P836" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="837" spans="1:16">
+      <c r="A837" s="1">
+        <v>1</v>
+      </c>
+      <c r="B837" t="s">
+        <v>194</v>
+      </c>
+      <c r="C837">
+        <v>-1.590793973337004</v>
+      </c>
+      <c r="D837" t="s">
+        <v>326</v>
+      </c>
+      <c r="E837">
+        <v>-1.480895764866737</v>
+      </c>
+      <c r="F837">
+        <v>1</v>
+      </c>
+      <c r="G837">
+        <v>0.058390793973337</v>
+      </c>
+      <c r="H837">
+        <v>0.05862089576486674</v>
+      </c>
+      <c r="I837">
+        <v>0.1098982084702662</v>
+      </c>
+      <c r="J837">
+        <v>1.202035830594669</v>
+      </c>
+      <c r="K837">
+        <v>24.95</v>
+      </c>
+      <c r="L837">
+        <v>28.4</v>
+      </c>
+      <c r="M837">
+        <v>25</v>
+      </c>
+      <c r="N837">
+        <v>28.57</v>
+      </c>
+      <c r="O837">
+        <v>1</v>
+      </c>
+      <c r="P837" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="838" spans="1:16">
+      <c r="A838" s="1">
+        <v>0</v>
+      </c>
+      <c r="B838" t="s">
         <v>196</v>
       </c>
-      <c r="C832">
+      <c r="C838">
         <v>-1.493533516516486</v>
       </c>
-      <c r="D832" t="s">
+      <c r="D838" t="s">
         <v>326</v>
       </c>
-      <c r="E832">
-        <v>-1.133039595707903</v>
-      </c>
-      <c r="F832">
-        <v>1</v>
-      </c>
-      <c r="G832">
+      <c r="E838">
+        <v>-1.183039595707903</v>
+      </c>
+      <c r="F838">
+        <v>1</v>
+      </c>
+      <c r="G838">
         <v>0.05789353351651649</v>
       </c>
-      <c r="H832">
-        <v>0.05837303959570791</v>
-      </c>
-      <c r="I832">
-        <v>0.3604939208085831</v>
-      </c>
-      <c r="J832">
+      <c r="H838">
+        <v>0.05832303959570791</v>
+      </c>
+      <c r="I838">
+        <v>0.3104939208085824</v>
+      </c>
+      <c r="J838">
         <v>1.190121583828316</v>
       </c>
-      <c r="K832">
+      <c r="K838">
         <v>24.95</v>
       </c>
-      <c r="L832">
+      <c r="L838">
         <v>28.2</v>
       </c>
-      <c r="M832">
+      <c r="M838">
         <v>25</v>
       </c>
-      <c r="N832">
-        <v>28.62</v>
-      </c>
-      <c r="O832">
-        <v>1</v>
-      </c>
-      <c r="P832" t="s">
+      <c r="N838">
+        <v>28.57</v>
+      </c>
+      <c r="O838">
+        <v>1</v>
+      </c>
+      <c r="P838" t="s">
         <v>190</v>
       </c>
     </row>
